--- a/리드지 발주현황.xlsx
+++ b/리드지 발주현황.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\유현아\Documents\GitHub\INTEROJO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{46BDFD88-332F-490D-B84E-41A484007AE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFD4709D-8178-4DE1-B038-AF0B2D47E46C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{500E376A-1243-49DE-9EFA-B2AD708B3011}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet5" sheetId="5" r:id="rId2"/>
+    <sheet name="구매발주현황" sheetId="1" r:id="rId1"/>
+    <sheet name="구매의뢰현황" sheetId="5" r:id="rId2"/>
     <sheet name="Sheet4" sheetId="4" r:id="rId3"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId5"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1593" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2663" uniqueCount="355">
   <si>
     <t>G/W</t>
   </si>
@@ -937,6 +937,177 @@
   </si>
   <si>
     <t>알루미늄리드지 (일본 T-garden_1D 55% Cheritta)_유광코팅</t>
+  </si>
+  <si>
+    <t>그룹웨어 문서번호</t>
+  </si>
+  <si>
+    <t>의뢰일자</t>
+  </si>
+  <si>
+    <t>내외자</t>
+  </si>
+  <si>
+    <t>최신발주일자(신규구분)</t>
+  </si>
+  <si>
+    <t>최신발주업체명</t>
+  </si>
+  <si>
+    <t>구분</t>
+  </si>
+  <si>
+    <t>용도구분</t>
+  </si>
+  <si>
+    <t>의뢰부서</t>
+  </si>
+  <si>
+    <t>단위</t>
+  </si>
+  <si>
+    <t>의뢰수량</t>
+  </si>
+  <si>
+    <t>발주누계</t>
+  </si>
+  <si>
+    <t>차이수량</t>
+  </si>
+  <si>
+    <t>발주잔량</t>
+  </si>
+  <si>
+    <t>수신자</t>
+  </si>
+  <si>
+    <t>수신부서명</t>
+  </si>
+  <si>
+    <t>요청일</t>
+  </si>
+  <si>
+    <t>관련문서</t>
+  </si>
+  <si>
+    <t>의뢰상태</t>
+  </si>
+  <si>
+    <t>의뢰공장</t>
+  </si>
+  <si>
+    <t>입고공장</t>
+  </si>
+  <si>
+    <t>입고창고</t>
+  </si>
+  <si>
+    <t>고유번호</t>
+  </si>
+  <si>
+    <t>20260506P227-0172</t>
+  </si>
+  <si>
+    <t>국내(원)</t>
+  </si>
+  <si>
+    <t>생산기획팀</t>
+  </si>
+  <si>
+    <t>완료</t>
+  </si>
+  <si>
+    <t>C관(2공장)</t>
+  </si>
+  <si>
+    <t>20260507P227-0022</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>20260512P227-0095</t>
+  </si>
+  <si>
+    <t>20260515P227-0077</t>
+  </si>
+  <si>
+    <t>20260519P227-0113</t>
+  </si>
+  <si>
+    <t>2026-06-02 오전 10:27:09</t>
+  </si>
+  <si>
+    <t>20260526P227-0018</t>
+  </si>
+  <si>
+    <t>20260529P227-0012</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>PR-2606010012</t>
+  </si>
+  <si>
+    <t>20260601P227-0128</t>
+  </si>
+  <si>
+    <t>BS0082</t>
+  </si>
+  <si>
+    <t>알루미늄리드지 (PIA 55% 1Day Clear UV)_유광 코팅</t>
+  </si>
+  <si>
+    <t>BS0082-001</t>
+  </si>
+  <si>
+    <t>2025-11-04</t>
+  </si>
+  <si>
+    <t>의뢰</t>
+  </si>
+  <si>
+    <t>2026-06-01 오후 5:47:49</t>
+  </si>
+  <si>
+    <t>BS0049</t>
+  </si>
+  <si>
+    <t>알루미늄리드지 (신시아_원데이UV모이스쳐)_무광 코팅</t>
+  </si>
+  <si>
+    <t>BS0049-002</t>
+  </si>
+  <si>
+    <t>2025-08-27</t>
+  </si>
+  <si>
+    <t>BS0354</t>
+  </si>
+  <si>
+    <t>알루미늄리드지 (PIA_1D 55% CoFANCY 리드지)</t>
+  </si>
+  <si>
+    <t>BS0354-001</t>
+  </si>
+  <si>
+    <t>신규</t>
+  </si>
+  <si>
+    <t>Cofancy 신제품</t>
+  </si>
+  <si>
+    <t>BS0290</t>
+  </si>
+  <si>
+    <t>알루미늄리드지 (태국 MG Medical Group_SISSE ONE DAY_Marie_Little Lady 리드지)</t>
+  </si>
+  <si>
+    <t>BS0290-001</t>
+  </si>
+  <si>
+    <t>2026-06-22</t>
   </si>
 </sst>
 </file>
@@ -982,7 +1153,16 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -8024,14 +8204,3968 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8105D0C-47A0-4625-B289-24FCAF816E36}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:AH38"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="X1" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="Y1" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="Z1" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="AA1" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="AB1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="AD1" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="AE1" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="AF1" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="AG1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AH1" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="R2" s="3">
+        <v>300000</v>
+      </c>
+      <c r="S2" s="3">
+        <v>300000</v>
+      </c>
+      <c r="T2" s="3">
+        <v>0</v>
+      </c>
+      <c r="U2" s="3">
+        <v>0</v>
+      </c>
+      <c r="V2" s="3">
+        <v>300000</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y2" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA2" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="AB2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC2" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD2" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AE2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG2" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH2" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="D3" s="3">
+        <v>2</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="R3" s="3">
+        <v>200000</v>
+      </c>
+      <c r="S3" s="3">
+        <v>200000</v>
+      </c>
+      <c r="T3" s="3">
+        <v>0</v>
+      </c>
+      <c r="U3" s="3">
+        <v>0</v>
+      </c>
+      <c r="V3" s="3">
+        <v>200000</v>
+      </c>
+      <c r="W3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X3" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y3" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA3" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="AB3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC3" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD3" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AE3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH3" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="D4" s="3">
+        <v>3</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="R4" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="S4" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="T4" s="3">
+        <v>0</v>
+      </c>
+      <c r="U4" s="3">
+        <v>0</v>
+      </c>
+      <c r="V4" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="W4" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X4" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y4" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="Z4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA4" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="AB4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC4" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD4" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AE4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH4" s="4" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="R5" s="3">
+        <v>200000</v>
+      </c>
+      <c r="S5" s="3">
+        <v>200000</v>
+      </c>
+      <c r="T5" s="3">
+        <v>0</v>
+      </c>
+      <c r="U5" s="3">
+        <v>0</v>
+      </c>
+      <c r="V5" s="3">
+        <v>200000</v>
+      </c>
+      <c r="W5" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y5" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="Z5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA5" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="AB5" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="AC5" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD5" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AE5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG5" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH5" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="D6" s="3">
+        <v>2</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="R6" s="3">
+        <v>200000</v>
+      </c>
+      <c r="S6" s="3">
+        <v>200000</v>
+      </c>
+      <c r="T6" s="3">
+        <v>0</v>
+      </c>
+      <c r="U6" s="3">
+        <v>0</v>
+      </c>
+      <c r="V6" s="3">
+        <v>200000</v>
+      </c>
+      <c r="W6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y6" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="Z6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA6" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="AB6" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="AC6" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD6" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AE6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH6" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="D7" s="3">
+        <v>3</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="P7" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q7" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="R7" s="3">
+        <v>200000</v>
+      </c>
+      <c r="S7" s="3">
+        <v>200000</v>
+      </c>
+      <c r="T7" s="3">
+        <v>0</v>
+      </c>
+      <c r="U7" s="3">
+        <v>0</v>
+      </c>
+      <c r="V7" s="3">
+        <v>200000</v>
+      </c>
+      <c r="W7" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y7" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="Z7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA7" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="AB7" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="AC7" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD7" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AE7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH7" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R8" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="S8" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="W8" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y8" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA8" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="AB8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC8" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD8" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AE8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH8" s="4" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="D9" s="3">
+        <v>2</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="P9" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R9" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="S9" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="T9" s="3">
+        <v>0</v>
+      </c>
+      <c r="U9" s="3">
+        <v>0</v>
+      </c>
+      <c r="V9" s="3">
+        <v>1248000</v>
+      </c>
+      <c r="W9" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X9" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y9" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA9" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="AB9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC9" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD9" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AE9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG9" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH9" s="4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="D10" s="3">
+        <v>3</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O10" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="P10" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R10" s="3">
+        <v>200000</v>
+      </c>
+      <c r="S10" s="3">
+        <v>200000</v>
+      </c>
+      <c r="T10" s="3">
+        <v>0</v>
+      </c>
+      <c r="U10" s="3">
+        <v>0</v>
+      </c>
+      <c r="V10" s="3">
+        <v>200000</v>
+      </c>
+      <c r="W10" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X10" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y10" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA10" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="AB10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC10" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD10" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AE10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG10" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH10" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="D11" s="3">
+        <v>4</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O11" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="P11" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R11" s="3">
+        <v>500000</v>
+      </c>
+      <c r="S11" s="3">
+        <v>500000</v>
+      </c>
+      <c r="T11" s="3">
+        <v>0</v>
+      </c>
+      <c r="U11" s="3">
+        <v>0</v>
+      </c>
+      <c r="V11" s="3">
+        <v>500000</v>
+      </c>
+      <c r="W11" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X11" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y11" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA11" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="AB11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC11" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD11" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AE11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG11" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH11" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="D12" s="3">
+        <v>5</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O12" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="P12" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R12" s="3">
+        <v>200000</v>
+      </c>
+      <c r="S12" s="3">
+        <v>200000</v>
+      </c>
+      <c r="T12" s="3">
+        <v>0</v>
+      </c>
+      <c r="U12" s="3">
+        <v>0</v>
+      </c>
+      <c r="V12" s="3">
+        <v>200000</v>
+      </c>
+      <c r="W12" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X12" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y12" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA12" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="AB12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC12" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD12" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AE12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG12" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH12" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="D13" s="3">
+        <v>6</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O13" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="P13" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R13" s="3">
+        <v>200000</v>
+      </c>
+      <c r="S13" s="3">
+        <v>200000</v>
+      </c>
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+      <c r="V13" s="3">
+        <v>200000</v>
+      </c>
+      <c r="W13" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X13" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y13" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA13" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="AB13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC13" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD13" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AE13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG13" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH13" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N14" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O14" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="P14" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q14" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R14" s="3">
+        <v>200000</v>
+      </c>
+      <c r="S14" s="3">
+        <v>200000</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
+        <v>200000</v>
+      </c>
+      <c r="W14" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X14" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y14" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="Z14" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA14" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="AB14" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC14" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD14" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AE14" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF14" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG14" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH14" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="D15" s="3">
+        <v>2</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N15" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O15" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="P15" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q15" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R15" s="3">
+        <v>300000</v>
+      </c>
+      <c r="S15" s="3">
+        <v>300000</v>
+      </c>
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+      <c r="W15" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X15" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y15" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z15" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA15" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="AB15" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC15" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD15" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AE15" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF15" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG15" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH15" s="4" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="D16" s="3">
+        <v>3</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N16" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O16" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="P16" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q16" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R16" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="S16" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="T16" s="3">
+        <v>0</v>
+      </c>
+      <c r="U16" s="3">
+        <v>0</v>
+      </c>
+      <c r="V16" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="W16" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X16" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y16" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z16" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA16" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="AB16" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC16" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD16" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AE16" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF16" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG16" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH16" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="D17" s="3">
+        <v>4</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N17" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O17" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="P17" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q17" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R17" s="3">
+        <v>300000</v>
+      </c>
+      <c r="S17" s="3">
+        <v>300000</v>
+      </c>
+      <c r="T17" s="3">
+        <v>0</v>
+      </c>
+      <c r="U17" s="3">
+        <v>0</v>
+      </c>
+      <c r="V17" s="3">
+        <v>0</v>
+      </c>
+      <c r="W17" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X17" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y17" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z17" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA17" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="AB17" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC17" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD17" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AE17" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF17" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG17" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH17" s="4" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="18" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="D18" s="3">
+        <v>5</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N18" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O18" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="P18" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q18" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R18" s="3">
+        <v>200000</v>
+      </c>
+      <c r="S18" s="3">
+        <v>200000</v>
+      </c>
+      <c r="T18" s="3">
+        <v>0</v>
+      </c>
+      <c r="U18" s="3">
+        <v>0</v>
+      </c>
+      <c r="V18" s="3">
+        <v>0</v>
+      </c>
+      <c r="W18" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X18" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y18" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="Z18" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA18" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="AB18" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC18" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD18" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AE18" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF18" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG18" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH18" s="4" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="19" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="D19" s="3">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N19" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O19" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="P19" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q19" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R19" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="S19" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="T19" s="3">
+        <v>0</v>
+      </c>
+      <c r="U19" s="3">
+        <v>0</v>
+      </c>
+      <c r="V19" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="W19" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X19" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y19" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z19" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA19" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="AB19" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC19" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD19" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AE19" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF19" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG19" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH19" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="20" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="D20" s="3">
+        <v>2</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L20" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N20" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O20" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="P20" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q20" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R20" s="3">
+        <v>1000000</v>
+      </c>
+      <c r="S20" s="3">
+        <v>1000000</v>
+      </c>
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
+        <v>474000</v>
+      </c>
+      <c r="W20" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X20" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y20" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z20" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA20" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="AB20" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC20" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD20" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AE20" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF20" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG20" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH20" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="D21" s="3">
+        <v>3</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L21" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N21" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O21" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="P21" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q21" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R21" s="3">
+        <v>500000</v>
+      </c>
+      <c r="S21" s="3">
+        <v>500000</v>
+      </c>
+      <c r="T21" s="3">
+        <v>0</v>
+      </c>
+      <c r="U21" s="3">
+        <v>0</v>
+      </c>
+      <c r="V21" s="3">
+        <v>500000</v>
+      </c>
+      <c r="W21" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X21" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y21" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="Z21" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA21" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="AB21" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC21" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD21" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AE21" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF21" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG21" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH21" s="4" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="22" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="D22" s="3">
+        <v>4</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L22" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N22" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O22" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="P22" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q22" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R22" s="3">
+        <v>200000</v>
+      </c>
+      <c r="S22" s="3">
+        <v>200000</v>
+      </c>
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X22" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y22" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="Z22" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA22" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="AB22" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC22" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD22" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AE22" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF22" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG22" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH22" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="D23" s="3">
+        <v>5</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L23" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N23" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O23" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="P23" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q23" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R23" s="3">
+        <v>500000</v>
+      </c>
+      <c r="S23" s="3">
+        <v>500000</v>
+      </c>
+      <c r="T23" s="3">
+        <v>0</v>
+      </c>
+      <c r="U23" s="3">
+        <v>0</v>
+      </c>
+      <c r="V23" s="3">
+        <v>0</v>
+      </c>
+      <c r="W23" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X23" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y23" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="Z23" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA23" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="AB23" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC23" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD23" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AE23" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF23" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG23" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH23" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="D24" s="3">
+        <v>6</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L24" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N24" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O24" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="P24" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q24" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R24" s="3">
+        <v>200000</v>
+      </c>
+      <c r="S24" s="3">
+        <v>200000</v>
+      </c>
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X24" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y24" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z24" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA24" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="AB24" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC24" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD24" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AE24" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF24" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG24" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH24" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="D25" s="3">
+        <v>1</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L25" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N25" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O25" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="P25" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q25" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R25" s="3">
+        <v>300000</v>
+      </c>
+      <c r="S25" s="3">
+        <v>300000</v>
+      </c>
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+      <c r="W25" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X25" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y25" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="Z25" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA25" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="AB25" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC25" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD25" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AE25" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF25" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG25" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH25" s="4" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="26" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A26" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="D26" s="3">
+        <v>2</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L26" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N26" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O26" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="P26" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q26" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R26" s="3">
+        <v>200000</v>
+      </c>
+      <c r="S26" s="3">
+        <v>200000</v>
+      </c>
+      <c r="T26" s="3">
+        <v>0</v>
+      </c>
+      <c r="U26" s="3">
+        <v>0</v>
+      </c>
+      <c r="V26" s="3">
+        <v>0</v>
+      </c>
+      <c r="W26" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X26" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y26" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="Z26" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA26" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="AB26" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC26" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD26" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AE26" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF26" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG26" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH26" s="4" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="27" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A27" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="D27" s="3">
+        <v>3</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L27" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M27" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N27" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O27" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="P27" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q27" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R27" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="S27" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="T27" s="3">
+        <v>0</v>
+      </c>
+      <c r="U27" s="3">
+        <v>0</v>
+      </c>
+      <c r="V27" s="3">
+        <v>1132000</v>
+      </c>
+      <c r="W27" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X27" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y27" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="Z27" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA27" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="AB27" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC27" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD27" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AE27" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF27" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG27" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH27" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="28" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A28" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="D28" s="3">
+        <v>4</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L28" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M28" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N28" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O28" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="P28" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q28" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R28" s="3">
+        <v>300000</v>
+      </c>
+      <c r="S28" s="3">
+        <v>300000</v>
+      </c>
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+      <c r="W28" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X28" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y28" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="Z28" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA28" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="AB28" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC28" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD28" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AE28" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF28" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG28" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH28" s="4" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="29" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A29" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="D29" s="3">
+        <v>5</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L29" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M29" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N29" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O29" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="P29" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q29" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R29" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="S29" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X29" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y29" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="Z29" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA29" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="AB29" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC29" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD29" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AE29" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF29" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG29" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH29" s="4" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="30" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A30" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="D30" s="3">
+        <v>6</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L30" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M30" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N30" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O30" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="P30" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q30" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R30" s="3">
+        <v>8000000</v>
+      </c>
+      <c r="S30" s="3">
+        <v>8000000</v>
+      </c>
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+      <c r="W30" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X30" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y30" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="Z30" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA30" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="AB30" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="AC30" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD30" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AE30" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF30" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG30" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH30" s="4" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="31" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="D31" s="3">
+        <v>7</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L31" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M31" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N31" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O31" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="P31" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q31" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R31" s="3">
+        <v>300000</v>
+      </c>
+      <c r="S31" s="3">
+        <v>300000</v>
+      </c>
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+      <c r="W31" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X31" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y31" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="Z31" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA31" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="AB31" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="AC31" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD31" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AE31" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF31" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG31" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH31" s="4" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="32" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A32" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="D32" s="3">
+        <v>1</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L32" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M32" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N32" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O32" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="P32" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q32" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="R32" s="3">
+        <v>1000000</v>
+      </c>
+      <c r="S32" s="3">
+        <v>1000000</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X32" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y32" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="Z32" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA32" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="AB32" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC32" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD32" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AE32" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF32" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG32" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH32" s="4" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="33" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="D33" s="3">
+        <v>1</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L33" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M33" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N33" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O33" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="P33" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q33" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R33" s="3">
+        <v>200000</v>
+      </c>
+      <c r="S33" s="3">
+        <v>0</v>
+      </c>
+      <c r="T33" s="3">
+        <v>-200000</v>
+      </c>
+      <c r="U33" s="3">
+        <v>200000</v>
+      </c>
+      <c r="V33" s="3">
+        <v>0</v>
+      </c>
+      <c r="W33" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X33" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y33" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="Z33" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA33" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="AB33" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC33" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD33" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AE33" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF33" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG33" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH33" s="4" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="34" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A34" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="D34" s="3">
+        <v>2</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L34" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M34" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N34" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O34" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="P34" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q34" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R34" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+      <c r="T34" s="3">
+        <v>-2000000</v>
+      </c>
+      <c r="U34" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+      <c r="W34" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X34" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y34" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="Z34" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA34" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="AB34" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC34" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD34" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AE34" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF34" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG34" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH34" s="4" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="35" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A35" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="D35" s="3">
+        <v>3</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="K35" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L35" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M35" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N35" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O35" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="P35" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q35" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R35" s="3">
+        <v>200000</v>
+      </c>
+      <c r="S35" s="3">
+        <v>0</v>
+      </c>
+      <c r="T35" s="3">
+        <v>-200000</v>
+      </c>
+      <c r="U35" s="3">
+        <v>200000</v>
+      </c>
+      <c r="V35" s="3">
+        <v>0</v>
+      </c>
+      <c r="W35" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X35" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y35" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="Z35" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA35" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="AB35" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC35" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD35" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AE35" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF35" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG35" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH35" s="4" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="36" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A36" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="D36" s="3">
+        <v>4</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="K36" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L36" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M36" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N36" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O36" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="P36" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q36" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R36" s="3">
+        <v>200000</v>
+      </c>
+      <c r="S36" s="3">
+        <v>0</v>
+      </c>
+      <c r="T36" s="3">
+        <v>-200000</v>
+      </c>
+      <c r="U36" s="3">
+        <v>200000</v>
+      </c>
+      <c r="V36" s="3">
+        <v>0</v>
+      </c>
+      <c r="W36" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X36" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y36" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="Z36" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA36" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="AB36" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC36" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD36" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AE36" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF36" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG36" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH36" s="4" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="37" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A37" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="D37" s="3">
+        <v>5</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="K37" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="L37" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O37" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="P37" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R37" s="3">
+        <v>3000000</v>
+      </c>
+      <c r="S37" s="3">
+        <v>0</v>
+      </c>
+      <c r="T37" s="3">
+        <v>-3000000</v>
+      </c>
+      <c r="U37" s="3">
+        <v>3000000</v>
+      </c>
+      <c r="V37" s="3">
+        <v>0</v>
+      </c>
+      <c r="W37" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X37" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y37" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="Z37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA37" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="AB37" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="AC37" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD37" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AE37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG37" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH37" s="4" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="38" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A38" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="D38" s="3">
+        <v>6</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="J38" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="K38" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="L38" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M38" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N38" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O38" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="P38" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q38" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R38" s="3">
+        <v>300000</v>
+      </c>
+      <c r="S38" s="3">
+        <v>0</v>
+      </c>
+      <c r="T38" s="3">
+        <v>-300000</v>
+      </c>
+      <c r="U38" s="3">
+        <v>300000</v>
+      </c>
+      <c r="V38" s="3">
+        <v>0</v>
+      </c>
+      <c r="W38" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X38" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y38" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="Z38" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA38" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="AB38" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC38" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD38" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="AE38" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF38" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG38" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH38" s="4" t="s">
+        <v>341</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/리드지 발주현황.xlsx
+++ b/리드지 발주현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\유현아\Documents\GitHub\INTEROJO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13D0742C-53BA-4C3A-8114-0E33D71BD2F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FEE8D1C-E739-4360-BE29-634C7349D2FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{500E376A-1243-49DE-9EFA-B2AD708B3011}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{500E376A-1243-49DE-9EFA-B2AD708B3011}"/>
   </bookViews>
   <sheets>
     <sheet name="구매발주현황" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1923" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1979" uniqueCount="271">
   <si>
     <t>G/W</t>
   </si>
@@ -786,10 +786,76 @@
     <t>PO-2606020008</t>
   </si>
   <si>
-    <t>2026-06-05 오전 9:11:29</t>
-  </si>
-  <si>
-    <t>2026-06-04 오후 9:28:08</t>
+    <t>2026-06-05 오후 3:36:03</t>
+  </si>
+  <si>
+    <t>2026-06-05 오후 3:35:08</t>
+  </si>
+  <si>
+    <t>2026-06-05 오후 3:36:19</t>
+  </si>
+  <si>
+    <t>2026-06-05 오후 3:36:50</t>
+  </si>
+  <si>
+    <t>2026-06-05 오후 3:36:38</t>
+  </si>
+  <si>
+    <t>2026-06-05 오전 11:59:46</t>
+  </si>
+  <si>
+    <t>PR-2605110005</t>
+  </si>
+  <si>
+    <t>20260511P227-0105</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>BS0333</t>
+  </si>
+  <si>
+    <t>알루미늄리드지 (Monthly_무지) (80mm)</t>
+  </si>
+  <si>
+    <t>BS0333-001</t>
+  </si>
+  <si>
+    <t>김령균</t>
+  </si>
+  <si>
+    <t>포장/물류팀</t>
+  </si>
+  <si>
+    <t>A관 공정부자재 / 정량 발주(발주점 도달)</t>
+  </si>
+  <si>
+    <t>S관(3공장)</t>
+  </si>
+  <si>
+    <t>PR-2605210002</t>
+  </si>
+  <si>
+    <t>20260521P227-0022</t>
+  </si>
+  <si>
+    <t>BS0005</t>
+  </si>
+  <si>
+    <t>알루미늄리드지 (Monthly_무지)</t>
+  </si>
+  <si>
+    <t>BS0005-002</t>
+  </si>
+  <si>
+    <t>주식회사 에이치앤케이</t>
+  </si>
+  <si>
+    <t>A관 공정부자재 / 발주점 도달</t>
+  </si>
+  <si>
+    <t>2026-06-02 오전 9:08:27</t>
   </si>
 </sst>
 </file>
@@ -1427,13 +1493,13 @@
         <v>34</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>35</v>
+        <v>244</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>35</v>
+        <v>244</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>36</v>
@@ -1445,34 +1511,30 @@
         <v>38</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>118</v>
+        <v>225</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>119</v>
+        <v>227</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="M3" s="3">
-        <v>200000</v>
-      </c>
-      <c r="N3" s="3">
-        <v>200000</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
+        <v>3000000</v>
+      </c>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3">
+        <v>3000000</v>
       </c>
       <c r="P3" s="3">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="Q3">
         <v>0</v>
       </c>
-      <c r="R3" s="3">
-        <v>200000</v>
-      </c>
+      <c r="R3" s="3"/>
       <c r="S3" s="1" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="T3" s="1" t="s">
         <v>44</v>
@@ -1484,10 +1546,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W3" s="4">
-        <v>1960000</v>
+        <v>29400000</v>
       </c>
       <c r="X3" s="2" t="s">
-        <v>112</v>
+        <v>177</v>
       </c>
       <c r="Y3" s="1" t="s">
         <v>47</v>
@@ -1499,22 +1561,22 @@
         <v>49</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>130</v>
+        <v>228</v>
       </c>
       <c r="AC3" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AD3" s="1" t="s">
-        <v>111</v>
+        <v>245</v>
       </c>
       <c r="AE3" s="1" t="s">
-        <v>52</v>
+        <v>246</v>
       </c>
       <c r="AF3" s="1" t="s">
-        <v>131</v>
+        <v>217</v>
       </c>
       <c r="AG3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.3">
@@ -1525,13 +1587,13 @@
         <v>34</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>36</v>
@@ -1543,31 +1605,31 @@
         <v>38</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>109</v>
+        <v>56</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>234</v>
+        <v>57</v>
       </c>
       <c r="M4" s="3">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="N4" s="3">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4" s="3">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="Q4">
         <v>0</v>
       </c>
       <c r="R4" s="3">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="S4" s="1" t="s">
         <v>43</v>
@@ -1582,10 +1644,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W4" s="4">
-        <v>1960000</v>
+        <v>19600000</v>
       </c>
       <c r="X4" s="2" t="s">
-        <v>112</v>
+        <v>58</v>
       </c>
       <c r="Y4" s="1" t="s">
         <v>47</v>
@@ -1596,23 +1658,20 @@
       <c r="AA4" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AB4" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="AC4" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AD4" s="1" t="s">
-        <v>111</v>
+        <v>51</v>
       </c>
       <c r="AE4" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="AF4" s="1" t="s">
-        <v>131</v>
+        <v>60</v>
       </c>
       <c r="AG4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.3">
@@ -1623,13 +1682,13 @@
         <v>34</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>36</v>
@@ -1641,34 +1700,30 @@
         <v>38</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="M5" s="3">
-        <v>300000</v>
-      </c>
-      <c r="N5" s="3">
-        <v>300000</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
+        <v>200000</v>
+      </c>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3">
+        <v>200000</v>
       </c>
       <c r="P5" s="3">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="Q5">
         <v>0</v>
       </c>
-      <c r="R5" s="3">
-        <v>300000</v>
-      </c>
+      <c r="R5" s="3"/>
       <c r="S5" s="1" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="T5" s="1" t="s">
         <v>44</v>
@@ -1677,13 +1732,13 @@
         <v>45</v>
       </c>
       <c r="V5">
-        <v>8.5</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="W5" s="4">
-        <v>2550000</v>
+        <v>1960000</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="Y5" s="1" t="s">
         <v>47</v>
@@ -1698,16 +1753,16 @@
         <v>50</v>
       </c>
       <c r="AD5" s="1" t="s">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="AE5" s="1" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="AF5" s="1" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="AG5">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.3">
@@ -1718,13 +1773,13 @@
         <v>34</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>36</v>
@@ -1736,34 +1791,30 @@
         <v>38</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="M6" s="3">
-        <v>2000000</v>
-      </c>
-      <c r="N6" s="3">
-        <v>2000000</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
+        <v>8000000</v>
+      </c>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3">
+        <v>8000000</v>
       </c>
       <c r="P6" s="3">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="Q6">
         <v>0</v>
       </c>
-      <c r="R6" s="3">
-        <v>2000000</v>
-      </c>
+      <c r="R6" s="3"/>
       <c r="S6" s="1" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="T6" s="1" t="s">
         <v>44</v>
@@ -1772,13 +1823,13 @@
         <v>45</v>
       </c>
       <c r="V6">
-        <v>6.7</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="W6" s="4">
-        <v>13400000</v>
+        <v>78400000</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="Y6" s="1" t="s">
         <v>47</v>
@@ -1789,20 +1840,23 @@
       <c r="AA6" s="1" t="s">
         <v>49</v>
       </c>
+      <c r="AB6" s="1" t="s">
+        <v>126</v>
+      </c>
       <c r="AC6" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AD6" s="1" t="s">
-        <v>164</v>
+        <v>127</v>
       </c>
       <c r="AE6" s="1" t="s">
-        <v>52</v>
+        <v>128</v>
       </c>
       <c r="AF6" s="1" t="s">
-        <v>53</v>
+        <v>129</v>
       </c>
       <c r="AG6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.3">
@@ -1813,13 +1867,13 @@
         <v>34</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>35</v>
+        <v>244</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>35</v>
+        <v>244</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>36</v>
@@ -1831,34 +1885,34 @@
         <v>38</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>115</v>
+        <v>55</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>235</v>
+        <v>57</v>
       </c>
       <c r="M7" s="3">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="N7" s="3">
-        <v>200000</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
+        <v>1529000</v>
+      </c>
+      <c r="O7" s="3">
+        <v>471000</v>
       </c>
       <c r="P7" s="3">
-        <v>200000</v>
+        <v>812000</v>
       </c>
       <c r="Q7">
         <v>0</v>
       </c>
       <c r="R7" s="3">
-        <v>200000</v>
+        <v>812000</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="T7" s="1" t="s">
         <v>44</v>
@@ -1870,10 +1924,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W7" s="4">
-        <v>1960000</v>
+        <v>19600000</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="Y7" s="1" t="s">
         <v>47</v>
@@ -1884,23 +1938,20 @@
       <c r="AA7" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AB7" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="AC7" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AD7" s="1" t="s">
-        <v>111</v>
+        <v>247</v>
       </c>
       <c r="AE7" s="1" t="s">
-        <v>52</v>
+        <v>246</v>
       </c>
       <c r="AF7" s="1" t="s">
-        <v>131</v>
+        <v>217</v>
       </c>
       <c r="AG7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.3">
@@ -1911,13 +1962,13 @@
         <v>34</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>114</v>
+        <v>35</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>114</v>
+        <v>35</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>114</v>
+        <v>35</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>36</v>
@@ -1929,34 +1980,34 @@
         <v>38</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>137</v>
+        <v>233</v>
       </c>
       <c r="M8" s="3">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="N8" s="3">
-        <v>1248000</v>
+        <v>200000</v>
       </c>
       <c r="O8" s="3">
-        <v>752000</v>
+        <v>0</v>
       </c>
       <c r="P8" s="3">
-        <v>1248000</v>
+        <v>200000</v>
       </c>
       <c r="Q8">
         <v>0</v>
       </c>
       <c r="R8" s="3">
-        <v>1248000</v>
+        <v>200000</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>133</v>
+        <v>43</v>
       </c>
       <c r="T8" s="1" t="s">
         <v>44</v>
@@ -1968,10 +2019,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W8" s="4">
-        <v>19600000</v>
+        <v>1960000</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="Y8" s="1" t="s">
         <v>47</v>
@@ -1982,20 +2033,23 @@
       <c r="AA8" s="1" t="s">
         <v>49</v>
       </c>
+      <c r="AB8" s="1" t="s">
+        <v>130</v>
+      </c>
       <c r="AC8" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AD8" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="AE8" s="1" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="AF8" s="1" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="AG8">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.3">
@@ -2006,13 +2060,13 @@
         <v>34</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>114</v>
+        <v>61</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>114</v>
+        <v>61</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>114</v>
+        <v>61</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>36</v>
@@ -2024,31 +2078,31 @@
         <v>38</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="M9" s="3">
-        <v>200000</v>
+        <v>500000</v>
       </c>
       <c r="N9" s="3">
-        <v>200000</v>
+        <v>500000</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9" s="3">
-        <v>200000</v>
+        <v>500000</v>
       </c>
       <c r="Q9">
         <v>0</v>
       </c>
       <c r="R9" s="3">
-        <v>200000</v>
+        <v>500000</v>
       </c>
       <c r="S9" s="1" t="s">
         <v>43</v>
@@ -2063,10 +2117,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W9" s="4">
-        <v>1960000</v>
+        <v>4900000</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>74</v>
+        <v>132</v>
       </c>
       <c r="Y9" s="1" t="s">
         <v>47</v>
@@ -2081,16 +2135,16 @@
         <v>50</v>
       </c>
       <c r="AD9" s="1" t="s">
-        <v>86</v>
+        <v>213</v>
       </c>
       <c r="AE9" s="1" t="s">
-        <v>138</v>
+        <v>68</v>
       </c>
       <c r="AF9" s="1" t="s">
-        <v>143</v>
+        <v>69</v>
       </c>
       <c r="AG9">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.3">
@@ -2101,13 +2155,13 @@
         <v>34</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>36</v>
@@ -2119,13 +2173,13 @@
         <v>38</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>103</v>
+        <v>55</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>104</v>
+        <v>56</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>105</v>
+        <v>57</v>
       </c>
       <c r="M10" s="3">
         <v>2000000</v>
@@ -2137,13 +2191,13 @@
         <v>0</v>
       </c>
       <c r="P10" s="3">
-        <v>2000000</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
+        <v>1664000</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>336000</v>
       </c>
       <c r="R10" s="3">
-        <v>2000000</v>
+        <v>1664000</v>
       </c>
       <c r="S10" s="1" t="s">
         <v>43</v>
@@ -2155,13 +2209,13 @@
         <v>45</v>
       </c>
       <c r="V10">
-        <v>6.7</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="W10" s="4">
-        <v>13400000</v>
+        <v>19600000</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="Y10" s="1" t="s">
         <v>47</v>
@@ -2176,16 +2230,16 @@
         <v>50</v>
       </c>
       <c r="AD10" s="1" t="s">
-        <v>149</v>
+        <v>239</v>
       </c>
       <c r="AE10" s="1" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="AF10" s="1" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="AG10">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.3">
@@ -2196,13 +2250,13 @@
         <v>34</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>36</v>
@@ -2214,34 +2268,30 @@
         <v>38</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>87</v>
+        <v>135</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>88</v>
+        <v>136</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>89</v>
+        <v>137</v>
       </c>
       <c r="M11" s="3">
-        <v>500000</v>
-      </c>
-      <c r="N11" s="3">
-        <v>500000</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
+        <v>2000000</v>
+      </c>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3">
+        <v>2000000</v>
       </c>
       <c r="P11" s="3">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="Q11">
         <v>0</v>
       </c>
-      <c r="R11" s="3">
-        <v>500000</v>
-      </c>
+      <c r="R11" s="3"/>
       <c r="S11" s="1" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="T11" s="1" t="s">
         <v>44</v>
@@ -2253,10 +2303,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W11" s="4">
-        <v>4900000</v>
+        <v>19600000</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="Y11" s="1" t="s">
         <v>47</v>
@@ -2271,16 +2321,16 @@
         <v>50</v>
       </c>
       <c r="AD11" s="1" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="AE11" s="1" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="AF11" s="1" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="AG11">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.3">
@@ -2291,13 +2341,13 @@
         <v>34</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>114</v>
+        <v>35</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>114</v>
+        <v>35</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>114</v>
+        <v>35</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>36</v>
@@ -2309,13 +2359,13 @@
         <v>38</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>97</v>
+        <v>234</v>
       </c>
       <c r="M12" s="3">
         <v>200000</v>
@@ -2351,7 +2401,7 @@
         <v>1960000</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="Y12" s="1" t="s">
         <v>47</v>
@@ -2362,20 +2412,23 @@
       <c r="AA12" s="1" t="s">
         <v>49</v>
       </c>
+      <c r="AB12" s="1" t="s">
+        <v>130</v>
+      </c>
       <c r="AC12" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AD12" s="1" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="AE12" s="1" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="AF12" s="1" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="AG12">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.3">
@@ -2386,13 +2439,13 @@
         <v>34</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>114</v>
+        <v>46</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>114</v>
+        <v>46</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>36</v>
@@ -2404,13 +2457,13 @@
         <v>38</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="M13" s="3">
         <v>200000</v>
@@ -2446,7 +2499,7 @@
         <v>1960000</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="Y13" s="1" t="s">
         <v>47</v>
@@ -2461,16 +2514,16 @@
         <v>50</v>
       </c>
       <c r="AD13" s="1" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="AE13" s="1" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="AF13" s="1" t="s">
-        <v>143</v>
+        <v>60</v>
       </c>
       <c r="AG13">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.3">
@@ -2481,13 +2534,13 @@
         <v>34</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>36</v>
@@ -2499,34 +2552,32 @@
         <v>38</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>55</v>
+        <v>139</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>56</v>
+        <v>140</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>57</v>
+        <v>237</v>
       </c>
       <c r="M14" s="3">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="N14" s="3">
-        <v>2000000</v>
-      </c>
-      <c r="O14">
-        <v>0</v>
+        <v>57600</v>
+      </c>
+      <c r="O14" s="3">
+        <v>142400</v>
       </c>
       <c r="P14" s="3">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="Q14">
         <v>0</v>
       </c>
-      <c r="R14" s="3">
-        <v>2000000</v>
-      </c>
+      <c r="R14" s="3"/>
       <c r="S14" s="1" t="s">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="T14" s="1" t="s">
         <v>44</v>
@@ -2535,13 +2586,13 @@
         <v>45</v>
       </c>
       <c r="V14">
-        <v>9.8000000000000007</v>
+        <v>34</v>
       </c>
       <c r="W14" s="4">
-        <v>19600000</v>
+        <v>6800000</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>58</v>
+        <v>142</v>
       </c>
       <c r="Y14" s="1" t="s">
         <v>47</v>
@@ -2556,16 +2607,16 @@
         <v>50</v>
       </c>
       <c r="AD14" s="1" t="s">
-        <v>51</v>
+        <v>248</v>
       </c>
       <c r="AE14" s="1" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="AF14" s="1" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="AG14">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.3">
@@ -2576,13 +2627,13 @@
         <v>34</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>46</v>
+        <v>94</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>46</v>
+        <v>94</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>36</v>
@@ -2594,13 +2645,13 @@
         <v>38</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="M15" s="3">
         <v>200000</v>
@@ -2636,7 +2687,7 @@
         <v>1960000</v>
       </c>
       <c r="X15" s="2" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="Y15" s="1" t="s">
         <v>47</v>
@@ -2651,16 +2702,16 @@
         <v>50</v>
       </c>
       <c r="AD15" s="1" t="s">
-        <v>75</v>
+        <v>240</v>
       </c>
       <c r="AE15" s="1" t="s">
-        <v>59</v>
+        <v>128</v>
       </c>
       <c r="AF15" s="1" t="s">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="AG15">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.3">
@@ -2671,13 +2722,13 @@
         <v>34</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>54</v>
+        <v>114</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>46</v>
+        <v>114</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>46</v>
+        <v>114</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>36</v>
@@ -2689,28 +2740,34 @@
         <v>38</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="M16" s="3">
-        <v>300000</v>
+        <v>2000000</v>
+      </c>
+      <c r="N16" s="3">
+        <v>1248000</v>
       </c>
       <c r="O16" s="3">
-        <v>300000</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
+        <v>752000</v>
+      </c>
+      <c r="P16" s="3">
+        <v>1248000</v>
       </c>
       <c r="Q16">
         <v>0</v>
       </c>
+      <c r="R16" s="3">
+        <v>1248000</v>
+      </c>
       <c r="S16" s="1" t="s">
-        <v>65</v>
+        <v>133</v>
       </c>
       <c r="T16" s="1" t="s">
         <v>44</v>
@@ -2719,13 +2776,13 @@
         <v>45</v>
       </c>
       <c r="V16">
-        <v>0</v>
-      </c>
-      <c r="W16">
-        <v>0</v>
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="W16" s="4">
+        <v>19600000</v>
       </c>
       <c r="X16" s="2" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="Y16" s="1" t="s">
         <v>47</v>
@@ -2740,16 +2797,16 @@
         <v>50</v>
       </c>
       <c r="AD16" s="1" t="s">
-        <v>156</v>
+        <v>107</v>
       </c>
       <c r="AE16" s="1" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="AF16" s="1" t="s">
-        <v>60</v>
+        <v>143</v>
       </c>
       <c r="AG16">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.3">
@@ -2760,13 +2817,13 @@
         <v>34</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>54</v>
+        <v>114</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>46</v>
+        <v>114</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>46</v>
+        <v>114</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>36</v>
@@ -2778,28 +2835,34 @@
         <v>38</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>157</v>
+        <v>83</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>158</v>
+        <v>84</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>159</v>
+        <v>85</v>
       </c>
       <c r="M17" s="3">
         <v>200000</v>
       </c>
+      <c r="N17" s="3">
+        <v>200000</v>
+      </c>
       <c r="O17" s="3">
+        <v>0</v>
+      </c>
+      <c r="P17" s="3">
         <v>200000</v>
       </c>
-      <c r="P17">
-        <v>0</v>
-      </c>
       <c r="Q17">
         <v>0</v>
       </c>
+      <c r="R17" s="3">
+        <v>200000</v>
+      </c>
       <c r="S17" s="1" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T17" s="1" t="s">
         <v>44</v>
@@ -2808,13 +2871,13 @@
         <v>45</v>
       </c>
       <c r="V17">
-        <v>34</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="W17" s="4">
-        <v>6800000</v>
+        <v>1960000</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>160</v>
+        <v>74</v>
       </c>
       <c r="Y17" s="1" t="s">
         <v>47</v>
@@ -2829,13 +2892,13 @@
         <v>50</v>
       </c>
       <c r="AD17" s="1" t="s">
-        <v>156</v>
+        <v>86</v>
       </c>
       <c r="AE17" s="1" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="AF17" s="1" t="s">
-        <v>60</v>
+        <v>143</v>
       </c>
       <c r="AG17">
         <v>5</v>
@@ -2849,13 +2912,13 @@
         <v>34</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>36</v>
@@ -2867,31 +2930,31 @@
         <v>38</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>165</v>
+        <v>55</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>166</v>
+        <v>56</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>167</v>
+        <v>57</v>
       </c>
       <c r="M18" s="3">
-        <v>300000</v>
+        <v>2000000</v>
       </c>
       <c r="N18" s="3">
-        <v>300000</v>
+        <v>2000000</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18" s="3">
-        <v>300000</v>
+        <v>2000000</v>
       </c>
       <c r="Q18">
         <v>0</v>
       </c>
       <c r="R18" s="3">
-        <v>300000</v>
+        <v>2000000</v>
       </c>
       <c r="S18" s="1" t="s">
         <v>43</v>
@@ -2906,10 +2969,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W18" s="4">
-        <v>2940000</v>
+        <v>19600000</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="Y18" s="1" t="s">
         <v>47</v>
@@ -2924,16 +2987,16 @@
         <v>50</v>
       </c>
       <c r="AD18" s="1" t="s">
-        <v>236</v>
+        <v>75</v>
       </c>
       <c r="AE18" s="1" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="AF18" s="1" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="AG18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.3">
@@ -2944,13 +3007,13 @@
         <v>34</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>36</v>
@@ -2962,19 +3025,19 @@
         <v>38</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>62</v>
+        <v>144</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>63</v>
+        <v>145</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>64</v>
+        <v>146</v>
       </c>
       <c r="M19" s="3">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="O19" s="3">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -2995,10 +3058,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W19" s="4">
-        <v>1960000</v>
+        <v>2940000</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>66</v>
+        <v>125</v>
       </c>
       <c r="Y19" s="1" t="s">
         <v>47</v>
@@ -3009,20 +3072,23 @@
       <c r="AA19" s="1" t="s">
         <v>49</v>
       </c>
+      <c r="AB19" s="1" t="s">
+        <v>147</v>
+      </c>
       <c r="AC19" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AD19" s="1" t="s">
-        <v>67</v>
+        <v>148</v>
       </c>
       <c r="AE19" s="1" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="AF19" s="1" t="s">
-        <v>69</v>
+        <v>129</v>
       </c>
       <c r="AG19">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.3">
@@ -3033,13 +3099,13 @@
         <v>34</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>61</v>
+        <v>244</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>61</v>
+        <v>244</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>36</v>
@@ -3051,34 +3117,30 @@
         <v>38</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>76</v>
+        <v>219</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>77</v>
+        <v>221</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>78</v>
+        <v>220</v>
       </c>
       <c r="M20" s="3">
-        <v>500000</v>
-      </c>
-      <c r="N20" s="3">
-        <v>500000</v>
-      </c>
-      <c r="O20">
-        <v>0</v>
+        <v>200000</v>
+      </c>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3">
+        <v>200000</v>
       </c>
       <c r="P20" s="3">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="Q20">
         <v>0</v>
       </c>
-      <c r="R20" s="3">
-        <v>500000</v>
-      </c>
+      <c r="R20" s="3"/>
       <c r="S20" s="1" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="T20" s="1" t="s">
         <v>44</v>
@@ -3090,10 +3152,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W20" s="4">
-        <v>4900000</v>
+        <v>1960000</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="Y20" s="1" t="s">
         <v>47</v>
@@ -3108,16 +3170,16 @@
         <v>50</v>
       </c>
       <c r="AD20" s="1" t="s">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="AE20" s="1" t="s">
-        <v>68</v>
+        <v>246</v>
       </c>
       <c r="AF20" s="1" t="s">
-        <v>69</v>
+        <v>217</v>
       </c>
       <c r="AG20">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.3">
@@ -3128,13 +3190,13 @@
         <v>34</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>36</v>
@@ -3146,28 +3208,34 @@
         <v>38</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>139</v>
+        <v>103</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>140</v>
+        <v>104</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>237</v>
+        <v>105</v>
       </c>
       <c r="M21" s="3">
-        <v>200000</v>
+        <v>2000000</v>
+      </c>
+      <c r="N21" s="3">
+        <v>2000000</v>
       </c>
       <c r="O21" s="3">
-        <v>200000</v>
-      </c>
-      <c r="P21">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P21" s="3">
+        <v>2000000</v>
       </c>
       <c r="Q21">
         <v>0</v>
       </c>
+      <c r="R21" s="3">
+        <v>2000000</v>
+      </c>
       <c r="S21" s="1" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T21" s="1" t="s">
         <v>44</v>
@@ -3176,13 +3244,13 @@
         <v>45</v>
       </c>
       <c r="V21">
-        <v>34</v>
+        <v>6.7</v>
       </c>
       <c r="W21" s="4">
-        <v>6800000</v>
+        <v>13400000</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>142</v>
+        <v>93</v>
       </c>
       <c r="Y21" s="1" t="s">
         <v>47</v>
@@ -3197,16 +3265,16 @@
         <v>50</v>
       </c>
       <c r="AD21" s="1" t="s">
-        <v>67</v>
+        <v>149</v>
       </c>
       <c r="AE21" s="1" t="s">
-        <v>68</v>
+        <v>138</v>
       </c>
       <c r="AF21" s="1" t="s">
-        <v>69</v>
+        <v>143</v>
       </c>
       <c r="AG21">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.3">
@@ -3217,13 +3285,13 @@
         <v>34</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>36</v>
@@ -3235,32 +3303,30 @@
         <v>38</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>56</v>
+        <v>241</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>57</v>
+        <v>152</v>
       </c>
       <c r="M22" s="3">
-        <v>2000000</v>
+        <v>300000</v>
       </c>
       <c r="N22" s="3">
-        <v>2000000</v>
+        <v>300000</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22" s="3">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="Q22">
         <v>0</v>
       </c>
-      <c r="R22" s="3">
-        <v>2000000</v>
-      </c>
+      <c r="R22" s="3"/>
       <c r="S22" s="1" t="s">
         <v>43</v>
       </c>
@@ -3274,10 +3340,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W22" s="4">
-        <v>19600000</v>
+        <v>2940000</v>
       </c>
       <c r="X22" s="2" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="Y22" s="1" t="s">
         <v>47</v>
@@ -3292,16 +3358,16 @@
         <v>50</v>
       </c>
       <c r="AD22" s="1" t="s">
-        <v>75</v>
+        <v>249</v>
       </c>
       <c r="AE22" s="1" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="AF22" s="1" t="s">
-        <v>69</v>
+        <v>129</v>
       </c>
       <c r="AG22">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.3">
@@ -3312,13 +3378,13 @@
         <v>34</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>61</v>
+        <v>244</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>61</v>
+        <v>244</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>36</v>
@@ -3330,34 +3396,30 @@
         <v>38</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>161</v>
+        <v>222</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>162</v>
+        <v>224</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>163</v>
+        <v>223</v>
       </c>
       <c r="M23" s="3">
-        <v>1000000</v>
-      </c>
-      <c r="N23" s="3">
-        <v>1000000</v>
-      </c>
-      <c r="O23">
-        <v>0</v>
+        <v>200000</v>
+      </c>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3">
+        <v>200000</v>
       </c>
       <c r="P23" s="3">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="Q23">
         <v>0</v>
       </c>
-      <c r="R23" s="3">
-        <v>1000000</v>
-      </c>
+      <c r="R23" s="3"/>
       <c r="S23" s="1" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="T23" s="1" t="s">
         <v>44</v>
@@ -3369,10 +3431,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W23" s="4">
-        <v>9800000</v>
+        <v>1960000</v>
       </c>
       <c r="X23" s="2" t="s">
-        <v>74</v>
+        <v>177</v>
       </c>
       <c r="Y23" s="1" t="s">
         <v>47</v>
@@ -3387,16 +3449,16 @@
         <v>50</v>
       </c>
       <c r="AD23" s="1" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="AE23" s="1" t="s">
-        <v>68</v>
+        <v>246</v>
       </c>
       <c r="AF23" s="1" t="s">
-        <v>69</v>
+        <v>217</v>
       </c>
       <c r="AG23">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.3">
@@ -3407,13 +3469,13 @@
         <v>34</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>36</v>
@@ -3425,28 +3487,34 @@
         <v>38</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>174</v>
+        <v>87</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>175</v>
+        <v>88</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>176</v>
+        <v>89</v>
       </c>
       <c r="M24" s="3">
         <v>500000</v>
       </c>
+      <c r="N24" s="3">
+        <v>500000</v>
+      </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>500000</v>
       </c>
-      <c r="P24">
-        <v>0</v>
-      </c>
       <c r="Q24">
         <v>0</v>
       </c>
+      <c r="R24" s="3">
+        <v>500000</v>
+      </c>
       <c r="S24" s="1" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T24" s="1" t="s">
         <v>44</v>
@@ -3461,7 +3529,7 @@
         <v>4900000</v>
       </c>
       <c r="X24" s="2" t="s">
-        <v>177</v>
+        <v>74</v>
       </c>
       <c r="Y24" s="1" t="s">
         <v>47</v>
@@ -3476,16 +3544,16 @@
         <v>50</v>
       </c>
       <c r="AD24" s="1" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="AE24" s="1" t="s">
-        <v>68</v>
+        <v>138</v>
       </c>
       <c r="AF24" s="1" t="s">
-        <v>69</v>
+        <v>143</v>
       </c>
       <c r="AG24">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.3">
@@ -3496,13 +3564,13 @@
         <v>34</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>36</v>
@@ -3514,28 +3582,34 @@
         <v>38</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="M25" s="3">
-        <v>8000000</v>
+        <v>300000</v>
+      </c>
+      <c r="N25" s="3">
+        <v>300000</v>
       </c>
       <c r="O25" s="3">
-        <v>8000000</v>
-      </c>
-      <c r="P25">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>300000</v>
       </c>
       <c r="Q25">
         <v>0</v>
       </c>
+      <c r="R25" s="3">
+        <v>300000</v>
+      </c>
       <c r="S25" s="1" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T25" s="1" t="s">
         <v>44</v>
@@ -3544,13 +3618,13 @@
         <v>45</v>
       </c>
       <c r="V25">
-        <v>9.8000000000000007</v>
+        <v>8.5</v>
       </c>
       <c r="W25" s="4">
-        <v>78400000</v>
+        <v>2550000</v>
       </c>
       <c r="X25" s="2" t="s">
-        <v>125</v>
+        <v>46</v>
       </c>
       <c r="Y25" s="1" t="s">
         <v>47</v>
@@ -3561,23 +3635,20 @@
       <c r="AA25" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AB25" s="1" t="s">
-        <v>126</v>
-      </c>
       <c r="AC25" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AD25" s="1" t="s">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="AE25" s="1" t="s">
-        <v>128</v>
+        <v>52</v>
       </c>
       <c r="AF25" s="1" t="s">
-        <v>129</v>
+        <v>53</v>
       </c>
       <c r="AG25">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:33" x14ac:dyDescent="0.3">
@@ -3588,13 +3659,13 @@
         <v>34</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>36</v>
@@ -3606,32 +3677,30 @@
         <v>38</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>55</v>
+        <v>153</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>56</v>
+        <v>154</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>57</v>
+        <v>155</v>
       </c>
       <c r="M26" s="3">
-        <v>2000000</v>
+        <v>300000</v>
       </c>
       <c r="N26" s="3">
-        <v>2000000</v>
+        <v>300000</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26" s="3">
-        <v>1664000</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="3">
-        <v>336000</v>
-      </c>
-      <c r="R26" s="3">
-        <v>1664000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R26" s="3"/>
       <c r="S26" s="1" t="s">
         <v>43</v>
       </c>
@@ -3642,13 +3711,13 @@
         <v>45</v>
       </c>
       <c r="V26">
-        <v>9.8000000000000007</v>
+        <v>0</v>
       </c>
       <c r="W26" s="4">
-        <v>19600000</v>
+        <v>0</v>
       </c>
       <c r="X26" s="2" t="s">
-        <v>134</v>
+        <v>58</v>
       </c>
       <c r="Y26" s="1" t="s">
         <v>47</v>
@@ -3663,16 +3732,16 @@
         <v>50</v>
       </c>
       <c r="AD26" s="1" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="AE26" s="1" t="s">
-        <v>128</v>
+        <v>59</v>
       </c>
       <c r="AF26" s="1" t="s">
-        <v>129</v>
+        <v>60</v>
       </c>
       <c r="AG26">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.3">
@@ -3683,13 +3752,13 @@
         <v>34</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>94</v>
+        <v>244</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>94</v>
+        <v>244</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>36</v>
@@ -3701,19 +3770,19 @@
         <v>38</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>136</v>
+        <v>91</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>137</v>
+        <v>92</v>
       </c>
       <c r="M27" s="3">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="O27" s="3">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -3734,10 +3803,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W27" s="4">
-        <v>19600000</v>
+        <v>1960000</v>
       </c>
       <c r="X27" s="2" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="Y27" s="1" t="s">
         <v>47</v>
@@ -3752,16 +3821,16 @@
         <v>50</v>
       </c>
       <c r="AD27" s="1" t="s">
-        <v>127</v>
+        <v>245</v>
       </c>
       <c r="AE27" s="1" t="s">
-        <v>128</v>
+        <v>246</v>
       </c>
       <c r="AF27" s="1" t="s">
-        <v>129</v>
+        <v>217</v>
       </c>
       <c r="AG27">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.3">
@@ -3772,13 +3841,13 @@
         <v>34</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>36</v>
@@ -3790,13 +3859,13 @@
         <v>38</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="M28" s="3">
         <v>200000</v>
@@ -3832,7 +3901,7 @@
         <v>1960000</v>
       </c>
       <c r="X28" s="2" t="s">
-        <v>132</v>
+        <v>74</v>
       </c>
       <c r="Y28" s="1" t="s">
         <v>47</v>
@@ -3847,16 +3916,16 @@
         <v>50</v>
       </c>
       <c r="AD28" s="1" t="s">
-        <v>240</v>
+        <v>98</v>
       </c>
       <c r="AE28" s="1" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="AF28" s="1" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="AG28">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.3">
@@ -3867,13 +3936,13 @@
         <v>34</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>36</v>
@@ -3885,19 +3954,19 @@
         <v>38</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="M29" s="3">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="O29" s="3">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="P29">
         <v>0</v>
@@ -3915,13 +3984,13 @@
         <v>45</v>
       </c>
       <c r="V29">
-        <v>9.8000000000000007</v>
+        <v>34</v>
       </c>
       <c r="W29" s="4">
-        <v>2940000</v>
+        <v>6800000</v>
       </c>
       <c r="X29" s="2" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="Y29" s="1" t="s">
         <v>47</v>
@@ -3932,23 +4001,20 @@
       <c r="AA29" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AB29" s="1" t="s">
-        <v>147</v>
-      </c>
       <c r="AC29" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AD29" s="1" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="AE29" s="1" t="s">
-        <v>128</v>
+        <v>59</v>
       </c>
       <c r="AF29" s="1" t="s">
-        <v>129</v>
+        <v>60</v>
       </c>
       <c r="AG29">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.3">
@@ -3959,13 +4025,13 @@
         <v>34</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>36</v>
@@ -3977,28 +4043,34 @@
         <v>38</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>241</v>
+        <v>91</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>152</v>
+        <v>92</v>
       </c>
       <c r="M30" s="3">
-        <v>300000</v>
+        <v>200000</v>
+      </c>
+      <c r="N30" s="3">
+        <v>200000</v>
       </c>
       <c r="O30" s="3">
-        <v>300000</v>
-      </c>
-      <c r="P30">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P30" s="3">
+        <v>200000</v>
       </c>
       <c r="Q30">
         <v>0</v>
       </c>
+      <c r="R30" s="3">
+        <v>200000</v>
+      </c>
       <c r="S30" s="1" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T30" s="1" t="s">
         <v>44</v>
@@ -4010,10 +4082,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W30" s="4">
-        <v>2940000</v>
+        <v>1960000</v>
       </c>
       <c r="X30" s="2" t="s">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="Y30" s="1" t="s">
         <v>47</v>
@@ -4028,16 +4100,16 @@
         <v>50</v>
       </c>
       <c r="AD30" s="1" t="s">
-        <v>127</v>
+        <v>86</v>
       </c>
       <c r="AE30" s="1" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="AF30" s="1" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="AG30">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.3">
@@ -4048,13 +4120,13 @@
         <v>34</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>36</v>
@@ -4066,28 +4138,34 @@
         <v>38</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>242</v>
+        <v>162</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>243</v>
+        <v>163</v>
       </c>
       <c r="M31" s="3">
-        <v>300000</v>
+        <v>1000000</v>
+      </c>
+      <c r="N31" s="3">
+        <v>1000000</v>
       </c>
       <c r="O31" s="3">
-        <v>300000</v>
-      </c>
-      <c r="P31">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P31" s="3">
+        <v>1000000</v>
       </c>
       <c r="Q31">
         <v>0</v>
       </c>
+      <c r="R31" s="3">
+        <v>1000000</v>
+      </c>
       <c r="S31" s="1" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T31" s="1" t="s">
         <v>44</v>
@@ -4099,10 +4177,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W31" s="4">
-        <v>2940000</v>
+        <v>9800000</v>
       </c>
       <c r="X31" s="2" t="s">
-        <v>132</v>
+        <v>74</v>
       </c>
       <c r="Y31" s="1" t="s">
         <v>47</v>
@@ -4117,16 +4195,16 @@
         <v>50</v>
       </c>
       <c r="AD31" s="1" t="s">
-        <v>127</v>
+        <v>238</v>
       </c>
       <c r="AE31" s="1" t="s">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="AF31" s="1" t="s">
-        <v>129</v>
+        <v>69</v>
       </c>
       <c r="AG31">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.3">
@@ -4137,13 +4215,13 @@
         <v>34</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>36</v>
@@ -4155,28 +4233,34 @@
         <v>38</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>168</v>
+        <v>103</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>170</v>
+        <v>105</v>
       </c>
       <c r="M32" s="3">
-        <v>1000000</v>
+        <v>2000000</v>
+      </c>
+      <c r="N32" s="3">
+        <v>2000000</v>
       </c>
       <c r="O32" s="3">
-        <v>1000000</v>
-      </c>
-      <c r="P32">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
+        <v>2000000</v>
       </c>
       <c r="Q32">
         <v>0</v>
       </c>
+      <c r="R32" s="3">
+        <v>2000000</v>
+      </c>
       <c r="S32" s="1" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T32" s="1" t="s">
         <v>44</v>
@@ -4185,13 +4269,13 @@
         <v>45</v>
       </c>
       <c r="V32">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
       <c r="W32" s="4">
-        <v>7700000</v>
+        <v>13400000</v>
       </c>
       <c r="X32" s="2" t="s">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="Y32" s="1" t="s">
         <v>47</v>
@@ -4206,16 +4290,16 @@
         <v>50</v>
       </c>
       <c r="AD32" s="1" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="AE32" s="1" t="s">
-        <v>172</v>
+        <v>52</v>
       </c>
       <c r="AF32" s="1" t="s">
-        <v>173</v>
+        <v>53</v>
       </c>
       <c r="AG32">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:33" x14ac:dyDescent="0.3">
@@ -4244,19 +4328,19 @@
         <v>38</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="M33" s="3">
-        <v>3000000</v>
+        <v>300000</v>
       </c>
       <c r="O33" s="3">
-        <v>3000000</v>
+        <v>300000</v>
       </c>
       <c r="P33">
         <v>0</v>
@@ -4277,10 +4361,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W33" s="4">
-        <v>29400000</v>
+        <v>2940000</v>
       </c>
       <c r="X33" s="2" t="s">
-        <v>177</v>
+        <v>232</v>
       </c>
       <c r="Y33" s="1" t="s">
         <v>47</v>
@@ -4291,9 +4375,6 @@
       <c r="AA33" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AB33" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="AC33" s="1" t="s">
         <v>50</v>
       </c>
@@ -4307,7 +4388,7 @@
         <v>217</v>
       </c>
       <c r="AG33">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:33" x14ac:dyDescent="0.3">
@@ -4318,13 +4399,13 @@
         <v>34</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>244</v>
+        <v>35</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>244</v>
+        <v>35</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>36</v>
@@ -4336,34 +4417,34 @@
         <v>38</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>55</v>
+        <v>115</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>57</v>
+        <v>235</v>
       </c>
       <c r="M34" s="3">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="N34" s="3">
-        <v>812000</v>
+        <v>200000</v>
       </c>
       <c r="O34" s="3">
-        <v>1188000</v>
+        <v>0</v>
       </c>
       <c r="P34" s="3">
-        <v>822000</v>
+        <v>200000</v>
       </c>
       <c r="Q34">
         <v>0</v>
       </c>
       <c r="R34" s="3">
-        <v>822000</v>
+        <v>200000</v>
       </c>
       <c r="S34" s="1" t="s">
-        <v>133</v>
+        <v>43</v>
       </c>
       <c r="T34" s="1" t="s">
         <v>44</v>
@@ -4375,10 +4456,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W34" s="4">
-        <v>19600000</v>
+        <v>1960000</v>
       </c>
       <c r="X34" s="2" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="Y34" s="1" t="s">
         <v>47</v>
@@ -4389,20 +4470,23 @@
       <c r="AA34" s="1" t="s">
         <v>49</v>
       </c>
+      <c r="AB34" s="1" t="s">
+        <v>130</v>
+      </c>
       <c r="AC34" s="1" t="s">
         <v>50</v>
       </c>
       <c r="AD34" s="1" t="s">
-        <v>247</v>
+        <v>111</v>
       </c>
       <c r="AE34" s="1" t="s">
-        <v>246</v>
+        <v>52</v>
       </c>
       <c r="AF34" s="1" t="s">
-        <v>217</v>
+        <v>131</v>
       </c>
       <c r="AG34">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:33" x14ac:dyDescent="0.3">
@@ -4413,13 +4497,13 @@
         <v>34</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>244</v>
+        <v>54</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>244</v>
+        <v>46</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>36</v>
@@ -4431,28 +4515,34 @@
         <v>38</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>219</v>
+        <v>165</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>221</v>
+        <v>166</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>220</v>
+        <v>167</v>
       </c>
       <c r="M35" s="3">
-        <v>200000</v>
+        <v>300000</v>
+      </c>
+      <c r="N35" s="3">
+        <v>300000</v>
       </c>
       <c r="O35" s="3">
-        <v>200000</v>
-      </c>
-      <c r="P35">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P35" s="3">
+        <v>300000</v>
       </c>
       <c r="Q35">
         <v>0</v>
       </c>
+      <c r="R35" s="3">
+        <v>300000</v>
+      </c>
       <c r="S35" s="1" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T35" s="1" t="s">
         <v>44</v>
@@ -4464,10 +4554,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W35" s="4">
-        <v>1960000</v>
+        <v>2940000</v>
       </c>
       <c r="X35" s="2" t="s">
-        <v>134</v>
+        <v>58</v>
       </c>
       <c r="Y35" s="1" t="s">
         <v>47</v>
@@ -4482,16 +4572,16 @@
         <v>50</v>
       </c>
       <c r="AD35" s="1" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="AE35" s="1" t="s">
-        <v>246</v>
+        <v>59</v>
       </c>
       <c r="AF35" s="1" t="s">
-        <v>217</v>
+        <v>60</v>
       </c>
       <c r="AG35">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:33" x14ac:dyDescent="0.3">
@@ -4502,13 +4592,13 @@
         <v>34</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>244</v>
+        <v>74</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>244</v>
+        <v>74</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>36</v>
@@ -4520,19 +4610,19 @@
         <v>38</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>222</v>
+        <v>168</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>224</v>
+        <v>169</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>223</v>
+        <v>170</v>
       </c>
       <c r="M36" s="3">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="O36" s="3">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="P36">
         <v>0</v>
@@ -4550,13 +4640,13 @@
         <v>45</v>
       </c>
       <c r="V36">
-        <v>9.8000000000000007</v>
+        <v>7.7</v>
       </c>
       <c r="W36" s="4">
-        <v>1960000</v>
+        <v>7700000</v>
       </c>
       <c r="X36" s="2" t="s">
-        <v>177</v>
+        <v>74</v>
       </c>
       <c r="Y36" s="1" t="s">
         <v>47</v>
@@ -4571,16 +4661,16 @@
         <v>50</v>
       </c>
       <c r="AD36" s="1" t="s">
-        <v>245</v>
+        <v>171</v>
       </c>
       <c r="AE36" s="1" t="s">
-        <v>246</v>
+        <v>172</v>
       </c>
       <c r="AF36" s="1" t="s">
-        <v>217</v>
+        <v>173</v>
       </c>
       <c r="AG36">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:33" x14ac:dyDescent="0.3">
@@ -4591,13 +4681,13 @@
         <v>34</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>244</v>
+        <v>61</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>244</v>
+        <v>61</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>36</v>
@@ -4609,19 +4699,19 @@
         <v>38</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>90</v>
+        <v>174</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>91</v>
+        <v>175</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>92</v>
+        <v>176</v>
       </c>
       <c r="M37" s="3">
-        <v>200000</v>
+        <v>500000</v>
       </c>
       <c r="O37" s="3">
-        <v>200000</v>
+        <v>500000</v>
       </c>
       <c r="P37">
         <v>0</v>
@@ -4642,10 +4732,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W37" s="4">
-        <v>1960000</v>
+        <v>4900000</v>
       </c>
       <c r="X37" s="2" t="s">
-        <v>134</v>
+        <v>177</v>
       </c>
       <c r="Y37" s="1" t="s">
         <v>47</v>
@@ -4660,16 +4750,16 @@
         <v>50</v>
       </c>
       <c r="AD37" s="1" t="s">
-        <v>245</v>
+        <v>67</v>
       </c>
       <c r="AE37" s="1" t="s">
-        <v>246</v>
+        <v>68</v>
       </c>
       <c r="AF37" s="1" t="s">
-        <v>217</v>
+        <v>69</v>
       </c>
       <c r="AG37">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:33" x14ac:dyDescent="0.3">
@@ -4680,13 +4770,13 @@
         <v>34</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>244</v>
+        <v>94</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>244</v>
+        <v>94</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>36</v>
@@ -4698,19 +4788,22 @@
         <v>38</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>229</v>
+        <v>178</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="M38" s="3">
         <v>300000</v>
       </c>
+      <c r="N38" s="3">
+        <v>300000</v>
+      </c>
       <c r="O38" s="3">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="P38">
         <v>0</v>
@@ -4719,7 +4812,7 @@
         <v>0</v>
       </c>
       <c r="S38" s="1" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T38" s="1" t="s">
         <v>44</v>
@@ -4734,7 +4827,7 @@
         <v>2940000</v>
       </c>
       <c r="X38" s="2" t="s">
-        <v>232</v>
+        <v>132</v>
       </c>
       <c r="Y38" s="1" t="s">
         <v>47</v>
@@ -4749,16 +4842,16 @@
         <v>50</v>
       </c>
       <c r="AD38" s="1" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="AE38" s="1" t="s">
-        <v>246</v>
+        <v>128</v>
       </c>
       <c r="AF38" s="1" t="s">
-        <v>217</v>
+        <v>129</v>
       </c>
       <c r="AG38">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.3">
@@ -4938,7 +5031,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8105D0C-47A0-4625-B289-24FCAF816E36}">
-  <dimension ref="A1:AH38"/>
+  <dimension ref="A1:AH40"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:34" x14ac:dyDescent="0.3">
@@ -5146,7 +5239,7 @@
         <v>47</v>
       </c>
       <c r="AH2" s="6" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.3">
@@ -5250,7 +5343,7 @@
         <v>47</v>
       </c>
       <c r="AH3" s="6" t="s">
-        <v>51</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.3">
@@ -5354,7 +5447,7 @@
         <v>47</v>
       </c>
       <c r="AH4" s="6" t="s">
-        <v>164</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.3">
@@ -5458,7 +5551,7 @@
         <v>47</v>
       </c>
       <c r="AH5" s="6" t="s">
-        <v>111</v>
+        <v>252</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.3">
@@ -5562,7 +5655,7 @@
         <v>47</v>
       </c>
       <c r="AH6" s="6" t="s">
-        <v>111</v>
+        <v>252</v>
       </c>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.3">
@@ -5666,7 +5759,7 @@
         <v>47</v>
       </c>
       <c r="AH7" s="6" t="s">
-        <v>111</v>
+        <v>252</v>
       </c>
     </row>
     <row r="8" spans="1:34" x14ac:dyDescent="0.3">
@@ -5674,31 +5767,31 @@
         <v>33</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>143</v>
+        <v>253</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>210</v>
+        <v>254</v>
       </c>
       <c r="D8" s="5">
         <v>1</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>121</v>
+        <v>255</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>204</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>103</v>
+        <v>256</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>105</v>
+        <v>257</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>104</v>
+        <v>258</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="K8" s="6" t="s">
         <v>36</v>
@@ -5713,19 +5806,19 @@
         <v>39</v>
       </c>
       <c r="O8" s="6" t="s">
-        <v>47</v>
+        <v>259</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>205</v>
+        <v>260</v>
       </c>
       <c r="Q8" s="6" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="R8" s="5">
-        <v>2000000</v>
+        <v>6000000</v>
       </c>
       <c r="S8" s="5">
-        <v>2000000</v>
+        <v>6000000</v>
       </c>
       <c r="T8" s="5">
         <v>0</v>
@@ -5734,7 +5827,7 @@
         <v>0</v>
       </c>
       <c r="V8" s="5">
-        <v>2000000</v>
+        <v>1908532</v>
       </c>
       <c r="W8" s="6" t="s">
         <v>50</v>
@@ -5743,7 +5836,7 @@
         <v>49</v>
       </c>
       <c r="Y8" s="7" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="Z8" s="6" t="s">
         <v>39</v>
@@ -5752,13 +5845,13 @@
         <v>206</v>
       </c>
       <c r="AB8" s="6" t="s">
-        <v>39</v>
+        <v>261</v>
       </c>
       <c r="AC8" s="6" t="s">
-        <v>207</v>
+        <v>262</v>
       </c>
       <c r="AD8" s="6" t="s">
-        <v>207</v>
+        <v>262</v>
       </c>
       <c r="AE8" s="6" t="s">
         <v>39</v>
@@ -5767,10 +5860,10 @@
         <v>39</v>
       </c>
       <c r="AG8" s="6" t="s">
-        <v>47</v>
+        <v>259</v>
       </c>
       <c r="AH8" s="6" t="s">
-        <v>149</v>
+        <v>252</v>
       </c>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.3">
@@ -5784,7 +5877,7 @@
         <v>210</v>
       </c>
       <c r="D9" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>121</v>
@@ -5793,16 +5886,16 @@
         <v>204</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>137</v>
+        <v>105</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="K9" s="6" t="s">
         <v>36</v>
@@ -5838,7 +5931,7 @@
         <v>0</v>
       </c>
       <c r="V9" s="5">
-        <v>1248000</v>
+        <v>2000000</v>
       </c>
       <c r="W9" s="6" t="s">
         <v>50</v>
@@ -5874,7 +5967,7 @@
         <v>47</v>
       </c>
       <c r="AH9" s="6" t="s">
-        <v>107</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.3">
@@ -5888,7 +5981,7 @@
         <v>210</v>
       </c>
       <c r="D10" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>121</v>
@@ -5897,16 +5990,16 @@
         <v>204</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K10" s="6" t="s">
         <v>36</v>
@@ -5930,10 +6023,10 @@
         <v>39</v>
       </c>
       <c r="R10" s="5">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="S10" s="5">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="T10" s="5">
         <v>0</v>
@@ -5942,7 +6035,7 @@
         <v>0</v>
       </c>
       <c r="V10" s="5">
-        <v>200000</v>
+        <v>1248000</v>
       </c>
       <c r="W10" s="6" t="s">
         <v>50</v>
@@ -5951,7 +6044,7 @@
         <v>49</v>
       </c>
       <c r="Y10" s="7" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="Z10" s="6" t="s">
         <v>39</v>
@@ -5978,7 +6071,7 @@
         <v>47</v>
       </c>
       <c r="AH10" s="6" t="s">
-        <v>98</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.3">
@@ -5992,7 +6085,7 @@
         <v>210</v>
       </c>
       <c r="D11" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>121</v>
@@ -6001,16 +6094,16 @@
         <v>204</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>36</v>
@@ -6034,10 +6127,10 @@
         <v>39</v>
       </c>
       <c r="R11" s="5">
-        <v>500000</v>
+        <v>200000</v>
       </c>
       <c r="S11" s="5">
-        <v>500000</v>
+        <v>200000</v>
       </c>
       <c r="T11" s="5">
         <v>0</v>
@@ -6046,7 +6139,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="5">
-        <v>500000</v>
+        <v>200000</v>
       </c>
       <c r="W11" s="6" t="s">
         <v>50</v>
@@ -6082,7 +6175,7 @@
         <v>47</v>
       </c>
       <c r="AH11" s="6" t="s">
-        <v>86</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.3">
@@ -6096,7 +6189,7 @@
         <v>210</v>
       </c>
       <c r="D12" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>121</v>
@@ -6105,13 +6198,13 @@
         <v>204</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>82</v>
@@ -6138,10 +6231,10 @@
         <v>39</v>
       </c>
       <c r="R12" s="5">
-        <v>200000</v>
+        <v>500000</v>
       </c>
       <c r="S12" s="5">
-        <v>200000</v>
+        <v>500000</v>
       </c>
       <c r="T12" s="5">
         <v>0</v>
@@ -6150,7 +6243,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="5">
-        <v>200000</v>
+        <v>500000</v>
       </c>
       <c r="W12" s="6" t="s">
         <v>50</v>
@@ -6186,7 +6279,7 @@
         <v>47</v>
       </c>
       <c r="AH12" s="6" t="s">
-        <v>86</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" spans="1:34" x14ac:dyDescent="0.3">
@@ -6200,7 +6293,7 @@
         <v>210</v>
       </c>
       <c r="D13" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>121</v>
@@ -6209,16 +6302,16 @@
         <v>204</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>244</v>
+        <v>82</v>
       </c>
       <c r="K13" s="6" t="s">
         <v>36</v>
@@ -6290,7 +6383,7 @@
         <v>47</v>
       </c>
       <c r="AH13" s="6" t="s">
-        <v>86</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.3">
@@ -6298,31 +6391,31 @@
         <v>33</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>60</v>
+        <v>143</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D14" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>204</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>74</v>
+        <v>244</v>
       </c>
       <c r="K14" s="6" t="s">
         <v>36</v>
@@ -6367,7 +6460,7 @@
         <v>49</v>
       </c>
       <c r="Y14" s="7" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="Z14" s="6" t="s">
         <v>39</v>
@@ -6394,7 +6487,7 @@
         <v>47</v>
       </c>
       <c r="AH14" s="6" t="s">
-        <v>75</v>
+        <v>252</v>
       </c>
     </row>
     <row r="15" spans="1:34" x14ac:dyDescent="0.3">
@@ -6408,7 +6501,7 @@
         <v>211</v>
       </c>
       <c r="D15" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>113</v>
@@ -6417,16 +6510,16 @@
         <v>204</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>165</v>
+        <v>79</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>216</v>
+        <v>74</v>
       </c>
       <c r="K15" s="6" t="s">
         <v>36</v>
@@ -6450,10 +6543,10 @@
         <v>39</v>
       </c>
       <c r="R15" s="5">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="S15" s="5">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="T15" s="5">
         <v>0</v>
@@ -6462,7 +6555,7 @@
         <v>0</v>
       </c>
       <c r="V15" s="5">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="W15" s="6" t="s">
         <v>50</v>
@@ -6471,7 +6564,7 @@
         <v>49</v>
       </c>
       <c r="Y15" s="7" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="Z15" s="6" t="s">
         <v>39</v>
@@ -6498,7 +6591,7 @@
         <v>47</v>
       </c>
       <c r="AH15" s="6" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="1:34" x14ac:dyDescent="0.3">
@@ -6512,7 +6605,7 @@
         <v>211</v>
       </c>
       <c r="D16" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>113</v>
@@ -6521,16 +6614,16 @@
         <v>204</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>55</v>
+        <v>165</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>57</v>
+        <v>167</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>56</v>
+        <v>166</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>244</v>
+        <v>216</v>
       </c>
       <c r="K16" s="6" t="s">
         <v>36</v>
@@ -6554,10 +6647,10 @@
         <v>39</v>
       </c>
       <c r="R16" s="5">
-        <v>2000000</v>
+        <v>300000</v>
       </c>
       <c r="S16" s="5">
-        <v>2000000</v>
+        <v>300000</v>
       </c>
       <c r="T16" s="5">
         <v>0</v>
@@ -6566,7 +6659,7 @@
         <v>0</v>
       </c>
       <c r="V16" s="5">
-        <v>2000000</v>
+        <v>300000</v>
       </c>
       <c r="W16" s="6" t="s">
         <v>50</v>
@@ -6602,7 +6695,7 @@
         <v>47</v>
       </c>
       <c r="AH16" s="6" t="s">
-        <v>51</v>
+        <v>236</v>
       </c>
     </row>
     <row r="17" spans="1:34" x14ac:dyDescent="0.3">
@@ -6616,7 +6709,7 @@
         <v>211</v>
       </c>
       <c r="D17" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>113</v>
@@ -6625,16 +6718,16 @@
         <v>204</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>153</v>
+        <v>55</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>155</v>
+        <v>57</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>154</v>
+        <v>56</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>46</v>
+        <v>244</v>
       </c>
       <c r="K17" s="6" t="s">
         <v>36</v>
@@ -6658,10 +6751,10 @@
         <v>39</v>
       </c>
       <c r="R17" s="5">
-        <v>300000</v>
+        <v>2000000</v>
       </c>
       <c r="S17" s="5">
-        <v>300000</v>
+        <v>2000000</v>
       </c>
       <c r="T17" s="5">
         <v>0</v>
@@ -6670,7 +6763,7 @@
         <v>0</v>
       </c>
       <c r="V17" s="5">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="W17" s="6" t="s">
         <v>50</v>
@@ -6706,7 +6799,7 @@
         <v>47</v>
       </c>
       <c r="AH17" s="6" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
     </row>
     <row r="18" spans="1:34" x14ac:dyDescent="0.3">
@@ -6720,7 +6813,7 @@
         <v>211</v>
       </c>
       <c r="D18" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>113</v>
@@ -6729,13 +6822,13 @@
         <v>204</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>46</v>
@@ -6762,10 +6855,10 @@
         <v>39</v>
       </c>
       <c r="R18" s="5">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="S18" s="5">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="T18" s="5">
         <v>0</v>
@@ -6783,7 +6876,7 @@
         <v>49</v>
       </c>
       <c r="Y18" s="7" t="s">
-        <v>160</v>
+        <v>58</v>
       </c>
       <c r="Z18" s="6" t="s">
         <v>39</v>
@@ -6810,7 +6903,7 @@
         <v>47</v>
       </c>
       <c r="AH18" s="6" t="s">
-        <v>156</v>
+        <v>250</v>
       </c>
     </row>
     <row r="19" spans="1:34" x14ac:dyDescent="0.3">
@@ -6818,31 +6911,31 @@
         <v>33</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D19" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>54</v>
+        <v>113</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>204</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>55</v>
+        <v>157</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>57</v>
+        <v>159</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>56</v>
+        <v>158</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>244</v>
+        <v>46</v>
       </c>
       <c r="K19" s="6" t="s">
         <v>36</v>
@@ -6866,10 +6959,10 @@
         <v>39</v>
       </c>
       <c r="R19" s="5">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="S19" s="5">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="T19" s="5">
         <v>0</v>
@@ -6878,7 +6971,7 @@
         <v>0</v>
       </c>
       <c r="V19" s="5">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="W19" s="6" t="s">
         <v>50</v>
@@ -6887,7 +6980,7 @@
         <v>49</v>
       </c>
       <c r="Y19" s="7" t="s">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="Z19" s="6" t="s">
         <v>39</v>
@@ -6914,7 +7007,7 @@
         <v>47</v>
       </c>
       <c r="AH19" s="6" t="s">
-        <v>75</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:34" x14ac:dyDescent="0.3">
@@ -6928,7 +7021,7 @@
         <v>212</v>
       </c>
       <c r="D20" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>54</v>
@@ -6937,13 +7030,13 @@
         <v>204</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>161</v>
+        <v>55</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>163</v>
+        <v>57</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>162</v>
+        <v>56</v>
       </c>
       <c r="J20" s="6" t="s">
         <v>244</v>
@@ -6970,10 +7063,10 @@
         <v>39</v>
       </c>
       <c r="R20" s="5">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="S20" s="5">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="T20" s="5">
         <v>0</v>
@@ -6982,7 +7075,7 @@
         <v>0</v>
       </c>
       <c r="V20" s="5">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="W20" s="6" t="s">
         <v>50</v>
@@ -7018,7 +7111,7 @@
         <v>47</v>
       </c>
       <c r="AH20" s="6" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
     </row>
     <row r="21" spans="1:34" x14ac:dyDescent="0.3">
@@ -7032,7 +7125,7 @@
         <v>212</v>
       </c>
       <c r="D21" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>54</v>
@@ -7041,16 +7134,16 @@
         <v>204</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>76</v>
+        <v>161</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>78</v>
+        <v>163</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>77</v>
+        <v>162</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>58</v>
+        <v>244</v>
       </c>
       <c r="K21" s="6" t="s">
         <v>36</v>
@@ -7074,10 +7167,10 @@
         <v>39</v>
       </c>
       <c r="R21" s="5">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
       <c r="S21" s="5">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
       <c r="T21" s="5">
         <v>0</v>
@@ -7086,7 +7179,7 @@
         <v>0</v>
       </c>
       <c r="V21" s="5">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
       <c r="W21" s="6" t="s">
         <v>50</v>
@@ -7095,7 +7188,7 @@
         <v>49</v>
       </c>
       <c r="Y21" s="7" t="s">
-        <v>132</v>
+        <v>74</v>
       </c>
       <c r="Z21" s="6" t="s">
         <v>39</v>
@@ -7122,7 +7215,7 @@
         <v>47</v>
       </c>
       <c r="AH21" s="6" t="s">
-        <v>213</v>
+        <v>238</v>
       </c>
     </row>
     <row r="22" spans="1:34" x14ac:dyDescent="0.3">
@@ -7136,7 +7229,7 @@
         <v>212</v>
       </c>
       <c r="D22" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>54</v>
@@ -7145,16 +7238,16 @@
         <v>204</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>139</v>
+        <v>76</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>140</v>
+        <v>77</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="K22" s="6" t="s">
         <v>36</v>
@@ -7178,10 +7271,10 @@
         <v>39</v>
       </c>
       <c r="R22" s="5">
-        <v>200000</v>
+        <v>500000</v>
       </c>
       <c r="S22" s="5">
-        <v>200000</v>
+        <v>500000</v>
       </c>
       <c r="T22" s="5">
         <v>0</v>
@@ -7190,7 +7283,7 @@
         <v>0</v>
       </c>
       <c r="V22" s="5">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="W22" s="6" t="s">
         <v>50</v>
@@ -7199,7 +7292,7 @@
         <v>49</v>
       </c>
       <c r="Y22" s="7" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="Z22" s="6" t="s">
         <v>39</v>
@@ -7226,7 +7319,7 @@
         <v>47</v>
       </c>
       <c r="AH22" s="6" t="s">
-        <v>67</v>
+        <v>252</v>
       </c>
     </row>
     <row r="23" spans="1:34" x14ac:dyDescent="0.3">
@@ -7240,7 +7333,7 @@
         <v>212</v>
       </c>
       <c r="D23" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>54</v>
@@ -7249,13 +7342,13 @@
         <v>204</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>174</v>
+        <v>139</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>176</v>
+        <v>141</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>61</v>
@@ -7282,10 +7375,10 @@
         <v>39</v>
       </c>
       <c r="R23" s="5">
-        <v>500000</v>
+        <v>200000</v>
       </c>
       <c r="S23" s="5">
-        <v>500000</v>
+        <v>200000</v>
       </c>
       <c r="T23" s="5">
         <v>0</v>
@@ -7303,7 +7396,7 @@
         <v>49</v>
       </c>
       <c r="Y23" s="7" t="s">
-        <v>177</v>
+        <v>142</v>
       </c>
       <c r="Z23" s="6" t="s">
         <v>39</v>
@@ -7330,7 +7423,7 @@
         <v>47</v>
       </c>
       <c r="AH23" s="6" t="s">
-        <v>67</v>
+        <v>248</v>
       </c>
     </row>
     <row r="24" spans="1:34" x14ac:dyDescent="0.3">
@@ -7344,7 +7437,7 @@
         <v>212</v>
       </c>
       <c r="D24" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>54</v>
@@ -7353,13 +7446,13 @@
         <v>204</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>62</v>
+        <v>174</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>64</v>
+        <v>176</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>63</v>
+        <v>175</v>
       </c>
       <c r="J24" s="6" t="s">
         <v>61</v>
@@ -7386,10 +7479,10 @@
         <v>39</v>
       </c>
       <c r="R24" s="5">
-        <v>200000</v>
+        <v>500000</v>
       </c>
       <c r="S24" s="5">
-        <v>200000</v>
+        <v>500000</v>
       </c>
       <c r="T24" s="5">
         <v>0</v>
@@ -7407,7 +7500,7 @@
         <v>49</v>
       </c>
       <c r="Y24" s="7" t="s">
-        <v>66</v>
+        <v>177</v>
       </c>
       <c r="Z24" s="6" t="s">
         <v>39</v>
@@ -7442,31 +7535,31 @@
         <v>33</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>129</v>
+        <v>69</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D25" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>204</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>178</v>
+        <v>62</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>180</v>
+        <v>64</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>179</v>
+        <v>63</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="K25" s="6" t="s">
         <v>36</v>
@@ -7490,10 +7583,10 @@
         <v>39</v>
       </c>
       <c r="R25" s="5">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="S25" s="5">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="T25" s="5">
         <v>0</v>
@@ -7511,7 +7604,7 @@
         <v>49</v>
       </c>
       <c r="Y25" s="7" t="s">
-        <v>132</v>
+        <v>66</v>
       </c>
       <c r="Z25" s="6" t="s">
         <v>39</v>
@@ -7538,7 +7631,7 @@
         <v>47</v>
       </c>
       <c r="AH25" s="6" t="s">
-        <v>127</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:34" x14ac:dyDescent="0.3">
@@ -7546,34 +7639,34 @@
         <v>33</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>129</v>
+        <v>263</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>214</v>
+        <v>264</v>
       </c>
       <c r="D26" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>204</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>71</v>
+        <v>265</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>73</v>
+        <v>266</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>72</v>
+        <v>267</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>244</v>
+        <v>94</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>36</v>
+        <v>268</v>
       </c>
       <c r="L26" s="6" t="s">
         <v>48</v>
@@ -7585,19 +7678,19 @@
         <v>39</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>47</v>
+        <v>259</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>205</v>
+        <v>260</v>
       </c>
       <c r="Q26" s="6" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="R26" s="5">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="S26" s="5">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="T26" s="5">
         <v>0</v>
@@ -7606,7 +7699,7 @@
         <v>0</v>
       </c>
       <c r="V26" s="5">
-        <v>200000</v>
+        <v>1476960</v>
       </c>
       <c r="W26" s="6" t="s">
         <v>50</v>
@@ -7615,7 +7708,7 @@
         <v>49</v>
       </c>
       <c r="Y26" s="7" t="s">
-        <v>132</v>
+        <v>74</v>
       </c>
       <c r="Z26" s="6" t="s">
         <v>39</v>
@@ -7624,13 +7717,13 @@
         <v>206</v>
       </c>
       <c r="AB26" s="6" t="s">
-        <v>39</v>
+        <v>269</v>
       </c>
       <c r="AC26" s="6" t="s">
-        <v>207</v>
+        <v>262</v>
       </c>
       <c r="AD26" s="6" t="s">
-        <v>207</v>
+        <v>262</v>
       </c>
       <c r="AE26" s="6" t="s">
         <v>39</v>
@@ -7639,10 +7732,10 @@
         <v>39</v>
       </c>
       <c r="AG26" s="6" t="s">
-        <v>47</v>
+        <v>259</v>
       </c>
       <c r="AH26" s="6" t="s">
-        <v>240</v>
+        <v>270</v>
       </c>
     </row>
     <row r="27" spans="1:34" x14ac:dyDescent="0.3">
@@ -7656,7 +7749,7 @@
         <v>214</v>
       </c>
       <c r="D27" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>94</v>
@@ -7665,16 +7758,16 @@
         <v>204</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>55</v>
+        <v>178</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>57</v>
+        <v>180</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>56</v>
+        <v>179</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>244</v>
+        <v>94</v>
       </c>
       <c r="K27" s="6" t="s">
         <v>36</v>
@@ -7698,10 +7791,10 @@
         <v>39</v>
       </c>
       <c r="R27" s="5">
-        <v>2000000</v>
+        <v>300000</v>
       </c>
       <c r="S27" s="5">
-        <v>2000000</v>
+        <v>300000</v>
       </c>
       <c r="T27" s="5">
         <v>0</v>
@@ -7710,7 +7803,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="5">
-        <v>1664000</v>
+        <v>0</v>
       </c>
       <c r="W27" s="6" t="s">
         <v>50</v>
@@ -7719,7 +7812,7 @@
         <v>49</v>
       </c>
       <c r="Y27" s="7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="Z27" s="6" t="s">
         <v>39</v>
@@ -7746,7 +7839,7 @@
         <v>47</v>
       </c>
       <c r="AH27" s="6" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
     </row>
     <row r="28" spans="1:34" x14ac:dyDescent="0.3">
@@ -7760,7 +7853,7 @@
         <v>214</v>
       </c>
       <c r="D28" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>94</v>
@@ -7769,16 +7862,16 @@
         <v>204</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>150</v>
+        <v>71</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>152</v>
+        <v>73</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>151</v>
+        <v>72</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>94</v>
+        <v>244</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>36</v>
@@ -7802,10 +7895,10 @@
         <v>39</v>
       </c>
       <c r="R28" s="5">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="S28" s="5">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="T28" s="5">
         <v>0</v>
@@ -7814,7 +7907,7 @@
         <v>0</v>
       </c>
       <c r="V28" s="5">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="W28" s="6" t="s">
         <v>50</v>
@@ -7823,7 +7916,7 @@
         <v>49</v>
       </c>
       <c r="Y28" s="7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="Z28" s="6" t="s">
         <v>39</v>
@@ -7850,7 +7943,7 @@
         <v>47</v>
       </c>
       <c r="AH28" s="6" t="s">
-        <v>127</v>
+        <v>240</v>
       </c>
     </row>
     <row r="29" spans="1:34" x14ac:dyDescent="0.3">
@@ -7864,7 +7957,7 @@
         <v>214</v>
       </c>
       <c r="D29" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>94</v>
@@ -7873,16 +7966,16 @@
         <v>204</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>135</v>
+        <v>55</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>137</v>
+        <v>57</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>136</v>
+        <v>56</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>94</v>
+        <v>244</v>
       </c>
       <c r="K29" s="6" t="s">
         <v>36</v>
@@ -7918,7 +8011,7 @@
         <v>0</v>
       </c>
       <c r="V29" s="5">
-        <v>0</v>
+        <v>1664000</v>
       </c>
       <c r="W29" s="6" t="s">
         <v>50</v>
@@ -7927,7 +8020,7 @@
         <v>49</v>
       </c>
       <c r="Y29" s="7" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="Z29" s="6" t="s">
         <v>39</v>
@@ -7954,7 +8047,7 @@
         <v>47</v>
       </c>
       <c r="AH29" s="6" t="s">
-        <v>127</v>
+        <v>252</v>
       </c>
     </row>
     <row r="30" spans="1:34" x14ac:dyDescent="0.3">
@@ -7968,7 +8061,7 @@
         <v>214</v>
       </c>
       <c r="D30" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>94</v>
@@ -7977,13 +8070,13 @@
         <v>204</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="J30" s="6" t="s">
         <v>94</v>
@@ -8010,10 +8103,10 @@
         <v>39</v>
       </c>
       <c r="R30" s="5">
-        <v>8000000</v>
+        <v>300000</v>
       </c>
       <c r="S30" s="5">
-        <v>8000000</v>
+        <v>300000</v>
       </c>
       <c r="T30" s="5">
         <v>0</v>
@@ -8031,7 +8124,7 @@
         <v>49</v>
       </c>
       <c r="Y30" s="7" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="Z30" s="6" t="s">
         <v>39</v>
@@ -8040,7 +8133,7 @@
         <v>206</v>
       </c>
       <c r="AB30" s="6" t="s">
-        <v>126</v>
+        <v>39</v>
       </c>
       <c r="AC30" s="6" t="s">
         <v>207</v>
@@ -8058,7 +8151,7 @@
         <v>47</v>
       </c>
       <c r="AH30" s="6" t="s">
-        <v>148</v>
+        <v>249</v>
       </c>
     </row>
     <row r="31" spans="1:34" x14ac:dyDescent="0.3">
@@ -8072,7 +8165,7 @@
         <v>214</v>
       </c>
       <c r="D31" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>94</v>
@@ -8081,13 +8174,13 @@
         <v>204</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="J31" s="6" t="s">
         <v>94</v>
@@ -8114,10 +8207,10 @@
         <v>39</v>
       </c>
       <c r="R31" s="5">
-        <v>300000</v>
+        <v>2000000</v>
       </c>
       <c r="S31" s="5">
-        <v>300000</v>
+        <v>2000000</v>
       </c>
       <c r="T31" s="5">
         <v>0</v>
@@ -8144,7 +8237,7 @@
         <v>206</v>
       </c>
       <c r="AB31" s="6" t="s">
-        <v>147</v>
+        <v>39</v>
       </c>
       <c r="AC31" s="6" t="s">
         <v>207</v>
@@ -8162,7 +8255,7 @@
         <v>47</v>
       </c>
       <c r="AH31" s="6" t="s">
-        <v>148</v>
+        <v>127</v>
       </c>
     </row>
     <row r="32" spans="1:34" x14ac:dyDescent="0.3">
@@ -8170,31 +8263,31 @@
         <v>33</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>173</v>
+        <v>129</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D32" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>204</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>168</v>
+        <v>122</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>170</v>
+        <v>124</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>169</v>
+        <v>123</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>36</v>
@@ -8215,13 +8308,13 @@
         <v>205</v>
       </c>
       <c r="Q32" s="6" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="R32" s="5">
-        <v>1000000</v>
+        <v>8000000</v>
       </c>
       <c r="S32" s="5">
-        <v>1000000</v>
+        <v>8000000</v>
       </c>
       <c r="T32" s="5">
         <v>0</v>
@@ -8239,7 +8332,7 @@
         <v>49</v>
       </c>
       <c r="Y32" s="7" t="s">
-        <v>216</v>
+        <v>125</v>
       </c>
       <c r="Z32" s="6" t="s">
         <v>39</v>
@@ -8248,7 +8341,7 @@
         <v>206</v>
       </c>
       <c r="AB32" s="6" t="s">
-        <v>39</v>
+        <v>126</v>
       </c>
       <c r="AC32" s="6" t="s">
         <v>207</v>
@@ -8266,7 +8359,7 @@
         <v>47</v>
       </c>
       <c r="AH32" s="6" t="s">
-        <v>171</v>
+        <v>148</v>
       </c>
     </row>
     <row r="33" spans="1:34" x14ac:dyDescent="0.3">
@@ -8274,31 +8367,31 @@
         <v>33</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>217</v>
+        <v>129</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D33" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="F33" s="6" t="s">
         <v>204</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>219</v>
+        <v>144</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>220</v>
+        <v>146</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>221</v>
+        <v>145</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>244</v>
+        <v>94</v>
       </c>
       <c r="K33" s="6" t="s">
         <v>36</v>
@@ -8322,10 +8415,10 @@
         <v>39</v>
       </c>
       <c r="R33" s="5">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="S33" s="5">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="T33" s="5">
         <v>0</v>
@@ -8343,7 +8436,7 @@
         <v>49</v>
       </c>
       <c r="Y33" s="7" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="Z33" s="6" t="s">
         <v>39</v>
@@ -8352,7 +8445,7 @@
         <v>206</v>
       </c>
       <c r="AB33" s="6" t="s">
-        <v>39</v>
+        <v>147</v>
       </c>
       <c r="AC33" s="6" t="s">
         <v>207</v>
@@ -8370,7 +8463,7 @@
         <v>47</v>
       </c>
       <c r="AH33" s="6" t="s">
-        <v>245</v>
+        <v>148</v>
       </c>
     </row>
     <row r="34" spans="1:34" x14ac:dyDescent="0.3">
@@ -8378,31 +8471,31 @@
         <v>33</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>217</v>
+        <v>173</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D34" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>204</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>55</v>
+        <v>168</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>57</v>
+        <v>170</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>56</v>
+        <v>169</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>244</v>
+        <v>74</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>36</v>
@@ -8423,13 +8516,13 @@
         <v>205</v>
       </c>
       <c r="Q34" s="6" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="R34" s="5">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
       <c r="S34" s="5">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
       <c r="T34" s="5">
         <v>0</v>
@@ -8438,7 +8531,7 @@
         <v>0</v>
       </c>
       <c r="V34" s="5">
-        <v>822000</v>
+        <v>0</v>
       </c>
       <c r="W34" s="6" t="s">
         <v>50</v>
@@ -8447,7 +8540,7 @@
         <v>49</v>
       </c>
       <c r="Y34" s="7" t="s">
-        <v>134</v>
+        <v>216</v>
       </c>
       <c r="Z34" s="6" t="s">
         <v>39</v>
@@ -8474,7 +8567,7 @@
         <v>47</v>
       </c>
       <c r="AH34" s="6" t="s">
-        <v>247</v>
+        <v>171</v>
       </c>
     </row>
     <row r="35" spans="1:34" x14ac:dyDescent="0.3">
@@ -8488,7 +8581,7 @@
         <v>218</v>
       </c>
       <c r="D35" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>58</v>
@@ -8497,13 +8590,13 @@
         <v>204</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>90</v>
+        <v>219</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>92</v>
+        <v>220</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>91</v>
+        <v>221</v>
       </c>
       <c r="J35" s="6" t="s">
         <v>244</v>
@@ -8592,7 +8685,7 @@
         <v>218</v>
       </c>
       <c r="D36" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>58</v>
@@ -8601,13 +8694,13 @@
         <v>204</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>222</v>
+        <v>55</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>223</v>
+        <v>57</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>224</v>
+        <v>56</v>
       </c>
       <c r="J36" s="6" t="s">
         <v>244</v>
@@ -8634,10 +8727,10 @@
         <v>39</v>
       </c>
       <c r="R36" s="5">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="S36" s="5">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="T36" s="5">
         <v>0</v>
@@ -8646,7 +8739,7 @@
         <v>0</v>
       </c>
       <c r="V36" s="5">
-        <v>0</v>
+        <v>812000</v>
       </c>
       <c r="W36" s="6" t="s">
         <v>50</v>
@@ -8655,7 +8748,7 @@
         <v>49</v>
       </c>
       <c r="Y36" s="7" t="s">
-        <v>177</v>
+        <v>134</v>
       </c>
       <c r="Z36" s="6" t="s">
         <v>39</v>
@@ -8682,7 +8775,7 @@
         <v>47</v>
       </c>
       <c r="AH36" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="37" spans="1:34" x14ac:dyDescent="0.3">
@@ -8696,7 +8789,7 @@
         <v>218</v>
       </c>
       <c r="D37" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>58</v>
@@ -8705,13 +8798,13 @@
         <v>204</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>225</v>
+        <v>90</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>226</v>
+        <v>92</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>227</v>
+        <v>91</v>
       </c>
       <c r="J37" s="6" t="s">
         <v>244</v>
@@ -8738,10 +8831,10 @@
         <v>39</v>
       </c>
       <c r="R37" s="5">
-        <v>3000000</v>
+        <v>200000</v>
       </c>
       <c r="S37" s="5">
-        <v>3000000</v>
+        <v>200000</v>
       </c>
       <c r="T37" s="5">
         <v>0</v>
@@ -8759,7 +8852,7 @@
         <v>49</v>
       </c>
       <c r="Y37" s="7" t="s">
-        <v>177</v>
+        <v>134</v>
       </c>
       <c r="Z37" s="6" t="s">
         <v>39</v>
@@ -8768,7 +8861,7 @@
         <v>206</v>
       </c>
       <c r="AB37" s="6" t="s">
-        <v>228</v>
+        <v>39</v>
       </c>
       <c r="AC37" s="6" t="s">
         <v>207</v>
@@ -8800,7 +8893,7 @@
         <v>218</v>
       </c>
       <c r="D38" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E38" s="7" t="s">
         <v>58</v>
@@ -8809,13 +8902,13 @@
         <v>204</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="J38" s="6" t="s">
         <v>244</v>
@@ -8842,10 +8935,10 @@
         <v>39</v>
       </c>
       <c r="R38" s="5">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="S38" s="5">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="T38" s="5">
         <v>0</v>
@@ -8863,7 +8956,7 @@
         <v>49</v>
       </c>
       <c r="Y38" s="7" t="s">
-        <v>232</v>
+        <v>177</v>
       </c>
       <c r="Z38" s="6" t="s">
         <v>39</v>
@@ -8890,6 +8983,214 @@
         <v>47</v>
       </c>
       <c r="AH38" s="6" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="39" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A39" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="D39" s="5">
+        <v>5</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="J39" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="K39" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="L39" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M39" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="N39" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="O39" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="P39" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q39" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R39" s="5">
+        <v>3000000</v>
+      </c>
+      <c r="S39" s="5">
+        <v>3000000</v>
+      </c>
+      <c r="T39" s="5">
+        <v>0</v>
+      </c>
+      <c r="U39" s="5">
+        <v>0</v>
+      </c>
+      <c r="V39" s="5">
+        <v>0</v>
+      </c>
+      <c r="W39" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="X39" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y39" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="Z39" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA39" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="AB39" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="AC39" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AD39" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AE39" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF39" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG39" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH39" s="6" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="40" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A40" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="D40" s="5">
+        <v>6</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="J40" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="K40" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="L40" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M40" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="N40" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="O40" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="P40" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q40" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R40" s="5">
+        <v>300000</v>
+      </c>
+      <c r="S40" s="5">
+        <v>300000</v>
+      </c>
+      <c r="T40" s="5">
+        <v>0</v>
+      </c>
+      <c r="U40" s="5">
+        <v>0</v>
+      </c>
+      <c r="V40" s="5">
+        <v>0</v>
+      </c>
+      <c r="W40" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="X40" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y40" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="Z40" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA40" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="AB40" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC40" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AD40" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="AE40" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF40" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG40" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH40" s="6" t="s">
         <v>245</v>
       </c>
     </row>

--- a/리드지 발주현황.xlsx
+++ b/리드지 발주현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\유현아\Documents\GitHub\INTEROJO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED8E157-C53C-4A15-AD6B-FE434776AB27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81DCE2FF-B84C-4EBD-900C-6C84DC958AF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{500E376A-1243-49DE-9EFA-B2AD708B3011}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{500E376A-1243-49DE-9EFA-B2AD708B3011}"/>
   </bookViews>
   <sheets>
     <sheet name="구매발주현황" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2187" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2355" uniqueCount="261">
   <si>
     <t>G/W</t>
   </si>
@@ -513,9 +513,6 @@
     <t>알루미늄리드지 (태국 MG Medical Group_SISSE ONE DAY_PoPo Milk Tea 리드지)</t>
   </si>
   <si>
-    <t>2026-05-18 오후 5:28:54</t>
-  </si>
-  <si>
     <t>BS0275</t>
   </si>
   <si>
@@ -771,27 +768,15 @@
     <t>2026-06-08 오후 5:13:55</t>
   </si>
   <si>
-    <t>2026-06-08 오후 2:50:28</t>
-  </si>
-  <si>
     <t>2026-06-08 오후 2:52:43</t>
   </si>
   <si>
-    <t>기안</t>
-  </si>
-  <si>
     <t>PR-2606080002</t>
   </si>
   <si>
     <t>20260608P227-0115</t>
   </si>
   <si>
-    <t>의뢰</t>
-  </si>
-  <si>
-    <t>2026-06-08 오후 4:04:01</t>
-  </si>
-  <si>
     <t>BS0336</t>
   </si>
   <si>
@@ -801,9 +786,6 @@
     <t>BS0336-001</t>
   </si>
   <si>
-    <t>2026-04-15</t>
-  </si>
-  <si>
     <t>2026-06-17</t>
   </si>
   <si>
@@ -816,9 +798,6 @@
     <t>BS0243-001</t>
   </si>
   <si>
-    <t>2026-04-27</t>
-  </si>
-  <si>
     <t>BS0352</t>
   </si>
   <si>
@@ -828,10 +807,25 @@
     <t>BS0352-001</t>
   </si>
   <si>
-    <t>신규</t>
-  </si>
-  <si>
     <t>신시아 축고정(수주 미접수)</t>
+  </si>
+  <si>
+    <t>2026-06-10 오후 12:01:33</t>
+  </si>
+  <si>
+    <t>2026-06-09</t>
+  </si>
+  <si>
+    <t>2026-06-09 오후 2:07:14</t>
+  </si>
+  <si>
+    <t>PO-2606090002</t>
+  </si>
+  <si>
+    <t>2026-06-09 오후 5:31:35</t>
+  </si>
+  <si>
+    <t>2026-06-10 오후 5:32:57</t>
   </si>
 </sst>
 </file>
@@ -1377,13 +1371,13 @@
         <v>34</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>36</v>
@@ -1398,34 +1392,34 @@
         <v>39</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>40</v>
+        <v>135</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>41</v>
+        <v>136</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>42</v>
+        <v>137</v>
       </c>
       <c r="M2" s="3">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="N2" s="3">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="O2" s="3">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="P2" s="3">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="3">
         <v>0</v>
       </c>
       <c r="R2" s="3">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="T2" s="4" t="s">
         <v>44</v>
@@ -1437,10 +1431,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W2" s="3">
-        <v>1960000</v>
+        <v>19600000</v>
       </c>
       <c r="X2" s="5" t="s">
-        <v>46</v>
+        <v>125</v>
       </c>
       <c r="Y2" s="4" t="s">
         <v>47</v>
@@ -1458,16 +1452,16 @@
         <v>50</v>
       </c>
       <c r="AD2" s="4" t="s">
-        <v>51</v>
+        <v>127</v>
       </c>
       <c r="AE2" s="4" t="s">
-        <v>52</v>
+        <v>128</v>
       </c>
       <c r="AF2" s="4" t="s">
-        <v>53</v>
+        <v>129</v>
       </c>
       <c r="AG2" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.3">
@@ -1478,13 +1472,13 @@
         <v>34</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>237</v>
+        <v>35</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>237</v>
+        <v>35</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>36</v>
@@ -1499,34 +1493,34 @@
         <v>39</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>225</v>
+        <v>108</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>227</v>
+        <v>109</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>226</v>
+        <v>110</v>
       </c>
       <c r="M3" s="3">
-        <v>3000000</v>
+        <v>200000</v>
       </c>
       <c r="N3" s="3">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="O3" s="3">
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="P3" s="3">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="Q3" s="3">
         <v>0</v>
       </c>
       <c r="R3" s="3">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="S3" s="4" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T3" s="4" t="s">
         <v>44</v>
@@ -1538,10 +1532,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W3" s="3">
-        <v>29400000</v>
+        <v>1960000</v>
       </c>
       <c r="X3" s="5" t="s">
-        <v>177</v>
+        <v>112</v>
       </c>
       <c r="Y3" s="4" t="s">
         <v>47</v>
@@ -1553,22 +1547,22 @@
         <v>49</v>
       </c>
       <c r="AB3" s="4" t="s">
-        <v>228</v>
+        <v>130</v>
       </c>
       <c r="AC3" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD3" s="4" t="s">
-        <v>238</v>
+        <v>111</v>
       </c>
       <c r="AE3" s="4" t="s">
-        <v>239</v>
+        <v>52</v>
       </c>
       <c r="AF3" s="4" t="s">
-        <v>217</v>
+        <v>131</v>
       </c>
       <c r="AG3" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.3">
@@ -1600,31 +1594,31 @@
         <v>39</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="M4" s="3">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="N4" s="3">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="O4" s="3">
         <v>0</v>
       </c>
       <c r="P4" s="3">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="Q4" s="3">
         <v>0</v>
       </c>
       <c r="R4" s="3">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="S4" s="4" t="s">
         <v>43</v>
@@ -1639,10 +1633,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W4" s="3">
-        <v>19600000</v>
+        <v>1960000</v>
       </c>
       <c r="X4" s="5" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="Y4" s="4" t="s">
         <v>47</v>
@@ -1660,7 +1654,7 @@
         <v>50</v>
       </c>
       <c r="AD4" s="4" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="AE4" s="4" t="s">
         <v>59</v>
@@ -1669,7 +1663,7 @@
         <v>60</v>
       </c>
       <c r="AG4" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.3">
@@ -1701,34 +1695,34 @@
         <v>39</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>62</v>
+        <v>139</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>63</v>
+        <v>140</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>64</v>
+        <v>141</v>
       </c>
       <c r="M5" s="3">
         <v>200000</v>
       </c>
       <c r="N5" s="3">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="O5" s="3">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="P5" s="3">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="Q5" s="3">
         <v>0</v>
       </c>
       <c r="R5" s="3">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T5" s="4" t="s">
         <v>44</v>
@@ -1737,13 +1731,13 @@
         <v>45</v>
       </c>
       <c r="V5" s="3">
-        <v>9.8000000000000007</v>
+        <v>34</v>
       </c>
       <c r="W5" s="3">
-        <v>1960000</v>
+        <v>6800000</v>
       </c>
       <c r="X5" s="5" t="s">
-        <v>66</v>
+        <v>142</v>
       </c>
       <c r="Y5" s="4" t="s">
         <v>47</v>
@@ -1761,7 +1755,7 @@
         <v>50</v>
       </c>
       <c r="AD5" s="4" t="s">
-        <v>67</v>
+        <v>255</v>
       </c>
       <c r="AE5" s="4" t="s">
         <v>68</v>
@@ -1770,7 +1764,7 @@
         <v>69</v>
       </c>
       <c r="AG5" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.3">
@@ -1802,34 +1796,34 @@
         <v>39</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>124</v>
+        <v>73</v>
       </c>
       <c r="M6" s="3">
-        <v>8000000</v>
+        <v>200000</v>
       </c>
       <c r="N6" s="3">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="O6" s="3">
-        <v>8000000</v>
+        <v>0</v>
       </c>
       <c r="P6" s="3">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="Q6" s="3">
         <v>0</v>
       </c>
       <c r="R6" s="3">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T6" s="4" t="s">
         <v>44</v>
@@ -1841,10 +1835,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W6" s="3">
-        <v>78400000</v>
+        <v>1960000</v>
       </c>
       <c r="X6" s="5" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="Y6" s="4" t="s">
         <v>47</v>
@@ -1856,13 +1850,13 @@
         <v>49</v>
       </c>
       <c r="AB6" s="4" t="s">
-        <v>126</v>
+        <v>39</v>
       </c>
       <c r="AC6" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD6" s="4" t="s">
-        <v>127</v>
+        <v>235</v>
       </c>
       <c r="AE6" s="4" t="s">
         <v>128</v>
@@ -1871,7 +1865,7 @@
         <v>129</v>
       </c>
       <c r="AG6" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.3">
@@ -1882,13 +1876,13 @@
         <v>34</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>58</v>
+        <v>256</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>36</v>
@@ -1903,34 +1897,34 @@
         <v>39</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>55</v>
+        <v>167</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>56</v>
+        <v>168</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>57</v>
+        <v>169</v>
       </c>
       <c r="M7" s="3">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="N7" s="3">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="O7" s="3">
-        <v>0</v>
+        <v>1500000</v>
       </c>
       <c r="P7" s="3">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="3">
         <v>0</v>
       </c>
       <c r="R7" s="3">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="T7" s="4" t="s">
         <v>44</v>
@@ -1939,13 +1933,13 @@
         <v>45</v>
       </c>
       <c r="V7" s="3">
-        <v>9.8000000000000007</v>
+        <v>7.7</v>
       </c>
       <c r="W7" s="3">
-        <v>19600000</v>
+        <v>11550000</v>
       </c>
       <c r="X7" s="5" t="s">
-        <v>134</v>
+        <v>66</v>
       </c>
       <c r="Y7" s="4" t="s">
         <v>47</v>
@@ -1963,16 +1957,16 @@
         <v>50</v>
       </c>
       <c r="AD7" s="4" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="AE7" s="4" t="s">
-        <v>239</v>
+        <v>258</v>
       </c>
       <c r="AF7" s="4" t="s">
-        <v>217</v>
+        <v>242</v>
       </c>
       <c r="AG7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.3">
@@ -1983,13 +1977,13 @@
         <v>34</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>35</v>
+        <v>256</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>35</v>
+        <v>256</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>35</v>
+        <v>256</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>36</v>
@@ -2004,34 +1998,34 @@
         <v>39</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>118</v>
+        <v>248</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>119</v>
+        <v>250</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>120</v>
+        <v>249</v>
       </c>
       <c r="M8" s="3">
         <v>200000</v>
       </c>
       <c r="N8" s="3">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="O8" s="3">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="P8" s="3">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
       </c>
       <c r="R8" s="3">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="T8" s="4" t="s">
         <v>44</v>
@@ -2046,7 +2040,7 @@
         <v>1960000</v>
       </c>
       <c r="X8" s="5" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="Y8" s="4" t="s">
         <v>47</v>
@@ -2058,22 +2052,22 @@
         <v>49</v>
       </c>
       <c r="AB8" s="4" t="s">
-        <v>130</v>
+        <v>39</v>
       </c>
       <c r="AC8" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD8" s="4" t="s">
-        <v>111</v>
+        <v>257</v>
       </c>
       <c r="AE8" s="4" t="s">
-        <v>52</v>
+        <v>258</v>
       </c>
       <c r="AF8" s="4" t="s">
-        <v>131</v>
+        <v>242</v>
       </c>
       <c r="AG8" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.3">
@@ -2084,13 +2078,13 @@
         <v>34</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>36</v>
@@ -2105,34 +2099,34 @@
         <v>39</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>76</v>
+        <v>135</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="M9" s="3">
-        <v>500000</v>
+        <v>2000000</v>
       </c>
       <c r="N9" s="3">
-        <v>500000</v>
+        <v>1248000</v>
       </c>
       <c r="O9" s="3">
-        <v>0</v>
+        <v>752000</v>
       </c>
       <c r="P9" s="3">
-        <v>500000</v>
+        <v>1248000</v>
       </c>
       <c r="Q9" s="3">
         <v>0</v>
       </c>
       <c r="R9" s="3">
-        <v>500000</v>
+        <v>1248000</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="T9" s="4" t="s">
         <v>44</v>
@@ -2144,10 +2138,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W9" s="3">
-        <v>4900000</v>
+        <v>19600000</v>
       </c>
       <c r="X9" s="5" t="s">
-        <v>132</v>
+        <v>93</v>
       </c>
       <c r="Y9" s="4" t="s">
         <v>47</v>
@@ -2165,16 +2159,16 @@
         <v>50</v>
       </c>
       <c r="AD9" s="4" t="s">
-        <v>213</v>
+        <v>107</v>
       </c>
       <c r="AE9" s="4" t="s">
-        <v>68</v>
+        <v>138</v>
       </c>
       <c r="AF9" s="4" t="s">
-        <v>69</v>
+        <v>143</v>
       </c>
       <c r="AG9" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.3">
@@ -2185,13 +2179,13 @@
         <v>34</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>36</v>
@@ -2206,31 +2200,31 @@
         <v>39</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="M10" s="3">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="N10" s="3">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="O10" s="3">
         <v>0</v>
       </c>
       <c r="P10" s="3">
-        <v>1664000</v>
+        <v>200000</v>
       </c>
       <c r="Q10" s="3">
-        <v>336000</v>
+        <v>0</v>
       </c>
       <c r="R10" s="3">
-        <v>1664000</v>
+        <v>200000</v>
       </c>
       <c r="S10" s="4" t="s">
         <v>43</v>
@@ -2245,10 +2239,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W10" s="3">
-        <v>19600000</v>
+        <v>1960000</v>
       </c>
       <c r="X10" s="5" t="s">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="Y10" s="4" t="s">
         <v>47</v>
@@ -2266,16 +2260,16 @@
         <v>50</v>
       </c>
       <c r="AD10" s="4" t="s">
-        <v>235</v>
+        <v>86</v>
       </c>
       <c r="AE10" s="4" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="AF10" s="4" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="AG10" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.3">
@@ -2286,13 +2280,13 @@
         <v>34</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>36</v>
@@ -2307,34 +2301,34 @@
         <v>39</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>135</v>
+        <v>55</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>136</v>
+        <v>56</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>137</v>
+        <v>57</v>
       </c>
       <c r="M11" s="3">
         <v>2000000</v>
       </c>
       <c r="N11" s="3">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="O11" s="3">
+        <v>0</v>
+      </c>
+      <c r="P11" s="3">
         <v>2000000</v>
       </c>
-      <c r="P11" s="3">
-        <v>0</v>
-      </c>
       <c r="Q11" s="3">
         <v>0</v>
       </c>
       <c r="R11" s="3">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T11" s="4" t="s">
         <v>44</v>
@@ -2349,7 +2343,7 @@
         <v>19600000</v>
       </c>
       <c r="X11" s="5" t="s">
-        <v>125</v>
+        <v>74</v>
       </c>
       <c r="Y11" s="4" t="s">
         <v>47</v>
@@ -2367,16 +2361,16 @@
         <v>50</v>
       </c>
       <c r="AD11" s="4" t="s">
-        <v>127</v>
+        <v>75</v>
       </c>
       <c r="AE11" s="4" t="s">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="AF11" s="4" t="s">
-        <v>129</v>
+        <v>69</v>
       </c>
       <c r="AG11" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.3">
@@ -2387,13 +2381,13 @@
         <v>34</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>36</v>
@@ -2408,31 +2402,31 @@
         <v>39</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>109</v>
+        <v>145</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>110</v>
+        <v>146</v>
       </c>
       <c r="M12" s="3">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="N12" s="3">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="O12" s="3">
         <v>0</v>
       </c>
       <c r="P12" s="3">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="Q12" s="3">
         <v>0</v>
       </c>
       <c r="R12" s="3">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="S12" s="4" t="s">
         <v>43</v>
@@ -2447,10 +2441,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W12" s="3">
-        <v>1960000</v>
+        <v>2940000</v>
       </c>
       <c r="X12" s="5" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="Y12" s="4" t="s">
         <v>47</v>
@@ -2462,22 +2456,22 @@
         <v>49</v>
       </c>
       <c r="AB12" s="4" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="AC12" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD12" s="4" t="s">
-        <v>111</v>
+        <v>259</v>
       </c>
       <c r="AE12" s="4" t="s">
-        <v>52</v>
+        <v>128</v>
       </c>
       <c r="AF12" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AG12" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.3">
@@ -2488,13 +2482,13 @@
         <v>34</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>54</v>
+        <v>256</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>46</v>
+        <v>256</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>46</v>
+        <v>256</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>36</v>
@@ -2509,34 +2503,34 @@
         <v>39</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="M13" s="3">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="N13" s="3">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="O13" s="3">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="P13" s="3">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="3">
         <v>0</v>
       </c>
       <c r="R13" s="3">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="S13" s="4" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="T13" s="4" t="s">
         <v>44</v>
@@ -2548,10 +2542,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W13" s="3">
-        <v>1960000</v>
+        <v>2940000</v>
       </c>
       <c r="X13" s="5" t="s">
-        <v>106</v>
+        <v>247</v>
       </c>
       <c r="Y13" s="4" t="s">
         <v>47</v>
@@ -2569,16 +2563,16 @@
         <v>50</v>
       </c>
       <c r="AD13" s="4" t="s">
-        <v>75</v>
+        <v>257</v>
       </c>
       <c r="AE13" s="4" t="s">
-        <v>59</v>
+        <v>258</v>
       </c>
       <c r="AF13" s="4" t="s">
-        <v>60</v>
+        <v>242</v>
       </c>
       <c r="AG13" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.3">
@@ -2589,13 +2583,13 @@
         <v>34</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>61</v>
+        <v>236</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>61</v>
+        <v>236</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>36</v>
@@ -2610,34 +2604,34 @@
         <v>39</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>139</v>
+        <v>218</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>140</v>
+        <v>220</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>141</v>
+        <v>219</v>
       </c>
       <c r="M14" s="3">
         <v>200000</v>
       </c>
       <c r="N14" s="3">
-        <v>57600</v>
+        <v>200000</v>
       </c>
       <c r="O14" s="3">
-        <v>142400</v>
+        <v>0</v>
       </c>
       <c r="P14" s="3">
-        <v>57600</v>
+        <v>200000</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
       <c r="R14" s="3">
-        <v>57600</v>
+        <v>200000</v>
       </c>
       <c r="S14" s="4" t="s">
-        <v>133</v>
+        <v>43</v>
       </c>
       <c r="T14" s="4" t="s">
         <v>44</v>
@@ -2646,13 +2640,13 @@
         <v>45</v>
       </c>
       <c r="V14" s="3">
-        <v>34</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="W14" s="3">
-        <v>6800000</v>
+        <v>1960000</v>
       </c>
       <c r="X14" s="5" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="Y14" s="4" t="s">
         <v>47</v>
@@ -2670,16 +2664,16 @@
         <v>50</v>
       </c>
       <c r="AD14" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AE14" s="4" t="s">
-        <v>68</v>
+        <v>238</v>
       </c>
       <c r="AF14" s="4" t="s">
-        <v>69</v>
+        <v>216</v>
       </c>
       <c r="AG14" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.3">
@@ -2690,13 +2684,13 @@
         <v>34</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>36</v>
@@ -2711,31 +2705,31 @@
         <v>39</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="M15" s="3">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="N15" s="3">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
       </c>
       <c r="P15" s="3">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
       <c r="R15" s="3">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="S15" s="4" t="s">
         <v>43</v>
@@ -2747,13 +2741,13 @@
         <v>45</v>
       </c>
       <c r="V15" s="3">
-        <v>9.8000000000000007</v>
+        <v>6.7</v>
       </c>
       <c r="W15" s="3">
-        <v>1960000</v>
+        <v>13400000</v>
       </c>
       <c r="X15" s="5" t="s">
-        <v>132</v>
+        <v>93</v>
       </c>
       <c r="Y15" s="4" t="s">
         <v>47</v>
@@ -2771,16 +2765,16 @@
         <v>50</v>
       </c>
       <c r="AD15" s="4" t="s">
-        <v>236</v>
+        <v>149</v>
       </c>
       <c r="AE15" s="4" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="AF15" s="4" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="AG15" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.3">
@@ -2791,13 +2785,13 @@
         <v>34</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>36</v>
@@ -2812,34 +2806,34 @@
         <v>39</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="M16" s="3">
-        <v>2000000</v>
+        <v>300000</v>
       </c>
       <c r="N16" s="3">
-        <v>1248000</v>
+        <v>300000</v>
       </c>
       <c r="O16" s="3">
-        <v>752000</v>
+        <v>0</v>
       </c>
       <c r="P16" s="3">
-        <v>1248000</v>
+        <v>300000</v>
       </c>
       <c r="Q16" s="3">
         <v>0</v>
       </c>
       <c r="R16" s="3">
-        <v>1248000</v>
+        <v>300000</v>
       </c>
       <c r="S16" s="4" t="s">
-        <v>133</v>
+        <v>43</v>
       </c>
       <c r="T16" s="4" t="s">
         <v>44</v>
@@ -2851,10 +2845,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W16" s="3">
-        <v>19600000</v>
+        <v>2940000</v>
       </c>
       <c r="X16" s="5" t="s">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="Y16" s="4" t="s">
         <v>47</v>
@@ -2872,16 +2866,16 @@
         <v>50</v>
       </c>
       <c r="AD16" s="4" t="s">
-        <v>107</v>
+        <v>240</v>
       </c>
       <c r="AE16" s="4" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="AF16" s="4" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="AG16" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.3">
@@ -2892,13 +2886,13 @@
         <v>34</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>114</v>
+        <v>236</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>114</v>
+        <v>236</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>114</v>
+        <v>58</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>36</v>
@@ -2913,13 +2907,13 @@
         <v>39</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>83</v>
+        <v>221</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>84</v>
+        <v>223</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>85</v>
+        <v>222</v>
       </c>
       <c r="M17" s="3">
         <v>200000</v>
@@ -2955,7 +2949,7 @@
         <v>1960000</v>
       </c>
       <c r="X17" s="5" t="s">
-        <v>74</v>
+        <v>176</v>
       </c>
       <c r="Y17" s="4" t="s">
         <v>47</v>
@@ -2973,16 +2967,16 @@
         <v>50</v>
       </c>
       <c r="AD17" s="4" t="s">
-        <v>86</v>
+        <v>260</v>
       </c>
       <c r="AE17" s="4" t="s">
-        <v>138</v>
+        <v>238</v>
       </c>
       <c r="AF17" s="4" t="s">
-        <v>143</v>
+        <v>216</v>
       </c>
       <c r="AG17" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.3">
@@ -2993,13 +2987,13 @@
         <v>34</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>36</v>
@@ -3014,31 +3008,31 @@
         <v>39</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="M18" s="3">
-        <v>2000000</v>
+        <v>500000</v>
       </c>
       <c r="N18" s="3">
-        <v>2000000</v>
+        <v>500000</v>
       </c>
       <c r="O18" s="3">
         <v>0</v>
       </c>
       <c r="P18" s="3">
-        <v>2000000</v>
+        <v>500000</v>
       </c>
       <c r="Q18" s="3">
         <v>0</v>
       </c>
       <c r="R18" s="3">
-        <v>2000000</v>
+        <v>500000</v>
       </c>
       <c r="S18" s="4" t="s">
         <v>43</v>
@@ -3053,7 +3047,7 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W18" s="3">
-        <v>19600000</v>
+        <v>4900000</v>
       </c>
       <c r="X18" s="5" t="s">
         <v>74</v>
@@ -3074,16 +3068,16 @@
         <v>50</v>
       </c>
       <c r="AD18" s="4" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="AE18" s="4" t="s">
-        <v>68</v>
+        <v>138</v>
       </c>
       <c r="AF18" s="4" t="s">
-        <v>69</v>
+        <v>143</v>
       </c>
       <c r="AG18" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.3">
@@ -3094,13 +3088,13 @@
         <v>34</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>36</v>
@@ -3115,34 +3109,34 @@
         <v>39</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>144</v>
+        <v>99</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>145</v>
+        <v>100</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>146</v>
+        <v>101</v>
       </c>
       <c r="M19" s="3">
         <v>300000</v>
       </c>
       <c r="N19" s="3">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="O19" s="3">
+        <v>0</v>
+      </c>
+      <c r="P19" s="3">
         <v>300000</v>
       </c>
-      <c r="P19" s="3">
-        <v>0</v>
-      </c>
       <c r="Q19" s="3">
         <v>0</v>
       </c>
       <c r="R19" s="3">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="S19" s="4" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T19" s="4" t="s">
         <v>44</v>
@@ -3151,13 +3145,13 @@
         <v>45</v>
       </c>
       <c r="V19" s="3">
-        <v>9.8000000000000007</v>
+        <v>8.5</v>
       </c>
       <c r="W19" s="3">
-        <v>2940000</v>
+        <v>2550000</v>
       </c>
       <c r="X19" s="5" t="s">
-        <v>125</v>
+        <v>46</v>
       </c>
       <c r="Y19" s="4" t="s">
         <v>47</v>
@@ -3169,22 +3163,22 @@
         <v>49</v>
       </c>
       <c r="AB19" s="4" t="s">
-        <v>147</v>
+        <v>39</v>
       </c>
       <c r="AC19" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD19" s="4" t="s">
-        <v>148</v>
+        <v>98</v>
       </c>
       <c r="AE19" s="4" t="s">
-        <v>128</v>
+        <v>52</v>
       </c>
       <c r="AF19" s="4" t="s">
-        <v>129</v>
+        <v>53</v>
       </c>
       <c r="AG19" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.3">
@@ -3195,13 +3189,13 @@
         <v>34</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>237</v>
+        <v>54</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>237</v>
+        <v>46</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>36</v>
@@ -3216,31 +3210,31 @@
         <v>39</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>219</v>
+        <v>153</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>221</v>
+        <v>154</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>220</v>
+        <v>155</v>
       </c>
       <c r="M20" s="3">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="N20" s="3">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
       <c r="P20" s="3">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
       <c r="R20" s="3">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="S20" s="4" t="s">
         <v>43</v>
@@ -3252,13 +3246,13 @@
         <v>45</v>
       </c>
       <c r="V20" s="3">
-        <v>9.8000000000000007</v>
+        <v>0</v>
       </c>
       <c r="W20" s="3">
-        <v>1960000</v>
+        <v>0</v>
       </c>
       <c r="X20" s="5" t="s">
-        <v>134</v>
+        <v>58</v>
       </c>
       <c r="Y20" s="4" t="s">
         <v>47</v>
@@ -3276,16 +3270,16 @@
         <v>50</v>
       </c>
       <c r="AD20" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AE20" s="4" t="s">
-        <v>239</v>
+        <v>59</v>
       </c>
       <c r="AF20" s="4" t="s">
-        <v>217</v>
+        <v>60</v>
       </c>
       <c r="AG20" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.3">
@@ -3296,13 +3290,13 @@
         <v>34</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>114</v>
+        <v>256</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>114</v>
+        <v>256</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>114</v>
+        <v>256</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>36</v>
@@ -3317,34 +3311,34 @@
         <v>39</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>103</v>
+        <v>55</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>104</v>
+        <v>56</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>105</v>
+        <v>57</v>
       </c>
       <c r="M21" s="3">
-        <v>2000000</v>
+        <v>5000000</v>
       </c>
       <c r="N21" s="3">
-        <v>2000000</v>
+        <v>1451000</v>
       </c>
       <c r="O21" s="3">
-        <v>0</v>
+        <v>3549000</v>
       </c>
       <c r="P21" s="3">
-        <v>2000000</v>
+        <v>1451000</v>
       </c>
       <c r="Q21" s="3">
         <v>0</v>
       </c>
       <c r="R21" s="3">
-        <v>2000000</v>
+        <v>1451000</v>
       </c>
       <c r="S21" s="4" t="s">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="T21" s="4" t="s">
         <v>44</v>
@@ -3353,13 +3347,13 @@
         <v>45</v>
       </c>
       <c r="V21" s="3">
-        <v>6.7</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="W21" s="3">
-        <v>13400000</v>
+        <v>49000000</v>
       </c>
       <c r="X21" s="5" t="s">
-        <v>93</v>
+        <v>176</v>
       </c>
       <c r="Y21" s="4" t="s">
         <v>47</v>
@@ -3377,16 +3371,16 @@
         <v>50</v>
       </c>
       <c r="AD21" s="4" t="s">
-        <v>149</v>
+        <v>260</v>
       </c>
       <c r="AE21" s="4" t="s">
-        <v>138</v>
+        <v>258</v>
       </c>
       <c r="AF21" s="4" t="s">
-        <v>143</v>
+        <v>242</v>
       </c>
       <c r="AG21" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.3">
@@ -3397,13 +3391,13 @@
         <v>34</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>94</v>
+        <v>256</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>94</v>
+        <v>256</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>94</v>
+        <v>256</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>36</v>
@@ -3418,34 +3412,34 @@
         <v>39</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>150</v>
+        <v>251</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>151</v>
+        <v>253</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>152</v>
+        <v>252</v>
       </c>
       <c r="M22" s="3">
-        <v>300000</v>
+        <v>500000</v>
       </c>
       <c r="N22" s="3">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="O22" s="3">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="P22" s="3">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
       <c r="R22" s="3">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="S22" s="4" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="T22" s="4" t="s">
         <v>44</v>
@@ -3457,10 +3451,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W22" s="3">
-        <v>2940000</v>
+        <v>4900000</v>
       </c>
       <c r="X22" s="5" t="s">
-        <v>134</v>
+        <v>231</v>
       </c>
       <c r="Y22" s="4" t="s">
         <v>47</v>
@@ -3472,22 +3466,22 @@
         <v>49</v>
       </c>
       <c r="AB22" s="4" t="s">
-        <v>39</v>
+        <v>254</v>
       </c>
       <c r="AC22" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD22" s="4" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="AE22" s="4" t="s">
-        <v>128</v>
+        <v>258</v>
       </c>
       <c r="AF22" s="4" t="s">
-        <v>129</v>
+        <v>242</v>
       </c>
       <c r="AG22" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.3">
@@ -3498,10 +3492,10 @@
         <v>34</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>58</v>
@@ -3519,34 +3513,34 @@
         <v>39</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>222</v>
+        <v>90</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>224</v>
+        <v>91</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>223</v>
+        <v>92</v>
       </c>
       <c r="M23" s="3">
         <v>200000</v>
       </c>
       <c r="N23" s="3">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="O23" s="3">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="P23" s="3">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="Q23" s="3">
         <v>0</v>
       </c>
       <c r="R23" s="3">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="S23" s="4" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T23" s="4" t="s">
         <v>44</v>
@@ -3561,7 +3555,7 @@
         <v>1960000</v>
       </c>
       <c r="X23" s="5" t="s">
-        <v>177</v>
+        <v>134</v>
       </c>
       <c r="Y23" s="4" t="s">
         <v>47</v>
@@ -3579,16 +3573,16 @@
         <v>50</v>
       </c>
       <c r="AD23" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="AE23" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="AE23" s="4" t="s">
-        <v>239</v>
-      </c>
       <c r="AF23" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AG23" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.3">
@@ -3620,31 +3614,31 @@
         <v>39</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="M24" s="3">
-        <v>500000</v>
+        <v>200000</v>
       </c>
       <c r="N24" s="3">
-        <v>500000</v>
+        <v>200000</v>
       </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
       <c r="P24" s="3">
-        <v>500000</v>
+        <v>200000</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
       <c r="R24" s="3">
-        <v>500000</v>
+        <v>200000</v>
       </c>
       <c r="S24" s="4" t="s">
         <v>43</v>
@@ -3659,7 +3653,7 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W24" s="3">
-        <v>4900000</v>
+        <v>1960000</v>
       </c>
       <c r="X24" s="5" t="s">
         <v>74</v>
@@ -3680,7 +3674,7 @@
         <v>50</v>
       </c>
       <c r="AD24" s="4" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="AE24" s="4" t="s">
         <v>138</v>
@@ -3689,7 +3683,7 @@
         <v>143</v>
       </c>
       <c r="AG24" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.3">
@@ -3700,13 +3694,13 @@
         <v>34</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>36</v>
@@ -3721,31 +3715,31 @@
         <v>39</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>99</v>
+        <v>156</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>100</v>
+        <v>157</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>101</v>
+        <v>158</v>
       </c>
       <c r="M25" s="3">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="N25" s="3">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="O25" s="3">
         <v>0</v>
       </c>
       <c r="P25" s="3">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="Q25" s="3">
         <v>0</v>
       </c>
       <c r="R25" s="3">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="S25" s="4" t="s">
         <v>43</v>
@@ -3757,13 +3751,13 @@
         <v>45</v>
       </c>
       <c r="V25" s="3">
-        <v>8.5</v>
+        <v>34</v>
       </c>
       <c r="W25" s="3">
-        <v>2550000</v>
+        <v>6800000</v>
       </c>
       <c r="X25" s="5" t="s">
-        <v>46</v>
+        <v>159</v>
       </c>
       <c r="Y25" s="4" t="s">
         <v>47</v>
@@ -3781,16 +3775,16 @@
         <v>50</v>
       </c>
       <c r="AD25" s="4" t="s">
-        <v>98</v>
+        <v>255</v>
       </c>
       <c r="AE25" s="4" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="AF25" s="4" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="AG25" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:33" x14ac:dyDescent="0.3">
@@ -3801,13 +3795,13 @@
         <v>34</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>54</v>
+        <v>114</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>46</v>
+        <v>114</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>46</v>
+        <v>114</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>36</v>
@@ -3822,31 +3816,31 @@
         <v>39</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>153</v>
+        <v>90</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>154</v>
+        <v>91</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>155</v>
+        <v>92</v>
       </c>
       <c r="M26" s="3">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="N26" s="3">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="O26" s="3">
         <v>0</v>
       </c>
       <c r="P26" s="3">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="Q26" s="3">
         <v>0</v>
       </c>
       <c r="R26" s="3">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="S26" s="4" t="s">
         <v>43</v>
@@ -3858,13 +3852,13 @@
         <v>45</v>
       </c>
       <c r="V26" s="3">
-        <v>0</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="W26" s="3">
-        <v>0</v>
+        <v>1960000</v>
       </c>
       <c r="X26" s="5" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="Y26" s="4" t="s">
         <v>47</v>
@@ -3882,16 +3876,16 @@
         <v>50</v>
       </c>
       <c r="AD26" s="4" t="s">
-        <v>241</v>
+        <v>86</v>
       </c>
       <c r="AE26" s="4" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="AF26" s="4" t="s">
-        <v>60</v>
+        <v>143</v>
       </c>
       <c r="AG26" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.3">
@@ -3902,13 +3896,13 @@
         <v>34</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>237</v>
+        <v>61</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>237</v>
+        <v>61</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>36</v>
@@ -3923,34 +3917,34 @@
         <v>39</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>91</v>
+        <v>161</v>
       </c>
       <c r="L27" s="4" t="s">
-        <v>92</v>
+        <v>162</v>
       </c>
       <c r="M27" s="3">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="N27" s="3">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="O27" s="3">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="P27" s="3">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="Q27" s="3">
         <v>0</v>
       </c>
       <c r="R27" s="3">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="S27" s="4" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T27" s="4" t="s">
         <v>44</v>
@@ -3962,10 +3956,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W27" s="3">
-        <v>1960000</v>
+        <v>9800000</v>
       </c>
       <c r="X27" s="5" t="s">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="Y27" s="4" t="s">
         <v>47</v>
@@ -3983,16 +3977,16 @@
         <v>50</v>
       </c>
       <c r="AD27" s="4" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="AE27" s="4" t="s">
-        <v>239</v>
+        <v>68</v>
       </c>
       <c r="AF27" s="4" t="s">
-        <v>217</v>
+        <v>69</v>
       </c>
       <c r="AG27" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.3">
@@ -4003,13 +3997,13 @@
         <v>34</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>114</v>
+        <v>35</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>114</v>
+        <v>35</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>114</v>
+        <v>35</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>36</v>
@@ -4024,31 +4018,31 @@
         <v>39</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="M28" s="3">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="N28" s="3">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="O28" s="3">
         <v>0</v>
       </c>
       <c r="P28" s="3">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="Q28" s="3">
         <v>0</v>
       </c>
       <c r="R28" s="3">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="S28" s="4" t="s">
         <v>43</v>
@@ -4060,13 +4054,13 @@
         <v>45</v>
       </c>
       <c r="V28" s="3">
-        <v>9.8000000000000007</v>
+        <v>6.7</v>
       </c>
       <c r="W28" s="3">
-        <v>1960000</v>
+        <v>13400000</v>
       </c>
       <c r="X28" s="5" t="s">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="Y28" s="4" t="s">
         <v>47</v>
@@ -4084,13 +4078,13 @@
         <v>50</v>
       </c>
       <c r="AD28" s="4" t="s">
-        <v>98</v>
+        <v>163</v>
       </c>
       <c r="AE28" s="4" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="AF28" s="4" t="s">
-        <v>143</v>
+        <v>53</v>
       </c>
       <c r="AG28" s="3">
         <v>3</v>
@@ -4104,13 +4098,13 @@
         <v>34</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>54</v>
+        <v>236</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>46</v>
+        <v>236</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>36</v>
@@ -4125,22 +4119,22 @@
         <v>39</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>157</v>
+        <v>228</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>158</v>
+        <v>230</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>159</v>
+        <v>229</v>
       </c>
       <c r="M29" s="3">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
       </c>
       <c r="O29" s="3">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
@@ -4161,13 +4155,13 @@
         <v>45</v>
       </c>
       <c r="V29" s="3">
-        <v>34</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="W29" s="3">
-        <v>6800000</v>
+        <v>2940000</v>
       </c>
       <c r="X29" s="5" t="s">
-        <v>160</v>
+        <v>231</v>
       </c>
       <c r="Y29" s="4" t="s">
         <v>47</v>
@@ -4185,16 +4179,16 @@
         <v>50</v>
       </c>
       <c r="AD29" s="4" t="s">
-        <v>156</v>
+        <v>237</v>
       </c>
       <c r="AE29" s="4" t="s">
-        <v>59</v>
+        <v>238</v>
       </c>
       <c r="AF29" s="4" t="s">
-        <v>60</v>
+        <v>216</v>
       </c>
       <c r="AG29" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.3">
@@ -4205,13 +4199,13 @@
         <v>34</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>114</v>
+        <v>35</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>114</v>
+        <v>35</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>114</v>
+        <v>35</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>36</v>
@@ -4226,13 +4220,13 @@
         <v>39</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="M30" s="3">
         <v>200000</v>
@@ -4268,7 +4262,7 @@
         <v>1960000</v>
       </c>
       <c r="X30" s="5" t="s">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="Y30" s="4" t="s">
         <v>47</v>
@@ -4280,22 +4274,22 @@
         <v>49</v>
       </c>
       <c r="AB30" s="4" t="s">
-        <v>39</v>
+        <v>130</v>
       </c>
       <c r="AC30" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD30" s="4" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="AE30" s="4" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="AF30" s="4" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="AG30" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.3">
@@ -4306,13 +4300,13 @@
         <v>34</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>36</v>
@@ -4327,31 +4321,31 @@
         <v>39</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="M31" s="3">
-        <v>1000000</v>
+        <v>300000</v>
       </c>
       <c r="N31" s="3">
-        <v>1000000</v>
+        <v>300000</v>
       </c>
       <c r="O31" s="3">
         <v>0</v>
       </c>
       <c r="P31" s="3">
-        <v>1000000</v>
+        <v>300000</v>
       </c>
       <c r="Q31" s="3">
         <v>0</v>
       </c>
       <c r="R31" s="3">
-        <v>1000000</v>
+        <v>300000</v>
       </c>
       <c r="S31" s="4" t="s">
         <v>43</v>
@@ -4366,10 +4360,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W31" s="3">
-        <v>9800000</v>
+        <v>2940000</v>
       </c>
       <c r="X31" s="5" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="Y31" s="4" t="s">
         <v>47</v>
@@ -4387,13 +4381,13 @@
         <v>50</v>
       </c>
       <c r="AD31" s="4" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AE31" s="4" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="AF31" s="4" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="AG31" s="3">
         <v>2</v>
@@ -4407,13 +4401,13 @@
         <v>34</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>36</v>
@@ -4428,34 +4422,34 @@
         <v>39</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>103</v>
+        <v>167</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>104</v>
+        <v>168</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>105</v>
+        <v>169</v>
       </c>
       <c r="M32" s="3">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
       <c r="N32" s="3">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="O32" s="3">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="P32" s="3">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
       <c r="R32" s="3">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="S32" s="4" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="T32" s="4" t="s">
         <v>44</v>
@@ -4464,13 +4458,13 @@
         <v>45</v>
       </c>
       <c r="V32" s="3">
-        <v>6.7</v>
+        <v>7.7</v>
       </c>
       <c r="W32" s="3">
-        <v>13400000</v>
+        <v>7700000</v>
       </c>
       <c r="X32" s="5" t="s">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="Y32" s="4" t="s">
         <v>47</v>
@@ -4488,16 +4482,16 @@
         <v>50</v>
       </c>
       <c r="AD32" s="4" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="AE32" s="4" t="s">
-        <v>52</v>
+        <v>171</v>
       </c>
       <c r="AF32" s="4" t="s">
-        <v>53</v>
+        <v>172</v>
       </c>
       <c r="AG32" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:33" x14ac:dyDescent="0.3">
@@ -4508,13 +4502,13 @@
         <v>34</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>237</v>
+        <v>61</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>237</v>
+        <v>61</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>36</v>
@@ -4529,22 +4523,22 @@
         <v>39</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>229</v>
+        <v>173</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>231</v>
+        <v>174</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>230</v>
+        <v>175</v>
       </c>
       <c r="M33" s="3">
-        <v>300000</v>
+        <v>500000</v>
       </c>
       <c r="N33" s="3">
         <v>0</v>
       </c>
       <c r="O33" s="3">
-        <v>300000</v>
+        <v>500000</v>
       </c>
       <c r="P33" s="3">
         <v>0</v>
@@ -4568,10 +4562,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W33" s="3">
-        <v>2940000</v>
+        <v>4900000</v>
       </c>
       <c r="X33" s="5" t="s">
-        <v>232</v>
+        <v>176</v>
       </c>
       <c r="Y33" s="4" t="s">
         <v>47</v>
@@ -4589,16 +4583,16 @@
         <v>50</v>
       </c>
       <c r="AD33" s="4" t="s">
-        <v>238</v>
+        <v>67</v>
       </c>
       <c r="AE33" s="4" t="s">
-        <v>239</v>
+        <v>68</v>
       </c>
       <c r="AF33" s="4" t="s">
-        <v>217</v>
+        <v>69</v>
       </c>
       <c r="AG33" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:33" x14ac:dyDescent="0.3">
@@ -4609,13 +4603,13 @@
         <v>34</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>36</v>
@@ -4630,31 +4624,31 @@
         <v>39</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>115</v>
+        <v>177</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>116</v>
+        <v>178</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>117</v>
+        <v>179</v>
       </c>
       <c r="M34" s="3">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="N34" s="3">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="O34" s="3">
         <v>0</v>
       </c>
       <c r="P34" s="3">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="Q34" s="3">
         <v>0</v>
       </c>
       <c r="R34" s="3">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="S34" s="4" t="s">
         <v>43</v>
@@ -4669,10 +4663,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W34" s="3">
-        <v>1960000</v>
+        <v>2940000</v>
       </c>
       <c r="X34" s="5" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="Y34" s="4" t="s">
         <v>47</v>
@@ -4684,19 +4678,19 @@
         <v>49</v>
       </c>
       <c r="AB34" s="4" t="s">
-        <v>130</v>
+        <v>39</v>
       </c>
       <c r="AC34" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD34" s="4" t="s">
-        <v>111</v>
+        <v>241</v>
       </c>
       <c r="AE34" s="4" t="s">
-        <v>52</v>
+        <v>128</v>
       </c>
       <c r="AF34" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AG34" s="3">
         <v>1</v>
@@ -4710,13 +4704,13 @@
         <v>34</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>54</v>
+        <v>256</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>46</v>
+        <v>256</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>46</v>
+        <v>256</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>36</v>
@@ -4731,34 +4725,34 @@
         <v>39</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>165</v>
+        <v>244</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>166</v>
+        <v>246</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>167</v>
+        <v>245</v>
       </c>
       <c r="M35" s="3">
-        <v>300000</v>
+        <v>1000000</v>
       </c>
       <c r="N35" s="3">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="O35" s="3">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="P35" s="3">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="Q35" s="3">
         <v>0</v>
       </c>
       <c r="R35" s="3">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="S35" s="4" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="T35" s="4" t="s">
         <v>44</v>
@@ -4770,10 +4764,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W35" s="3">
-        <v>2940000</v>
+        <v>9800000</v>
       </c>
       <c r="X35" s="5" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="Y35" s="4" t="s">
         <v>47</v>
@@ -4791,16 +4785,16 @@
         <v>50</v>
       </c>
       <c r="AD35" s="4" t="s">
-        <v>233</v>
+        <v>257</v>
       </c>
       <c r="AE35" s="4" t="s">
-        <v>59</v>
+        <v>258</v>
       </c>
       <c r="AF35" s="4" t="s">
-        <v>60</v>
+        <v>242</v>
       </c>
       <c r="AG35" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:33" x14ac:dyDescent="0.3">
@@ -4811,13 +4805,13 @@
         <v>34</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>74</v>
+        <v>256</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>74</v>
+        <v>256</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>74</v>
+        <v>256</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>36</v>
@@ -4832,34 +4826,34 @@
         <v>39</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="M36" s="3">
-        <v>1000000</v>
+        <v>200000</v>
       </c>
       <c r="N36" s="3">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="O36" s="3">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="P36" s="3">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="Q36" s="3">
         <v>0</v>
       </c>
       <c r="R36" s="3">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="S36" s="4" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T36" s="4" t="s">
         <v>44</v>
@@ -4868,13 +4862,13 @@
         <v>45</v>
       </c>
       <c r="V36" s="3">
-        <v>7.7</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="W36" s="3">
-        <v>7700000</v>
+        <v>1960000</v>
       </c>
       <c r="X36" s="5" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="Y36" s="4" t="s">
         <v>47</v>
@@ -4892,13 +4886,13 @@
         <v>50</v>
       </c>
       <c r="AD36" s="4" t="s">
-        <v>171</v>
+        <v>260</v>
       </c>
       <c r="AE36" s="4" t="s">
-        <v>172</v>
+        <v>258</v>
       </c>
       <c r="AF36" s="4" t="s">
-        <v>173</v>
+        <v>242</v>
       </c>
       <c r="AG36" s="3">
         <v>1</v>
@@ -4912,13 +4906,13 @@
         <v>34</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>36</v>
@@ -4933,34 +4927,34 @@
         <v>39</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>174</v>
+        <v>40</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>175</v>
+        <v>41</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>176</v>
+        <v>42</v>
       </c>
       <c r="M37" s="3">
-        <v>500000</v>
+        <v>200000</v>
       </c>
       <c r="N37" s="3">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="O37" s="3">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="P37" s="3">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="Q37" s="3">
         <v>0</v>
       </c>
       <c r="R37" s="3">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="S37" s="4" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T37" s="4" t="s">
         <v>44</v>
@@ -4972,10 +4966,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W37" s="3">
-        <v>4900000</v>
+        <v>1960000</v>
       </c>
       <c r="X37" s="5" t="s">
-        <v>177</v>
+        <v>46</v>
       </c>
       <c r="Y37" s="4" t="s">
         <v>47</v>
@@ -4993,16 +4987,16 @@
         <v>50</v>
       </c>
       <c r="AD37" s="4" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="AE37" s="4" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="AF37" s="4" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="AG37" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:33" x14ac:dyDescent="0.3">
@@ -5013,13 +5007,13 @@
         <v>34</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>36</v>
@@ -5034,31 +5028,31 @@
         <v>39</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>178</v>
+        <v>118</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>179</v>
+        <v>119</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="M38" s="3">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="N38" s="3">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="O38" s="3">
         <v>0</v>
       </c>
       <c r="P38" s="3">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="Q38" s="3">
         <v>0</v>
       </c>
       <c r="R38" s="3">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="S38" s="4" t="s">
         <v>43</v>
@@ -5073,10 +5067,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W38" s="3">
-        <v>2940000</v>
+        <v>1960000</v>
       </c>
       <c r="X38" s="5" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="Y38" s="4" t="s">
         <v>47</v>
@@ -5088,65 +5082,730 @@
         <v>49</v>
       </c>
       <c r="AB38" s="4" t="s">
-        <v>39</v>
+        <v>130</v>
       </c>
       <c r="AC38" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD38" s="4" t="s">
-        <v>243</v>
+        <v>111</v>
       </c>
       <c r="AE38" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF38" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG38" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A39" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J39" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="K39" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="L39" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="M39" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="N39" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="O39" s="3">
+        <v>0</v>
+      </c>
+      <c r="P39" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="Q39" s="3">
+        <v>0</v>
+      </c>
+      <c r="R39" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="S39" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="T39" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="U39" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="V39" s="3">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="W39" s="3">
+        <v>19600000</v>
+      </c>
+      <c r="X39" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y39" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z39" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA39" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB39" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC39" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD39" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AE39" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AF39" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AG39" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A40" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J40" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="K40" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="L40" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="M40" s="3">
+        <v>500000</v>
+      </c>
+      <c r="N40" s="3">
+        <v>500000</v>
+      </c>
+      <c r="O40" s="3">
+        <v>0</v>
+      </c>
+      <c r="P40" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Q40" s="3">
+        <v>0</v>
+      </c>
+      <c r="R40" s="3">
+        <v>500000</v>
+      </c>
+      <c r="S40" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="T40" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="U40" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="V40" s="3">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="W40" s="3">
+        <v>4900000</v>
+      </c>
+      <c r="X40" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="Y40" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z40" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA40" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB40" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC40" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD40" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="AE40" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF40" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="AG40" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A41" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J41" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="K41" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="L41" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="M41" s="3">
+        <v>200000</v>
+      </c>
+      <c r="N41" s="3">
+        <v>0</v>
+      </c>
+      <c r="O41" s="3">
+        <v>200000</v>
+      </c>
+      <c r="P41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>0</v>
+      </c>
+      <c r="R41" s="3">
+        <v>0</v>
+      </c>
+      <c r="S41" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="T41" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="U41" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="V41" s="3">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="W41" s="3">
+        <v>1960000</v>
+      </c>
+      <c r="X41" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y41" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z41" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA41" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB41" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC41" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD41" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="AE41" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF41" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="AG41" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A42" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="K42" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="L42" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="M42" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="N42" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
+        <v>1664000</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>336000</v>
+      </c>
+      <c r="R42" s="3">
+        <v>1664000</v>
+      </c>
+      <c r="S42" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="T42" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="U42" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="V42" s="3">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="W42" s="3">
+        <v>19600000</v>
+      </c>
+      <c r="X42" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y42" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z42" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA42" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB42" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC42" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD42" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="AE42" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="AF38" s="4" t="s">
+      <c r="AF42" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="AG38" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="X39" s="2"/>
-    </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="X40" s="2"/>
-    </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="X41" s="2"/>
-    </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="X42" s="2"/>
+      <c r="AG42" s="3">
+        <v>3</v>
+      </c>
     </row>
     <row r="43" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="X43" s="2"/>
+      <c r="A43" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="K43" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="L43" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="M43" s="3">
+        <v>8000000</v>
+      </c>
+      <c r="N43" s="3">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3">
+        <v>8000000</v>
+      </c>
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="T43" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="U43" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="V43" s="3">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="W43" s="3">
+        <v>78400000</v>
+      </c>
+      <c r="X43" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y43" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z43" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA43" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB43" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="AC43" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD43" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="AE43" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF43" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="AG43" s="3">
+        <v>6</v>
+      </c>
     </row>
     <row r="44" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="X44" s="2"/>
+      <c r="A44" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="L44" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="M44" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="N44" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="S44" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="T44" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="U44" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="V44" s="3">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="W44" s="3">
+        <v>19600000</v>
+      </c>
+      <c r="X44" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y44" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z44" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA44" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB44" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC44" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD44" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="AE44" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="AF44" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="AG44" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="45" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="X45" s="2"/>
+      <c r="A45" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J45" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L45" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="M45" s="3">
+        <v>3000000</v>
+      </c>
+      <c r="N45" s="3">
+        <v>0</v>
+      </c>
+      <c r="O45" s="3">
+        <v>3000000</v>
+      </c>
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+      <c r="S45" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="T45" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="U45" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="V45" s="3">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="W45" s="3">
+        <v>29400000</v>
+      </c>
+      <c r="X45" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="Y45" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z45" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA45" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB45" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="AC45" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD45" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="AE45" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="AF45" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="AG45" s="3">
+        <v>5</v>
+      </c>
     </row>
     <row r="46" spans="1:33" x14ac:dyDescent="0.3">
       <c r="C46" s="2"/>
@@ -5294,16 +5953,16 @@
         <v>31</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>32</v>
       </c>
       <c r="E1" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>182</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>183</v>
       </c>
       <c r="G1" s="7" t="s">
         <v>9</v>
@@ -5315,16 +5974,16 @@
         <v>10</v>
       </c>
       <c r="J1" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="K1" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="L1" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="M1" s="7" t="s">
         <v>186</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>187</v>
       </c>
       <c r="N1" s="7" t="s">
         <v>5</v>
@@ -5333,55 +5992,55 @@
         <v>24</v>
       </c>
       <c r="P1" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q1" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="R1" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="S1" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>192</v>
-      </c>
-      <c r="U1" s="6" t="s">
-        <v>193</v>
       </c>
       <c r="V1" s="6" t="s">
         <v>17</v>
       </c>
       <c r="W1" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="X1" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="X1" s="7" t="s">
+      <c r="Y1" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="Y1" s="7" t="s">
+      <c r="Z1" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="Z1" s="7" t="s">
+      <c r="AA1" s="7" t="s">
         <v>197</v>
-      </c>
-      <c r="AA1" s="7" t="s">
-        <v>198</v>
       </c>
       <c r="AB1" s="7" t="s">
         <v>27</v>
       </c>
       <c r="AC1" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="AD1" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="AD1" s="7" t="s">
+      <c r="AE1" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="AE1" s="7" t="s">
+      <c r="AF1" s="7" t="s">
         <v>201</v>
-      </c>
-      <c r="AF1" s="7" t="s">
-        <v>202</v>
       </c>
       <c r="AG1" s="7" t="s">
         <v>28</v>
@@ -5398,7 +6057,7 @@
         <v>53</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D2" s="6">
         <v>1</v>
@@ -5407,7 +6066,7 @@
         <v>70</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G2" s="7" t="s">
         <v>99</v>
@@ -5437,7 +6096,7 @@
         <v>47</v>
       </c>
       <c r="P2" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q2" s="7" t="s">
         <v>45</v>
@@ -5470,16 +6129,16 @@
         <v>39</v>
       </c>
       <c r="AA2" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC2" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="AB2" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC2" s="7" t="s">
-        <v>207</v>
-      </c>
       <c r="AD2" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE2" s="7" t="s">
         <v>39</v>
@@ -5491,7 +6150,7 @@
         <v>47</v>
       </c>
       <c r="AH2" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.3">
@@ -5502,7 +6161,7 @@
         <v>53</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D3" s="6">
         <v>2</v>
@@ -5511,7 +6170,7 @@
         <v>70</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>40</v>
@@ -5541,7 +6200,7 @@
         <v>47</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q3" s="7" t="s">
         <v>45</v>
@@ -5574,16 +6233,16 @@
         <v>39</v>
       </c>
       <c r="AA3" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB3" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC3" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="AB3" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC3" s="7" t="s">
-        <v>207</v>
-      </c>
       <c r="AD3" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE3" s="7" t="s">
         <v>39</v>
@@ -5595,7 +6254,7 @@
         <v>47</v>
       </c>
       <c r="AH3" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.3">
@@ -5606,7 +6265,7 @@
         <v>53</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D4" s="6">
         <v>3</v>
@@ -5615,7 +6274,7 @@
         <v>70</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>103</v>
@@ -5645,7 +6304,7 @@
         <v>47</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q4" s="7" t="s">
         <v>45</v>
@@ -5678,16 +6337,16 @@
         <v>39</v>
       </c>
       <c r="AA4" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB4" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC4" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="AB4" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC4" s="7" t="s">
-        <v>207</v>
-      </c>
       <c r="AD4" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE4" s="7" t="s">
         <v>39</v>
@@ -5699,7 +6358,7 @@
         <v>47</v>
       </c>
       <c r="AH4" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.3">
@@ -5710,16 +6369,16 @@
         <v>131</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D5" s="6">
         <v>1</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>115</v>
@@ -5749,7 +6408,7 @@
         <v>47</v>
       </c>
       <c r="P5" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q5" s="7" t="s">
         <v>45</v>
@@ -5782,16 +6441,16 @@
         <v>39</v>
       </c>
       <c r="AA5" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AB5" s="7" t="s">
         <v>130</v>
       </c>
       <c r="AC5" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AD5" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE5" s="7" t="s">
         <v>39</v>
@@ -5803,7 +6462,7 @@
         <v>47</v>
       </c>
       <c r="AH5" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.3">
@@ -5814,16 +6473,16 @@
         <v>131</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D6" s="6">
         <v>2</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>108</v>
@@ -5853,7 +6512,7 @@
         <v>47</v>
       </c>
       <c r="P6" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q6" s="7" t="s">
         <v>45</v>
@@ -5886,16 +6545,16 @@
         <v>39</v>
       </c>
       <c r="AA6" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AB6" s="7" t="s">
         <v>130</v>
       </c>
       <c r="AC6" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AD6" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE6" s="7" t="s">
         <v>39</v>
@@ -5907,7 +6566,7 @@
         <v>47</v>
       </c>
       <c r="AH6" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.3">
@@ -5918,16 +6577,16 @@
         <v>131</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D7" s="6">
         <v>3</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>118</v>
@@ -5957,7 +6616,7 @@
         <v>47</v>
       </c>
       <c r="P7" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q7" s="7" t="s">
         <v>45</v>
@@ -5990,16 +6649,16 @@
         <v>39</v>
       </c>
       <c r="AA7" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AB7" s="7" t="s">
         <v>130</v>
       </c>
       <c r="AC7" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AD7" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE7" s="7" t="s">
         <v>39</v>
@@ -6011,7 +6670,7 @@
         <v>47</v>
       </c>
       <c r="AH7" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8" spans="1:34" x14ac:dyDescent="0.3">
@@ -6022,7 +6681,7 @@
         <v>143</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D8" s="6">
         <v>1</v>
@@ -6031,7 +6690,7 @@
         <v>121</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G8" s="7" t="s">
         <v>103</v>
@@ -6061,7 +6720,7 @@
         <v>47</v>
       </c>
       <c r="P8" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q8" s="7" t="s">
         <v>39</v>
@@ -6094,16 +6753,16 @@
         <v>39</v>
       </c>
       <c r="AA8" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC8" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="AB8" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC8" s="7" t="s">
-        <v>207</v>
-      </c>
       <c r="AD8" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE8" s="7" t="s">
         <v>39</v>
@@ -6115,7 +6774,7 @@
         <v>47</v>
       </c>
       <c r="AH8" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.3">
@@ -6126,7 +6785,7 @@
         <v>143</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D9" s="6">
         <v>2</v>
@@ -6135,7 +6794,7 @@
         <v>121</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>135</v>
@@ -6165,7 +6824,7 @@
         <v>47</v>
       </c>
       <c r="P9" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q9" s="7" t="s">
         <v>39</v>
@@ -6198,16 +6857,16 @@
         <v>39</v>
       </c>
       <c r="AA9" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC9" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="AB9" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC9" s="7" t="s">
-        <v>207</v>
-      </c>
       <c r="AD9" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE9" s="7" t="s">
         <v>39</v>
@@ -6219,7 +6878,7 @@
         <v>47</v>
       </c>
       <c r="AH9" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.3">
@@ -6230,7 +6889,7 @@
         <v>143</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D10" s="6">
         <v>3</v>
@@ -6239,7 +6898,7 @@
         <v>121</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>95</v>
@@ -6251,7 +6910,7 @@
         <v>96</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>93</v>
+        <v>256</v>
       </c>
       <c r="K10" s="7" t="s">
         <v>36</v>
@@ -6269,7 +6928,7 @@
         <v>47</v>
       </c>
       <c r="P10" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q10" s="7" t="s">
         <v>39</v>
@@ -6302,16 +6961,16 @@
         <v>39</v>
       </c>
       <c r="AA10" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB10" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC10" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="AB10" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC10" s="7" t="s">
-        <v>207</v>
-      </c>
       <c r="AD10" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE10" s="7" t="s">
         <v>39</v>
@@ -6323,7 +6982,7 @@
         <v>47</v>
       </c>
       <c r="AH10" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.3">
@@ -6334,7 +6993,7 @@
         <v>143</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D11" s="6">
         <v>4</v>
@@ -6343,7 +7002,7 @@
         <v>121</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>87</v>
@@ -6373,7 +7032,7 @@
         <v>47</v>
       </c>
       <c r="P11" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q11" s="7" t="s">
         <v>39</v>
@@ -6406,16 +7065,16 @@
         <v>39</v>
       </c>
       <c r="AA11" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB11" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC11" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="AB11" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC11" s="7" t="s">
-        <v>207</v>
-      </c>
       <c r="AD11" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE11" s="7" t="s">
         <v>39</v>
@@ -6427,7 +7086,7 @@
         <v>47</v>
       </c>
       <c r="AH11" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.3">
@@ -6438,7 +7097,7 @@
         <v>143</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D12" s="6">
         <v>5</v>
@@ -6447,7 +7106,7 @@
         <v>121</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>83</v>
@@ -6477,7 +7136,7 @@
         <v>47</v>
       </c>
       <c r="P12" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q12" s="7" t="s">
         <v>39</v>
@@ -6510,16 +7169,16 @@
         <v>39</v>
       </c>
       <c r="AA12" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB12" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC12" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="AB12" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC12" s="7" t="s">
-        <v>207</v>
-      </c>
       <c r="AD12" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE12" s="7" t="s">
         <v>39</v>
@@ -6531,7 +7190,7 @@
         <v>47</v>
       </c>
       <c r="AH12" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="13" spans="1:34" x14ac:dyDescent="0.3">
@@ -6542,7 +7201,7 @@
         <v>143</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D13" s="6">
         <v>6</v>
@@ -6551,7 +7210,7 @@
         <v>121</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>90</v>
@@ -6563,7 +7222,7 @@
         <v>91</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="K13" s="7" t="s">
         <v>36</v>
@@ -6581,7 +7240,7 @@
         <v>47</v>
       </c>
       <c r="P13" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q13" s="7" t="s">
         <v>39</v>
@@ -6614,16 +7273,16 @@
         <v>39</v>
       </c>
       <c r="AA13" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB13" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC13" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="AB13" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC13" s="7" t="s">
-        <v>207</v>
-      </c>
       <c r="AD13" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE13" s="7" t="s">
         <v>39</v>
@@ -6635,7 +7294,7 @@
         <v>47</v>
       </c>
       <c r="AH13" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.3">
@@ -6646,7 +7305,7 @@
         <v>60</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D14" s="6">
         <v>1</v>
@@ -6655,7 +7314,7 @@
         <v>113</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>79</v>
@@ -6685,7 +7344,7 @@
         <v>47</v>
       </c>
       <c r="P14" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q14" s="7" t="s">
         <v>39</v>
@@ -6718,16 +7377,16 @@
         <v>39</v>
       </c>
       <c r="AA14" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB14" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC14" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="AB14" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC14" s="7" t="s">
-        <v>207</v>
-      </c>
       <c r="AD14" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE14" s="7" t="s">
         <v>39</v>
@@ -6739,7 +7398,7 @@
         <v>47</v>
       </c>
       <c r="AH14" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="15" spans="1:34" x14ac:dyDescent="0.3">
@@ -6750,7 +7409,7 @@
         <v>60</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D15" s="6">
         <v>2</v>
@@ -6759,19 +7418,19 @@
         <v>113</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G15" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="I15" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="H15" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="J15" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K15" s="7" t="s">
         <v>36</v>
@@ -6789,7 +7448,7 @@
         <v>47</v>
       </c>
       <c r="P15" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q15" s="7" t="s">
         <v>39</v>
@@ -6822,16 +7481,16 @@
         <v>39</v>
       </c>
       <c r="AA15" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB15" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC15" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="AB15" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC15" s="7" t="s">
-        <v>207</v>
-      </c>
       <c r="AD15" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE15" s="7" t="s">
         <v>39</v>
@@ -6843,7 +7502,7 @@
         <v>47</v>
       </c>
       <c r="AH15" s="7" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="16" spans="1:34" x14ac:dyDescent="0.3">
@@ -6854,7 +7513,7 @@
         <v>60</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D16" s="6">
         <v>3</v>
@@ -6863,7 +7522,7 @@
         <v>113</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>55</v>
@@ -6875,7 +7534,7 @@
         <v>56</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>142</v>
+        <v>256</v>
       </c>
       <c r="K16" s="7" t="s">
         <v>36</v>
@@ -6893,7 +7552,7 @@
         <v>47</v>
       </c>
       <c r="P16" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q16" s="7" t="s">
         <v>39</v>
@@ -6926,16 +7585,16 @@
         <v>39</v>
       </c>
       <c r="AA16" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB16" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC16" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="AB16" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC16" s="7" t="s">
-        <v>207</v>
-      </c>
       <c r="AD16" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE16" s="7" t="s">
         <v>39</v>
@@ -6947,7 +7606,7 @@
         <v>47</v>
       </c>
       <c r="AH16" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="17" spans="1:34" x14ac:dyDescent="0.3">
@@ -6958,7 +7617,7 @@
         <v>60</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D17" s="6">
         <v>4</v>
@@ -6967,7 +7626,7 @@
         <v>113</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>153</v>
@@ -6997,7 +7656,7 @@
         <v>47</v>
       </c>
       <c r="P17" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q17" s="7" t="s">
         <v>39</v>
@@ -7030,16 +7689,16 @@
         <v>39</v>
       </c>
       <c r="AA17" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB17" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC17" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="AB17" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC17" s="7" t="s">
-        <v>207</v>
-      </c>
       <c r="AD17" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE17" s="7" t="s">
         <v>39</v>
@@ -7051,7 +7710,7 @@
         <v>47</v>
       </c>
       <c r="AH17" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="18" spans="1:34" x14ac:dyDescent="0.3">
@@ -7062,7 +7721,7 @@
         <v>60</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D18" s="6">
         <v>5</v>
@@ -7071,19 +7730,19 @@
         <v>113</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G18" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="I18" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="H18" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>158</v>
-      </c>
       <c r="J18" s="7" t="s">
-        <v>46</v>
+        <v>256</v>
       </c>
       <c r="K18" s="7" t="s">
         <v>36</v>
@@ -7101,7 +7760,7 @@
         <v>47</v>
       </c>
       <c r="P18" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q18" s="7" t="s">
         <v>39</v>
@@ -7119,7 +7778,7 @@
         <v>0</v>
       </c>
       <c r="V18" s="6">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="W18" s="7" t="s">
         <v>50</v>
@@ -7128,22 +7787,22 @@
         <v>49</v>
       </c>
       <c r="Y18" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Z18" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AA18" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB18" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC18" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="AB18" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC18" s="7" t="s">
-        <v>207</v>
-      </c>
       <c r="AD18" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE18" s="7" t="s">
         <v>39</v>
@@ -7155,7 +7814,7 @@
         <v>47</v>
       </c>
       <c r="AH18" s="7" t="s">
-        <v>156</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="1:34" x14ac:dyDescent="0.3">
@@ -7166,7 +7825,7 @@
         <v>69</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D19" s="6">
         <v>1</v>
@@ -7175,7 +7834,7 @@
         <v>54</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>55</v>
@@ -7187,7 +7846,7 @@
         <v>56</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>142</v>
+        <v>256</v>
       </c>
       <c r="K19" s="7" t="s">
         <v>36</v>
@@ -7205,7 +7864,7 @@
         <v>47</v>
       </c>
       <c r="P19" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q19" s="7" t="s">
         <v>39</v>
@@ -7238,16 +7897,16 @@
         <v>39</v>
       </c>
       <c r="AA19" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB19" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC19" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="AB19" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC19" s="7" t="s">
-        <v>207</v>
-      </c>
       <c r="AD19" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE19" s="7" t="s">
         <v>39</v>
@@ -7259,7 +7918,7 @@
         <v>47</v>
       </c>
       <c r="AH19" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="20" spans="1:34" x14ac:dyDescent="0.3">
@@ -7270,7 +7929,7 @@
         <v>69</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D20" s="6">
         <v>2</v>
@@ -7279,19 +7938,19 @@
         <v>54</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G20" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="I20" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="H20" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>162</v>
-      </c>
       <c r="J20" s="7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="K20" s="7" t="s">
         <v>36</v>
@@ -7309,7 +7968,7 @@
         <v>47</v>
       </c>
       <c r="P20" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q20" s="7" t="s">
         <v>39</v>
@@ -7342,16 +8001,16 @@
         <v>39</v>
       </c>
       <c r="AA20" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB20" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC20" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="AB20" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC20" s="7" t="s">
-        <v>207</v>
-      </c>
       <c r="AD20" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE20" s="7" t="s">
         <v>39</v>
@@ -7363,7 +8022,7 @@
         <v>47</v>
       </c>
       <c r="AH20" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="21" spans="1:34" x14ac:dyDescent="0.3">
@@ -7374,7 +8033,7 @@
         <v>69</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D21" s="6">
         <v>3</v>
@@ -7383,7 +8042,7 @@
         <v>54</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G21" s="7" t="s">
         <v>76</v>
@@ -7413,7 +8072,7 @@
         <v>47</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q21" s="7" t="s">
         <v>39</v>
@@ -7446,16 +8105,16 @@
         <v>39</v>
       </c>
       <c r="AA21" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB21" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC21" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="AB21" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC21" s="7" t="s">
-        <v>207</v>
-      </c>
       <c r="AD21" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE21" s="7" t="s">
         <v>39</v>
@@ -7467,7 +8126,7 @@
         <v>47</v>
       </c>
       <c r="AH21" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="22" spans="1:34" x14ac:dyDescent="0.3">
@@ -7478,7 +8137,7 @@
         <v>69</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D22" s="6">
         <v>4</v>
@@ -7487,7 +8146,7 @@
         <v>54</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G22" s="7" t="s">
         <v>139</v>
@@ -7499,7 +8158,7 @@
         <v>140</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>61</v>
+        <v>256</v>
       </c>
       <c r="K22" s="7" t="s">
         <v>36</v>
@@ -7517,7 +8176,7 @@
         <v>47</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q22" s="7" t="s">
         <v>39</v>
@@ -7535,7 +8194,7 @@
         <v>0</v>
       </c>
       <c r="V22" s="6">
-        <v>57600</v>
+        <v>200000</v>
       </c>
       <c r="W22" s="7" t="s">
         <v>50</v>
@@ -7550,16 +8209,16 @@
         <v>39</v>
       </c>
       <c r="AA22" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB22" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC22" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="AB22" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC22" s="7" t="s">
-        <v>207</v>
-      </c>
       <c r="AD22" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE22" s="7" t="s">
         <v>39</v>
@@ -7571,7 +8230,7 @@
         <v>47</v>
       </c>
       <c r="AH22" s="7" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
     </row>
     <row r="23" spans="1:34" x14ac:dyDescent="0.3">
@@ -7582,7 +8241,7 @@
         <v>69</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D23" s="6">
         <v>5</v>
@@ -7591,16 +8250,16 @@
         <v>54</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G23" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="I23" s="7" t="s">
         <v>174</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>175</v>
       </c>
       <c r="J23" s="7" t="s">
         <v>61</v>
@@ -7621,7 +8280,7 @@
         <v>47</v>
       </c>
       <c r="P23" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q23" s="7" t="s">
         <v>39</v>
@@ -7648,22 +8307,22 @@
         <v>49</v>
       </c>
       <c r="Y23" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Z23" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AA23" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB23" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC23" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="AB23" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC23" s="7" t="s">
-        <v>207</v>
-      </c>
       <c r="AD23" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE23" s="7" t="s">
         <v>39</v>
@@ -7686,7 +8345,7 @@
         <v>69</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D24" s="6">
         <v>6</v>
@@ -7695,7 +8354,7 @@
         <v>54</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G24" s="7" t="s">
         <v>62</v>
@@ -7725,7 +8384,7 @@
         <v>47</v>
       </c>
       <c r="P24" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q24" s="7" t="s">
         <v>39</v>
@@ -7758,16 +8417,16 @@
         <v>39</v>
       </c>
       <c r="AA24" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB24" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC24" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="AB24" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC24" s="7" t="s">
-        <v>207</v>
-      </c>
       <c r="AD24" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE24" s="7" t="s">
         <v>39</v>
@@ -7790,7 +8449,7 @@
         <v>129</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D25" s="6">
         <v>1</v>
@@ -7799,16 +8458,16 @@
         <v>94</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G25" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="I25" s="7" t="s">
         <v>178</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>179</v>
       </c>
       <c r="J25" s="7" t="s">
         <v>132</v>
@@ -7829,7 +8488,7 @@
         <v>47</v>
       </c>
       <c r="P25" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q25" s="7" t="s">
         <v>39</v>
@@ -7862,16 +8521,16 @@
         <v>39</v>
       </c>
       <c r="AA25" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB25" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC25" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="AB25" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC25" s="7" t="s">
-        <v>207</v>
-      </c>
       <c r="AD25" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE25" s="7" t="s">
         <v>39</v>
@@ -7883,7 +8542,7 @@
         <v>47</v>
       </c>
       <c r="AH25" s="7" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="26" spans="1:34" x14ac:dyDescent="0.3">
@@ -7894,7 +8553,7 @@
         <v>129</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D26" s="6">
         <v>2</v>
@@ -7903,7 +8562,7 @@
         <v>94</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G26" s="7" t="s">
         <v>71</v>
@@ -7915,7 +8574,7 @@
         <v>72</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="K26" s="7" t="s">
         <v>36</v>
@@ -7933,7 +8592,7 @@
         <v>47</v>
       </c>
       <c r="P26" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q26" s="7" t="s">
         <v>39</v>
@@ -7966,16 +8625,16 @@
         <v>39</v>
       </c>
       <c r="AA26" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB26" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC26" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="AB26" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC26" s="7" t="s">
-        <v>207</v>
-      </c>
       <c r="AD26" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE26" s="7" t="s">
         <v>39</v>
@@ -7987,7 +8646,7 @@
         <v>47</v>
       </c>
       <c r="AH26" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="27" spans="1:34" x14ac:dyDescent="0.3">
@@ -7998,7 +8657,7 @@
         <v>129</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D27" s="6">
         <v>3</v>
@@ -8007,7 +8666,7 @@
         <v>94</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G27" s="7" t="s">
         <v>55</v>
@@ -8019,7 +8678,7 @@
         <v>56</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>142</v>
+        <v>256</v>
       </c>
       <c r="K27" s="7" t="s">
         <v>36</v>
@@ -8037,7 +8696,7 @@
         <v>47</v>
       </c>
       <c r="P27" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q27" s="7" t="s">
         <v>39</v>
@@ -8070,16 +8729,16 @@
         <v>39</v>
       </c>
       <c r="AA27" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB27" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC27" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="AB27" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC27" s="7" t="s">
-        <v>207</v>
-      </c>
       <c r="AD27" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE27" s="7" t="s">
         <v>39</v>
@@ -8091,7 +8750,7 @@
         <v>47</v>
       </c>
       <c r="AH27" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="28" spans="1:34" x14ac:dyDescent="0.3">
@@ -8102,7 +8761,7 @@
         <v>129</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D28" s="6">
         <v>4</v>
@@ -8111,7 +8770,7 @@
         <v>94</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G28" s="7" t="s">
         <v>150</v>
@@ -8141,7 +8800,7 @@
         <v>47</v>
       </c>
       <c r="P28" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q28" s="7" t="s">
         <v>39</v>
@@ -8174,16 +8833,16 @@
         <v>39</v>
       </c>
       <c r="AA28" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB28" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC28" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="AB28" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC28" s="7" t="s">
-        <v>207</v>
-      </c>
       <c r="AD28" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE28" s="7" t="s">
         <v>39</v>
@@ -8195,7 +8854,7 @@
         <v>47</v>
       </c>
       <c r="AH28" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="29" spans="1:34" x14ac:dyDescent="0.3">
@@ -8206,7 +8865,7 @@
         <v>129</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D29" s="6">
         <v>5</v>
@@ -8215,7 +8874,7 @@
         <v>94</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G29" s="7" t="s">
         <v>135</v>
@@ -8245,7 +8904,7 @@
         <v>47</v>
       </c>
       <c r="P29" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q29" s="7" t="s">
         <v>39</v>
@@ -8278,16 +8937,16 @@
         <v>39</v>
       </c>
       <c r="AA29" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB29" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC29" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="AB29" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC29" s="7" t="s">
-        <v>207</v>
-      </c>
       <c r="AD29" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE29" s="7" t="s">
         <v>39</v>
@@ -8310,7 +8969,7 @@
         <v>129</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D30" s="6">
         <v>6</v>
@@ -8319,7 +8978,7 @@
         <v>94</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G30" s="7" t="s">
         <v>122</v>
@@ -8349,7 +9008,7 @@
         <v>47</v>
       </c>
       <c r="P30" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q30" s="7" t="s">
         <v>39</v>
@@ -8382,16 +9041,16 @@
         <v>39</v>
       </c>
       <c r="AA30" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AB30" s="7" t="s">
         <v>126</v>
       </c>
       <c r="AC30" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AD30" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE30" s="7" t="s">
         <v>39</v>
@@ -8414,7 +9073,7 @@
         <v>129</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D31" s="6">
         <v>7</v>
@@ -8423,7 +9082,7 @@
         <v>94</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G31" s="7" t="s">
         <v>144</v>
@@ -8435,7 +9094,7 @@
         <v>145</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>94</v>
+        <v>256</v>
       </c>
       <c r="K31" s="7" t="s">
         <v>36</v>
@@ -8453,7 +9112,7 @@
         <v>47</v>
       </c>
       <c r="P31" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q31" s="7" t="s">
         <v>39</v>
@@ -8471,7 +9130,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="6">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="W31" s="7" t="s">
         <v>50</v>
@@ -8486,16 +9145,16 @@
         <v>39</v>
       </c>
       <c r="AA31" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AB31" s="7" t="s">
         <v>147</v>
       </c>
       <c r="AC31" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AD31" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE31" s="7" t="s">
         <v>39</v>
@@ -8507,7 +9166,7 @@
         <v>47</v>
       </c>
       <c r="AH31" s="7" t="s">
-        <v>148</v>
+        <v>259</v>
       </c>
     </row>
     <row r="32" spans="1:34" x14ac:dyDescent="0.3">
@@ -8515,10 +9174,10 @@
         <v>33</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D32" s="6">
         <v>1</v>
@@ -8527,19 +9186,19 @@
         <v>74</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G32" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="I32" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="H32" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="I32" s="7" t="s">
-        <v>169</v>
-      </c>
       <c r="J32" s="7" t="s">
-        <v>74</v>
+        <v>256</v>
       </c>
       <c r="K32" s="7" t="s">
         <v>36</v>
@@ -8557,7 +9216,7 @@
         <v>47</v>
       </c>
       <c r="P32" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q32" s="7" t="s">
         <v>45</v>
@@ -8584,22 +9243,22 @@
         <v>49</v>
       </c>
       <c r="Y32" s="8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Z32" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AA32" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB32" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC32" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="AB32" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC32" s="7" t="s">
-        <v>207</v>
-      </c>
       <c r="AD32" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE32" s="7" t="s">
         <v>39</v>
@@ -8611,7 +9270,7 @@
         <v>47</v>
       </c>
       <c r="AH32" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="33" spans="1:34" x14ac:dyDescent="0.3">
@@ -8619,10 +9278,10 @@
         <v>33</v>
       </c>
       <c r="B33" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C33" s="7" t="s">
         <v>217</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>218</v>
       </c>
       <c r="D33" s="6">
         <v>1</v>
@@ -8631,16 +9290,16 @@
         <v>58</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G33" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="H33" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="H33" s="7" t="s">
+      <c r="I33" s="7" t="s">
         <v>220</v>
-      </c>
-      <c r="I33" s="7" t="s">
-        <v>221</v>
       </c>
       <c r="J33" s="7" t="s">
         <v>142</v>
@@ -8661,7 +9320,7 @@
         <v>47</v>
       </c>
       <c r="P33" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q33" s="7" t="s">
         <v>39</v>
@@ -8694,16 +9353,16 @@
         <v>39</v>
       </c>
       <c r="AA33" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB33" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC33" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="AB33" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC33" s="7" t="s">
-        <v>207</v>
-      </c>
       <c r="AD33" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE33" s="7" t="s">
         <v>39</v>
@@ -8715,7 +9374,7 @@
         <v>47</v>
       </c>
       <c r="AH33" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="34" spans="1:34" x14ac:dyDescent="0.3">
@@ -8723,10 +9382,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C34" s="7" t="s">
         <v>217</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>218</v>
       </c>
       <c r="D34" s="6">
         <v>2</v>
@@ -8735,7 +9394,7 @@
         <v>58</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G34" s="7" t="s">
         <v>55</v>
@@ -8747,7 +9406,7 @@
         <v>56</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>142</v>
+        <v>256</v>
       </c>
       <c r="K34" s="7" t="s">
         <v>36</v>
@@ -8765,7 +9424,7 @@
         <v>47</v>
       </c>
       <c r="P34" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q34" s="7" t="s">
         <v>39</v>
@@ -8798,16 +9457,16 @@
         <v>39</v>
       </c>
       <c r="AA34" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB34" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC34" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="AB34" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC34" s="7" t="s">
-        <v>207</v>
-      </c>
       <c r="AD34" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE34" s="7" t="s">
         <v>39</v>
@@ -8819,7 +9478,7 @@
         <v>47</v>
       </c>
       <c r="AH34" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="35" spans="1:34" x14ac:dyDescent="0.3">
@@ -8827,10 +9486,10 @@
         <v>33</v>
       </c>
       <c r="B35" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C35" s="7" t="s">
         <v>217</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>218</v>
       </c>
       <c r="D35" s="6">
         <v>3</v>
@@ -8839,7 +9498,7 @@
         <v>58</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G35" s="7" t="s">
         <v>90</v>
@@ -8851,7 +9510,7 @@
         <v>91</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="K35" s="7" t="s">
         <v>36</v>
@@ -8869,7 +9528,7 @@
         <v>47</v>
       </c>
       <c r="P35" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q35" s="7" t="s">
         <v>39</v>
@@ -8887,7 +9546,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="6">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="W35" s="7" t="s">
         <v>50</v>
@@ -8902,16 +9561,16 @@
         <v>39</v>
       </c>
       <c r="AA35" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB35" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC35" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="AB35" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC35" s="7" t="s">
-        <v>207</v>
-      </c>
       <c r="AD35" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE35" s="7" t="s">
         <v>39</v>
@@ -8923,7 +9582,7 @@
         <v>47</v>
       </c>
       <c r="AH35" s="7" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
     </row>
     <row r="36" spans="1:34" x14ac:dyDescent="0.3">
@@ -8931,10 +9590,10 @@
         <v>33</v>
       </c>
       <c r="B36" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C36" s="7" t="s">
         <v>217</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>218</v>
       </c>
       <c r="D36" s="6">
         <v>4</v>
@@ -8943,19 +9602,19 @@
         <v>58</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G36" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="H36" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="H36" s="7" t="s">
+      <c r="I36" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="I36" s="7" t="s">
-        <v>224</v>
-      </c>
       <c r="J36" s="7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="K36" s="7" t="s">
         <v>36</v>
@@ -8973,7 +9632,7 @@
         <v>47</v>
       </c>
       <c r="P36" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q36" s="7" t="s">
         <v>39</v>
@@ -8991,7 +9650,7 @@
         <v>0</v>
       </c>
       <c r="V36" s="6">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="W36" s="7" t="s">
         <v>50</v>
@@ -9000,22 +9659,22 @@
         <v>49</v>
       </c>
       <c r="Y36" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Z36" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AA36" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB36" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC36" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="AB36" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC36" s="7" t="s">
-        <v>207</v>
-      </c>
       <c r="AD36" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE36" s="7" t="s">
         <v>39</v>
@@ -9027,7 +9686,7 @@
         <v>47</v>
       </c>
       <c r="AH36" s="7" t="s">
-        <v>238</v>
+        <v>260</v>
       </c>
     </row>
     <row r="37" spans="1:34" x14ac:dyDescent="0.3">
@@ -9035,10 +9694,10 @@
         <v>33</v>
       </c>
       <c r="B37" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C37" s="7" t="s">
         <v>217</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>218</v>
       </c>
       <c r="D37" s="6">
         <v>5</v>
@@ -9047,19 +9706,19 @@
         <v>58</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G37" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="H37" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="H37" s="7" t="s">
+      <c r="I37" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="I37" s="7" t="s">
-        <v>227</v>
-      </c>
       <c r="J37" s="7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="K37" s="7" t="s">
         <v>36</v>
@@ -9077,7 +9736,7 @@
         <v>47</v>
       </c>
       <c r="P37" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q37" s="7" t="s">
         <v>39</v>
@@ -9104,22 +9763,22 @@
         <v>49</v>
       </c>
       <c r="Y37" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Z37" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AA37" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB37" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="AC37" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="AB37" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="AC37" s="7" t="s">
-        <v>207</v>
-      </c>
       <c r="AD37" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE37" s="7" t="s">
         <v>39</v>
@@ -9131,7 +9790,7 @@
         <v>47</v>
       </c>
       <c r="AH37" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="38" spans="1:34" x14ac:dyDescent="0.3">
@@ -9139,10 +9798,10 @@
         <v>33</v>
       </c>
       <c r="B38" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C38" s="7" t="s">
         <v>217</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>218</v>
       </c>
       <c r="D38" s="6">
         <v>6</v>
@@ -9151,19 +9810,19 @@
         <v>58</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G38" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="H38" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="H38" s="7" t="s">
+      <c r="I38" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="I38" s="7" t="s">
-        <v>231</v>
-      </c>
       <c r="J38" s="7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="K38" s="7" t="s">
         <v>36</v>
@@ -9181,7 +9840,7 @@
         <v>47</v>
       </c>
       <c r="P38" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q38" s="7" t="s">
         <v>39</v>
@@ -9208,22 +9867,22 @@
         <v>49</v>
       </c>
       <c r="Y38" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Z38" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AA38" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB38" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC38" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="AB38" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC38" s="7" t="s">
-        <v>207</v>
-      </c>
       <c r="AD38" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE38" s="7" t="s">
         <v>39</v>
@@ -9235,18 +9894,18 @@
         <v>47</v>
       </c>
       <c r="AH38" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="39" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
-        <v>244</v>
+        <v>33</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D39" s="6">
         <v>1</v>
@@ -9255,7 +9914,7 @@
         <v>142</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G39" s="7" t="s">
         <v>144</v>
@@ -9267,7 +9926,7 @@
         <v>145</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>94</v>
+        <v>256</v>
       </c>
       <c r="K39" s="7" t="s">
         <v>36</v>
@@ -9285,7 +9944,7 @@
         <v>47</v>
       </c>
       <c r="P39" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q39" s="7" t="s">
         <v>39</v>
@@ -9294,16 +9953,16 @@
         <v>200000</v>
       </c>
       <c r="S39" s="6">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="T39" s="6">
-        <v>-200000</v>
+        <v>0</v>
       </c>
       <c r="U39" s="6">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="V39" s="6">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="W39" s="7" t="s">
         <v>50</v>
@@ -9318,16 +9977,16 @@
         <v>39</v>
       </c>
       <c r="AA39" s="7" t="s">
-        <v>247</v>
+        <v>205</v>
       </c>
       <c r="AB39" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AC39" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AD39" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE39" s="7" t="s">
         <v>39</v>
@@ -9339,18 +9998,18 @@
         <v>47</v>
       </c>
       <c r="AH39" s="7" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
     </row>
     <row r="40" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
-        <v>244</v>
+        <v>33</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D40" s="6">
         <v>2</v>
@@ -9359,7 +10018,7 @@
         <v>142</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G40" s="7" t="s">
         <v>55</v>
@@ -9371,7 +10030,7 @@
         <v>56</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>142</v>
+        <v>256</v>
       </c>
       <c r="K40" s="7" t="s">
         <v>36</v>
@@ -9389,7 +10048,7 @@
         <v>47</v>
       </c>
       <c r="P40" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q40" s="7" t="s">
         <v>39</v>
@@ -9398,16 +10057,16 @@
         <v>5000000</v>
       </c>
       <c r="S40" s="6">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="T40" s="6">
-        <v>-5000000</v>
+        <v>0</v>
       </c>
       <c r="U40" s="6">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="V40" s="6">
-        <v>0</v>
+        <v>1451000</v>
       </c>
       <c r="W40" s="7" t="s">
         <v>50</v>
@@ -9416,22 +10075,22 @@
         <v>49</v>
       </c>
       <c r="Y40" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Z40" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AA40" s="7" t="s">
-        <v>247</v>
+        <v>205</v>
       </c>
       <c r="AB40" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AC40" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AD40" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE40" s="7" t="s">
         <v>39</v>
@@ -9443,18 +10102,18 @@
         <v>47</v>
       </c>
       <c r="AH40" s="7" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
     </row>
     <row r="41" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
-        <v>244</v>
+        <v>33</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D41" s="6">
         <v>3</v>
@@ -9463,19 +10122,19 @@
         <v>142</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G41" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="I41" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="H41" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="I41" s="7" t="s">
-        <v>169</v>
-      </c>
       <c r="J41" s="7" t="s">
-        <v>74</v>
+        <v>256</v>
       </c>
       <c r="K41" s="7" t="s">
         <v>36</v>
@@ -9493,7 +10152,7 @@
         <v>47</v>
       </c>
       <c r="P41" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q41" s="7" t="s">
         <v>39</v>
@@ -9502,13 +10161,13 @@
         <v>1500000</v>
       </c>
       <c r="S41" s="6">
-        <v>0</v>
+        <v>1500000</v>
       </c>
       <c r="T41" s="6">
-        <v>-1500000</v>
+        <v>0</v>
       </c>
       <c r="U41" s="6">
-        <v>1500000</v>
+        <v>0</v>
       </c>
       <c r="V41" s="6">
         <v>0</v>
@@ -9526,16 +10185,16 @@
         <v>39</v>
       </c>
       <c r="AA41" s="7" t="s">
-        <v>247</v>
+        <v>205</v>
       </c>
       <c r="AB41" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AC41" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AD41" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE41" s="7" t="s">
         <v>39</v>
@@ -9547,18 +10206,18 @@
         <v>47</v>
       </c>
       <c r="AH41" s="7" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
     </row>
     <row r="42" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
-        <v>244</v>
+        <v>33</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D42" s="6">
         <v>4</v>
@@ -9567,19 +10226,19 @@
         <v>142</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="I42" s="7" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="K42" s="7" t="s">
         <v>36</v>
@@ -9597,7 +10256,7 @@
         <v>47</v>
       </c>
       <c r="P42" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q42" s="7" t="s">
         <v>39</v>
@@ -9606,13 +10265,13 @@
         <v>1000000</v>
       </c>
       <c r="S42" s="6">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="T42" s="6">
-        <v>-1000000</v>
+        <v>0</v>
       </c>
       <c r="U42" s="6">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="V42" s="6">
         <v>0</v>
@@ -9630,16 +10289,16 @@
         <v>39</v>
       </c>
       <c r="AA42" s="7" t="s">
-        <v>247</v>
+        <v>205</v>
       </c>
       <c r="AB42" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AC42" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AD42" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE42" s="7" t="s">
         <v>39</v>
@@ -9651,18 +10310,18 @@
         <v>47</v>
       </c>
       <c r="AH42" s="7" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
     </row>
     <row r="43" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
-        <v>244</v>
+        <v>33</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D43" s="6">
         <v>5</v>
@@ -9671,7 +10330,7 @@
         <v>142</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G43" s="7" t="s">
         <v>95</v>
@@ -9683,7 +10342,7 @@
         <v>96</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>93</v>
+        <v>256</v>
       </c>
       <c r="K43" s="7" t="s">
         <v>36</v>
@@ -9701,7 +10360,7 @@
         <v>47</v>
       </c>
       <c r="P43" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q43" s="7" t="s">
         <v>39</v>
@@ -9710,13 +10369,13 @@
         <v>300000</v>
       </c>
       <c r="S43" s="6">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="T43" s="6">
-        <v>-300000</v>
+        <v>0</v>
       </c>
       <c r="U43" s="6">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="V43" s="6">
         <v>0</v>
@@ -9728,22 +10387,22 @@
         <v>49</v>
       </c>
       <c r="Y43" s="8" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="Z43" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AA43" s="7" t="s">
-        <v>247</v>
+        <v>205</v>
       </c>
       <c r="AB43" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AC43" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AD43" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE43" s="7" t="s">
         <v>39</v>
@@ -9755,18 +10414,18 @@
         <v>47</v>
       </c>
       <c r="AH43" s="7" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
     </row>
     <row r="44" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
-        <v>244</v>
+        <v>33</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D44" s="6">
         <v>6</v>
@@ -9775,19 +10434,19 @@
         <v>142</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="I44" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="J44" s="7" t="s">
         <v>256</v>
-      </c>
-      <c r="J44" s="7" t="s">
-        <v>257</v>
       </c>
       <c r="K44" s="7" t="s">
         <v>36</v>
@@ -9805,7 +10464,7 @@
         <v>47</v>
       </c>
       <c r="P44" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q44" s="7" t="s">
         <v>39</v>
@@ -9814,13 +10473,13 @@
         <v>200000</v>
       </c>
       <c r="S44" s="6">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="T44" s="6">
-        <v>-200000</v>
+        <v>0</v>
       </c>
       <c r="U44" s="6">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="V44" s="6">
         <v>0</v>
@@ -9838,16 +10497,16 @@
         <v>39</v>
       </c>
       <c r="AA44" s="7" t="s">
-        <v>247</v>
+        <v>205</v>
       </c>
       <c r="AB44" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AC44" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AD44" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE44" s="7" t="s">
         <v>39</v>
@@ -9859,18 +10518,18 @@
         <v>47</v>
       </c>
       <c r="AH44" s="7" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
     </row>
     <row r="45" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
-        <v>244</v>
+        <v>33</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D45" s="6">
         <v>7</v>
@@ -9879,22 +10538,22 @@
         <v>142</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="K45" s="7" t="s">
-        <v>261</v>
+        <v>36</v>
       </c>
       <c r="L45" s="7" t="s">
         <v>48</v>
@@ -9909,7 +10568,7 @@
         <v>47</v>
       </c>
       <c r="P45" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q45" s="7" t="s">
         <v>39</v>
@@ -9918,13 +10577,13 @@
         <v>500000</v>
       </c>
       <c r="S45" s="6">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="T45" s="6">
-        <v>-500000</v>
+        <v>0</v>
       </c>
       <c r="U45" s="6">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="V45" s="6">
         <v>0</v>
@@ -9936,22 +10595,22 @@
         <v>49</v>
       </c>
       <c r="Y45" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Z45" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AA45" s="7" t="s">
-        <v>247</v>
+        <v>205</v>
       </c>
       <c r="AB45" s="7" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="AC45" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AD45" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AE45" s="7" t="s">
         <v>39</v>
@@ -9963,7 +10622,7 @@
         <v>47</v>
       </c>
       <c r="AH45" s="7" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>

--- a/리드지 발주현황.xlsx
+++ b/리드지 발주현황.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\유현아\Documents\GitHub\INTEROJO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9829B5D0-4985-4856-99ED-D1BDF6147E33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E88777FC-9933-405A-8624-96BF66FA8507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{500E376A-1243-49DE-9EFA-B2AD708B3011}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2595" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2667" uniqueCount="282">
   <si>
     <t>G/W</t>
   </si>
@@ -864,21 +864,12 @@
     <t>20260601P227-0128</t>
   </si>
   <si>
-    <t>2026-06-16 오후 2:58:30</t>
-  </si>
-  <si>
     <t>20260608P227-0115</t>
   </si>
   <si>
-    <t>2026-06-16 오후 2:57:56</t>
-  </si>
-  <si>
     <t>20260611P227-0019</t>
   </si>
   <si>
-    <t>2026-06-16 오후 2:58:45</t>
-  </si>
-  <si>
     <t>PR-2606160003</t>
   </si>
   <si>
@@ -888,13 +879,16 @@
     <t>2026-06-16</t>
   </si>
   <si>
-    <t>의뢰</t>
-  </si>
-  <si>
-    <t>2026-06-16 오전 10:55:32</t>
-  </si>
-  <si>
     <t>2026-06-24</t>
+  </si>
+  <si>
+    <t>2026-06-16 오후 4:59:12</t>
+  </si>
+  <si>
+    <t>2026-06-16 오후 4:27:33</t>
+  </si>
+  <si>
+    <t>PO-2606160005</t>
   </si>
 </sst>
 </file>
@@ -3157,13 +3151,13 @@
         <v>34</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>109</v>
+        <v>277</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>109</v>
+        <v>277</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>109</v>
+        <v>277</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>36</v>
@@ -3178,34 +3172,34 @@
         <v>39</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="M19" s="6">
         <v>500000</v>
       </c>
       <c r="N19" s="6">
+        <v>0</v>
+      </c>
+      <c r="O19" s="6">
         <v>500000</v>
       </c>
-      <c r="O19" s="6">
-        <v>0</v>
-      </c>
       <c r="P19" s="6">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="6">
         <v>0</v>
       </c>
       <c r="R19" s="6">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="S19" s="7" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="T19" s="7" t="s">
         <v>44</v>
@@ -3220,7 +3214,7 @@
         <v>4900000</v>
       </c>
       <c r="X19" s="8" t="s">
-        <v>72</v>
+        <v>278</v>
       </c>
       <c r="Y19" s="7" t="s">
         <v>47</v>
@@ -3238,16 +3232,16 @@
         <v>50</v>
       </c>
       <c r="AD19" s="7" t="s">
-        <v>83</v>
+        <v>280</v>
       </c>
       <c r="AE19" s="7" t="s">
-        <v>132</v>
+        <v>281</v>
       </c>
       <c r="AF19" s="7" t="s">
-        <v>137</v>
+        <v>275</v>
       </c>
       <c r="AG19" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.3">
@@ -3258,13 +3252,13 @@
         <v>34</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>213</v>
+        <v>109</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>213</v>
+        <v>109</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>36</v>
@@ -3279,34 +3273,34 @@
         <v>39</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>221</v>
+        <v>84</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>222</v>
+        <v>85</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>223</v>
+        <v>86</v>
       </c>
       <c r="M20" s="6">
-        <v>20000</v>
+        <v>500000</v>
       </c>
       <c r="N20" s="6">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="O20" s="6">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P20" s="6">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="Q20" s="6">
         <v>0</v>
       </c>
       <c r="R20" s="6">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="S20" s="7" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T20" s="7" t="s">
         <v>44</v>
@@ -3318,10 +3312,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W20" s="6">
-        <v>196000</v>
+        <v>4900000</v>
       </c>
       <c r="X20" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Y20" s="7" t="s">
         <v>47</v>
@@ -3339,16 +3333,16 @@
         <v>50</v>
       </c>
       <c r="AD20" s="7" t="s">
-        <v>217</v>
+        <v>83</v>
       </c>
       <c r="AE20" s="7" t="s">
-        <v>218</v>
+        <v>132</v>
       </c>
       <c r="AF20" s="7" t="s">
-        <v>219</v>
+        <v>137</v>
       </c>
       <c r="AG20" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.3">
@@ -3359,13 +3353,13 @@
         <v>34</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>35</v>
+        <v>213</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>35</v>
+        <v>128</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>35</v>
+        <v>213</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>36</v>
@@ -3380,34 +3374,34 @@
         <v>39</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>96</v>
+        <v>221</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>97</v>
+        <v>222</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>98</v>
+        <v>223</v>
       </c>
       <c r="M21" s="6">
-        <v>300000</v>
+        <v>20000</v>
       </c>
       <c r="N21" s="6">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="O21" s="6">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="P21" s="6">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="6">
         <v>0</v>
       </c>
       <c r="R21" s="6">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="S21" s="7" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="T21" s="7" t="s">
         <v>44</v>
@@ -3416,13 +3410,13 @@
         <v>45</v>
       </c>
       <c r="V21" s="6">
-        <v>8.5</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="W21" s="6">
-        <v>2550000</v>
+        <v>196000</v>
       </c>
       <c r="X21" s="8" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="Y21" s="7" t="s">
         <v>47</v>
@@ -3440,16 +3434,16 @@
         <v>50</v>
       </c>
       <c r="AD21" s="7" t="s">
-        <v>95</v>
+        <v>217</v>
       </c>
       <c r="AE21" s="7" t="s">
-        <v>52</v>
+        <v>218</v>
       </c>
       <c r="AF21" s="7" t="s">
-        <v>53</v>
+        <v>219</v>
       </c>
       <c r="AG21" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.3">
@@ -3460,13 +3454,13 @@
         <v>34</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>36</v>
@@ -3481,13 +3475,13 @@
         <v>39</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>146</v>
+        <v>96</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>147</v>
+        <v>97</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>148</v>
+        <v>98</v>
       </c>
       <c r="M22" s="6">
         <v>300000</v>
@@ -3517,13 +3511,13 @@
         <v>45</v>
       </c>
       <c r="V22" s="6">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W22" s="6">
-        <v>0</v>
+        <v>2550000</v>
       </c>
       <c r="X22" s="8" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="Y22" s="7" t="s">
         <v>47</v>
@@ -3541,16 +3535,16 @@
         <v>50</v>
       </c>
       <c r="AD22" s="7" t="s">
-        <v>194</v>
+        <v>95</v>
       </c>
       <c r="AE22" s="7" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="AF22" s="7" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="AG22" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.3">
@@ -3561,13 +3555,13 @@
         <v>34</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>209</v>
+        <v>54</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>209</v>
+        <v>46</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>209</v>
+        <v>46</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>36</v>
@@ -3582,34 +3576,34 @@
         <v>39</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>55</v>
+        <v>146</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>56</v>
+        <v>147</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>57</v>
+        <v>148</v>
       </c>
       <c r="M23" s="6">
-        <v>5000000</v>
+        <v>300000</v>
       </c>
       <c r="N23" s="6">
-        <v>2478000</v>
+        <v>300000</v>
       </c>
       <c r="O23" s="6">
-        <v>2522000</v>
+        <v>0</v>
       </c>
       <c r="P23" s="6">
-        <v>2478000</v>
+        <v>300000</v>
       </c>
       <c r="Q23" s="6">
         <v>0</v>
       </c>
       <c r="R23" s="6">
-        <v>2478000</v>
+        <v>300000</v>
       </c>
       <c r="S23" s="7" t="s">
-        <v>127</v>
+        <v>43</v>
       </c>
       <c r="T23" s="7" t="s">
         <v>44</v>
@@ -3618,13 +3612,13 @@
         <v>45</v>
       </c>
       <c r="V23" s="6">
-        <v>9.8000000000000007</v>
+        <v>0</v>
       </c>
       <c r="W23" s="6">
-        <v>49000000</v>
+        <v>0</v>
       </c>
       <c r="X23" s="8" t="s">
-        <v>168</v>
+        <v>58</v>
       </c>
       <c r="Y23" s="7" t="s">
         <v>47</v>
@@ -3642,16 +3636,16 @@
         <v>50</v>
       </c>
       <c r="AD23" s="7" t="s">
-        <v>229</v>
+        <v>194</v>
       </c>
       <c r="AE23" s="7" t="s">
-        <v>211</v>
+        <v>59</v>
       </c>
       <c r="AF23" s="7" t="s">
-        <v>196</v>
+        <v>60</v>
       </c>
       <c r="AG23" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.3">
@@ -3683,34 +3677,34 @@
         <v>39</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>204</v>
+        <v>55</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>206</v>
+        <v>56</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>205</v>
+        <v>57</v>
       </c>
       <c r="M24" s="6">
-        <v>500000</v>
+        <v>5000000</v>
       </c>
       <c r="N24" s="6">
-        <v>0</v>
+        <v>2478000</v>
       </c>
       <c r="O24" s="6">
-        <v>500000</v>
+        <v>2522000</v>
       </c>
       <c r="P24" s="6">
-        <v>0</v>
+        <v>2478000</v>
       </c>
       <c r="Q24" s="6">
         <v>0</v>
       </c>
       <c r="R24" s="6">
-        <v>0</v>
+        <v>2478000</v>
       </c>
       <c r="S24" s="7" t="s">
-        <v>65</v>
+        <v>127</v>
       </c>
       <c r="T24" s="7" t="s">
         <v>44</v>
@@ -3722,10 +3716,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W24" s="6">
-        <v>4900000</v>
+        <v>49000000</v>
       </c>
       <c r="X24" s="8" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="Y24" s="7" t="s">
         <v>47</v>
@@ -3737,13 +3731,13 @@
         <v>49</v>
       </c>
       <c r="AB24" s="7" t="s">
-        <v>207</v>
+        <v>39</v>
       </c>
       <c r="AC24" s="7" t="s">
         <v>50</v>
       </c>
       <c r="AD24" s="7" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="AE24" s="7" t="s">
         <v>211</v>
@@ -3752,7 +3746,7 @@
         <v>196</v>
       </c>
       <c r="AG24" s="6">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.3">
@@ -3763,13 +3757,13 @@
         <v>34</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>58</v>
+        <v>209</v>
       </c>
       <c r="F25" s="7" t="s">
         <v>36</v>
@@ -3784,34 +3778,34 @@
         <v>39</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>87</v>
+        <v>204</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>88</v>
+        <v>206</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>89</v>
+        <v>205</v>
       </c>
       <c r="M25" s="6">
-        <v>200000</v>
+        <v>500000</v>
       </c>
       <c r="N25" s="6">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="O25" s="6">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="P25" s="6">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="6">
         <v>0</v>
       </c>
       <c r="R25" s="6">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="S25" s="7" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="T25" s="7" t="s">
         <v>44</v>
@@ -3823,10 +3817,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W25" s="6">
-        <v>1960000</v>
+        <v>4900000</v>
       </c>
       <c r="X25" s="8" t="s">
-        <v>128</v>
+        <v>187</v>
       </c>
       <c r="Y25" s="7" t="s">
         <v>47</v>
@@ -3838,22 +3832,22 @@
         <v>49</v>
       </c>
       <c r="AB25" s="7" t="s">
-        <v>39</v>
+        <v>207</v>
       </c>
       <c r="AC25" s="7" t="s">
         <v>50</v>
       </c>
       <c r="AD25" s="7" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AE25" s="7" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="AF25" s="7" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="AG25" s="6">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:33" x14ac:dyDescent="0.3">
@@ -3864,13 +3858,13 @@
         <v>34</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>109</v>
+        <v>191</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>109</v>
+        <v>191</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>109</v>
+        <v>58</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>36</v>
@@ -3885,13 +3879,13 @@
         <v>39</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="M26" s="6">
         <v>200000</v>
@@ -3927,7 +3921,7 @@
         <v>1960000</v>
       </c>
       <c r="X26" s="8" t="s">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="Y26" s="7" t="s">
         <v>47</v>
@@ -3945,13 +3939,13 @@
         <v>50</v>
       </c>
       <c r="AD26" s="7" t="s">
-        <v>95</v>
+        <v>212</v>
       </c>
       <c r="AE26" s="7" t="s">
-        <v>132</v>
+        <v>193</v>
       </c>
       <c r="AF26" s="7" t="s">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="AG26" s="6">
         <v>3</v>
@@ -3965,13 +3959,13 @@
         <v>34</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>54</v>
+        <v>277</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>46</v>
+        <v>277</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>46</v>
+        <v>277</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>36</v>
@@ -3986,34 +3980,34 @@
         <v>39</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>149</v>
+        <v>180</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>150</v>
+        <v>182</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="M27" s="6">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="N27" s="6">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="O27" s="6">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="P27" s="6">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="Q27" s="6">
         <v>0</v>
       </c>
       <c r="R27" s="6">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="S27" s="7" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="T27" s="7" t="s">
         <v>44</v>
@@ -4022,13 +4016,13 @@
         <v>45</v>
       </c>
       <c r="V27" s="6">
-        <v>34</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="W27" s="6">
-        <v>6800000</v>
+        <v>19600000</v>
       </c>
       <c r="X27" s="8" t="s">
-        <v>152</v>
+        <v>119</v>
       </c>
       <c r="Y27" s="7" t="s">
         <v>47</v>
@@ -4046,16 +4040,16 @@
         <v>50</v>
       </c>
       <c r="AD27" s="7" t="s">
-        <v>208</v>
+        <v>280</v>
       </c>
       <c r="AE27" s="7" t="s">
-        <v>59</v>
+        <v>281</v>
       </c>
       <c r="AF27" s="7" t="s">
-        <v>60</v>
+        <v>275</v>
       </c>
       <c r="AG27" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.3">
@@ -4066,13 +4060,13 @@
         <v>34</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>213</v>
+        <v>109</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>213</v>
+        <v>109</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>36</v>
@@ -4087,31 +4081,31 @@
         <v>39</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>224</v>
+        <v>92</v>
       </c>
       <c r="K28" s="7" t="s">
-        <v>225</v>
+        <v>93</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>226</v>
+        <v>94</v>
       </c>
       <c r="M28" s="6">
-        <v>1500000</v>
+        <v>200000</v>
       </c>
       <c r="N28" s="6">
-        <v>1500000</v>
+        <v>200000</v>
       </c>
       <c r="O28" s="6">
         <v>0</v>
       </c>
       <c r="P28" s="6">
-        <v>528000</v>
+        <v>200000</v>
       </c>
       <c r="Q28" s="6">
         <v>0</v>
       </c>
       <c r="R28" s="6">
-        <v>528000</v>
+        <v>200000</v>
       </c>
       <c r="S28" s="7" t="s">
         <v>43</v>
@@ -4126,10 +4120,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W28" s="6">
-        <v>14700000</v>
+        <v>1960000</v>
       </c>
       <c r="X28" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Y28" s="7" t="s">
         <v>47</v>
@@ -4147,16 +4141,16 @@
         <v>50</v>
       </c>
       <c r="AD28" s="7" t="s">
-        <v>277</v>
+        <v>95</v>
       </c>
       <c r="AE28" s="7" t="s">
-        <v>218</v>
+        <v>132</v>
       </c>
       <c r="AF28" s="7" t="s">
-        <v>219</v>
+        <v>137</v>
       </c>
       <c r="AG28" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.3">
@@ -4167,13 +4161,13 @@
         <v>34</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>109</v>
+        <v>54</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>36</v>
@@ -4188,13 +4182,13 @@
         <v>39</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>87</v>
+        <v>149</v>
       </c>
       <c r="K29" s="7" t="s">
-        <v>88</v>
+        <v>150</v>
       </c>
       <c r="L29" s="7" t="s">
-        <v>89</v>
+        <v>151</v>
       </c>
       <c r="M29" s="6">
         <v>200000</v>
@@ -4224,13 +4218,13 @@
         <v>45</v>
       </c>
       <c r="V29" s="6">
-        <v>9.8000000000000007</v>
+        <v>34</v>
       </c>
       <c r="W29" s="6">
-        <v>1960000</v>
+        <v>6800000</v>
       </c>
       <c r="X29" s="8" t="s">
-        <v>72</v>
+        <v>152</v>
       </c>
       <c r="Y29" s="7" t="s">
         <v>47</v>
@@ -4248,16 +4242,16 @@
         <v>50</v>
       </c>
       <c r="AD29" s="7" t="s">
-        <v>83</v>
+        <v>208</v>
       </c>
       <c r="AE29" s="7" t="s">
-        <v>132</v>
+        <v>59</v>
       </c>
       <c r="AF29" s="7" t="s">
-        <v>137</v>
+        <v>60</v>
       </c>
       <c r="AG29" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.3">
@@ -4268,13 +4262,13 @@
         <v>34</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>61</v>
+        <v>213</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>61</v>
+        <v>128</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>61</v>
+        <v>213</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>36</v>
@@ -4289,31 +4283,31 @@
         <v>39</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>153</v>
+        <v>224</v>
       </c>
       <c r="K30" s="7" t="s">
-        <v>154</v>
+        <v>225</v>
       </c>
       <c r="L30" s="7" t="s">
-        <v>155</v>
+        <v>226</v>
       </c>
       <c r="M30" s="6">
-        <v>1000000</v>
+        <v>1500000</v>
       </c>
       <c r="N30" s="6">
-        <v>1000000</v>
+        <v>1500000</v>
       </c>
       <c r="O30" s="6">
         <v>0</v>
       </c>
       <c r="P30" s="6">
-        <v>1000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q30" s="6">
         <v>0</v>
       </c>
       <c r="R30" s="6">
-        <v>1000000</v>
+        <v>1500000</v>
       </c>
       <c r="S30" s="7" t="s">
         <v>43</v>
@@ -4328,10 +4322,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W30" s="6">
-        <v>9800000</v>
+        <v>14700000</v>
       </c>
       <c r="X30" s="8" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="Y30" s="7" t="s">
         <v>47</v>
@@ -4349,16 +4343,16 @@
         <v>50</v>
       </c>
       <c r="AD30" s="7" t="s">
-        <v>189</v>
+        <v>279</v>
       </c>
       <c r="AE30" s="7" t="s">
-        <v>67</v>
+        <v>218</v>
       </c>
       <c r="AF30" s="7" t="s">
-        <v>68</v>
+        <v>219</v>
       </c>
       <c r="AG30" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.3">
@@ -4369,13 +4363,13 @@
         <v>34</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>35</v>
+        <v>109</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>35</v>
+        <v>109</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>35</v>
+        <v>109</v>
       </c>
       <c r="F31" s="7" t="s">
         <v>36</v>
@@ -4390,31 +4384,31 @@
         <v>39</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="K31" s="7" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="L31" s="7" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="M31" s="6">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="N31" s="6">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="O31" s="6">
         <v>0</v>
       </c>
       <c r="P31" s="6">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="Q31" s="6">
         <v>0</v>
       </c>
       <c r="R31" s="6">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="S31" s="7" t="s">
         <v>43</v>
@@ -4426,13 +4420,13 @@
         <v>45</v>
       </c>
       <c r="V31" s="6">
-        <v>6.7</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="W31" s="6">
-        <v>13400000</v>
+        <v>1960000</v>
       </c>
       <c r="X31" s="8" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="Y31" s="7" t="s">
         <v>47</v>
@@ -4450,16 +4444,16 @@
         <v>50</v>
       </c>
       <c r="AD31" s="7" t="s">
-        <v>156</v>
+        <v>83</v>
       </c>
       <c r="AE31" s="7" t="s">
-        <v>52</v>
+        <v>132</v>
       </c>
       <c r="AF31" s="7" t="s">
-        <v>53</v>
+        <v>137</v>
       </c>
       <c r="AG31" s="6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.3">
@@ -4470,13 +4464,13 @@
         <v>34</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>191</v>
+        <v>61</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>191</v>
+        <v>61</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>36</v>
@@ -4491,34 +4485,34 @@
         <v>39</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="K32" s="7" t="s">
-        <v>186</v>
+        <v>154</v>
       </c>
       <c r="L32" s="7" t="s">
-        <v>185</v>
+        <v>155</v>
       </c>
       <c r="M32" s="6">
-        <v>300000</v>
+        <v>1000000</v>
       </c>
       <c r="N32" s="6">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="O32" s="6">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="P32" s="6">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="Q32" s="6">
         <v>0</v>
       </c>
       <c r="R32" s="6">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="S32" s="7" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T32" s="7" t="s">
         <v>44</v>
@@ -4530,10 +4524,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W32" s="6">
-        <v>2940000</v>
+        <v>9800000</v>
       </c>
       <c r="X32" s="8" t="s">
-        <v>187</v>
+        <v>72</v>
       </c>
       <c r="Y32" s="7" t="s">
         <v>47</v>
@@ -4551,16 +4545,16 @@
         <v>50</v>
       </c>
       <c r="AD32" s="7" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="AE32" s="7" t="s">
-        <v>193</v>
+        <v>67</v>
       </c>
       <c r="AF32" s="7" t="s">
-        <v>173</v>
+        <v>68</v>
       </c>
       <c r="AG32" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:33" x14ac:dyDescent="0.3">
@@ -4592,31 +4586,31 @@
         <v>39</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="L33" s="7" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="M33" s="6">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="N33" s="6">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="O33" s="6">
         <v>0</v>
       </c>
       <c r="P33" s="6">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="Q33" s="6">
         <v>0</v>
       </c>
       <c r="R33" s="6">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="S33" s="7" t="s">
         <v>43</v>
@@ -4628,10 +4622,10 @@
         <v>45</v>
       </c>
       <c r="V33" s="6">
-        <v>9.8000000000000007</v>
+        <v>6.7</v>
       </c>
       <c r="W33" s="6">
-        <v>1960000</v>
+        <v>13400000</v>
       </c>
       <c r="X33" s="8" t="s">
         <v>108</v>
@@ -4646,22 +4640,22 @@
         <v>49</v>
       </c>
       <c r="AB33" s="7" t="s">
-        <v>124</v>
+        <v>39</v>
       </c>
       <c r="AC33" s="7" t="s">
         <v>50</v>
       </c>
       <c r="AD33" s="7" t="s">
-        <v>107</v>
+        <v>156</v>
       </c>
       <c r="AE33" s="7" t="s">
         <v>52</v>
       </c>
       <c r="AF33" s="7" t="s">
-        <v>125</v>
+        <v>53</v>
       </c>
       <c r="AG33" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:33" x14ac:dyDescent="0.3">
@@ -4672,13 +4666,13 @@
         <v>34</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>54</v>
+        <v>191</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>46</v>
+        <v>191</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>36</v>
@@ -4693,34 +4687,34 @@
         <v>39</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="K34" s="7" t="s">
-        <v>158</v>
+        <v>186</v>
       </c>
       <c r="L34" s="7" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="M34" s="6">
         <v>300000</v>
       </c>
       <c r="N34" s="6">
+        <v>0</v>
+      </c>
+      <c r="O34" s="6">
         <v>300000</v>
       </c>
-      <c r="O34" s="6">
-        <v>0</v>
-      </c>
       <c r="P34" s="6">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="Q34" s="6">
         <v>0</v>
       </c>
       <c r="R34" s="6">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="S34" s="7" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="T34" s="7" t="s">
         <v>44</v>
@@ -4735,7 +4729,7 @@
         <v>2940000</v>
       </c>
       <c r="X34" s="8" t="s">
-        <v>58</v>
+        <v>187</v>
       </c>
       <c r="Y34" s="7" t="s">
         <v>47</v>
@@ -4753,16 +4747,16 @@
         <v>50</v>
       </c>
       <c r="AD34" s="7" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="AE34" s="7" t="s">
-        <v>59</v>
+        <v>193</v>
       </c>
       <c r="AF34" s="7" t="s">
-        <v>60</v>
+        <v>173</v>
       </c>
       <c r="AG34" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:33" x14ac:dyDescent="0.3">
@@ -4773,13 +4767,13 @@
         <v>34</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="F35" s="7" t="s">
         <v>36</v>
@@ -4794,34 +4788,34 @@
         <v>39</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="K35" s="7" t="s">
-        <v>161</v>
+        <v>111</v>
       </c>
       <c r="L35" s="7" t="s">
-        <v>162</v>
+        <v>112</v>
       </c>
       <c r="M35" s="6">
-        <v>1000000</v>
+        <v>200000</v>
       </c>
       <c r="N35" s="6">
-        <v>345000</v>
+        <v>200000</v>
       </c>
       <c r="O35" s="6">
-        <v>655000</v>
+        <v>0</v>
       </c>
       <c r="P35" s="6">
-        <v>345000</v>
+        <v>200000</v>
       </c>
       <c r="Q35" s="6">
         <v>0</v>
       </c>
       <c r="R35" s="6">
-        <v>345000</v>
+        <v>200000</v>
       </c>
       <c r="S35" s="7" t="s">
-        <v>127</v>
+        <v>43</v>
       </c>
       <c r="T35" s="7" t="s">
         <v>44</v>
@@ -4830,13 +4824,13 @@
         <v>45</v>
       </c>
       <c r="V35" s="6">
-        <v>7.7</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="W35" s="6">
-        <v>7700000</v>
+        <v>1960000</v>
       </c>
       <c r="X35" s="8" t="s">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="Y35" s="7" t="s">
         <v>47</v>
@@ -4848,19 +4842,19 @@
         <v>49</v>
       </c>
       <c r="AB35" s="7" t="s">
-        <v>39</v>
+        <v>124</v>
       </c>
       <c r="AC35" s="7" t="s">
         <v>50</v>
       </c>
       <c r="AD35" s="7" t="s">
-        <v>227</v>
+        <v>107</v>
       </c>
       <c r="AE35" s="7" t="s">
-        <v>163</v>
+        <v>52</v>
       </c>
       <c r="AF35" s="7" t="s">
-        <v>164</v>
+        <v>125</v>
       </c>
       <c r="AG35" s="6">
         <v>1</v>
@@ -4874,13 +4868,13 @@
         <v>34</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>36</v>
@@ -4895,31 +4889,31 @@
         <v>39</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="K36" s="7" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="L36" s="7" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="M36" s="6">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="N36" s="6">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="O36" s="6">
         <v>0</v>
       </c>
       <c r="P36" s="6">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="Q36" s="6">
         <v>0</v>
       </c>
       <c r="R36" s="6">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="S36" s="7" t="s">
         <v>43</v>
@@ -4934,10 +4928,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W36" s="6">
-        <v>4900000</v>
+        <v>2940000</v>
       </c>
       <c r="X36" s="8" t="s">
-        <v>168</v>
+        <v>58</v>
       </c>
       <c r="Y36" s="7" t="s">
         <v>47</v>
@@ -4955,16 +4949,16 @@
         <v>50</v>
       </c>
       <c r="AD36" s="7" t="s">
-        <v>228</v>
+        <v>188</v>
       </c>
       <c r="AE36" s="7" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="AF36" s="7" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="AG36" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:33" x14ac:dyDescent="0.3">
@@ -4975,13 +4969,13 @@
         <v>34</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="F37" s="7" t="s">
         <v>36</v>
@@ -4996,34 +4990,34 @@
         <v>39</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="K37" s="7" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="L37" s="7" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="M37" s="6">
-        <v>300000</v>
+        <v>1000000</v>
       </c>
       <c r="N37" s="6">
-        <v>300000</v>
+        <v>345000</v>
       </c>
       <c r="O37" s="6">
-        <v>0</v>
+        <v>655000</v>
       </c>
       <c r="P37" s="6">
-        <v>300000</v>
+        <v>345000</v>
       </c>
       <c r="Q37" s="6">
         <v>0</v>
       </c>
       <c r="R37" s="6">
-        <v>300000</v>
+        <v>345000</v>
       </c>
       <c r="S37" s="7" t="s">
-        <v>43</v>
+        <v>127</v>
       </c>
       <c r="T37" s="7" t="s">
         <v>44</v>
@@ -5032,13 +5026,13 @@
         <v>45</v>
       </c>
       <c r="V37" s="6">
-        <v>9.8000000000000007</v>
+        <v>7.7</v>
       </c>
       <c r="W37" s="6">
-        <v>2940000</v>
+        <v>7700000</v>
       </c>
       <c r="X37" s="8" t="s">
-        <v>126</v>
+        <v>72</v>
       </c>
       <c r="Y37" s="7" t="s">
         <v>47</v>
@@ -5056,13 +5050,13 @@
         <v>50</v>
       </c>
       <c r="AD37" s="7" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="AE37" s="7" t="s">
-        <v>122</v>
+        <v>163</v>
       </c>
       <c r="AF37" s="7" t="s">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="AG37" s="6">
         <v>1</v>
@@ -5076,13 +5070,13 @@
         <v>34</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>209</v>
+        <v>61</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>209</v>
+        <v>61</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>209</v>
+        <v>61</v>
       </c>
       <c r="F38" s="7" t="s">
         <v>36</v>
@@ -5097,34 +5091,34 @@
         <v>39</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>197</v>
+        <v>165</v>
       </c>
       <c r="K38" s="7" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="L38" s="7" t="s">
-        <v>198</v>
+        <v>167</v>
       </c>
       <c r="M38" s="6">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="N38" s="6">
-        <v>720000</v>
+        <v>500000</v>
       </c>
       <c r="O38" s="6">
-        <v>280000</v>
+        <v>0</v>
       </c>
       <c r="P38" s="6">
-        <v>240000</v>
+        <v>500000</v>
       </c>
       <c r="Q38" s="6">
         <v>0</v>
       </c>
       <c r="R38" s="6">
-        <v>240000</v>
+        <v>500000</v>
       </c>
       <c r="S38" s="7" t="s">
-        <v>127</v>
+        <v>43</v>
       </c>
       <c r="T38" s="7" t="s">
         <v>44</v>
@@ -5136,10 +5130,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W38" s="6">
-        <v>9800000</v>
+        <v>4900000</v>
       </c>
       <c r="X38" s="8" t="s">
-        <v>66</v>
+        <v>168</v>
       </c>
       <c r="Y38" s="7" t="s">
         <v>47</v>
@@ -5157,16 +5151,16 @@
         <v>50</v>
       </c>
       <c r="AD38" s="7" t="s">
-        <v>275</v>
+        <v>228</v>
       </c>
       <c r="AE38" s="7" t="s">
-        <v>211</v>
+        <v>67</v>
       </c>
       <c r="AF38" s="7" t="s">
-        <v>196</v>
+        <v>68</v>
       </c>
       <c r="AG38" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.3">
@@ -5177,13 +5171,13 @@
         <v>34</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>209</v>
+        <v>91</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>209</v>
+        <v>91</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>209</v>
+        <v>91</v>
       </c>
       <c r="F39" s="7" t="s">
         <v>36</v>
@@ -5198,31 +5192,31 @@
         <v>39</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>138</v>
+        <v>169</v>
       </c>
       <c r="K39" s="7" t="s">
-        <v>139</v>
+        <v>170</v>
       </c>
       <c r="L39" s="7" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="M39" s="6">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="N39" s="6">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="O39" s="6">
         <v>0</v>
       </c>
       <c r="P39" s="6">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="Q39" s="6">
         <v>0</v>
       </c>
       <c r="R39" s="6">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="S39" s="7" t="s">
         <v>43</v>
@@ -5237,10 +5231,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W39" s="6">
-        <v>1960000</v>
+        <v>2940000</v>
       </c>
       <c r="X39" s="8" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="Y39" s="7" t="s">
         <v>47</v>
@@ -5258,13 +5252,13 @@
         <v>50</v>
       </c>
       <c r="AD39" s="7" t="s">
-        <v>220</v>
+        <v>195</v>
       </c>
       <c r="AE39" s="7" t="s">
-        <v>211</v>
+        <v>122</v>
       </c>
       <c r="AF39" s="7" t="s">
-        <v>196</v>
+        <v>123</v>
       </c>
       <c r="AG39" s="6">
         <v>1</v>
@@ -5278,13 +5272,13 @@
         <v>34</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>35</v>
+        <v>209</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>35</v>
+        <v>209</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>35</v>
+        <v>209</v>
       </c>
       <c r="F40" s="7" t="s">
         <v>36</v>
@@ -5299,34 +5293,34 @@
         <v>39</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>40</v>
+        <v>197</v>
       </c>
       <c r="K40" s="7" t="s">
-        <v>41</v>
+        <v>199</v>
       </c>
       <c r="L40" s="7" t="s">
-        <v>42</v>
+        <v>198</v>
       </c>
       <c r="M40" s="6">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="N40" s="6">
-        <v>200000</v>
+        <v>720000</v>
       </c>
       <c r="O40" s="6">
-        <v>0</v>
+        <v>280000</v>
       </c>
       <c r="P40" s="6">
-        <v>200000</v>
+        <v>720000</v>
       </c>
       <c r="Q40" s="6">
         <v>0</v>
       </c>
       <c r="R40" s="6">
-        <v>200000</v>
+        <v>720000</v>
       </c>
       <c r="S40" s="7" t="s">
-        <v>43</v>
+        <v>127</v>
       </c>
       <c r="T40" s="7" t="s">
         <v>44</v>
@@ -5338,10 +5332,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W40" s="6">
-        <v>1960000</v>
+        <v>9800000</v>
       </c>
       <c r="X40" s="8" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="Y40" s="7" t="s">
         <v>47</v>
@@ -5359,16 +5353,16 @@
         <v>50</v>
       </c>
       <c r="AD40" s="7" t="s">
-        <v>51</v>
+        <v>279</v>
       </c>
       <c r="AE40" s="7" t="s">
-        <v>52</v>
+        <v>211</v>
       </c>
       <c r="AF40" s="7" t="s">
-        <v>53</v>
+        <v>196</v>
       </c>
       <c r="AG40" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:33" x14ac:dyDescent="0.3">
@@ -5379,13 +5373,13 @@
         <v>34</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>35</v>
+        <v>209</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>35</v>
+        <v>209</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>35</v>
+        <v>209</v>
       </c>
       <c r="F41" s="7" t="s">
         <v>36</v>
@@ -5400,13 +5394,13 @@
         <v>39</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="K41" s="7" t="s">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="L41" s="7" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="M41" s="6">
         <v>200000</v>
@@ -5442,7 +5436,7 @@
         <v>1960000</v>
       </c>
       <c r="X41" s="8" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="Y41" s="7" t="s">
         <v>47</v>
@@ -5454,22 +5448,22 @@
         <v>49</v>
       </c>
       <c r="AB41" s="7" t="s">
-        <v>124</v>
+        <v>39</v>
       </c>
       <c r="AC41" s="7" t="s">
         <v>50</v>
       </c>
       <c r="AD41" s="7" t="s">
-        <v>107</v>
+        <v>220</v>
       </c>
       <c r="AE41" s="7" t="s">
-        <v>52</v>
+        <v>211</v>
       </c>
       <c r="AF41" s="7" t="s">
-        <v>125</v>
+        <v>196</v>
       </c>
       <c r="AG41" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:33" x14ac:dyDescent="0.3">
@@ -5480,13 +5474,13 @@
         <v>34</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>54</v>
+        <v>277</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>46</v>
+        <v>277</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>46</v>
+        <v>277</v>
       </c>
       <c r="F42" s="7" t="s">
         <v>36</v>
@@ -5501,34 +5495,34 @@
         <v>39</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>55</v>
+        <v>153</v>
       </c>
       <c r="K42" s="7" t="s">
-        <v>56</v>
+        <v>154</v>
       </c>
       <c r="L42" s="7" t="s">
-        <v>57</v>
+        <v>155</v>
       </c>
       <c r="M42" s="6">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
       <c r="N42" s="6">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="O42" s="6">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="P42" s="6">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="Q42" s="6">
         <v>0</v>
       </c>
       <c r="R42" s="6">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="S42" s="7" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="T42" s="7" t="s">
         <v>44</v>
@@ -5540,10 +5534,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W42" s="6">
-        <v>19600000</v>
+        <v>9800000</v>
       </c>
       <c r="X42" s="8" t="s">
-        <v>58</v>
+        <v>278</v>
       </c>
       <c r="Y42" s="7" t="s">
         <v>47</v>
@@ -5561,13 +5555,13 @@
         <v>50</v>
       </c>
       <c r="AD42" s="7" t="s">
-        <v>51</v>
+        <v>280</v>
       </c>
       <c r="AE42" s="7" t="s">
-        <v>59</v>
+        <v>281</v>
       </c>
       <c r="AF42" s="7" t="s">
-        <v>60</v>
+        <v>275</v>
       </c>
       <c r="AG42" s="6">
         <v>3</v>
@@ -5581,13 +5575,13 @@
         <v>34</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="F43" s="7" t="s">
         <v>36</v>
@@ -5602,31 +5596,31 @@
         <v>39</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="K43" s="7" t="s">
-        <v>75</v>
+        <v>41</v>
       </c>
       <c r="L43" s="7" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="M43" s="6">
-        <v>500000</v>
+        <v>200000</v>
       </c>
       <c r="N43" s="6">
-        <v>500000</v>
+        <v>200000</v>
       </c>
       <c r="O43" s="6">
         <v>0</v>
       </c>
       <c r="P43" s="6">
-        <v>500000</v>
+        <v>200000</v>
       </c>
       <c r="Q43" s="6">
         <v>0</v>
       </c>
       <c r="R43" s="6">
-        <v>500000</v>
+        <v>200000</v>
       </c>
       <c r="S43" s="7" t="s">
         <v>43</v>
@@ -5641,10 +5635,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W43" s="6">
-        <v>4900000</v>
+        <v>1960000</v>
       </c>
       <c r="X43" s="8" t="s">
-        <v>126</v>
+        <v>46</v>
       </c>
       <c r="Y43" s="7" t="s">
         <v>47</v>
@@ -5662,16 +5656,16 @@
         <v>50</v>
       </c>
       <c r="AD43" s="7" t="s">
-        <v>172</v>
+        <v>51</v>
       </c>
       <c r="AE43" s="7" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="AF43" s="7" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="AG43" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:33" x14ac:dyDescent="0.3">
@@ -5682,13 +5676,13 @@
         <v>34</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="F44" s="7" t="s">
         <v>36</v>
@@ -5703,13 +5697,13 @@
         <v>39</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>62</v>
+        <v>113</v>
       </c>
       <c r="K44" s="7" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="L44" s="7" t="s">
-        <v>64</v>
+        <v>115</v>
       </c>
       <c r="M44" s="6">
         <v>200000</v>
@@ -5745,7 +5739,7 @@
         <v>1960000</v>
       </c>
       <c r="X44" s="8" t="s">
-        <v>66</v>
+        <v>108</v>
       </c>
       <c r="Y44" s="7" t="s">
         <v>47</v>
@@ -5757,22 +5751,22 @@
         <v>49</v>
       </c>
       <c r="AB44" s="7" t="s">
-        <v>39</v>
+        <v>124</v>
       </c>
       <c r="AC44" s="7" t="s">
         <v>50</v>
       </c>
       <c r="AD44" s="7" t="s">
-        <v>229</v>
+        <v>107</v>
       </c>
       <c r="AE44" s="7" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="AF44" s="7" t="s">
-        <v>68</v>
+        <v>125</v>
       </c>
       <c r="AG44" s="6">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:33" x14ac:dyDescent="0.3">
@@ -5783,13 +5777,13 @@
         <v>34</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>91</v>
+        <v>46</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>91</v>
+        <v>46</v>
       </c>
       <c r="F45" s="7" t="s">
         <v>36</v>
@@ -5846,7 +5840,7 @@
         <v>19600000</v>
       </c>
       <c r="X45" s="8" t="s">
-        <v>128</v>
+        <v>58</v>
       </c>
       <c r="Y45" s="7" t="s">
         <v>47</v>
@@ -5864,13 +5858,13 @@
         <v>50</v>
       </c>
       <c r="AD45" s="7" t="s">
-        <v>229</v>
+        <v>51</v>
       </c>
       <c r="AE45" s="7" t="s">
-        <v>122</v>
+        <v>59</v>
       </c>
       <c r="AF45" s="7" t="s">
-        <v>123</v>
+        <v>60</v>
       </c>
       <c r="AG45" s="6">
         <v>3</v>
@@ -5884,13 +5878,13 @@
         <v>34</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="F46" s="7" t="s">
         <v>36</v>
@@ -5905,34 +5899,34 @@
         <v>39</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
       <c r="K46" s="7" t="s">
-        <v>117</v>
+        <v>75</v>
       </c>
       <c r="L46" s="7" t="s">
-        <v>118</v>
+        <v>76</v>
       </c>
       <c r="M46" s="6">
-        <v>8000000</v>
+        <v>500000</v>
       </c>
       <c r="N46" s="6">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="O46" s="6">
-        <v>8000000</v>
+        <v>0</v>
       </c>
       <c r="P46" s="6">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="Q46" s="6">
         <v>0</v>
       </c>
       <c r="R46" s="6">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="S46" s="7" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T46" s="7" t="s">
         <v>44</v>
@@ -5944,10 +5938,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W46" s="6">
-        <v>78400000</v>
+        <v>4900000</v>
       </c>
       <c r="X46" s="8" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="Y46" s="7" t="s">
         <v>47</v>
@@ -5959,22 +5953,22 @@
         <v>49</v>
       </c>
       <c r="AB46" s="7" t="s">
-        <v>120</v>
+        <v>39</v>
       </c>
       <c r="AC46" s="7" t="s">
         <v>50</v>
       </c>
       <c r="AD46" s="7" t="s">
-        <v>121</v>
+        <v>172</v>
       </c>
       <c r="AE46" s="7" t="s">
-        <v>122</v>
+        <v>67</v>
       </c>
       <c r="AF46" s="7" t="s">
-        <v>123</v>
+        <v>68</v>
       </c>
       <c r="AG46" s="6">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:33" x14ac:dyDescent="0.3">
@@ -5985,13 +5979,13 @@
         <v>34</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>191</v>
+        <v>61</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>191</v>
+        <v>61</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F47" s="7" t="s">
         <v>36</v>
@@ -6006,31 +6000,31 @@
         <v>39</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="K47" s="7" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="L47" s="7" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="M47" s="6">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="N47" s="6">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="O47" s="6">
         <v>0</v>
       </c>
       <c r="P47" s="6">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="Q47" s="6">
         <v>0</v>
       </c>
       <c r="R47" s="6">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="S47" s="7" t="s">
         <v>43</v>
@@ -6045,10 +6039,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W47" s="6">
-        <v>19600000</v>
+        <v>1960000</v>
       </c>
       <c r="X47" s="8" t="s">
-        <v>128</v>
+        <v>66</v>
       </c>
       <c r="Y47" s="7" t="s">
         <v>47</v>
@@ -6066,16 +6060,16 @@
         <v>50</v>
       </c>
       <c r="AD47" s="7" t="s">
-        <v>194</v>
+        <v>229</v>
       </c>
       <c r="AE47" s="7" t="s">
-        <v>193</v>
+        <v>67</v>
       </c>
       <c r="AF47" s="7" t="s">
-        <v>173</v>
+        <v>68</v>
       </c>
       <c r="AG47" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:33" x14ac:dyDescent="0.3">
@@ -6086,13 +6080,13 @@
         <v>34</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>191</v>
+        <v>91</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>191</v>
+        <v>91</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="F48" s="7" t="s">
         <v>36</v>
@@ -6107,34 +6101,34 @@
         <v>39</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>180</v>
+        <v>55</v>
       </c>
       <c r="K48" s="7" t="s">
-        <v>182</v>
+        <v>56</v>
       </c>
       <c r="L48" s="7" t="s">
-        <v>181</v>
+        <v>57</v>
       </c>
       <c r="M48" s="6">
-        <v>3000000</v>
+        <v>2000000</v>
       </c>
       <c r="N48" s="6">
-        <v>2036000</v>
+        <v>2000000</v>
       </c>
       <c r="O48" s="6">
-        <v>964000</v>
+        <v>0</v>
       </c>
       <c r="P48" s="6">
-        <v>1464000</v>
+        <v>2000000</v>
       </c>
       <c r="Q48" s="6">
         <v>0</v>
       </c>
       <c r="R48" s="6">
-        <v>1464000</v>
+        <v>2000000</v>
       </c>
       <c r="S48" s="7" t="s">
-        <v>127</v>
+        <v>43</v>
       </c>
       <c r="T48" s="7" t="s">
         <v>44</v>
@@ -6146,10 +6140,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W48" s="6">
-        <v>29400000</v>
+        <v>19600000</v>
       </c>
       <c r="X48" s="8" t="s">
-        <v>168</v>
+        <v>128</v>
       </c>
       <c r="Y48" s="7" t="s">
         <v>47</v>
@@ -6161,115 +6155,400 @@
         <v>49</v>
       </c>
       <c r="AB48" s="7" t="s">
-        <v>183</v>
+        <v>39</v>
       </c>
       <c r="AC48" s="7" t="s">
         <v>50</v>
       </c>
       <c r="AD48" s="7" t="s">
-        <v>273</v>
+        <v>229</v>
       </c>
       <c r="AE48" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="AF48" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="AG48" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A49" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="I49" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="J49" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="K49" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="L49" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="M49" s="6">
+        <v>8000000</v>
+      </c>
+      <c r="N49" s="6">
+        <v>0</v>
+      </c>
+      <c r="O49" s="6">
+        <v>8000000</v>
+      </c>
+      <c r="P49" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="6">
+        <v>0</v>
+      </c>
+      <c r="R49" s="6">
+        <v>0</v>
+      </c>
+      <c r="S49" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="T49" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="U49" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="V49" s="6">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="W49" s="6">
+        <v>78400000</v>
+      </c>
+      <c r="X49" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y49" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z49" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA49" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB49" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="AC49" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD49" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE49" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="AF49" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="AG49" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A50" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H50" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="I50" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="J50" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="K50" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="L50" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="M50" s="6">
+        <v>2000000</v>
+      </c>
+      <c r="N50" s="6">
+        <v>2000000</v>
+      </c>
+      <c r="O50" s="6">
+        <v>0</v>
+      </c>
+      <c r="P50" s="6">
+        <v>2000000</v>
+      </c>
+      <c r="Q50" s="6">
+        <v>0</v>
+      </c>
+      <c r="R50" s="6">
+        <v>2000000</v>
+      </c>
+      <c r="S50" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="T50" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="U50" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="V50" s="6">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="W50" s="6">
+        <v>19600000</v>
+      </c>
+      <c r="X50" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y50" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z50" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA50" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB50" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC50" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD50" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="AE50" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="AF48" s="7" t="s">
+      <c r="AF50" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="AG48" s="6">
+      <c r="AG50" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A51" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H51" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="I51" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="J51" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="K51" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="L51" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="M51" s="6">
+        <v>3000000</v>
+      </c>
+      <c r="N51" s="6">
+        <v>2036000</v>
+      </c>
+      <c r="O51" s="6">
+        <v>964000</v>
+      </c>
+      <c r="P51" s="6">
+        <v>2036000</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>0</v>
+      </c>
+      <c r="R51" s="6">
+        <v>2036000</v>
+      </c>
+      <c r="S51" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="T51" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="U51" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="V51" s="6">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="W51" s="6">
+        <v>29400000</v>
+      </c>
+      <c r="X51" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y51" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z51" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA51" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB51" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="AC51" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD51" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="AE51" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="AF51" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="AG51" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.3">
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="X49" s="2"/>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.3">
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="X50" s="2"/>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.3">
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="X51" s="2"/>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:33" x14ac:dyDescent="0.3">
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
       <c r="X52" s="2"/>
     </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:33" x14ac:dyDescent="0.3">
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>
       <c r="X53" s="2"/>
     </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:33" x14ac:dyDescent="0.3">
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
       <c r="E54" s="2"/>
       <c r="X54" s="2"/>
     </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:33" x14ac:dyDescent="0.3">
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
       <c r="E55" s="2"/>
       <c r="X55" s="2"/>
     </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:33" x14ac:dyDescent="0.3">
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
       <c r="E56" s="2"/>
       <c r="X56" s="2"/>
     </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:33" x14ac:dyDescent="0.3">
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
       <c r="X57" s="2"/>
     </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:33" x14ac:dyDescent="0.3">
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
       <c r="X58" s="2"/>
     </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:33" x14ac:dyDescent="0.3">
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
       <c r="E59" s="2"/>
       <c r="X59" s="2"/>
     </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:33" x14ac:dyDescent="0.3">
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
       <c r="E60" s="2"/>
       <c r="X60" s="2"/>
     </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:33" x14ac:dyDescent="0.3">
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
       <c r="E61" s="2"/>
       <c r="X61" s="2"/>
     </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:33" x14ac:dyDescent="0.3">
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
       <c r="E62" s="2"/>
       <c r="X62" s="2"/>
     </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:33" x14ac:dyDescent="0.3">
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
       <c r="E63" s="2"/>
       <c r="X63" s="2"/>
     </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:33" x14ac:dyDescent="0.3">
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
       <c r="E64" s="2"/>
@@ -8304,7 +8583,7 @@
         <v>154</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>191</v>
+        <v>277</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>36</v>
@@ -8408,7 +8687,7 @@
         <v>75</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>58</v>
+        <v>277</v>
       </c>
       <c r="K21" s="4" t="s">
         <v>36</v>
@@ -10072,7 +10351,7 @@
         <v>182</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>191</v>
+        <v>277</v>
       </c>
       <c r="K37" s="4" t="s">
         <v>36</v>
@@ -10108,7 +10387,7 @@
         <v>0</v>
       </c>
       <c r="V37" s="3">
-        <v>1464000</v>
+        <v>2036000</v>
       </c>
       <c r="W37" s="4" t="s">
         <v>50</v>
@@ -10144,7 +10423,7 @@
         <v>47</v>
       </c>
       <c r="AH37" s="4" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="38" spans="1:34" x14ac:dyDescent="0.3">
@@ -10259,7 +10538,7 @@
         <v>196</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D39" s="3">
         <v>1</v>
@@ -10363,7 +10642,7 @@
         <v>196</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D40" s="3">
         <v>2</v>
@@ -10467,7 +10746,7 @@
         <v>196</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D41" s="3">
         <v>3</v>
@@ -10571,7 +10850,7 @@
         <v>196</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D42" s="3">
         <v>4</v>
@@ -10628,7 +10907,7 @@
         <v>0</v>
       </c>
       <c r="V42" s="3">
-        <v>240000</v>
+        <v>720000</v>
       </c>
       <c r="W42" s="4" t="s">
         <v>50</v>
@@ -10664,7 +10943,7 @@
         <v>47</v>
       </c>
       <c r="AH42" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="43" spans="1:34" x14ac:dyDescent="0.3">
@@ -10675,7 +10954,7 @@
         <v>196</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D43" s="3">
         <v>5</v>
@@ -10779,7 +11058,7 @@
         <v>196</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D44" s="3">
         <v>6</v>
@@ -10883,7 +11162,7 @@
         <v>196</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D45" s="3">
         <v>7</v>
@@ -10987,7 +11266,7 @@
         <v>219</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D46" s="3">
         <v>1</v>
@@ -11044,7 +11323,7 @@
         <v>0</v>
       </c>
       <c r="V46" s="3">
-        <v>528000</v>
+        <v>1500000</v>
       </c>
       <c r="W46" s="4" t="s">
         <v>50</v>
@@ -11080,7 +11359,7 @@
         <v>47</v>
       </c>
       <c r="AH46" s="4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="47" spans="1:34" x14ac:dyDescent="0.3">
@@ -11091,7 +11370,7 @@
         <v>219</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D47" s="3">
         <v>2</v>
@@ -11195,7 +11474,7 @@
         <v>219</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D48" s="3">
         <v>3</v>
@@ -11296,16 +11575,16 @@
         <v>33</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D49" s="3">
         <v>1</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>254</v>
@@ -11320,7 +11599,7 @@
         <v>182</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>191</v>
+        <v>277</v>
       </c>
       <c r="K49" s="4" t="s">
         <v>36</v>
@@ -11347,13 +11626,13 @@
         <v>2000000</v>
       </c>
       <c r="S49" s="3">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="T49" s="3">
-        <v>-2000000</v>
+        <v>0</v>
       </c>
       <c r="U49" s="3">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
@@ -11371,7 +11650,7 @@
         <v>39</v>
       </c>
       <c r="AA49" s="4" t="s">
-        <v>281</v>
+        <v>256</v>
       </c>
       <c r="AB49" s="4" t="s">
         <v>39</v>
@@ -11392,7 +11671,7 @@
         <v>47</v>
       </c>
       <c r="AH49" s="4" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="50" spans="1:34" x14ac:dyDescent="0.3">
@@ -11400,16 +11679,16 @@
         <v>33</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D50" s="3">
         <v>2</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>254</v>
@@ -11424,7 +11703,7 @@
         <v>75</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>58</v>
+        <v>277</v>
       </c>
       <c r="K50" s="4" t="s">
         <v>36</v>
@@ -11451,13 +11730,13 @@
         <v>500000</v>
       </c>
       <c r="S50" s="3">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="T50" s="3">
-        <v>-500000</v>
+        <v>0</v>
       </c>
       <c r="U50" s="3">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="V50" s="3">
         <v>0</v>
@@ -11469,13 +11748,13 @@
         <v>49</v>
       </c>
       <c r="Y50" s="5" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="Z50" s="4" t="s">
         <v>39</v>
       </c>
       <c r="AA50" s="4" t="s">
-        <v>281</v>
+        <v>256</v>
       </c>
       <c r="AB50" s="4" t="s">
         <v>39</v>
@@ -11496,7 +11775,7 @@
         <v>47</v>
       </c>
       <c r="AH50" s="4" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="51" spans="1:34" x14ac:dyDescent="0.3">
@@ -11504,16 +11783,16 @@
         <v>33</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D51" s="3">
         <v>3</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>254</v>
@@ -11528,7 +11807,7 @@
         <v>154</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>191</v>
+        <v>277</v>
       </c>
       <c r="K51" s="4" t="s">
         <v>36</v>
@@ -11555,13 +11834,13 @@
         <v>1000000</v>
       </c>
       <c r="S51" s="3">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="T51" s="3">
-        <v>-1000000</v>
+        <v>0</v>
       </c>
       <c r="U51" s="3">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="V51" s="3">
         <v>0</v>
@@ -11573,13 +11852,13 @@
         <v>49</v>
       </c>
       <c r="Y51" s="5" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="Z51" s="4" t="s">
         <v>39</v>
       </c>
       <c r="AA51" s="4" t="s">
-        <v>281</v>
+        <v>256</v>
       </c>
       <c r="AB51" s="4" t="s">
         <v>39</v>
@@ -11600,7 +11879,7 @@
         <v>47</v>
       </c>
       <c r="AH51" s="4" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>

--- a/리드지 발주현황.xlsx
+++ b/리드지 발주현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\유현아\Documents\GitHub\INTEROJO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BC1245D-5CE3-4141-BB4A-743C79F932A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E66EF61-4A8B-4872-921A-EEE79E064E15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{500E376A-1243-49DE-9EFA-B2AD708B3011}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{500E376A-1243-49DE-9EFA-B2AD708B3011}"/>
   </bookViews>
   <sheets>
     <sheet name="구매발주현황" sheetId="1" r:id="rId1"/>
@@ -405,9 +405,6 @@
     <t>PIA 신제품 축고정 15.0</t>
   </si>
   <si>
-    <t>2026-05-26 오후 4:11:27</t>
-  </si>
-  <si>
     <t>PO-2605260009</t>
   </si>
   <si>
@@ -849,9 +846,6 @@
     <t>20260526P227-0018</t>
   </si>
   <si>
-    <t>2026-05-26 오후 4:11:28</t>
-  </si>
-  <si>
     <t>20260529P227-0012</t>
   </si>
   <si>
@@ -885,10 +879,16 @@
     <t>PO-2606160005</t>
   </si>
   <si>
-    <t>2026-06-17 오후 5:59:14</t>
-  </si>
-  <si>
     <t>2026-06-17 오후 5:59:48</t>
+  </si>
+  <si>
+    <t>2026-06-18 오후 5:06:56</t>
+  </si>
+  <si>
+    <t>2026-06-18 오전 9:16:17</t>
+  </si>
+  <si>
+    <t>2026-06-18 오후 3:55:55</t>
   </si>
 </sst>
 </file>
@@ -1455,34 +1455,34 @@
         <v>39</v>
       </c>
       <c r="J2" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>129</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>130</v>
       </c>
       <c r="M2" s="3">
         <v>2000000</v>
       </c>
       <c r="N2" s="3">
-        <v>0</v>
+        <v>351000</v>
       </c>
       <c r="O2" s="3">
-        <v>2000000</v>
+        <v>1649000</v>
       </c>
       <c r="P2" s="3">
-        <v>0</v>
+        <v>351000</v>
       </c>
       <c r="Q2" s="3">
         <v>0</v>
       </c>
       <c r="R2" s="3">
-        <v>0</v>
+        <v>351000</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>65</v>
+        <v>125</v>
       </c>
       <c r="T2" s="4" t="s">
         <v>44</v>
@@ -1515,13 +1515,13 @@
         <v>50</v>
       </c>
       <c r="AD2" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="AE2" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="AE2" s="4" t="s">
+      <c r="AF2" s="4" t="s">
         <v>121</v>
-      </c>
-      <c r="AF2" s="4" t="s">
-        <v>122</v>
       </c>
       <c r="AG2" s="3">
         <v>5</v>
@@ -1610,7 +1610,7 @@
         <v>49</v>
       </c>
       <c r="AB3" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AC3" s="4" t="s">
         <v>50</v>
@@ -1622,7 +1622,7 @@
         <v>52</v>
       </c>
       <c r="AF3" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG3" s="3">
         <v>2</v>
@@ -1636,13 +1636,13 @@
         <v>34</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>36</v>
@@ -1657,14 +1657,14 @@
         <v>39</v>
       </c>
       <c r="J4" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="K4" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="L4" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="L4" s="4" t="s">
-        <v>214</v>
-      </c>
       <c r="M4" s="3">
         <v>200000</v>
       </c>
@@ -1675,13 +1675,13 @@
         <v>0</v>
       </c>
       <c r="P4" s="3">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="Q4" s="3">
         <v>0</v>
       </c>
       <c r="R4" s="3">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="S4" s="4" t="s">
         <v>43</v>
@@ -1699,7 +1699,7 @@
         <v>1960000</v>
       </c>
       <c r="X4" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Y4" s="4" t="s">
         <v>47</v>
@@ -1720,10 +1720,10 @@
         <v>280</v>
       </c>
       <c r="AE4" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="AF4" s="4" t="s">
         <v>216</v>
-      </c>
-      <c r="AF4" s="4" t="s">
-        <v>217</v>
       </c>
       <c r="AG4" s="3">
         <v>3</v>
@@ -1859,13 +1859,13 @@
         <v>39</v>
       </c>
       <c r="J6" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="K6" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="L6" s="4" t="s">
         <v>133</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>134</v>
       </c>
       <c r="M6" s="3">
         <v>200000</v>
@@ -1901,7 +1901,7 @@
         <v>6800000</v>
       </c>
       <c r="X6" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y6" s="4" t="s">
         <v>47</v>
@@ -1919,7 +1919,7 @@
         <v>50</v>
       </c>
       <c r="AD6" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AE6" s="4" t="s">
         <v>67</v>
@@ -2002,7 +2002,7 @@
         <v>1960000</v>
       </c>
       <c r="X7" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Y7" s="4" t="s">
         <v>47</v>
@@ -2020,13 +2020,13 @@
         <v>50</v>
       </c>
       <c r="AD7" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AE7" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="AF7" s="4" t="s">
         <v>121</v>
-      </c>
-      <c r="AF7" s="4" t="s">
-        <v>122</v>
       </c>
       <c r="AG7" s="3">
         <v>2</v>
@@ -2040,13 +2040,13 @@
         <v>34</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>36</v>
@@ -2061,13 +2061,13 @@
         <v>39</v>
       </c>
       <c r="J8" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="K8" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="L8" s="4" t="s">
         <v>160</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>161</v>
       </c>
       <c r="M8" s="3">
         <v>1500000</v>
@@ -2121,13 +2121,13 @@
         <v>50</v>
       </c>
       <c r="AD8" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="AE8" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="AE8" s="4" t="s">
-        <v>209</v>
-      </c>
       <c r="AF8" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG8" s="3">
         <v>3</v>
@@ -2141,13 +2141,13 @@
         <v>34</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>36</v>
@@ -2162,13 +2162,13 @@
         <v>39</v>
       </c>
       <c r="J9" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="L9" s="4" t="s">
         <v>199</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>200</v>
       </c>
       <c r="M9" s="3">
         <v>200000</v>
@@ -2222,13 +2222,13 @@
         <v>50</v>
       </c>
       <c r="AD9" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="AE9" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="AE9" s="4" t="s">
-        <v>209</v>
-      </c>
       <c r="AF9" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG9" s="3">
         <v>6</v>
@@ -2263,34 +2263,34 @@
         <v>39</v>
       </c>
       <c r="J10" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="K10" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="L10" s="4" t="s">
         <v>129</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>130</v>
       </c>
       <c r="M10" s="3">
         <v>2000000</v>
       </c>
       <c r="N10" s="3">
-        <v>1874000</v>
+        <v>2000000</v>
       </c>
       <c r="O10" s="3">
-        <v>126000</v>
+        <v>0</v>
       </c>
       <c r="P10" s="3">
-        <v>1874000</v>
+        <v>2000000</v>
       </c>
       <c r="Q10" s="3">
         <v>0</v>
       </c>
       <c r="R10" s="3">
-        <v>1874000</v>
+        <v>2000000</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>126</v>
+        <v>43</v>
       </c>
       <c r="T10" s="4" t="s">
         <v>44</v>
@@ -2323,13 +2323,13 @@
         <v>50</v>
       </c>
       <c r="AD10" s="4" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="AE10" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AF10" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AG10" s="3">
         <v>2</v>
@@ -2427,10 +2427,10 @@
         <v>83</v>
       </c>
       <c r="AE11" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AF11" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AG11" s="3">
         <v>5</v>
@@ -2566,13 +2566,13 @@
         <v>39</v>
       </c>
       <c r="J13" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="K13" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="L13" s="4" t="s">
         <v>138</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>139</v>
       </c>
       <c r="M13" s="3">
         <v>300000</v>
@@ -2620,19 +2620,19 @@
         <v>49</v>
       </c>
       <c r="AB13" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AC13" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD13" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AE13" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="AF13" s="4" t="s">
         <v>121</v>
-      </c>
-      <c r="AF13" s="4" t="s">
-        <v>122</v>
       </c>
       <c r="AG13" s="3">
         <v>7</v>
@@ -2646,13 +2646,13 @@
         <v>34</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>36</v>
@@ -2709,7 +2709,7 @@
         <v>2940000</v>
       </c>
       <c r="X14" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Y14" s="4" t="s">
         <v>47</v>
@@ -2727,13 +2727,13 @@
         <v>50</v>
       </c>
       <c r="AD14" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="AE14" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="AE14" s="4" t="s">
-        <v>209</v>
-      </c>
       <c r="AF14" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG14" s="3">
         <v>5</v>
@@ -2747,10 +2747,10 @@
         <v>34</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>58</v>
@@ -2768,13 +2768,13 @@
         <v>39</v>
       </c>
       <c r="J15" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="L15" s="4" t="s">
         <v>173</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="L15" s="4" t="s">
-        <v>174</v>
       </c>
       <c r="M15" s="3">
         <v>200000</v>
@@ -2810,7 +2810,7 @@
         <v>1960000</v>
       </c>
       <c r="X15" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Y15" s="4" t="s">
         <v>47</v>
@@ -2828,13 +2828,13 @@
         <v>50</v>
       </c>
       <c r="AD15" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AE15" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AF15" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG15" s="3">
         <v>1</v>
@@ -2929,13 +2929,13 @@
         <v>50</v>
       </c>
       <c r="AD16" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AE16" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AF16" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AG16" s="3">
         <v>1</v>
@@ -2970,13 +2970,13 @@
         <v>39</v>
       </c>
       <c r="J17" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="K17" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="K17" s="4" t="s">
+      <c r="L17" s="4" t="s">
         <v>143</v>
-      </c>
-      <c r="L17" s="4" t="s">
-        <v>144</v>
       </c>
       <c r="M17" s="3">
         <v>300000</v>
@@ -3012,7 +3012,7 @@
         <v>2940000</v>
       </c>
       <c r="X17" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Y17" s="4" t="s">
         <v>47</v>
@@ -3030,13 +3030,13 @@
         <v>50</v>
       </c>
       <c r="AD17" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AE17" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="AF17" s="4" t="s">
         <v>121</v>
-      </c>
-      <c r="AF17" s="4" t="s">
-        <v>122</v>
       </c>
       <c r="AG17" s="3">
         <v>4</v>
@@ -3050,10 +3050,10 @@
         <v>34</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>58</v>
@@ -3071,13 +3071,13 @@
         <v>39</v>
       </c>
       <c r="J18" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="L18" s="4" t="s">
         <v>176</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="L18" s="4" t="s">
-        <v>177</v>
       </c>
       <c r="M18" s="3">
         <v>200000</v>
@@ -3113,7 +3113,7 @@
         <v>1960000</v>
       </c>
       <c r="X18" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Y18" s="4" t="s">
         <v>47</v>
@@ -3131,13 +3131,13 @@
         <v>50</v>
       </c>
       <c r="AD18" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AE18" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AF18" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG18" s="3">
         <v>4</v>
@@ -3151,13 +3151,13 @@
         <v>34</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>36</v>
@@ -3214,7 +3214,7 @@
         <v>4900000</v>
       </c>
       <c r="X19" s="5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="Y19" s="4" t="s">
         <v>47</v>
@@ -3232,13 +3232,13 @@
         <v>50</v>
       </c>
       <c r="AD19" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AE19" s="4" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="AF19" s="4" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="AG19" s="3">
         <v>2</v>
@@ -3336,10 +3336,10 @@
         <v>83</v>
       </c>
       <c r="AE20" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AF20" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AG20" s="3">
         <v>4</v>
@@ -3353,13 +3353,13 @@
         <v>34</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>36</v>
@@ -3374,13 +3374,13 @@
         <v>39</v>
       </c>
       <c r="J21" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="K21" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="K21" s="4" t="s">
+      <c r="L21" s="4" t="s">
         <v>220</v>
-      </c>
-      <c r="L21" s="4" t="s">
-        <v>221</v>
       </c>
       <c r="M21" s="3">
         <v>20000</v>
@@ -3434,13 +3434,13 @@
         <v>50</v>
       </c>
       <c r="AD21" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="AE21" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="AE21" s="4" t="s">
+      <c r="AF21" s="4" t="s">
         <v>216</v>
-      </c>
-      <c r="AF21" s="4" t="s">
-        <v>217</v>
       </c>
       <c r="AG21" s="3">
         <v>2</v>
@@ -3576,13 +3576,13 @@
         <v>39</v>
       </c>
       <c r="J23" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="K23" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="K23" s="4" t="s">
+      <c r="L23" s="4" t="s">
         <v>146</v>
-      </c>
-      <c r="L23" s="4" t="s">
-        <v>147</v>
       </c>
       <c r="M23" s="3">
         <v>300000</v>
@@ -3636,7 +3636,7 @@
         <v>50</v>
       </c>
       <c r="AD23" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AE23" s="4" t="s">
         <v>59</v>
@@ -3656,13 +3656,13 @@
         <v>34</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>36</v>
@@ -3704,7 +3704,7 @@
         <v>2478000</v>
       </c>
       <c r="S24" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="T24" s="4" t="s">
         <v>44</v>
@@ -3719,7 +3719,7 @@
         <v>49000000</v>
       </c>
       <c r="X24" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Y24" s="4" t="s">
         <v>47</v>
@@ -3737,13 +3737,13 @@
         <v>50</v>
       </c>
       <c r="AD24" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AE24" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AF24" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG24" s="3">
         <v>2</v>
@@ -3757,13 +3757,13 @@
         <v>34</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>36</v>
@@ -3778,13 +3778,13 @@
         <v>39</v>
       </c>
       <c r="J25" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="L25" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="K25" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="L25" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="M25" s="3">
         <v>500000</v>
@@ -3820,7 +3820,7 @@
         <v>4900000</v>
       </c>
       <c r="X25" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Y25" s="4" t="s">
         <v>47</v>
@@ -3832,19 +3832,19 @@
         <v>49</v>
       </c>
       <c r="AB25" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AC25" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD25" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="AE25" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="AE25" s="4" t="s">
-        <v>209</v>
-      </c>
       <c r="AF25" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG25" s="3">
         <v>7</v>
@@ -3858,10 +3858,10 @@
         <v>34</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>58</v>
@@ -3921,7 +3921,7 @@
         <v>1960000</v>
       </c>
       <c r="X26" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Y26" s="4" t="s">
         <v>47</v>
@@ -3939,13 +3939,13 @@
         <v>50</v>
       </c>
       <c r="AD26" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AE26" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AF26" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG26" s="3">
         <v>3</v>
@@ -3959,13 +3959,13 @@
         <v>34</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>36</v>
@@ -3980,13 +3980,13 @@
         <v>39</v>
       </c>
       <c r="J27" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="L27" s="4" t="s">
         <v>179</v>
-      </c>
-      <c r="K27" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="L27" s="4" t="s">
-        <v>180</v>
       </c>
       <c r="M27" s="3">
         <v>2000000</v>
@@ -4007,7 +4007,7 @@
         <v>115000</v>
       </c>
       <c r="S27" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="T27" s="4" t="s">
         <v>44</v>
@@ -4040,13 +4040,13 @@
         <v>50</v>
       </c>
       <c r="AD27" s="4" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="AE27" s="4" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="AF27" s="4" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="AG27" s="3">
         <v>1</v>
@@ -4144,10 +4144,10 @@
         <v>95</v>
       </c>
       <c r="AE28" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AF28" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AG28" s="3">
         <v>3</v>
@@ -4182,13 +4182,13 @@
         <v>39</v>
       </c>
       <c r="J29" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="K29" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="K29" s="4" t="s">
+      <c r="L29" s="4" t="s">
         <v>149</v>
-      </c>
-      <c r="L29" s="4" t="s">
-        <v>150</v>
       </c>
       <c r="M29" s="3">
         <v>200000</v>
@@ -4224,7 +4224,7 @@
         <v>6800000</v>
       </c>
       <c r="X29" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Y29" s="4" t="s">
         <v>47</v>
@@ -4242,7 +4242,7 @@
         <v>50</v>
       </c>
       <c r="AD29" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AE29" s="4" t="s">
         <v>59</v>
@@ -4262,13 +4262,13 @@
         <v>34</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>36</v>
@@ -4283,13 +4283,13 @@
         <v>39</v>
       </c>
       <c r="J30" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="K30" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="K30" s="4" t="s">
+      <c r="L30" s="4" t="s">
         <v>223</v>
-      </c>
-      <c r="L30" s="4" t="s">
-        <v>224</v>
       </c>
       <c r="M30" s="3">
         <v>1500000</v>
@@ -4343,13 +4343,13 @@
         <v>50</v>
       </c>
       <c r="AD30" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AE30" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="AF30" s="4" t="s">
         <v>216</v>
-      </c>
-      <c r="AF30" s="4" t="s">
-        <v>217</v>
       </c>
       <c r="AG30" s="3">
         <v>1</v>
@@ -4447,10 +4447,10 @@
         <v>83</v>
       </c>
       <c r="AE31" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AF31" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AG31" s="3">
         <v>6</v>
@@ -4485,13 +4485,13 @@
         <v>39</v>
       </c>
       <c r="J32" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="K32" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="K32" s="4" t="s">
+      <c r="L32" s="4" t="s">
         <v>153</v>
-      </c>
-      <c r="L32" s="4" t="s">
-        <v>154</v>
       </c>
       <c r="M32" s="3">
         <v>1000000</v>
@@ -4545,7 +4545,7 @@
         <v>50</v>
       </c>
       <c r="AD32" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AE32" s="4" t="s">
         <v>67</v>
@@ -4646,7 +4646,7 @@
         <v>50</v>
       </c>
       <c r="AD33" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AE33" s="4" t="s">
         <v>52</v>
@@ -4666,10 +4666,10 @@
         <v>34</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>58</v>
@@ -4687,34 +4687,34 @@
         <v>39</v>
       </c>
       <c r="J34" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="L34" s="4" t="s">
         <v>183</v>
-      </c>
-      <c r="K34" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="L34" s="4" t="s">
-        <v>184</v>
       </c>
       <c r="M34" s="3">
         <v>300000</v>
       </c>
       <c r="N34" s="3">
-        <v>154000</v>
+        <v>300000</v>
       </c>
       <c r="O34" s="3">
-        <v>146000</v>
+        <v>0</v>
       </c>
       <c r="P34" s="3">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="Q34" s="3">
         <v>0</v>
       </c>
       <c r="R34" s="3">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="S34" s="4" t="s">
-        <v>126</v>
+        <v>43</v>
       </c>
       <c r="T34" s="4" t="s">
         <v>44</v>
@@ -4729,7 +4729,7 @@
         <v>2940000</v>
       </c>
       <c r="X34" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Y34" s="4" t="s">
         <v>47</v>
@@ -4747,13 +4747,13 @@
         <v>50</v>
       </c>
       <c r="AD34" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AE34" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AF34" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG34" s="3">
         <v>6</v>
@@ -4842,7 +4842,7 @@
         <v>49</v>
       </c>
       <c r="AB35" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AC35" s="4" t="s">
         <v>50</v>
@@ -4854,7 +4854,7 @@
         <v>52</v>
       </c>
       <c r="AF35" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG35" s="3">
         <v>1</v>
@@ -4889,13 +4889,13 @@
         <v>39</v>
       </c>
       <c r="J36" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="K36" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="K36" s="4" t="s">
+      <c r="L36" s="4" t="s">
         <v>157</v>
-      </c>
-      <c r="L36" s="4" t="s">
-        <v>158</v>
       </c>
       <c r="M36" s="3">
         <v>300000</v>
@@ -4949,7 +4949,7 @@
         <v>50</v>
       </c>
       <c r="AD36" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AE36" s="4" t="s">
         <v>59</v>
@@ -4990,13 +4990,13 @@
         <v>39</v>
       </c>
       <c r="J37" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="K37" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="K37" s="4" t="s">
+      <c r="L37" s="4" t="s">
         <v>160</v>
-      </c>
-      <c r="L37" s="4" t="s">
-        <v>161</v>
       </c>
       <c r="M37" s="3">
         <v>1000000</v>
@@ -5017,7 +5017,7 @@
         <v>345000</v>
       </c>
       <c r="S37" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="T37" s="4" t="s">
         <v>44</v>
@@ -5050,13 +5050,13 @@
         <v>50</v>
       </c>
       <c r="AD37" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AE37" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="AF37" s="4" t="s">
         <v>162</v>
-      </c>
-      <c r="AF37" s="4" t="s">
-        <v>163</v>
       </c>
       <c r="AG37" s="3">
         <v>1</v>
@@ -5091,13 +5091,13 @@
         <v>39</v>
       </c>
       <c r="J38" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="K38" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="K38" s="4" t="s">
+      <c r="L38" s="4" t="s">
         <v>165</v>
-      </c>
-      <c r="L38" s="4" t="s">
-        <v>166</v>
       </c>
       <c r="M38" s="3">
         <v>500000</v>
@@ -5133,7 +5133,7 @@
         <v>4900000</v>
       </c>
       <c r="X38" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Y38" s="4" t="s">
         <v>47</v>
@@ -5151,7 +5151,7 @@
         <v>50</v>
       </c>
       <c r="AD38" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AE38" s="4" t="s">
         <v>67</v>
@@ -5192,13 +5192,13 @@
         <v>39</v>
       </c>
       <c r="J39" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="K39" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="K39" s="4" t="s">
+      <c r="L39" s="4" t="s">
         <v>169</v>
-      </c>
-      <c r="L39" s="4" t="s">
-        <v>170</v>
       </c>
       <c r="M39" s="3">
         <v>300000</v>
@@ -5234,7 +5234,7 @@
         <v>2940000</v>
       </c>
       <c r="X39" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Y39" s="4" t="s">
         <v>47</v>
@@ -5252,13 +5252,13 @@
         <v>50</v>
       </c>
       <c r="AD39" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AE39" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="AF39" s="4" t="s">
         <v>121</v>
-      </c>
-      <c r="AF39" s="4" t="s">
-        <v>122</v>
       </c>
       <c r="AG39" s="3">
         <v>1</v>
@@ -5272,13 +5272,13 @@
         <v>34</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>36</v>
@@ -5293,13 +5293,13 @@
         <v>39</v>
       </c>
       <c r="J40" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="K40" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="L40" s="4" t="s">
         <v>195</v>
-      </c>
-      <c r="K40" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="L40" s="4" t="s">
-        <v>196</v>
       </c>
       <c r="M40" s="3">
         <v>1000000</v>
@@ -5353,13 +5353,13 @@
         <v>50</v>
       </c>
       <c r="AD40" s="4" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="AE40" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AF40" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG40" s="3">
         <v>4</v>
@@ -5373,13 +5373,13 @@
         <v>34</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>36</v>
@@ -5394,31 +5394,31 @@
         <v>39</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="L41" s="4" t="s">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="M41" s="3">
-        <v>200000</v>
+        <v>500000</v>
       </c>
       <c r="N41" s="3">
-        <v>200000</v>
+        <v>500000</v>
       </c>
       <c r="O41" s="3">
         <v>0</v>
       </c>
       <c r="P41" s="3">
-        <v>200000</v>
+        <v>500000</v>
       </c>
       <c r="Q41" s="3">
         <v>0</v>
       </c>
       <c r="R41" s="3">
-        <v>200000</v>
+        <v>500000</v>
       </c>
       <c r="S41" s="4" t="s">
         <v>43</v>
@@ -5433,10 +5433,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W41" s="3">
-        <v>1960000</v>
+        <v>4900000</v>
       </c>
       <c r="X41" s="5" t="s">
-        <v>46</v>
+        <v>124</v>
       </c>
       <c r="Y41" s="4" t="s">
         <v>47</v>
@@ -5454,16 +5454,16 @@
         <v>50</v>
       </c>
       <c r="AD41" s="4" t="s">
-        <v>51</v>
+        <v>170</v>
       </c>
       <c r="AE41" s="4" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="AF41" s="4" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="AG41" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:33" x14ac:dyDescent="0.3">
@@ -5474,13 +5474,13 @@
         <v>34</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>36</v>
@@ -5495,13 +5495,13 @@
         <v>39</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>113</v>
+        <v>63</v>
       </c>
       <c r="L42" s="4" t="s">
-        <v>114</v>
+        <v>64</v>
       </c>
       <c r="M42" s="3">
         <v>200000</v>
@@ -5537,7 +5537,7 @@
         <v>1960000</v>
       </c>
       <c r="X42" s="5" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="Y42" s="4" t="s">
         <v>47</v>
@@ -5549,22 +5549,22 @@
         <v>49</v>
       </c>
       <c r="AB42" s="4" t="s">
-        <v>123</v>
+        <v>39</v>
       </c>
       <c r="AC42" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD42" s="4" t="s">
-        <v>106</v>
+        <v>226</v>
       </c>
       <c r="AE42" s="4" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="AF42" s="4" t="s">
-        <v>124</v>
+        <v>68</v>
       </c>
       <c r="AG42" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:33" x14ac:dyDescent="0.3">
@@ -5575,13 +5575,13 @@
         <v>34</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="F43" s="4" t="s">
         <v>36</v>
@@ -5638,7 +5638,7 @@
         <v>19600000</v>
       </c>
       <c r="X43" s="5" t="s">
-        <v>58</v>
+        <v>126</v>
       </c>
       <c r="Y43" s="4" t="s">
         <v>47</v>
@@ -5656,13 +5656,13 @@
         <v>50</v>
       </c>
       <c r="AD43" s="4" t="s">
-        <v>51</v>
+        <v>226</v>
       </c>
       <c r="AE43" s="4" t="s">
-        <v>59</v>
+        <v>120</v>
       </c>
       <c r="AF43" s="4" t="s">
-        <v>60</v>
+        <v>121</v>
       </c>
       <c r="AG43" s="3">
         <v>3</v>
@@ -5676,13 +5676,13 @@
         <v>34</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>36</v>
@@ -5697,34 +5697,34 @@
         <v>39</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>74</v>
+        <v>115</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="L44" s="4" t="s">
-        <v>76</v>
+        <v>117</v>
       </c>
       <c r="M44" s="3">
-        <v>500000</v>
+        <v>8000000</v>
       </c>
       <c r="N44" s="3">
-        <v>500000</v>
+        <v>960000</v>
       </c>
       <c r="O44" s="3">
-        <v>0</v>
+        <v>7040000</v>
       </c>
       <c r="P44" s="3">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
       </c>
       <c r="R44" s="3">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="S44" s="4" t="s">
-        <v>43</v>
+        <v>125</v>
       </c>
       <c r="T44" s="4" t="s">
         <v>44</v>
@@ -5736,10 +5736,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W44" s="3">
-        <v>4900000</v>
+        <v>78400000</v>
       </c>
       <c r="X44" s="5" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="Y44" s="4" t="s">
         <v>47</v>
@@ -5751,22 +5751,22 @@
         <v>49</v>
       </c>
       <c r="AB44" s="4" t="s">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="AC44" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD44" s="4" t="s">
-        <v>171</v>
+        <v>281</v>
       </c>
       <c r="AE44" s="4" t="s">
-        <v>67</v>
+        <v>120</v>
       </c>
       <c r="AF44" s="4" t="s">
-        <v>68</v>
+        <v>121</v>
       </c>
       <c r="AG44" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:33" x14ac:dyDescent="0.3">
@@ -5777,13 +5777,13 @@
         <v>34</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>61</v>
+        <v>189</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>61</v>
+        <v>189</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>36</v>
@@ -5798,31 +5798,31 @@
         <v>39</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="M45" s="3">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="N45" s="3">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="O45" s="3">
         <v>0</v>
       </c>
       <c r="P45" s="3">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="Q45" s="3">
         <v>0</v>
       </c>
       <c r="R45" s="3">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="S45" s="4" t="s">
         <v>43</v>
@@ -5837,10 +5837,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W45" s="3">
-        <v>1960000</v>
+        <v>19600000</v>
       </c>
       <c r="X45" s="5" t="s">
-        <v>66</v>
+        <v>126</v>
       </c>
       <c r="Y45" s="4" t="s">
         <v>47</v>
@@ -5858,16 +5858,16 @@
         <v>50</v>
       </c>
       <c r="AD45" s="4" t="s">
-        <v>227</v>
+        <v>191</v>
       </c>
       <c r="AE45" s="4" t="s">
-        <v>67</v>
+        <v>190</v>
       </c>
       <c r="AF45" s="4" t="s">
-        <v>68</v>
+        <v>171</v>
       </c>
       <c r="AG45" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:33" x14ac:dyDescent="0.3">
@@ -5878,13 +5878,13 @@
         <v>34</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>91</v>
+        <v>189</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>91</v>
+        <v>189</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>36</v>
@@ -5899,31 +5899,31 @@
         <v>39</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>55</v>
+        <v>178</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>56</v>
+        <v>180</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>57</v>
+        <v>179</v>
       </c>
       <c r="M46" s="3">
-        <v>2000000</v>
+        <v>3000000</v>
       </c>
       <c r="N46" s="3">
-        <v>2000000</v>
+        <v>3000000</v>
       </c>
       <c r="O46" s="3">
         <v>0</v>
       </c>
       <c r="P46" s="3">
-        <v>2000000</v>
+        <v>3000000</v>
       </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
       <c r="R46" s="3">
-        <v>2000000</v>
+        <v>3000000</v>
       </c>
       <c r="S46" s="4" t="s">
         <v>43</v>
@@ -5938,10 +5938,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W46" s="3">
-        <v>19600000</v>
+        <v>29400000</v>
       </c>
       <c r="X46" s="5" t="s">
-        <v>127</v>
+        <v>166</v>
       </c>
       <c r="Y46" s="4" t="s">
         <v>47</v>
@@ -5953,22 +5953,22 @@
         <v>49</v>
       </c>
       <c r="AB46" s="4" t="s">
-        <v>39</v>
+        <v>181</v>
       </c>
       <c r="AC46" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD46" s="4" t="s">
-        <v>227</v>
+        <v>278</v>
       </c>
       <c r="AE46" s="4" t="s">
-        <v>121</v>
+        <v>190</v>
       </c>
       <c r="AF46" s="4" t="s">
-        <v>122</v>
+        <v>171</v>
       </c>
       <c r="AG46" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:33" x14ac:dyDescent="0.3">
@@ -5979,13 +5979,13 @@
         <v>34</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>36</v>
@@ -6000,34 +6000,34 @@
         <v>39</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>115</v>
+        <v>40</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>116</v>
+        <v>41</v>
       </c>
       <c r="L47" s="4" t="s">
-        <v>117</v>
+        <v>42</v>
       </c>
       <c r="M47" s="3">
-        <v>8000000</v>
+        <v>200000</v>
       </c>
       <c r="N47" s="3">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="O47" s="3">
-        <v>8000000</v>
+        <v>0</v>
       </c>
       <c r="P47" s="3">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
       </c>
       <c r="R47" s="3">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="S47" s="4" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T47" s="4" t="s">
         <v>44</v>
@@ -6039,10 +6039,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W47" s="3">
-        <v>78400000</v>
+        <v>1960000</v>
       </c>
       <c r="X47" s="5" t="s">
-        <v>118</v>
+        <v>46</v>
       </c>
       <c r="Y47" s="4" t="s">
         <v>47</v>
@@ -6054,22 +6054,22 @@
         <v>49</v>
       </c>
       <c r="AB47" s="4" t="s">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="AC47" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD47" s="4" t="s">
-        <v>120</v>
+        <v>51</v>
       </c>
       <c r="AE47" s="4" t="s">
-        <v>121</v>
+        <v>52</v>
       </c>
       <c r="AF47" s="4" t="s">
-        <v>122</v>
+        <v>53</v>
       </c>
       <c r="AG47" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:33" x14ac:dyDescent="0.3">
@@ -6080,13 +6080,13 @@
         <v>34</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>190</v>
+        <v>35</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>190</v>
+        <v>35</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>36</v>
@@ -6101,31 +6101,31 @@
         <v>39</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>55</v>
+        <v>112</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>56</v>
+        <v>113</v>
       </c>
       <c r="L48" s="4" t="s">
-        <v>57</v>
+        <v>114</v>
       </c>
       <c r="M48" s="3">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="N48" s="3">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="O48" s="3">
         <v>0</v>
       </c>
       <c r="P48" s="3">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="Q48" s="3">
         <v>0</v>
       </c>
       <c r="R48" s="3">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="S48" s="4" t="s">
         <v>43</v>
@@ -6140,10 +6140,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W48" s="3">
-        <v>19600000</v>
+        <v>1960000</v>
       </c>
       <c r="X48" s="5" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="Y48" s="4" t="s">
         <v>47</v>
@@ -6155,22 +6155,22 @@
         <v>49</v>
       </c>
       <c r="AB48" s="4" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="AC48" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD48" s="4" t="s">
-        <v>192</v>
+        <v>106</v>
       </c>
       <c r="AE48" s="4" t="s">
-        <v>191</v>
+        <v>52</v>
       </c>
       <c r="AF48" s="4" t="s">
-        <v>172</v>
+        <v>123</v>
       </c>
       <c r="AG48" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:33" x14ac:dyDescent="0.3">
@@ -6181,13 +6181,13 @@
         <v>34</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>190</v>
+        <v>54</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>190</v>
+        <v>46</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>36</v>
@@ -6202,31 +6202,31 @@
         <v>39</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>179</v>
+        <v>55</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>181</v>
+        <v>56</v>
       </c>
       <c r="L49" s="4" t="s">
-        <v>180</v>
+        <v>57</v>
       </c>
       <c r="M49" s="3">
-        <v>3000000</v>
+        <v>2000000</v>
       </c>
       <c r="N49" s="3">
-        <v>3000000</v>
+        <v>2000000</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
       </c>
       <c r="P49" s="3">
-        <v>3000000</v>
+        <v>2000000</v>
       </c>
       <c r="Q49" s="3">
         <v>0</v>
       </c>
       <c r="R49" s="3">
-        <v>3000000</v>
+        <v>2000000</v>
       </c>
       <c r="S49" s="4" t="s">
         <v>43</v>
@@ -6241,10 +6241,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W49" s="3">
-        <v>29400000</v>
+        <v>19600000</v>
       </c>
       <c r="X49" s="5" t="s">
-        <v>167</v>
+        <v>58</v>
       </c>
       <c r="Y49" s="4" t="s">
         <v>47</v>
@@ -6256,22 +6256,22 @@
         <v>49</v>
       </c>
       <c r="AB49" s="4" t="s">
-        <v>182</v>
+        <v>39</v>
       </c>
       <c r="AC49" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD49" s="4" t="s">
-        <v>281</v>
+        <v>51</v>
       </c>
       <c r="AE49" s="4" t="s">
-        <v>191</v>
+        <v>59</v>
       </c>
       <c r="AF49" s="4" t="s">
-        <v>172</v>
+        <v>60</v>
       </c>
       <c r="AG49" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:33" x14ac:dyDescent="0.3">
@@ -6282,13 +6282,13 @@
         <v>34</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>36</v>
@@ -6303,13 +6303,13 @@
         <v>39</v>
       </c>
       <c r="J50" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="K50" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="K50" s="4" t="s">
+      <c r="L50" s="4" t="s">
         <v>138</v>
-      </c>
-      <c r="L50" s="4" t="s">
-        <v>139</v>
       </c>
       <c r="M50" s="3">
         <v>200000</v>
@@ -6345,7 +6345,7 @@
         <v>1960000</v>
       </c>
       <c r="X50" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Y50" s="4" t="s">
         <v>47</v>
@@ -6363,13 +6363,13 @@
         <v>50</v>
       </c>
       <c r="AD50" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AE50" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AF50" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG50" s="3">
         <v>1</v>
@@ -6383,13 +6383,13 @@
         <v>34</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>36</v>
@@ -6404,13 +6404,13 @@
         <v>39</v>
       </c>
       <c r="J51" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="K51" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="K51" s="4" t="s">
+      <c r="L51" s="4" t="s">
         <v>153</v>
-      </c>
-      <c r="L51" s="4" t="s">
-        <v>154</v>
       </c>
       <c r="M51" s="3">
         <v>1000000</v>
@@ -6446,7 +6446,7 @@
         <v>9800000</v>
       </c>
       <c r="X51" s="5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="Y51" s="4" t="s">
         <v>47</v>
@@ -6464,13 +6464,13 @@
         <v>50</v>
       </c>
       <c r="AD51" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AE51" s="4" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="AF51" s="4" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="AG51" s="3">
         <v>3</v>
@@ -6586,16 +6586,16 @@
         <v>31</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>32</v>
       </c>
       <c r="E1" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>229</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>230</v>
       </c>
       <c r="G1" s="7" t="s">
         <v>9</v>
@@ -6607,16 +6607,16 @@
         <v>10</v>
       </c>
       <c r="J1" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="K1" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="L1" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="M1" s="7" t="s">
         <v>233</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>234</v>
       </c>
       <c r="N1" s="7" t="s">
         <v>5</v>
@@ -6625,55 +6625,55 @@
         <v>24</v>
       </c>
       <c r="P1" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q1" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="R1" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="S1" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>239</v>
-      </c>
-      <c r="U1" s="6" t="s">
-        <v>240</v>
       </c>
       <c r="V1" s="6" t="s">
         <v>17</v>
       </c>
       <c r="W1" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="X1" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="X1" s="7" t="s">
+      <c r="Y1" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="Y1" s="7" t="s">
+      <c r="Z1" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="Z1" s="7" t="s">
+      <c r="AA1" s="7" t="s">
         <v>244</v>
-      </c>
-      <c r="AA1" s="7" t="s">
-        <v>245</v>
       </c>
       <c r="AB1" s="7" t="s">
         <v>27</v>
       </c>
       <c r="AC1" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="AD1" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="AD1" s="7" t="s">
+      <c r="AE1" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="AE1" s="7" t="s">
+      <c r="AF1" s="7" t="s">
         <v>248</v>
-      </c>
-      <c r="AF1" s="7" t="s">
-        <v>249</v>
       </c>
       <c r="AG1" s="7" t="s">
         <v>28</v>
@@ -6690,16 +6690,16 @@
         <v>53</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D2" s="6">
         <v>1</v>
       </c>
       <c r="E2" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="F2" s="7" t="s">
         <v>251</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>252</v>
       </c>
       <c r="G2" s="7" t="s">
         <v>96</v>
@@ -6729,7 +6729,7 @@
         <v>47</v>
       </c>
       <c r="P2" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q2" s="7" t="s">
         <v>45</v>
@@ -6762,28 +6762,28 @@
         <v>39</v>
       </c>
       <c r="AA2" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC2" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB2" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC2" s="7" t="s">
+      <c r="AD2" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="AE2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG2" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH2" s="7" t="s">
         <v>255</v>
-      </c>
-      <c r="AD2" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="AE2" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF2" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG2" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH2" s="7" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.3">
@@ -6794,16 +6794,16 @@
         <v>53</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D3" s="6">
         <v>2</v>
       </c>
       <c r="E3" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>251</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>252</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>40</v>
@@ -6833,7 +6833,7 @@
         <v>47</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q3" s="7" t="s">
         <v>45</v>
@@ -6866,28 +6866,28 @@
         <v>39</v>
       </c>
       <c r="AA3" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB3" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC3" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB3" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC3" s="7" t="s">
+      <c r="AD3" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="AE3" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF3" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG3" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH3" s="7" t="s">
         <v>255</v>
-      </c>
-      <c r="AD3" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="AE3" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF3" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG3" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH3" s="7" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.3">
@@ -6898,16 +6898,16 @@
         <v>53</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D4" s="6">
         <v>3</v>
       </c>
       <c r="E4" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>251</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>252</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>99</v>
@@ -6919,7 +6919,7 @@
         <v>100</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K4" s="7" t="s">
         <v>36</v>
@@ -6937,7 +6937,7 @@
         <v>47</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q4" s="7" t="s">
         <v>45</v>
@@ -6970,28 +6970,28 @@
         <v>39</v>
       </c>
       <c r="AA4" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB4" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC4" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB4" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC4" s="7" t="s">
+      <c r="AD4" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="AE4" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF4" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG4" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH4" s="7" t="s">
         <v>255</v>
-      </c>
-      <c r="AD4" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="AE4" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF4" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG4" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH4" s="7" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.3">
@@ -6999,19 +6999,19 @@
         <v>33</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D5" s="6">
         <v>1</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>109</v>
@@ -7041,7 +7041,7 @@
         <v>47</v>
       </c>
       <c r="P5" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q5" s="7" t="s">
         <v>45</v>
@@ -7074,28 +7074,28 @@
         <v>39</v>
       </c>
       <c r="AA5" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB5" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="AC5" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB5" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="AC5" s="7" t="s">
+      <c r="AD5" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="AE5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG5" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH5" s="7" t="s">
         <v>255</v>
-      </c>
-      <c r="AD5" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="AE5" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF5" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG5" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH5" s="7" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.3">
@@ -7103,19 +7103,19 @@
         <v>33</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D6" s="6">
         <v>2</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>103</v>
@@ -7145,7 +7145,7 @@
         <v>47</v>
       </c>
       <c r="P6" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q6" s="7" t="s">
         <v>45</v>
@@ -7178,28 +7178,28 @@
         <v>39</v>
       </c>
       <c r="AA6" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB6" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="AC6" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB6" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="AC6" s="7" t="s">
+      <c r="AD6" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="AE6" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF6" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG6" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH6" s="7" t="s">
         <v>255</v>
-      </c>
-      <c r="AD6" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="AE6" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF6" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG6" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH6" s="7" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.3">
@@ -7207,19 +7207,19 @@
         <v>33</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D7" s="6">
         <v>3</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>112</v>
@@ -7249,7 +7249,7 @@
         <v>47</v>
       </c>
       <c r="P7" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q7" s="7" t="s">
         <v>45</v>
@@ -7282,28 +7282,28 @@
         <v>39</v>
       </c>
       <c r="AA7" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB7" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="AC7" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB7" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="AC7" s="7" t="s">
+      <c r="AD7" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="AE7" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF7" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG7" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH7" s="7" t="s">
         <v>255</v>
-      </c>
-      <c r="AD7" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="AE7" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF7" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG7" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH7" s="7" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="8" spans="1:34" x14ac:dyDescent="0.3">
@@ -7311,19 +7311,19 @@
         <v>33</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D8" s="6">
         <v>1</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G8" s="7" t="s">
         <v>99</v>
@@ -7335,7 +7335,7 @@
         <v>100</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K8" s="7" t="s">
         <v>36</v>
@@ -7353,7 +7353,7 @@
         <v>47</v>
       </c>
       <c r="P8" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q8" s="7" t="s">
         <v>39</v>
@@ -7386,28 +7386,28 @@
         <v>39</v>
       </c>
       <c r="AA8" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC8" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB8" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC8" s="7" t="s">
+      <c r="AD8" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="AE8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG8" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH8" s="7" t="s">
         <v>255</v>
-      </c>
-      <c r="AD8" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="AE8" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF8" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG8" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH8" s="7" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.3">
@@ -7415,28 +7415,28 @@
         <v>33</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D9" s="6">
         <v>2</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G9" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="I9" s="7" t="s">
         <v>128</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>129</v>
       </c>
       <c r="J9" s="7" t="s">
         <v>91</v>
@@ -7457,7 +7457,7 @@
         <v>47</v>
       </c>
       <c r="P9" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q9" s="7" t="s">
         <v>39</v>
@@ -7475,7 +7475,7 @@
         <v>0</v>
       </c>
       <c r="V9" s="6">
-        <v>1874000</v>
+        <v>2000000</v>
       </c>
       <c r="W9" s="7" t="s">
         <v>50</v>
@@ -7490,16 +7490,16 @@
         <v>39</v>
       </c>
       <c r="AA9" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC9" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB9" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC9" s="7" t="s">
-        <v>255</v>
-      </c>
       <c r="AD9" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AE9" s="7" t="s">
         <v>39</v>
@@ -7511,7 +7511,7 @@
         <v>47</v>
       </c>
       <c r="AH9" s="7" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.3">
@@ -7519,19 +7519,19 @@
         <v>33</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D10" s="6">
         <v>3</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>92</v>
@@ -7543,7 +7543,7 @@
         <v>93</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K10" s="7" t="s">
         <v>36</v>
@@ -7561,7 +7561,7 @@
         <v>47</v>
       </c>
       <c r="P10" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q10" s="7" t="s">
         <v>39</v>
@@ -7594,28 +7594,28 @@
         <v>39</v>
       </c>
       <c r="AA10" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB10" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC10" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB10" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC10" s="7" t="s">
+      <c r="AD10" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="AE10" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF10" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG10" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH10" s="7" t="s">
         <v>255</v>
-      </c>
-      <c r="AD10" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="AE10" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF10" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG10" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH10" s="7" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.3">
@@ -7623,19 +7623,19 @@
         <v>33</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D11" s="6">
         <v>4</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>84</v>
@@ -7647,7 +7647,7 @@
         <v>85</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="K11" s="7" t="s">
         <v>36</v>
@@ -7665,7 +7665,7 @@
         <v>47</v>
       </c>
       <c r="P11" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q11" s="7" t="s">
         <v>39</v>
@@ -7698,28 +7698,28 @@
         <v>39</v>
       </c>
       <c r="AA11" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB11" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC11" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB11" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC11" s="7" t="s">
+      <c r="AD11" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="AE11" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF11" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG11" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH11" s="7" t="s">
         <v>255</v>
-      </c>
-      <c r="AD11" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="AE11" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF11" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG11" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH11" s="7" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.3">
@@ -7727,19 +7727,19 @@
         <v>33</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D12" s="6">
         <v>5</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>80</v>
@@ -7751,7 +7751,7 @@
         <v>81</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="K12" s="7" t="s">
         <v>36</v>
@@ -7769,7 +7769,7 @@
         <v>47</v>
       </c>
       <c r="P12" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q12" s="7" t="s">
         <v>39</v>
@@ -7802,28 +7802,28 @@
         <v>39</v>
       </c>
       <c r="AA12" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB12" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC12" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB12" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC12" s="7" t="s">
+      <c r="AD12" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="AE12" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF12" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG12" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH12" s="7" t="s">
         <v>255</v>
-      </c>
-      <c r="AD12" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="AE12" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF12" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG12" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH12" s="7" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="13" spans="1:34" x14ac:dyDescent="0.3">
@@ -7831,19 +7831,19 @@
         <v>33</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D13" s="6">
         <v>6</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>87</v>
@@ -7855,7 +7855,7 @@
         <v>88</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K13" s="7" t="s">
         <v>36</v>
@@ -7873,7 +7873,7 @@
         <v>47</v>
       </c>
       <c r="P13" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q13" s="7" t="s">
         <v>39</v>
@@ -7906,28 +7906,28 @@
         <v>39</v>
       </c>
       <c r="AA13" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB13" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC13" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB13" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC13" s="7" t="s">
+      <c r="AD13" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="AE13" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF13" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG13" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH13" s="7" t="s">
         <v>255</v>
-      </c>
-      <c r="AD13" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="AE13" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF13" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG13" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH13" s="7" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.3">
@@ -7938,16 +7938,16 @@
         <v>60</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D14" s="6">
         <v>1</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>77</v>
@@ -7977,7 +7977,7 @@
         <v>47</v>
       </c>
       <c r="P14" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q14" s="7" t="s">
         <v>39</v>
@@ -8010,28 +8010,28 @@
         <v>39</v>
       </c>
       <c r="AA14" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB14" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC14" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB14" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC14" s="7" t="s">
+      <c r="AD14" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="AE14" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF14" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG14" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH14" s="7" t="s">
         <v>255</v>
-      </c>
-      <c r="AD14" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="AE14" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF14" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG14" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH14" s="7" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="15" spans="1:34" x14ac:dyDescent="0.3">
@@ -8042,28 +8042,28 @@
         <v>60</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D15" s="6">
         <v>2</v>
       </c>
       <c r="E15" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="J15" s="7" t="s">
         <v>264</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>265</v>
       </c>
       <c r="K15" s="7" t="s">
         <v>36</v>
@@ -8081,7 +8081,7 @@
         <v>47</v>
       </c>
       <c r="P15" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q15" s="7" t="s">
         <v>39</v>
@@ -8114,16 +8114,16 @@
         <v>39</v>
       </c>
       <c r="AA15" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB15" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC15" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB15" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC15" s="7" t="s">
-        <v>255</v>
-      </c>
       <c r="AD15" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AE15" s="7" t="s">
         <v>39</v>
@@ -8135,7 +8135,7 @@
         <v>47</v>
       </c>
       <c r="AH15" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16" spans="1:34" x14ac:dyDescent="0.3">
@@ -8146,16 +8146,16 @@
         <v>60</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D16" s="6">
         <v>3</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>55</v>
@@ -8167,7 +8167,7 @@
         <v>56</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K16" s="7" t="s">
         <v>36</v>
@@ -8185,7 +8185,7 @@
         <v>47</v>
       </c>
       <c r="P16" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q16" s="7" t="s">
         <v>39</v>
@@ -8218,28 +8218,28 @@
         <v>39</v>
       </c>
       <c r="AA16" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB16" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC16" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB16" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC16" s="7" t="s">
+      <c r="AD16" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="AE16" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF16" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG16" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH16" s="7" t="s">
         <v>255</v>
-      </c>
-      <c r="AD16" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="AE16" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF16" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG16" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH16" s="7" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="17" spans="1:34" x14ac:dyDescent="0.3">
@@ -8250,28 +8250,28 @@
         <v>60</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D17" s="6">
         <v>4</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G17" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="I17" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="H17" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>146</v>
-      </c>
       <c r="J17" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K17" s="7" t="s">
         <v>36</v>
@@ -8289,7 +8289,7 @@
         <v>47</v>
       </c>
       <c r="P17" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q17" s="7" t="s">
         <v>39</v>
@@ -8322,16 +8322,16 @@
         <v>39</v>
       </c>
       <c r="AA17" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB17" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC17" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB17" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC17" s="7" t="s">
-        <v>255</v>
-      </c>
       <c r="AD17" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AE17" s="7" t="s">
         <v>39</v>
@@ -8343,7 +8343,7 @@
         <v>47</v>
       </c>
       <c r="AH17" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="18" spans="1:34" x14ac:dyDescent="0.3">
@@ -8354,28 +8354,28 @@
         <v>60</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D18" s="6">
         <v>5</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G18" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="I18" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="H18" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>149</v>
-      </c>
       <c r="J18" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K18" s="7" t="s">
         <v>36</v>
@@ -8393,7 +8393,7 @@
         <v>47</v>
       </c>
       <c r="P18" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q18" s="7" t="s">
         <v>39</v>
@@ -8420,22 +8420,22 @@
         <v>49</v>
       </c>
       <c r="Y18" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Z18" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AA18" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB18" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC18" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB18" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC18" s="7" t="s">
-        <v>255</v>
-      </c>
       <c r="AD18" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AE18" s="7" t="s">
         <v>39</v>
@@ -8447,7 +8447,7 @@
         <v>47</v>
       </c>
       <c r="AH18" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="19" spans="1:34" x14ac:dyDescent="0.3">
@@ -8458,7 +8458,7 @@
         <v>68</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D19" s="6">
         <v>1</v>
@@ -8467,7 +8467,7 @@
         <v>54</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>55</v>
@@ -8479,7 +8479,7 @@
         <v>56</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K19" s="7" t="s">
         <v>36</v>
@@ -8497,7 +8497,7 @@
         <v>47</v>
       </c>
       <c r="P19" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q19" s="7" t="s">
         <v>39</v>
@@ -8530,28 +8530,28 @@
         <v>39</v>
       </c>
       <c r="AA19" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB19" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC19" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB19" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC19" s="7" t="s">
+      <c r="AD19" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="AE19" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF19" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG19" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH19" s="7" t="s">
         <v>255</v>
-      </c>
-      <c r="AD19" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="AE19" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF19" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG19" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH19" s="7" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="20" spans="1:34" x14ac:dyDescent="0.3">
@@ -8562,7 +8562,7 @@
         <v>68</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D20" s="6">
         <v>2</v>
@@ -8571,19 +8571,19 @@
         <v>54</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G20" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="I20" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="H20" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>153</v>
-      </c>
       <c r="J20" s="7" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="K20" s="7" t="s">
         <v>36</v>
@@ -8601,7 +8601,7 @@
         <v>47</v>
       </c>
       <c r="P20" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q20" s="7" t="s">
         <v>39</v>
@@ -8634,16 +8634,16 @@
         <v>39</v>
       </c>
       <c r="AA20" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB20" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC20" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB20" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC20" s="7" t="s">
-        <v>255</v>
-      </c>
       <c r="AD20" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AE20" s="7" t="s">
         <v>39</v>
@@ -8655,7 +8655,7 @@
         <v>47</v>
       </c>
       <c r="AH20" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="21" spans="1:34" x14ac:dyDescent="0.3">
@@ -8666,7 +8666,7 @@
         <v>68</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D21" s="6">
         <v>3</v>
@@ -8675,7 +8675,7 @@
         <v>54</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G21" s="7" t="s">
         <v>74</v>
@@ -8687,7 +8687,7 @@
         <v>75</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="K21" s="7" t="s">
         <v>36</v>
@@ -8705,7 +8705,7 @@
         <v>47</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q21" s="7" t="s">
         <v>39</v>
@@ -8732,34 +8732,34 @@
         <v>49</v>
       </c>
       <c r="Y21" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Z21" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AA21" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB21" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC21" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB21" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC21" s="7" t="s">
+      <c r="AD21" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="AE21" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF21" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG21" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH21" s="7" t="s">
         <v>255</v>
-      </c>
-      <c r="AD21" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="AE21" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF21" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG21" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH21" s="7" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="22" spans="1:34" x14ac:dyDescent="0.3">
@@ -8770,7 +8770,7 @@
         <v>68</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D22" s="6">
         <v>4</v>
@@ -8779,19 +8779,19 @@
         <v>54</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G22" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I22" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="H22" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>133</v>
-      </c>
       <c r="J22" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K22" s="7" t="s">
         <v>36</v>
@@ -8809,7 +8809,7 @@
         <v>47</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q22" s="7" t="s">
         <v>39</v>
@@ -8836,22 +8836,22 @@
         <v>49</v>
       </c>
       <c r="Y22" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z22" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AA22" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB22" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC22" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB22" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC22" s="7" t="s">
-        <v>255</v>
-      </c>
       <c r="AD22" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AE22" s="7" t="s">
         <v>39</v>
@@ -8863,7 +8863,7 @@
         <v>47</v>
       </c>
       <c r="AH22" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="23" spans="1:34" x14ac:dyDescent="0.3">
@@ -8874,7 +8874,7 @@
         <v>68</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D23" s="6">
         <v>5</v>
@@ -8883,19 +8883,19 @@
         <v>54</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G23" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="I23" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="H23" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>165</v>
-      </c>
       <c r="J23" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K23" s="7" t="s">
         <v>36</v>
@@ -8913,7 +8913,7 @@
         <v>47</v>
       </c>
       <c r="P23" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q23" s="7" t="s">
         <v>39</v>
@@ -8940,22 +8940,22 @@
         <v>49</v>
       </c>
       <c r="Y23" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Z23" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AA23" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB23" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC23" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB23" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC23" s="7" t="s">
-        <v>255</v>
-      </c>
       <c r="AD23" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AE23" s="7" t="s">
         <v>39</v>
@@ -8967,7 +8967,7 @@
         <v>47</v>
       </c>
       <c r="AH23" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="24" spans="1:34" x14ac:dyDescent="0.3">
@@ -8978,7 +8978,7 @@
         <v>68</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D24" s="6">
         <v>6</v>
@@ -8987,7 +8987,7 @@
         <v>54</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G24" s="7" t="s">
         <v>62</v>
@@ -8999,7 +8999,7 @@
         <v>63</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K24" s="7" t="s">
         <v>36</v>
@@ -9017,7 +9017,7 @@
         <v>47</v>
       </c>
       <c r="P24" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q24" s="7" t="s">
         <v>39</v>
@@ -9050,16 +9050,16 @@
         <v>39</v>
       </c>
       <c r="AA24" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB24" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC24" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB24" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC24" s="7" t="s">
-        <v>255</v>
-      </c>
       <c r="AD24" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AE24" s="7" t="s">
         <v>39</v>
@@ -9071,7 +9071,7 @@
         <v>47</v>
       </c>
       <c r="AH24" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="25" spans="1:34" x14ac:dyDescent="0.3">
@@ -9079,10 +9079,10 @@
         <v>33</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D25" s="6">
         <v>1</v>
@@ -9091,19 +9091,19 @@
         <v>91</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G25" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="I25" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="H25" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>169</v>
-      </c>
       <c r="J25" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K25" s="7" t="s">
         <v>36</v>
@@ -9121,7 +9121,7 @@
         <v>47</v>
       </c>
       <c r="P25" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q25" s="7" t="s">
         <v>39</v>
@@ -9148,22 +9148,22 @@
         <v>49</v>
       </c>
       <c r="Y25" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Z25" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AA25" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB25" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC25" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB25" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC25" s="7" t="s">
-        <v>255</v>
-      </c>
       <c r="AD25" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AE25" s="7" t="s">
         <v>39</v>
@@ -9175,7 +9175,7 @@
         <v>47</v>
       </c>
       <c r="AH25" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="26" spans="1:34" x14ac:dyDescent="0.3">
@@ -9183,10 +9183,10 @@
         <v>33</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D26" s="6">
         <v>2</v>
@@ -9195,7 +9195,7 @@
         <v>91</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G26" s="7" t="s">
         <v>69</v>
@@ -9207,7 +9207,7 @@
         <v>70</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K26" s="7" t="s">
         <v>36</v>
@@ -9225,7 +9225,7 @@
         <v>47</v>
       </c>
       <c r="P26" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q26" s="7" t="s">
         <v>39</v>
@@ -9252,22 +9252,22 @@
         <v>49</v>
       </c>
       <c r="Y26" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Z26" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AA26" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB26" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC26" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB26" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC26" s="7" t="s">
-        <v>255</v>
-      </c>
       <c r="AD26" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AE26" s="7" t="s">
         <v>39</v>
@@ -9279,7 +9279,7 @@
         <v>47</v>
       </c>
       <c r="AH26" s="7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="27" spans="1:34" x14ac:dyDescent="0.3">
@@ -9287,10 +9287,10 @@
         <v>33</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D27" s="6">
         <v>3</v>
@@ -9299,7 +9299,7 @@
         <v>91</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G27" s="7" t="s">
         <v>55</v>
@@ -9311,7 +9311,7 @@
         <v>56</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K27" s="7" t="s">
         <v>36</v>
@@ -9329,7 +9329,7 @@
         <v>47</v>
       </c>
       <c r="P27" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q27" s="7" t="s">
         <v>39</v>
@@ -9356,22 +9356,22 @@
         <v>49</v>
       </c>
       <c r="Y27" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Z27" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AA27" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB27" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC27" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB27" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC27" s="7" t="s">
-        <v>255</v>
-      </c>
       <c r="AD27" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AE27" s="7" t="s">
         <v>39</v>
@@ -9383,7 +9383,7 @@
         <v>47</v>
       </c>
       <c r="AH27" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="28" spans="1:34" x14ac:dyDescent="0.3">
@@ -9391,10 +9391,10 @@
         <v>33</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D28" s="6">
         <v>4</v>
@@ -9403,19 +9403,19 @@
         <v>91</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G28" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="I28" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="H28" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="I28" s="7" t="s">
-        <v>143</v>
-      </c>
       <c r="J28" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K28" s="7" t="s">
         <v>36</v>
@@ -9433,7 +9433,7 @@
         <v>47</v>
       </c>
       <c r="P28" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q28" s="7" t="s">
         <v>39</v>
@@ -9460,22 +9460,22 @@
         <v>49</v>
       </c>
       <c r="Y28" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Z28" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AA28" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB28" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC28" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB28" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC28" s="7" t="s">
-        <v>255</v>
-      </c>
       <c r="AD28" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AE28" s="7" t="s">
         <v>39</v>
@@ -9487,7 +9487,7 @@
         <v>47</v>
       </c>
       <c r="AH28" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="29" spans="1:34" x14ac:dyDescent="0.3">
@@ -9495,10 +9495,10 @@
         <v>33</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D29" s="6">
         <v>5</v>
@@ -9507,16 +9507,16 @@
         <v>91</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G29" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="I29" s="7" t="s">
         <v>128</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>129</v>
       </c>
       <c r="J29" s="7" t="s">
         <v>91</v>
@@ -9537,7 +9537,7 @@
         <v>47</v>
       </c>
       <c r="P29" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q29" s="7" t="s">
         <v>39</v>
@@ -9555,7 +9555,7 @@
         <v>0</v>
       </c>
       <c r="V29" s="6">
-        <v>0</v>
+        <v>351000</v>
       </c>
       <c r="W29" s="7" t="s">
         <v>50</v>
@@ -9570,16 +9570,16 @@
         <v>39</v>
       </c>
       <c r="AA29" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB29" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC29" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB29" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC29" s="7" t="s">
-        <v>255</v>
-      </c>
       <c r="AD29" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AE29" s="7" t="s">
         <v>39</v>
@@ -9591,7 +9591,7 @@
         <v>47</v>
       </c>
       <c r="AH29" s="7" t="s">
-        <v>120</v>
+        <v>279</v>
       </c>
     </row>
     <row r="30" spans="1:34" x14ac:dyDescent="0.3">
@@ -9599,10 +9599,10 @@
         <v>33</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D30" s="6">
         <v>6</v>
@@ -9611,7 +9611,7 @@
         <v>91</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G30" s="7" t="s">
         <v>115</v>
@@ -9641,7 +9641,7 @@
         <v>47</v>
       </c>
       <c r="P30" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q30" s="7" t="s">
         <v>39</v>
@@ -9674,16 +9674,16 @@
         <v>39</v>
       </c>
       <c r="AA30" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AB30" s="7" t="s">
         <v>119</v>
       </c>
       <c r="AC30" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AD30" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AE30" s="7" t="s">
         <v>39</v>
@@ -9695,7 +9695,7 @@
         <v>47</v>
       </c>
       <c r="AH30" s="7" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
     </row>
     <row r="31" spans="1:34" x14ac:dyDescent="0.3">
@@ -9703,10 +9703,10 @@
         <v>33</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D31" s="6">
         <v>7</v>
@@ -9715,19 +9715,19 @@
         <v>91</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G31" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I31" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="H31" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>138</v>
-      </c>
       <c r="J31" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K31" s="7" t="s">
         <v>36</v>
@@ -9745,7 +9745,7 @@
         <v>47</v>
       </c>
       <c r="P31" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q31" s="7" t="s">
         <v>39</v>
@@ -9778,16 +9778,16 @@
         <v>39</v>
       </c>
       <c r="AA31" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB31" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="AC31" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB31" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="AC31" s="7" t="s">
-        <v>255</v>
-      </c>
       <c r="AD31" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AE31" s="7" t="s">
         <v>39</v>
@@ -9799,7 +9799,7 @@
         <v>47</v>
       </c>
       <c r="AH31" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="32" spans="1:34" x14ac:dyDescent="0.3">
@@ -9807,10 +9807,10 @@
         <v>33</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D32" s="6">
         <v>1</v>
@@ -9819,19 +9819,19 @@
         <v>72</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G32" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="I32" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="H32" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="I32" s="7" t="s">
-        <v>160</v>
-      </c>
       <c r="J32" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K32" s="7" t="s">
         <v>36</v>
@@ -9849,7 +9849,7 @@
         <v>47</v>
       </c>
       <c r="P32" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q32" s="7" t="s">
         <v>45</v>
@@ -9876,22 +9876,22 @@
         <v>49</v>
       </c>
       <c r="Y32" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Z32" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AA32" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB32" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC32" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB32" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC32" s="7" t="s">
-        <v>255</v>
-      </c>
       <c r="AD32" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AE32" s="7" t="s">
         <v>39</v>
@@ -9903,7 +9903,7 @@
         <v>47</v>
       </c>
       <c r="AH32" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="33" spans="1:34" x14ac:dyDescent="0.3">
@@ -9911,10 +9911,10 @@
         <v>33</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D33" s="6">
         <v>1</v>
@@ -9923,19 +9923,19 @@
         <v>58</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G33" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="H33" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="H33" s="7" t="s">
+      <c r="I33" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="I33" s="7" t="s">
-        <v>175</v>
-      </c>
       <c r="J33" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K33" s="7" t="s">
         <v>36</v>
@@ -9953,7 +9953,7 @@
         <v>47</v>
       </c>
       <c r="P33" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q33" s="7" t="s">
         <v>39</v>
@@ -9980,22 +9980,22 @@
         <v>49</v>
       </c>
       <c r="Y33" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Z33" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AA33" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB33" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC33" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB33" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC33" s="7" t="s">
-        <v>255</v>
-      </c>
       <c r="AD33" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AE33" s="7" t="s">
         <v>39</v>
@@ -10007,7 +10007,7 @@
         <v>47</v>
       </c>
       <c r="AH33" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="34" spans="1:34" x14ac:dyDescent="0.3">
@@ -10015,10 +10015,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D34" s="6">
         <v>2</v>
@@ -10027,7 +10027,7 @@
         <v>58</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G34" s="7" t="s">
         <v>55</v>
@@ -10039,7 +10039,7 @@
         <v>56</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K34" s="7" t="s">
         <v>36</v>
@@ -10057,7 +10057,7 @@
         <v>47</v>
       </c>
       <c r="P34" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q34" s="7" t="s">
         <v>39</v>
@@ -10084,22 +10084,22 @@
         <v>49</v>
       </c>
       <c r="Y34" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Z34" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AA34" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB34" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC34" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB34" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC34" s="7" t="s">
-        <v>255</v>
-      </c>
       <c r="AD34" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AE34" s="7" t="s">
         <v>39</v>
@@ -10111,7 +10111,7 @@
         <v>47</v>
       </c>
       <c r="AH34" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="35" spans="1:34" x14ac:dyDescent="0.3">
@@ -10119,10 +10119,10 @@
         <v>33</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D35" s="6">
         <v>3</v>
@@ -10131,7 +10131,7 @@
         <v>58</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G35" s="7" t="s">
         <v>87</v>
@@ -10143,7 +10143,7 @@
         <v>88</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K35" s="7" t="s">
         <v>36</v>
@@ -10161,7 +10161,7 @@
         <v>47</v>
       </c>
       <c r="P35" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q35" s="7" t="s">
         <v>39</v>
@@ -10188,22 +10188,22 @@
         <v>49</v>
       </c>
       <c r="Y35" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Z35" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AA35" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB35" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC35" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB35" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC35" s="7" t="s">
-        <v>255</v>
-      </c>
       <c r="AD35" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AE35" s="7" t="s">
         <v>39</v>
@@ -10215,7 +10215,7 @@
         <v>47</v>
       </c>
       <c r="AH35" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="36" spans="1:34" x14ac:dyDescent="0.3">
@@ -10223,10 +10223,10 @@
         <v>33</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D36" s="6">
         <v>4</v>
@@ -10235,19 +10235,19 @@
         <v>58</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G36" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="H36" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="H36" s="7" t="s">
+      <c r="I36" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="I36" s="7" t="s">
-        <v>178</v>
-      </c>
       <c r="J36" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K36" s="7" t="s">
         <v>36</v>
@@ -10265,7 +10265,7 @@
         <v>47</v>
       </c>
       <c r="P36" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q36" s="7" t="s">
         <v>39</v>
@@ -10292,22 +10292,22 @@
         <v>49</v>
       </c>
       <c r="Y36" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Z36" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AA36" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB36" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC36" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB36" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC36" s="7" t="s">
-        <v>255</v>
-      </c>
       <c r="AD36" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AE36" s="7" t="s">
         <v>39</v>
@@ -10319,7 +10319,7 @@
         <v>47</v>
       </c>
       <c r="AH36" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="37" spans="1:34" x14ac:dyDescent="0.3">
@@ -10327,10 +10327,10 @@
         <v>33</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D37" s="6">
         <v>5</v>
@@ -10339,19 +10339,19 @@
         <v>58</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G37" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="H37" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="H37" s="7" t="s">
+      <c r="I37" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="I37" s="7" t="s">
-        <v>181</v>
-      </c>
       <c r="J37" s="7" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="K37" s="7" t="s">
         <v>36</v>
@@ -10369,7 +10369,7 @@
         <v>47</v>
       </c>
       <c r="P37" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q37" s="7" t="s">
         <v>39</v>
@@ -10396,22 +10396,22 @@
         <v>49</v>
       </c>
       <c r="Y37" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Z37" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AA37" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB37" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="AC37" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB37" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="AC37" s="7" t="s">
-        <v>255</v>
-      </c>
       <c r="AD37" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AE37" s="7" t="s">
         <v>39</v>
@@ -10423,7 +10423,7 @@
         <v>47</v>
       </c>
       <c r="AH37" s="7" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="38" spans="1:34" x14ac:dyDescent="0.3">
@@ -10431,10 +10431,10 @@
         <v>33</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D38" s="6">
         <v>6</v>
@@ -10443,19 +10443,19 @@
         <v>58</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G38" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="H38" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="H38" s="7" t="s">
+      <c r="I38" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="I38" s="7" t="s">
-        <v>185</v>
-      </c>
       <c r="J38" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K38" s="7" t="s">
         <v>36</v>
@@ -10473,7 +10473,7 @@
         <v>47</v>
       </c>
       <c r="P38" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q38" s="7" t="s">
         <v>39</v>
@@ -10491,7 +10491,7 @@
         <v>0</v>
       </c>
       <c r="V38" s="6">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="W38" s="7" t="s">
         <v>50</v>
@@ -10500,22 +10500,22 @@
         <v>49</v>
       </c>
       <c r="Y38" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Z38" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AA38" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB38" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC38" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB38" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC38" s="7" t="s">
-        <v>255</v>
-      </c>
       <c r="AD38" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AE38" s="7" t="s">
         <v>39</v>
@@ -10527,7 +10527,7 @@
         <v>47</v>
       </c>
       <c r="AH38" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="39" spans="1:34" x14ac:dyDescent="0.3">
@@ -10535,31 +10535,31 @@
         <v>33</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D39" s="6">
         <v>1</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G39" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I39" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="H39" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="I39" s="7" t="s">
-        <v>138</v>
-      </c>
       <c r="J39" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K39" s="7" t="s">
         <v>36</v>
@@ -10577,7 +10577,7 @@
         <v>47</v>
       </c>
       <c r="P39" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q39" s="7" t="s">
         <v>39</v>
@@ -10604,22 +10604,22 @@
         <v>49</v>
       </c>
       <c r="Y39" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Z39" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AA39" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB39" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC39" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB39" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC39" s="7" t="s">
-        <v>255</v>
-      </c>
       <c r="AD39" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AE39" s="7" t="s">
         <v>39</v>
@@ -10631,7 +10631,7 @@
         <v>47</v>
       </c>
       <c r="AH39" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="40" spans="1:34" x14ac:dyDescent="0.3">
@@ -10639,19 +10639,19 @@
         <v>33</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D40" s="6">
         <v>2</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G40" s="7" t="s">
         <v>55</v>
@@ -10663,7 +10663,7 @@
         <v>56</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K40" s="7" t="s">
         <v>36</v>
@@ -10681,7 +10681,7 @@
         <v>47</v>
       </c>
       <c r="P40" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q40" s="7" t="s">
         <v>39</v>
@@ -10708,22 +10708,22 @@
         <v>49</v>
       </c>
       <c r="Y40" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Z40" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AA40" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB40" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC40" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB40" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC40" s="7" t="s">
-        <v>255</v>
-      </c>
       <c r="AD40" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AE40" s="7" t="s">
         <v>39</v>
@@ -10735,7 +10735,7 @@
         <v>47</v>
       </c>
       <c r="AH40" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="41" spans="1:34" x14ac:dyDescent="0.3">
@@ -10743,31 +10743,31 @@
         <v>33</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D41" s="6">
         <v>3</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G41" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="I41" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="H41" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="I41" s="7" t="s">
-        <v>160</v>
-      </c>
       <c r="J41" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K41" s="7" t="s">
         <v>36</v>
@@ -10785,7 +10785,7 @@
         <v>47</v>
       </c>
       <c r="P41" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q41" s="7" t="s">
         <v>39</v>
@@ -10818,16 +10818,16 @@
         <v>39</v>
       </c>
       <c r="AA41" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB41" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC41" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB41" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC41" s="7" t="s">
-        <v>255</v>
-      </c>
       <c r="AD41" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AE41" s="7" t="s">
         <v>39</v>
@@ -10839,7 +10839,7 @@
         <v>47</v>
       </c>
       <c r="AH41" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="42" spans="1:34" x14ac:dyDescent="0.3">
@@ -10847,31 +10847,31 @@
         <v>33</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D42" s="6">
         <v>4</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G42" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="H42" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="H42" s="7" t="s">
+      <c r="I42" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="I42" s="7" t="s">
+      <c r="J42" s="7" t="s">
         <v>197</v>
-      </c>
-      <c r="J42" s="7" t="s">
-        <v>198</v>
       </c>
       <c r="K42" s="7" t="s">
         <v>36</v>
@@ -10889,7 +10889,7 @@
         <v>47</v>
       </c>
       <c r="P42" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q42" s="7" t="s">
         <v>39</v>
@@ -10922,16 +10922,16 @@
         <v>39</v>
       </c>
       <c r="AA42" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB42" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC42" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB42" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC42" s="7" t="s">
-        <v>255</v>
-      </c>
       <c r="AD42" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AE42" s="7" t="s">
         <v>39</v>
@@ -10943,7 +10943,7 @@
         <v>47</v>
       </c>
       <c r="AH42" s="7" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="43" spans="1:34" x14ac:dyDescent="0.3">
@@ -10951,19 +10951,19 @@
         <v>33</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D43" s="6">
         <v>5</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G43" s="7" t="s">
         <v>92</v>
@@ -10975,7 +10975,7 @@
         <v>93</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K43" s="7" t="s">
         <v>36</v>
@@ -10993,7 +10993,7 @@
         <v>47</v>
       </c>
       <c r="P43" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q43" s="7" t="s">
         <v>39</v>
@@ -11020,22 +11020,22 @@
         <v>49</v>
       </c>
       <c r="Y43" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Z43" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AA43" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB43" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC43" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB43" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC43" s="7" t="s">
-        <v>255</v>
-      </c>
       <c r="AD43" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AE43" s="7" t="s">
         <v>39</v>
@@ -11047,7 +11047,7 @@
         <v>47</v>
       </c>
       <c r="AH43" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="44" spans="1:34" x14ac:dyDescent="0.3">
@@ -11055,31 +11055,31 @@
         <v>33</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D44" s="6">
         <v>6</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G44" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="H44" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="H44" s="7" t="s">
+      <c r="I44" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="I44" s="7" t="s">
-        <v>201</v>
-      </c>
       <c r="J44" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K44" s="7" t="s">
         <v>36</v>
@@ -11097,7 +11097,7 @@
         <v>47</v>
       </c>
       <c r="P44" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q44" s="7" t="s">
         <v>39</v>
@@ -11130,16 +11130,16 @@
         <v>39</v>
       </c>
       <c r="AA44" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB44" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC44" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB44" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC44" s="7" t="s">
-        <v>255</v>
-      </c>
       <c r="AD44" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AE44" s="7" t="s">
         <v>39</v>
@@ -11151,7 +11151,7 @@
         <v>47</v>
       </c>
       <c r="AH44" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="45" spans="1:34" x14ac:dyDescent="0.3">
@@ -11159,31 +11159,31 @@
         <v>33</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D45" s="6">
         <v>7</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G45" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="H45" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="H45" s="7" t="s">
+      <c r="I45" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="I45" s="7" t="s">
-        <v>204</v>
-      </c>
       <c r="J45" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K45" s="7" t="s">
         <v>36</v>
@@ -11201,7 +11201,7 @@
         <v>47</v>
       </c>
       <c r="P45" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q45" s="7" t="s">
         <v>39</v>
@@ -11228,22 +11228,22 @@
         <v>49</v>
       </c>
       <c r="Y45" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Z45" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AA45" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB45" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="AC45" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB45" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="AC45" s="7" t="s">
-        <v>255</v>
-      </c>
       <c r="AD45" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AE45" s="7" t="s">
         <v>39</v>
@@ -11255,7 +11255,7 @@
         <v>47</v>
       </c>
       <c r="AH45" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="46" spans="1:34" x14ac:dyDescent="0.3">
@@ -11263,28 +11263,28 @@
         <v>33</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D46" s="6">
         <v>1</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G46" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="I46" s="7" t="s">
         <v>222</v>
-      </c>
-      <c r="H46" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="I46" s="7" t="s">
-        <v>223</v>
       </c>
       <c r="J46" s="7" t="s">
         <v>66</v>
@@ -11305,7 +11305,7 @@
         <v>47</v>
       </c>
       <c r="P46" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q46" s="7" t="s">
         <v>39</v>
@@ -11338,16 +11338,16 @@
         <v>39</v>
       </c>
       <c r="AA46" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB46" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC46" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB46" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC46" s="7" t="s">
-        <v>255</v>
-      </c>
       <c r="AD46" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AE46" s="7" t="s">
         <v>39</v>
@@ -11359,7 +11359,7 @@
         <v>47</v>
       </c>
       <c r="AH46" s="7" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="47" spans="1:34" x14ac:dyDescent="0.3">
@@ -11367,31 +11367,31 @@
         <v>33</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D47" s="6">
         <v>2</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G47" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="I47" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="H47" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="I47" s="7" t="s">
-        <v>220</v>
-      </c>
       <c r="J47" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K47" s="7" t="s">
         <v>36</v>
@@ -11409,7 +11409,7 @@
         <v>47</v>
       </c>
       <c r="P47" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q47" s="7" t="s">
         <v>39</v>
@@ -11442,16 +11442,16 @@
         <v>39</v>
       </c>
       <c r="AA47" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB47" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC47" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB47" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC47" s="7" t="s">
-        <v>255</v>
-      </c>
       <c r="AD47" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AE47" s="7" t="s">
         <v>39</v>
@@ -11463,7 +11463,7 @@
         <v>47</v>
       </c>
       <c r="AH47" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="48" spans="1:34" x14ac:dyDescent="0.3">
@@ -11471,31 +11471,31 @@
         <v>33</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D48" s="6">
         <v>3</v>
       </c>
       <c r="E48" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="G48" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="F48" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="G48" s="7" t="s">
+      <c r="H48" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="I48" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="H48" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="I48" s="7" t="s">
-        <v>213</v>
-      </c>
       <c r="J48" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K48" s="7" t="s">
         <v>36</v>
@@ -11513,7 +11513,7 @@
         <v>47</v>
       </c>
       <c r="P48" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q48" s="7" t="s">
         <v>39</v>
@@ -11531,7 +11531,7 @@
         <v>0</v>
       </c>
       <c r="V48" s="6">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="W48" s="7" t="s">
         <v>50</v>
@@ -11540,22 +11540,22 @@
         <v>49</v>
       </c>
       <c r="Y48" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Z48" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AA48" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB48" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC48" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB48" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC48" s="7" t="s">
-        <v>255</v>
-      </c>
       <c r="AD48" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AE48" s="7" t="s">
         <v>39</v>
@@ -11575,31 +11575,31 @@
         <v>33</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D49" s="6">
         <v>1</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G49" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="H49" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="H49" s="7" t="s">
+      <c r="I49" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="I49" s="7" t="s">
-        <v>181</v>
-      </c>
       <c r="J49" s="7" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="K49" s="7" t="s">
         <v>36</v>
@@ -11617,7 +11617,7 @@
         <v>47</v>
       </c>
       <c r="P49" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q49" s="7" t="s">
         <v>39</v>
@@ -11650,16 +11650,16 @@
         <v>39</v>
       </c>
       <c r="AA49" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB49" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC49" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="AB49" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC49" s="7" t="s">
-        <v>255</v>
-      </c>
       <c r="AD49" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AE49" s="7" t="s">
         <v>39</v>
@@ -11671,7 +11671,7 @@
         <v>47</v>
       </c>
       <c r="AH49" s="7" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="50" spans="1:34" x14ac:dyDescent="0.3">
@@ -11679,19 +11679,19 @@
         <v>33</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D50" s="6">
         <v>2</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G50" s="7" t="s">
         <v>74</v>
@@ -11703,7 +11703,7 @@
         <v>75</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="K50" s="7" t="s">
         <v>36</v>
@@ -11721,7 +11721,7 @@
         <v>47</v>
       </c>
       <c r="P50" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q50" s="7" t="s">
         <v>39</v>
@@ -11748,34 +11748,34 @@
         <v>49</v>
       </c>
       <c r="Y50" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="Z50" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA50" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB50" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC50" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="AD50" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="AE50" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF50" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG50" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH50" s="7" t="s">
         <v>276</v>
-      </c>
-      <c r="Z50" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AA50" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="AB50" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC50" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="AD50" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="AE50" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF50" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG50" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH50" s="7" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="51" spans="1:34" x14ac:dyDescent="0.3">
@@ -11783,31 +11783,31 @@
         <v>33</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D51" s="6">
         <v>3</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G51" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="H51" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="I51" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="H51" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="I51" s="7" t="s">
-        <v>153</v>
-      </c>
       <c r="J51" s="7" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="K51" s="7" t="s">
         <v>36</v>
@@ -11825,7 +11825,7 @@
         <v>47</v>
       </c>
       <c r="P51" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q51" s="7" t="s">
         <v>39</v>
@@ -11852,34 +11852,34 @@
         <v>49</v>
       </c>
       <c r="Y51" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="Z51" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA51" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB51" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC51" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="AD51" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="AE51" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF51" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG51" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH51" s="7" t="s">
         <v>276</v>
-      </c>
-      <c r="Z51" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AA51" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="AB51" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC51" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="AD51" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="AE51" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF51" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG51" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH51" s="7" t="s">
-        <v>278</v>
       </c>
     </row>
   </sheetData>

--- a/리드지 발주현황.xlsx
+++ b/리드지 발주현황.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\유현아\Documents\GitHub\INTEROJO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E66EF61-4A8B-4872-921A-EEE79E064E15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CCBF8DD-29DF-4D26-8C7C-FF1B85D61547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{500E376A-1243-49DE-9EFA-B2AD708B3011}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2667" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2823" uniqueCount="294">
   <si>
     <t>G/W</t>
   </si>
@@ -888,7 +888,43 @@
     <t>2026-06-18 오전 9:16:17</t>
   </si>
   <si>
-    <t>2026-06-18 오후 3:55:55</t>
+    <t>BS0343</t>
+  </si>
+  <si>
+    <t>BS0343-001</t>
+  </si>
+  <si>
+    <t>알루미늄리드지 (렌즈미 CleanFit O2 clear 1Day (30개입))</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-06-19 오전 11:44:09</t>
+  </si>
+  <si>
+    <t>PO-2606190003</t>
+  </si>
+  <si>
+    <t>PR-2606190005</t>
+  </si>
+  <si>
+    <t>2026-06-19 오후 3:14:46</t>
+  </si>
+  <si>
+    <t>BS0031</t>
+  </si>
+  <si>
+    <t>BS0031-004</t>
+  </si>
+  <si>
+    <t>알루미늄리드지 (원데이-MPG&amp;E)_유광 코팅</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>20260619P227-0027</t>
   </si>
 </sst>
 </file>
@@ -2242,13 +2278,13 @@
         <v>34</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>36</v>
@@ -2263,34 +2299,34 @@
         <v>39</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>127</v>
+        <v>281</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>128</v>
+        <v>282</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>129</v>
+        <v>283</v>
       </c>
       <c r="M10" s="3">
-        <v>2000000</v>
+        <v>300000</v>
       </c>
       <c r="N10" s="3">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="O10" s="3">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="P10" s="3">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="3">
         <v>0</v>
       </c>
       <c r="R10" s="3">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="T10" s="4" t="s">
         <v>44</v>
@@ -2302,10 +2338,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W10" s="3">
-        <v>19600000</v>
+        <v>2940000</v>
       </c>
       <c r="X10" s="5" t="s">
-        <v>90</v>
+        <v>284</v>
       </c>
       <c r="Y10" s="4" t="s">
         <v>47</v>
@@ -2323,13 +2359,13 @@
         <v>50</v>
       </c>
       <c r="AD10" s="4" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="AE10" s="4" t="s">
-        <v>130</v>
+        <v>286</v>
       </c>
       <c r="AF10" s="4" t="s">
-        <v>135</v>
+        <v>287</v>
       </c>
       <c r="AG10" s="3">
         <v>2</v>
@@ -2364,31 +2400,31 @@
         <v>39</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>80</v>
+        <v>127</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>82</v>
+        <v>129</v>
       </c>
       <c r="M11" s="3">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="N11" s="3">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="O11" s="3">
         <v>0</v>
       </c>
       <c r="P11" s="3">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="Q11" s="3">
         <v>0</v>
       </c>
       <c r="R11" s="3">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="S11" s="4" t="s">
         <v>43</v>
@@ -2403,10 +2439,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W11" s="3">
-        <v>1960000</v>
+        <v>19600000</v>
       </c>
       <c r="X11" s="5" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="Y11" s="4" t="s">
         <v>47</v>
@@ -2424,7 +2460,7 @@
         <v>50</v>
       </c>
       <c r="AD11" s="4" t="s">
-        <v>83</v>
+        <v>279</v>
       </c>
       <c r="AE11" s="4" t="s">
         <v>130</v>
@@ -2433,7 +2469,7 @@
         <v>135</v>
       </c>
       <c r="AG11" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.3">
@@ -2444,13 +2480,13 @@
         <v>34</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>61</v>
+        <v>108</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>61</v>
+        <v>108</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>61</v>
+        <v>108</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>36</v>
@@ -2465,31 +2501,31 @@
         <v>39</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="M12" s="3">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="N12" s="3">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="O12" s="3">
         <v>0</v>
       </c>
       <c r="P12" s="3">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="Q12" s="3">
         <v>0</v>
       </c>
       <c r="R12" s="3">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="S12" s="4" t="s">
         <v>43</v>
@@ -2504,7 +2540,7 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W12" s="3">
-        <v>19600000</v>
+        <v>1960000</v>
       </c>
       <c r="X12" s="5" t="s">
         <v>72</v>
@@ -2525,16 +2561,16 @@
         <v>50</v>
       </c>
       <c r="AD12" s="4" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AE12" s="4" t="s">
-        <v>67</v>
+        <v>130</v>
       </c>
       <c r="AF12" s="4" t="s">
-        <v>68</v>
+        <v>135</v>
       </c>
       <c r="AG12" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.3">
@@ -2545,13 +2581,13 @@
         <v>34</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>36</v>
@@ -2566,31 +2602,31 @@
         <v>39</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>136</v>
+        <v>55</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>137</v>
+        <v>56</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>138</v>
+        <v>57</v>
       </c>
       <c r="M13" s="3">
-        <v>300000</v>
+        <v>2000000</v>
       </c>
       <c r="N13" s="3">
-        <v>300000</v>
+        <v>2000000</v>
       </c>
       <c r="O13" s="3">
         <v>0</v>
       </c>
       <c r="P13" s="3">
-        <v>300000</v>
+        <v>2000000</v>
       </c>
       <c r="Q13" s="3">
         <v>0</v>
       </c>
       <c r="R13" s="3">
-        <v>300000</v>
+        <v>2000000</v>
       </c>
       <c r="S13" s="4" t="s">
         <v>43</v>
@@ -2605,10 +2641,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W13" s="3">
-        <v>2940000</v>
+        <v>19600000</v>
       </c>
       <c r="X13" s="5" t="s">
-        <v>118</v>
+        <v>72</v>
       </c>
       <c r="Y13" s="4" t="s">
         <v>47</v>
@@ -2620,22 +2656,22 @@
         <v>49</v>
       </c>
       <c r="AB13" s="4" t="s">
-        <v>139</v>
+        <v>39</v>
       </c>
       <c r="AC13" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD13" s="4" t="s">
-        <v>209</v>
+        <v>73</v>
       </c>
       <c r="AE13" s="4" t="s">
-        <v>120</v>
+        <v>67</v>
       </c>
       <c r="AF13" s="4" t="s">
-        <v>121</v>
+        <v>68</v>
       </c>
       <c r="AG13" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.3">
@@ -2646,13 +2682,13 @@
         <v>34</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>206</v>
+        <v>91</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>206</v>
+        <v>91</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>206</v>
+        <v>91</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>36</v>
@@ -2667,34 +2703,34 @@
         <v>39</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>92</v>
+        <v>136</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>93</v>
+        <v>137</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>94</v>
+        <v>138</v>
       </c>
       <c r="M14" s="3">
         <v>300000</v>
       </c>
       <c r="N14" s="3">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>300000</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
       <c r="R14" s="3">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="S14" s="4" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T14" s="4" t="s">
         <v>44</v>
@@ -2709,7 +2745,7 @@
         <v>2940000</v>
       </c>
       <c r="X14" s="5" t="s">
-        <v>197</v>
+        <v>118</v>
       </c>
       <c r="Y14" s="4" t="s">
         <v>47</v>
@@ -2721,22 +2757,22 @@
         <v>49</v>
       </c>
       <c r="AB14" s="4" t="s">
-        <v>39</v>
+        <v>139</v>
       </c>
       <c r="AC14" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD14" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AE14" s="4" t="s">
-        <v>208</v>
+        <v>120</v>
       </c>
       <c r="AF14" s="4" t="s">
-        <v>193</v>
+        <v>121</v>
       </c>
       <c r="AG14" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.3">
@@ -2747,13 +2783,13 @@
         <v>34</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>58</v>
+        <v>206</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>36</v>
@@ -2768,31 +2804,31 @@
         <v>39</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>172</v>
+        <v>92</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>174</v>
+        <v>93</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>173</v>
+        <v>94</v>
       </c>
       <c r="M15" s="3">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="N15" s="3">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
       </c>
       <c r="P15" s="3">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
       <c r="R15" s="3">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="S15" s="4" t="s">
         <v>43</v>
@@ -2807,10 +2843,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W15" s="3">
-        <v>1960000</v>
+        <v>2940000</v>
       </c>
       <c r="X15" s="5" t="s">
-        <v>126</v>
+        <v>197</v>
       </c>
       <c r="Y15" s="4" t="s">
         <v>47</v>
@@ -2828,16 +2864,16 @@
         <v>50</v>
       </c>
       <c r="AD15" s="4" t="s">
-        <v>191</v>
+        <v>288</v>
       </c>
       <c r="AE15" s="4" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="AF15" s="4" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AG15" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.3">
@@ -2848,13 +2884,13 @@
         <v>34</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>108</v>
+        <v>189</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>108</v>
+        <v>189</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>108</v>
+        <v>58</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>36</v>
@@ -2869,31 +2905,31 @@
         <v>39</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>99</v>
+        <v>172</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>100</v>
+        <v>174</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>101</v>
+        <v>173</v>
       </c>
       <c r="M16" s="3">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="N16" s="3">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="O16" s="3">
         <v>0</v>
       </c>
       <c r="P16" s="3">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="Q16" s="3">
         <v>0</v>
       </c>
       <c r="R16" s="3">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="S16" s="4" t="s">
         <v>43</v>
@@ -2905,13 +2941,13 @@
         <v>45</v>
       </c>
       <c r="V16" s="3">
-        <v>6.7</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="W16" s="3">
-        <v>13400000</v>
+        <v>1960000</v>
       </c>
       <c r="X16" s="5" t="s">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="Y16" s="4" t="s">
         <v>47</v>
@@ -2929,13 +2965,13 @@
         <v>50</v>
       </c>
       <c r="AD16" s="4" t="s">
-        <v>140</v>
+        <v>191</v>
       </c>
       <c r="AE16" s="4" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="AF16" s="4" t="s">
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="AG16" s="3">
         <v>1</v>
@@ -2949,13 +2985,13 @@
         <v>34</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>36</v>
@@ -2970,31 +3006,31 @@
         <v>39</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>141</v>
+        <v>99</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>143</v>
+        <v>101</v>
       </c>
       <c r="M17" s="3">
-        <v>300000</v>
+        <v>2000000</v>
       </c>
       <c r="N17" s="3">
-        <v>300000</v>
+        <v>2000000</v>
       </c>
       <c r="O17" s="3">
         <v>0</v>
       </c>
       <c r="P17" s="3">
-        <v>300000</v>
+        <v>2000000</v>
       </c>
       <c r="Q17" s="3">
         <v>0</v>
       </c>
       <c r="R17" s="3">
-        <v>300000</v>
+        <v>2000000</v>
       </c>
       <c r="S17" s="4" t="s">
         <v>43</v>
@@ -3006,13 +3042,13 @@
         <v>45</v>
       </c>
       <c r="V17" s="3">
-        <v>9.8000000000000007</v>
+        <v>6.7</v>
       </c>
       <c r="W17" s="3">
-        <v>2940000</v>
+        <v>13400000</v>
       </c>
       <c r="X17" s="5" t="s">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="Y17" s="4" t="s">
         <v>47</v>
@@ -3030,16 +3066,16 @@
         <v>50</v>
       </c>
       <c r="AD17" s="4" t="s">
-        <v>191</v>
+        <v>140</v>
       </c>
       <c r="AE17" s="4" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AF17" s="4" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="AG17" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.3">
@@ -3050,13 +3086,13 @@
         <v>34</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>189</v>
+        <v>91</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>189</v>
+        <v>91</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>36</v>
@@ -3071,31 +3107,31 @@
         <v>39</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>175</v>
+        <v>141</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>177</v>
+        <v>142</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>176</v>
+        <v>143</v>
       </c>
       <c r="M18" s="3">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="N18" s="3">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="O18" s="3">
         <v>0</v>
       </c>
       <c r="P18" s="3">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="Q18" s="3">
         <v>0</v>
       </c>
       <c r="R18" s="3">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="S18" s="4" t="s">
         <v>43</v>
@@ -3110,10 +3146,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W18" s="3">
-        <v>1960000</v>
+        <v>2940000</v>
       </c>
       <c r="X18" s="5" t="s">
-        <v>166</v>
+        <v>126</v>
       </c>
       <c r="Y18" s="4" t="s">
         <v>47</v>
@@ -3131,13 +3167,13 @@
         <v>50</v>
       </c>
       <c r="AD18" s="4" t="s">
-        <v>217</v>
+        <v>191</v>
       </c>
       <c r="AE18" s="4" t="s">
-        <v>190</v>
+        <v>120</v>
       </c>
       <c r="AF18" s="4" t="s">
-        <v>171</v>
+        <v>121</v>
       </c>
       <c r="AG18" s="3">
         <v>4</v>
@@ -3151,13 +3187,13 @@
         <v>34</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>273</v>
+        <v>189</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>273</v>
+        <v>189</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>273</v>
+        <v>58</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>36</v>
@@ -3172,34 +3208,34 @@
         <v>39</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>74</v>
+        <v>175</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>75</v>
+        <v>177</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>76</v>
+        <v>176</v>
       </c>
       <c r="M19" s="3">
-        <v>500000</v>
+        <v>200000</v>
       </c>
       <c r="N19" s="3">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="O19" s="3">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="P19" s="3">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="Q19" s="3">
         <v>0</v>
       </c>
       <c r="R19" s="3">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="S19" s="4" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T19" s="4" t="s">
         <v>44</v>
@@ -3211,10 +3247,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W19" s="3">
-        <v>4900000</v>
+        <v>1960000</v>
       </c>
       <c r="X19" s="5" t="s">
-        <v>274</v>
+        <v>166</v>
       </c>
       <c r="Y19" s="4" t="s">
         <v>47</v>
@@ -3232,16 +3268,16 @@
         <v>50</v>
       </c>
       <c r="AD19" s="4" t="s">
-        <v>276</v>
+        <v>217</v>
       </c>
       <c r="AE19" s="4" t="s">
-        <v>277</v>
+        <v>190</v>
       </c>
       <c r="AF19" s="4" t="s">
-        <v>271</v>
+        <v>171</v>
       </c>
       <c r="AG19" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.3">
@@ -3252,13 +3288,13 @@
         <v>34</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>108</v>
+        <v>273</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>108</v>
+        <v>273</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>108</v>
+        <v>273</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>36</v>
@@ -3273,34 +3309,34 @@
         <v>39</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="M20" s="3">
         <v>500000</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>500000</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
       <c r="R20" s="3">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="S20" s="4" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="T20" s="4" t="s">
         <v>44</v>
@@ -3315,7 +3351,7 @@
         <v>4900000</v>
       </c>
       <c r="X20" s="5" t="s">
-        <v>72</v>
+        <v>274</v>
       </c>
       <c r="Y20" s="4" t="s">
         <v>47</v>
@@ -3333,16 +3369,16 @@
         <v>50</v>
       </c>
       <c r="AD20" s="4" t="s">
-        <v>83</v>
+        <v>276</v>
       </c>
       <c r="AE20" s="4" t="s">
-        <v>130</v>
+        <v>277</v>
       </c>
       <c r="AF20" s="4" t="s">
-        <v>135</v>
+        <v>271</v>
       </c>
       <c r="AG20" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.3">
@@ -3353,13 +3389,13 @@
         <v>34</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>210</v>
+        <v>108</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>210</v>
+        <v>108</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>36</v>
@@ -3374,34 +3410,34 @@
         <v>39</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>218</v>
+        <v>84</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>219</v>
+        <v>85</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>220</v>
+        <v>86</v>
       </c>
       <c r="M21" s="3">
-        <v>20000</v>
+        <v>500000</v>
       </c>
       <c r="N21" s="3">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="O21" s="3">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P21" s="3">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="Q21" s="3">
         <v>0</v>
       </c>
       <c r="R21" s="3">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="S21" s="4" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T21" s="4" t="s">
         <v>44</v>
@@ -3413,10 +3449,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W21" s="3">
-        <v>196000</v>
+        <v>4900000</v>
       </c>
       <c r="X21" s="5" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Y21" s="4" t="s">
         <v>47</v>
@@ -3434,16 +3470,16 @@
         <v>50</v>
       </c>
       <c r="AD21" s="4" t="s">
-        <v>214</v>
+        <v>83</v>
       </c>
       <c r="AE21" s="4" t="s">
-        <v>215</v>
+        <v>130</v>
       </c>
       <c r="AF21" s="4" t="s">
-        <v>216</v>
+        <v>135</v>
       </c>
       <c r="AG21" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.3">
@@ -3454,13 +3490,13 @@
         <v>34</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>35</v>
+        <v>210</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>35</v>
+        <v>126</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>35</v>
+        <v>210</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>36</v>
@@ -3475,34 +3511,34 @@
         <v>39</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>96</v>
+        <v>218</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>97</v>
+        <v>219</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>98</v>
+        <v>220</v>
       </c>
       <c r="M22" s="3">
-        <v>300000</v>
+        <v>20000</v>
       </c>
       <c r="N22" s="3">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="O22" s="3">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="P22" s="3">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
       <c r="R22" s="3">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="S22" s="4" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="T22" s="4" t="s">
         <v>44</v>
@@ -3511,13 +3547,13 @@
         <v>45</v>
       </c>
       <c r="V22" s="3">
-        <v>8.5</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="W22" s="3">
-        <v>2550000</v>
+        <v>196000</v>
       </c>
       <c r="X22" s="5" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="Y22" s="4" t="s">
         <v>47</v>
@@ -3535,16 +3571,16 @@
         <v>50</v>
       </c>
       <c r="AD22" s="4" t="s">
-        <v>95</v>
+        <v>214</v>
       </c>
       <c r="AE22" s="4" t="s">
-        <v>52</v>
+        <v>215</v>
       </c>
       <c r="AF22" s="4" t="s">
-        <v>53</v>
+        <v>216</v>
       </c>
       <c r="AG22" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.3">
@@ -3555,13 +3591,13 @@
         <v>34</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>36</v>
@@ -3576,13 +3612,13 @@
         <v>39</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>144</v>
+        <v>96</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>145</v>
+        <v>97</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>146</v>
+        <v>98</v>
       </c>
       <c r="M23" s="3">
         <v>300000</v>
@@ -3612,13 +3648,13 @@
         <v>45</v>
       </c>
       <c r="V23" s="3">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W23" s="3">
-        <v>0</v>
+        <v>2550000</v>
       </c>
       <c r="X23" s="5" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="Y23" s="4" t="s">
         <v>47</v>
@@ -3636,16 +3672,16 @@
         <v>50</v>
       </c>
       <c r="AD23" s="4" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="AE23" s="4" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="AF23" s="4" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="AG23" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.3">
@@ -3656,13 +3692,13 @@
         <v>34</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>206</v>
+        <v>54</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>206</v>
+        <v>46</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>206</v>
+        <v>46</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>36</v>
@@ -3677,34 +3713,34 @@
         <v>39</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>55</v>
+        <v>144</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>56</v>
+        <v>145</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>57</v>
+        <v>146</v>
       </c>
       <c r="M24" s="3">
-        <v>5000000</v>
+        <v>300000</v>
       </c>
       <c r="N24" s="3">
-        <v>2478000</v>
+        <v>300000</v>
       </c>
       <c r="O24" s="3">
-        <v>2522000</v>
+        <v>0</v>
       </c>
       <c r="P24" s="3">
-        <v>2478000</v>
+        <v>300000</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
       <c r="R24" s="3">
-        <v>2478000</v>
+        <v>300000</v>
       </c>
       <c r="S24" s="4" t="s">
-        <v>125</v>
+        <v>43</v>
       </c>
       <c r="T24" s="4" t="s">
         <v>44</v>
@@ -3713,13 +3749,13 @@
         <v>45</v>
       </c>
       <c r="V24" s="3">
-        <v>9.8000000000000007</v>
+        <v>0</v>
       </c>
       <c r="W24" s="3">
-        <v>49000000</v>
+        <v>0</v>
       </c>
       <c r="X24" s="5" t="s">
-        <v>166</v>
+        <v>58</v>
       </c>
       <c r="Y24" s="4" t="s">
         <v>47</v>
@@ -3737,16 +3773,16 @@
         <v>50</v>
       </c>
       <c r="AD24" s="4" t="s">
-        <v>226</v>
+        <v>191</v>
       </c>
       <c r="AE24" s="4" t="s">
-        <v>208</v>
+        <v>59</v>
       </c>
       <c r="AF24" s="4" t="s">
-        <v>193</v>
+        <v>60</v>
       </c>
       <c r="AG24" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.3">
@@ -3757,13 +3793,13 @@
         <v>34</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>206</v>
+        <v>118</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>206</v>
+        <v>118</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>206</v>
+        <v>118</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>36</v>
@@ -3778,13 +3814,13 @@
         <v>39</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>201</v>
+        <v>289</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>203</v>
+        <v>290</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>202</v>
+        <v>291</v>
       </c>
       <c r="M25" s="3">
         <v>500000</v>
@@ -3820,7 +3856,7 @@
         <v>4900000</v>
       </c>
       <c r="X25" s="5" t="s">
-        <v>185</v>
+        <v>292</v>
       </c>
       <c r="Y25" s="4" t="s">
         <v>47</v>
@@ -3832,22 +3868,22 @@
         <v>49</v>
       </c>
       <c r="AB25" s="4" t="s">
-        <v>204</v>
+        <v>39</v>
       </c>
       <c r="AC25" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD25" s="4" t="s">
-        <v>207</v>
+        <v>285</v>
       </c>
       <c r="AE25" s="4" t="s">
-        <v>208</v>
+        <v>286</v>
       </c>
       <c r="AF25" s="4" t="s">
-        <v>193</v>
+        <v>287</v>
       </c>
       <c r="AG25" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:33" x14ac:dyDescent="0.3">
@@ -3858,13 +3894,13 @@
         <v>34</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>58</v>
+        <v>206</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>36</v>
@@ -3879,34 +3915,34 @@
         <v>39</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="M26" s="3">
-        <v>200000</v>
+        <v>5000000</v>
       </c>
       <c r="N26" s="3">
-        <v>200000</v>
+        <v>2478000</v>
       </c>
       <c r="O26" s="3">
-        <v>0</v>
+        <v>2522000</v>
       </c>
       <c r="P26" s="3">
-        <v>200000</v>
+        <v>2478000</v>
       </c>
       <c r="Q26" s="3">
         <v>0</v>
       </c>
       <c r="R26" s="3">
-        <v>200000</v>
+        <v>2478000</v>
       </c>
       <c r="S26" s="4" t="s">
-        <v>43</v>
+        <v>125</v>
       </c>
       <c r="T26" s="4" t="s">
         <v>44</v>
@@ -3918,10 +3954,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W26" s="3">
-        <v>1960000</v>
+        <v>49000000</v>
       </c>
       <c r="X26" s="5" t="s">
-        <v>126</v>
+        <v>166</v>
       </c>
       <c r="Y26" s="4" t="s">
         <v>47</v>
@@ -3939,16 +3975,16 @@
         <v>50</v>
       </c>
       <c r="AD26" s="4" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="AE26" s="4" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="AF26" s="4" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="AG26" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.3">
@@ -3959,13 +3995,13 @@
         <v>34</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>273</v>
+        <v>206</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>273</v>
+        <v>206</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>273</v>
+        <v>206</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>36</v>
@@ -3980,34 +4016,34 @@
         <v>39</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="L27" s="4" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="M27" s="3">
-        <v>2000000</v>
+        <v>500000</v>
       </c>
       <c r="N27" s="3">
-        <v>115000</v>
+        <v>0</v>
       </c>
       <c r="O27" s="3">
-        <v>1885000</v>
+        <v>500000</v>
       </c>
       <c r="P27" s="3">
-        <v>115000</v>
+        <v>0</v>
       </c>
       <c r="Q27" s="3">
         <v>0</v>
       </c>
       <c r="R27" s="3">
-        <v>115000</v>
+        <v>0</v>
       </c>
       <c r="S27" s="4" t="s">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="T27" s="4" t="s">
         <v>44</v>
@@ -4019,10 +4055,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W27" s="3">
-        <v>19600000</v>
+        <v>4900000</v>
       </c>
       <c r="X27" s="5" t="s">
-        <v>118</v>
+        <v>185</v>
       </c>
       <c r="Y27" s="4" t="s">
         <v>47</v>
@@ -4034,22 +4070,22 @@
         <v>49</v>
       </c>
       <c r="AB27" s="4" t="s">
-        <v>39</v>
+        <v>204</v>
       </c>
       <c r="AC27" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD27" s="4" t="s">
-        <v>278</v>
+        <v>207</v>
       </c>
       <c r="AE27" s="4" t="s">
-        <v>277</v>
+        <v>208</v>
       </c>
       <c r="AF27" s="4" t="s">
-        <v>271</v>
+        <v>193</v>
       </c>
       <c r="AG27" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.3">
@@ -4060,13 +4096,13 @@
         <v>34</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>108</v>
+        <v>189</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>108</v>
+        <v>189</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>108</v>
+        <v>58</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>36</v>
@@ -4081,13 +4117,13 @@
         <v>39</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="M28" s="3">
         <v>200000</v>
@@ -4123,7 +4159,7 @@
         <v>1960000</v>
       </c>
       <c r="X28" s="5" t="s">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="Y28" s="4" t="s">
         <v>47</v>
@@ -4141,13 +4177,13 @@
         <v>50</v>
       </c>
       <c r="AD28" s="4" t="s">
-        <v>95</v>
+        <v>209</v>
       </c>
       <c r="AE28" s="4" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="AF28" s="4" t="s">
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="AG28" s="3">
         <v>3</v>
@@ -4161,13 +4197,13 @@
         <v>34</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>54</v>
+        <v>273</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>46</v>
+        <v>273</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>46</v>
+        <v>273</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>36</v>
@@ -4182,34 +4218,34 @@
         <v>39</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>147</v>
+        <v>178</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="M29" s="3">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="N29" s="3">
-        <v>200000</v>
+        <v>743000</v>
       </c>
       <c r="O29" s="3">
-        <v>0</v>
+        <v>1257000</v>
       </c>
       <c r="P29" s="3">
-        <v>200000</v>
+        <v>115000</v>
       </c>
       <c r="Q29" s="3">
         <v>0</v>
       </c>
       <c r="R29" s="3">
-        <v>200000</v>
+        <v>115000</v>
       </c>
       <c r="S29" s="4" t="s">
-        <v>43</v>
+        <v>125</v>
       </c>
       <c r="T29" s="4" t="s">
         <v>44</v>
@@ -4218,13 +4254,13 @@
         <v>45</v>
       </c>
       <c r="V29" s="3">
-        <v>34</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="W29" s="3">
-        <v>6800000</v>
+        <v>19600000</v>
       </c>
       <c r="X29" s="5" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
       <c r="Y29" s="4" t="s">
         <v>47</v>
@@ -4242,16 +4278,16 @@
         <v>50</v>
       </c>
       <c r="AD29" s="4" t="s">
-        <v>205</v>
+        <v>288</v>
       </c>
       <c r="AE29" s="4" t="s">
-        <v>59</v>
+        <v>277</v>
       </c>
       <c r="AF29" s="4" t="s">
-        <v>60</v>
+        <v>271</v>
       </c>
       <c r="AG29" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.3">
@@ -4262,13 +4298,13 @@
         <v>34</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>210</v>
+        <v>118</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>210</v>
+        <v>118</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>36</v>
@@ -4283,34 +4319,34 @@
         <v>39</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>221</v>
+        <v>178</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>222</v>
+        <v>180</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>223</v>
+        <v>179</v>
       </c>
       <c r="M30" s="3">
-        <v>1500000</v>
+        <v>1000000</v>
       </c>
       <c r="N30" s="3">
-        <v>1500000</v>
+        <v>0</v>
       </c>
       <c r="O30" s="3">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="P30" s="3">
-        <v>1500000</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="3">
         <v>0</v>
       </c>
       <c r="R30" s="3">
-        <v>1500000</v>
+        <v>0</v>
       </c>
       <c r="S30" s="4" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="T30" s="4" t="s">
         <v>44</v>
@@ -4322,10 +4358,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W30" s="3">
-        <v>14700000</v>
+        <v>9800000</v>
       </c>
       <c r="X30" s="5" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="Y30" s="4" t="s">
         <v>47</v>
@@ -4343,13 +4379,13 @@
         <v>50</v>
       </c>
       <c r="AD30" s="4" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="AE30" s="4" t="s">
-        <v>215</v>
+        <v>286</v>
       </c>
       <c r="AF30" s="4" t="s">
-        <v>216</v>
+        <v>287</v>
       </c>
       <c r="AG30" s="3">
         <v>1</v>
@@ -4384,13 +4420,13 @@
         <v>39</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="M31" s="3">
         <v>200000</v>
@@ -4444,7 +4480,7 @@
         <v>50</v>
       </c>
       <c r="AD31" s="4" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AE31" s="4" t="s">
         <v>130</v>
@@ -4453,7 +4489,7 @@
         <v>135</v>
       </c>
       <c r="AG31" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.3">
@@ -4464,13 +4500,13 @@
         <v>34</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>36</v>
@@ -4485,31 +4521,31 @@
         <v>39</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="M32" s="3">
-        <v>1000000</v>
+        <v>200000</v>
       </c>
       <c r="N32" s="3">
-        <v>1000000</v>
+        <v>200000</v>
       </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
       <c r="P32" s="3">
-        <v>1000000</v>
+        <v>200000</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
       <c r="R32" s="3">
-        <v>1000000</v>
+        <v>200000</v>
       </c>
       <c r="S32" s="4" t="s">
         <v>43</v>
@@ -4521,13 +4557,13 @@
         <v>45</v>
       </c>
       <c r="V32" s="3">
-        <v>9.8000000000000007</v>
+        <v>34</v>
       </c>
       <c r="W32" s="3">
-        <v>9800000</v>
+        <v>6800000</v>
       </c>
       <c r="X32" s="5" t="s">
-        <v>72</v>
+        <v>150</v>
       </c>
       <c r="Y32" s="4" t="s">
         <v>47</v>
@@ -4545,16 +4581,16 @@
         <v>50</v>
       </c>
       <c r="AD32" s="4" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="AE32" s="4" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="AF32" s="4" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="AG32" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:33" x14ac:dyDescent="0.3">
@@ -4565,13 +4601,13 @@
         <v>34</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>35</v>
+        <v>210</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>35</v>
+        <v>126</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>35</v>
+        <v>210</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>36</v>
@@ -4586,31 +4622,31 @@
         <v>39</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>99</v>
+        <v>221</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>100</v>
+        <v>222</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>101</v>
+        <v>223</v>
       </c>
       <c r="M33" s="3">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="N33" s="3">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="O33" s="3">
         <v>0</v>
       </c>
       <c r="P33" s="3">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="Q33" s="3">
         <v>0</v>
       </c>
       <c r="R33" s="3">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="S33" s="4" t="s">
         <v>43</v>
@@ -4622,13 +4658,13 @@
         <v>45</v>
       </c>
       <c r="V33" s="3">
-        <v>6.7</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="W33" s="3">
-        <v>13400000</v>
+        <v>14700000</v>
       </c>
       <c r="X33" s="5" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="Y33" s="4" t="s">
         <v>47</v>
@@ -4646,16 +4682,16 @@
         <v>50</v>
       </c>
       <c r="AD33" s="4" t="s">
-        <v>154</v>
+        <v>275</v>
       </c>
       <c r="AE33" s="4" t="s">
-        <v>52</v>
+        <v>215</v>
       </c>
       <c r="AF33" s="4" t="s">
-        <v>53</v>
+        <v>216</v>
       </c>
       <c r="AG33" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:33" x14ac:dyDescent="0.3">
@@ -4666,13 +4702,13 @@
         <v>34</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>189</v>
+        <v>108</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>189</v>
+        <v>108</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>58</v>
+        <v>108</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>36</v>
@@ -4687,31 +4723,31 @@
         <v>39</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>182</v>
+        <v>87</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>184</v>
+        <v>88</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>183</v>
+        <v>89</v>
       </c>
       <c r="M34" s="3">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="N34" s="3">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="O34" s="3">
         <v>0</v>
       </c>
       <c r="P34" s="3">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="Q34" s="3">
         <v>0</v>
       </c>
       <c r="R34" s="3">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="S34" s="4" t="s">
         <v>43</v>
@@ -4726,10 +4762,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W34" s="3">
-        <v>2940000</v>
+        <v>1960000</v>
       </c>
       <c r="X34" s="5" t="s">
-        <v>185</v>
+        <v>72</v>
       </c>
       <c r="Y34" s="4" t="s">
         <v>47</v>
@@ -4747,13 +4783,13 @@
         <v>50</v>
       </c>
       <c r="AD34" s="4" t="s">
-        <v>279</v>
+        <v>83</v>
       </c>
       <c r="AE34" s="4" t="s">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="AF34" s="4" t="s">
-        <v>171</v>
+        <v>135</v>
       </c>
       <c r="AG34" s="3">
         <v>6</v>
@@ -4767,13 +4803,13 @@
         <v>34</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>36</v>
@@ -4788,31 +4824,31 @@
         <v>39</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>109</v>
+        <v>151</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>110</v>
+        <v>152</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>111</v>
+        <v>153</v>
       </c>
       <c r="M35" s="3">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="N35" s="3">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="O35" s="3">
         <v>0</v>
       </c>
       <c r="P35" s="3">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="Q35" s="3">
         <v>0</v>
       </c>
       <c r="R35" s="3">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="S35" s="4" t="s">
         <v>43</v>
@@ -4827,10 +4863,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W35" s="3">
-        <v>1960000</v>
+        <v>9800000</v>
       </c>
       <c r="X35" s="5" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="Y35" s="4" t="s">
         <v>47</v>
@@ -4842,22 +4878,22 @@
         <v>49</v>
       </c>
       <c r="AB35" s="4" t="s">
-        <v>122</v>
+        <v>39</v>
       </c>
       <c r="AC35" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD35" s="4" t="s">
-        <v>106</v>
+        <v>187</v>
       </c>
       <c r="AE35" s="4" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="AF35" s="4" t="s">
-        <v>123</v>
+        <v>68</v>
       </c>
       <c r="AG35" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:33" x14ac:dyDescent="0.3">
@@ -4868,13 +4904,13 @@
         <v>34</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>36</v>
@@ -4889,31 +4925,31 @@
         <v>39</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>155</v>
+        <v>99</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>156</v>
+        <v>100</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>157</v>
+        <v>101</v>
       </c>
       <c r="M36" s="3">
-        <v>300000</v>
+        <v>2000000</v>
       </c>
       <c r="N36" s="3">
-        <v>300000</v>
+        <v>2000000</v>
       </c>
       <c r="O36" s="3">
         <v>0</v>
       </c>
       <c r="P36" s="3">
-        <v>300000</v>
+        <v>2000000</v>
       </c>
       <c r="Q36" s="3">
         <v>0</v>
       </c>
       <c r="R36" s="3">
-        <v>300000</v>
+        <v>2000000</v>
       </c>
       <c r="S36" s="4" t="s">
         <v>43</v>
@@ -4925,13 +4961,13 @@
         <v>45</v>
       </c>
       <c r="V36" s="3">
-        <v>9.8000000000000007</v>
+        <v>6.7</v>
       </c>
       <c r="W36" s="3">
-        <v>2940000</v>
+        <v>13400000</v>
       </c>
       <c r="X36" s="5" t="s">
-        <v>58</v>
+        <v>107</v>
       </c>
       <c r="Y36" s="4" t="s">
         <v>47</v>
@@ -4949,16 +4985,16 @@
         <v>50</v>
       </c>
       <c r="AD36" s="4" t="s">
-        <v>186</v>
+        <v>154</v>
       </c>
       <c r="AE36" s="4" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="AF36" s="4" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="AG36" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:33" x14ac:dyDescent="0.3">
@@ -4969,13 +5005,13 @@
         <v>34</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>36</v>
@@ -4990,34 +5026,34 @@
         <v>39</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="M37" s="3">
-        <v>1000000</v>
+        <v>300000</v>
       </c>
       <c r="N37" s="3">
-        <v>345000</v>
+        <v>300000</v>
       </c>
       <c r="O37" s="3">
-        <v>655000</v>
+        <v>0</v>
       </c>
       <c r="P37" s="3">
-        <v>345000</v>
+        <v>300000</v>
       </c>
       <c r="Q37" s="3">
         <v>0</v>
       </c>
       <c r="R37" s="3">
-        <v>345000</v>
+        <v>300000</v>
       </c>
       <c r="S37" s="4" t="s">
-        <v>125</v>
+        <v>43</v>
       </c>
       <c r="T37" s="4" t="s">
         <v>44</v>
@@ -5026,13 +5062,13 @@
         <v>45</v>
       </c>
       <c r="V37" s="3">
-        <v>7.7</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="W37" s="3">
-        <v>7700000</v>
+        <v>2940000</v>
       </c>
       <c r="X37" s="5" t="s">
-        <v>72</v>
+        <v>185</v>
       </c>
       <c r="Y37" s="4" t="s">
         <v>47</v>
@@ -5050,16 +5086,16 @@
         <v>50</v>
       </c>
       <c r="AD37" s="4" t="s">
-        <v>224</v>
+        <v>279</v>
       </c>
       <c r="AE37" s="4" t="s">
-        <v>161</v>
+        <v>190</v>
       </c>
       <c r="AF37" s="4" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AG37" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:33" x14ac:dyDescent="0.3">
@@ -5070,13 +5106,13 @@
         <v>34</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>36</v>
@@ -5091,31 +5127,31 @@
         <v>39</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>165</v>
+        <v>111</v>
       </c>
       <c r="M38" s="3">
-        <v>500000</v>
+        <v>200000</v>
       </c>
       <c r="N38" s="3">
-        <v>500000</v>
+        <v>200000</v>
       </c>
       <c r="O38" s="3">
         <v>0</v>
       </c>
       <c r="P38" s="3">
-        <v>500000</v>
+        <v>200000</v>
       </c>
       <c r="Q38" s="3">
         <v>0</v>
       </c>
       <c r="R38" s="3">
-        <v>500000</v>
+        <v>200000</v>
       </c>
       <c r="S38" s="4" t="s">
         <v>43</v>
@@ -5130,10 +5166,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W38" s="3">
-        <v>4900000</v>
+        <v>1960000</v>
       </c>
       <c r="X38" s="5" t="s">
-        <v>166</v>
+        <v>107</v>
       </c>
       <c r="Y38" s="4" t="s">
         <v>47</v>
@@ -5145,22 +5181,22 @@
         <v>49</v>
       </c>
       <c r="AB38" s="4" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="AC38" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD38" s="4" t="s">
-        <v>225</v>
+        <v>106</v>
       </c>
       <c r="AE38" s="4" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="AF38" s="4" t="s">
-        <v>68</v>
+        <v>123</v>
       </c>
       <c r="AG38" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.3">
@@ -5171,13 +5207,13 @@
         <v>34</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>91</v>
+        <v>46</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>91</v>
+        <v>46</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>36</v>
@@ -5192,13 +5228,13 @@
         <v>39</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="L39" s="4" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="M39" s="3">
         <v>300000</v>
@@ -5234,7 +5270,7 @@
         <v>2940000</v>
       </c>
       <c r="X39" s="5" t="s">
-        <v>124</v>
+        <v>58</v>
       </c>
       <c r="Y39" s="4" t="s">
         <v>47</v>
@@ -5252,16 +5288,16 @@
         <v>50</v>
       </c>
       <c r="AD39" s="4" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="AE39" s="4" t="s">
-        <v>120</v>
+        <v>59</v>
       </c>
       <c r="AF39" s="4" t="s">
-        <v>121</v>
+        <v>60</v>
       </c>
       <c r="AG39" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:33" x14ac:dyDescent="0.3">
@@ -5272,13 +5308,13 @@
         <v>34</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>206</v>
+        <v>72</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>206</v>
+        <v>72</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>206</v>
+        <v>72</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>36</v>
@@ -5293,34 +5329,34 @@
         <v>39</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>194</v>
+        <v>158</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>196</v>
+        <v>159</v>
       </c>
       <c r="L40" s="4" t="s">
-        <v>195</v>
+        <v>160</v>
       </c>
       <c r="M40" s="3">
         <v>1000000</v>
       </c>
       <c r="N40" s="3">
-        <v>1000000</v>
+        <v>345000</v>
       </c>
       <c r="O40" s="3">
-        <v>0</v>
+        <v>655000</v>
       </c>
       <c r="P40" s="3">
-        <v>1000000</v>
+        <v>345000</v>
       </c>
       <c r="Q40" s="3">
         <v>0</v>
       </c>
       <c r="R40" s="3">
-        <v>1000000</v>
+        <v>345000</v>
       </c>
       <c r="S40" s="4" t="s">
-        <v>43</v>
+        <v>125</v>
       </c>
       <c r="T40" s="4" t="s">
         <v>44</v>
@@ -5329,13 +5365,13 @@
         <v>45</v>
       </c>
       <c r="V40" s="3">
-        <v>9.8000000000000007</v>
+        <v>7.7</v>
       </c>
       <c r="W40" s="3">
-        <v>9800000</v>
+        <v>7700000</v>
       </c>
       <c r="X40" s="5" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Y40" s="4" t="s">
         <v>47</v>
@@ -5353,16 +5389,16 @@
         <v>50</v>
       </c>
       <c r="AD40" s="4" t="s">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="AE40" s="4" t="s">
-        <v>208</v>
+        <v>161</v>
       </c>
       <c r="AF40" s="4" t="s">
-        <v>193</v>
+        <v>162</v>
       </c>
       <c r="AG40" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:33" x14ac:dyDescent="0.3">
@@ -5394,13 +5430,13 @@
         <v>39</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>74</v>
+        <v>163</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>75</v>
+        <v>164</v>
       </c>
       <c r="L41" s="4" t="s">
-        <v>76</v>
+        <v>165</v>
       </c>
       <c r="M41" s="3">
         <v>500000</v>
@@ -5436,7 +5472,7 @@
         <v>4900000</v>
       </c>
       <c r="X41" s="5" t="s">
-        <v>124</v>
+        <v>166</v>
       </c>
       <c r="Y41" s="4" t="s">
         <v>47</v>
@@ -5454,7 +5490,7 @@
         <v>50</v>
       </c>
       <c r="AD41" s="4" t="s">
-        <v>170</v>
+        <v>225</v>
       </c>
       <c r="AE41" s="4" t="s">
         <v>67</v>
@@ -5463,7 +5499,7 @@
         <v>68</v>
       </c>
       <c r="AG41" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:33" x14ac:dyDescent="0.3">
@@ -5474,13 +5510,13 @@
         <v>34</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>36</v>
@@ -5495,31 +5531,31 @@
         <v>39</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>62</v>
+        <v>167</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>63</v>
+        <v>168</v>
       </c>
       <c r="L42" s="4" t="s">
-        <v>64</v>
+        <v>169</v>
       </c>
       <c r="M42" s="3">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="N42" s="3">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
       </c>
       <c r="P42" s="3">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
       <c r="R42" s="3">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="S42" s="4" t="s">
         <v>43</v>
@@ -5534,10 +5570,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W42" s="3">
-        <v>1960000</v>
+        <v>2940000</v>
       </c>
       <c r="X42" s="5" t="s">
-        <v>66</v>
+        <v>124</v>
       </c>
       <c r="Y42" s="4" t="s">
         <v>47</v>
@@ -5555,16 +5591,16 @@
         <v>50</v>
       </c>
       <c r="AD42" s="4" t="s">
-        <v>226</v>
+        <v>192</v>
       </c>
       <c r="AE42" s="4" t="s">
-        <v>67</v>
+        <v>120</v>
       </c>
       <c r="AF42" s="4" t="s">
-        <v>68</v>
+        <v>121</v>
       </c>
       <c r="AG42" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:33" x14ac:dyDescent="0.3">
@@ -5575,13 +5611,13 @@
         <v>34</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>91</v>
+        <v>206</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>91</v>
+        <v>206</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>91</v>
+        <v>206</v>
       </c>
       <c r="F43" s="4" t="s">
         <v>36</v>
@@ -5596,31 +5632,31 @@
         <v>39</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>55</v>
+        <v>194</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>56</v>
+        <v>196</v>
       </c>
       <c r="L43" s="4" t="s">
-        <v>57</v>
+        <v>195</v>
       </c>
       <c r="M43" s="3">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
       <c r="N43" s="3">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
       </c>
       <c r="P43" s="3">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
       </c>
       <c r="R43" s="3">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
       <c r="S43" s="4" t="s">
         <v>43</v>
@@ -5635,10 +5671,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W43" s="3">
-        <v>19600000</v>
+        <v>9800000</v>
       </c>
       <c r="X43" s="5" t="s">
-        <v>126</v>
+        <v>66</v>
       </c>
       <c r="Y43" s="4" t="s">
         <v>47</v>
@@ -5656,16 +5692,16 @@
         <v>50</v>
       </c>
       <c r="AD43" s="4" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
       <c r="AE43" s="4" t="s">
-        <v>120</v>
+        <v>208</v>
       </c>
       <c r="AF43" s="4" t="s">
-        <v>121</v>
+        <v>193</v>
       </c>
       <c r="AG43" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:33" x14ac:dyDescent="0.3">
@@ -5676,13 +5712,13 @@
         <v>34</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>36</v>
@@ -5697,34 +5733,34 @@
         <v>39</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>115</v>
+        <v>40</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>116</v>
+        <v>41</v>
       </c>
       <c r="L44" s="4" t="s">
-        <v>117</v>
+        <v>42</v>
       </c>
       <c r="M44" s="3">
-        <v>8000000</v>
+        <v>200000</v>
       </c>
       <c r="N44" s="3">
-        <v>960000</v>
+        <v>200000</v>
       </c>
       <c r="O44" s="3">
-        <v>7040000</v>
+        <v>0</v>
       </c>
       <c r="P44" s="3">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
       </c>
       <c r="R44" s="3">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="S44" s="4" t="s">
-        <v>125</v>
+        <v>43</v>
       </c>
       <c r="T44" s="4" t="s">
         <v>44</v>
@@ -5736,10 +5772,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W44" s="3">
-        <v>78400000</v>
+        <v>1960000</v>
       </c>
       <c r="X44" s="5" t="s">
-        <v>118</v>
+        <v>46</v>
       </c>
       <c r="Y44" s="4" t="s">
         <v>47</v>
@@ -5751,22 +5787,22 @@
         <v>49</v>
       </c>
       <c r="AB44" s="4" t="s">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="AC44" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD44" s="4" t="s">
-        <v>281</v>
+        <v>51</v>
       </c>
       <c r="AE44" s="4" t="s">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="AF44" s="4" t="s">
-        <v>121</v>
+        <v>53</v>
       </c>
       <c r="AG44" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:33" x14ac:dyDescent="0.3">
@@ -5777,13 +5813,13 @@
         <v>34</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>189</v>
+        <v>35</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>189</v>
+        <v>35</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>36</v>
@@ -5798,31 +5834,31 @@
         <v>39</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>55</v>
+        <v>112</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>56</v>
+        <v>113</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>57</v>
+        <v>114</v>
       </c>
       <c r="M45" s="3">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="N45" s="3">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="O45" s="3">
         <v>0</v>
       </c>
       <c r="P45" s="3">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="Q45" s="3">
         <v>0</v>
       </c>
       <c r="R45" s="3">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="S45" s="4" t="s">
         <v>43</v>
@@ -5837,10 +5873,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W45" s="3">
-        <v>19600000</v>
+        <v>1960000</v>
       </c>
       <c r="X45" s="5" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="Y45" s="4" t="s">
         <v>47</v>
@@ -5852,22 +5888,22 @@
         <v>49</v>
       </c>
       <c r="AB45" s="4" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="AC45" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD45" s="4" t="s">
-        <v>191</v>
+        <v>106</v>
       </c>
       <c r="AE45" s="4" t="s">
-        <v>190</v>
+        <v>52</v>
       </c>
       <c r="AF45" s="4" t="s">
-        <v>171</v>
+        <v>123</v>
       </c>
       <c r="AG45" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:33" x14ac:dyDescent="0.3">
@@ -5878,13 +5914,13 @@
         <v>34</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>189</v>
+        <v>54</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>189</v>
+        <v>46</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>36</v>
@@ -5899,31 +5935,31 @@
         <v>39</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>178</v>
+        <v>55</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>180</v>
+        <v>56</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>179</v>
+        <v>57</v>
       </c>
       <c r="M46" s="3">
-        <v>3000000</v>
+        <v>2000000</v>
       </c>
       <c r="N46" s="3">
-        <v>3000000</v>
+        <v>2000000</v>
       </c>
       <c r="O46" s="3">
         <v>0</v>
       </c>
       <c r="P46" s="3">
-        <v>3000000</v>
+        <v>2000000</v>
       </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
       <c r="R46" s="3">
-        <v>3000000</v>
+        <v>2000000</v>
       </c>
       <c r="S46" s="4" t="s">
         <v>43</v>
@@ -5938,10 +5974,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W46" s="3">
-        <v>29400000</v>
+        <v>19600000</v>
       </c>
       <c r="X46" s="5" t="s">
-        <v>166</v>
+        <v>58</v>
       </c>
       <c r="Y46" s="4" t="s">
         <v>47</v>
@@ -5953,22 +5989,22 @@
         <v>49</v>
       </c>
       <c r="AB46" s="4" t="s">
-        <v>181</v>
+        <v>39</v>
       </c>
       <c r="AC46" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD46" s="4" t="s">
-        <v>278</v>
+        <v>51</v>
       </c>
       <c r="AE46" s="4" t="s">
-        <v>190</v>
+        <v>59</v>
       </c>
       <c r="AF46" s="4" t="s">
-        <v>171</v>
+        <v>60</v>
       </c>
       <c r="AG46" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:33" x14ac:dyDescent="0.3">
@@ -5979,13 +6015,13 @@
         <v>34</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>36</v>
@@ -6000,31 +6036,31 @@
         <v>39</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="L47" s="4" t="s">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="M47" s="3">
-        <v>200000</v>
+        <v>500000</v>
       </c>
       <c r="N47" s="3">
-        <v>200000</v>
+        <v>500000</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
       </c>
       <c r="P47" s="3">
-        <v>200000</v>
+        <v>500000</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
       </c>
       <c r="R47" s="3">
-        <v>200000</v>
+        <v>500000</v>
       </c>
       <c r="S47" s="4" t="s">
         <v>43</v>
@@ -6039,10 +6075,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W47" s="3">
-        <v>1960000</v>
+        <v>4900000</v>
       </c>
       <c r="X47" s="5" t="s">
-        <v>46</v>
+        <v>124</v>
       </c>
       <c r="Y47" s="4" t="s">
         <v>47</v>
@@ -6060,16 +6096,16 @@
         <v>50</v>
       </c>
       <c r="AD47" s="4" t="s">
-        <v>51</v>
+        <v>170</v>
       </c>
       <c r="AE47" s="4" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="AF47" s="4" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="AG47" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:33" x14ac:dyDescent="0.3">
@@ -6080,13 +6116,13 @@
         <v>34</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>36</v>
@@ -6101,13 +6137,13 @@
         <v>39</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>113</v>
+        <v>63</v>
       </c>
       <c r="L48" s="4" t="s">
-        <v>114</v>
+        <v>64</v>
       </c>
       <c r="M48" s="3">
         <v>200000</v>
@@ -6143,7 +6179,7 @@
         <v>1960000</v>
       </c>
       <c r="X48" s="5" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="Y48" s="4" t="s">
         <v>47</v>
@@ -6155,22 +6191,22 @@
         <v>49</v>
       </c>
       <c r="AB48" s="4" t="s">
-        <v>122</v>
+        <v>39</v>
       </c>
       <c r="AC48" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD48" s="4" t="s">
-        <v>106</v>
+        <v>226</v>
       </c>
       <c r="AE48" s="4" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="AF48" s="4" t="s">
-        <v>123</v>
+        <v>68</v>
       </c>
       <c r="AG48" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:33" x14ac:dyDescent="0.3">
@@ -6181,13 +6217,13 @@
         <v>34</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>36</v>
@@ -6244,7 +6280,7 @@
         <v>19600000</v>
       </c>
       <c r="X49" s="5" t="s">
-        <v>58</v>
+        <v>126</v>
       </c>
       <c r="Y49" s="4" t="s">
         <v>47</v>
@@ -6262,13 +6298,13 @@
         <v>50</v>
       </c>
       <c r="AD49" s="4" t="s">
-        <v>51</v>
+        <v>226</v>
       </c>
       <c r="AE49" s="4" t="s">
-        <v>59</v>
+        <v>120</v>
       </c>
       <c r="AF49" s="4" t="s">
-        <v>60</v>
+        <v>121</v>
       </c>
       <c r="AG49" s="3">
         <v>3</v>
@@ -6282,13 +6318,13 @@
         <v>34</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>206</v>
+        <v>91</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>206</v>
+        <v>91</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>206</v>
+        <v>91</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>36</v>
@@ -6303,34 +6339,34 @@
         <v>39</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="L50" s="4" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="M50" s="3">
-        <v>200000</v>
+        <v>8000000</v>
       </c>
       <c r="N50" s="3">
-        <v>200000</v>
+        <v>1672000</v>
       </c>
       <c r="O50" s="3">
-        <v>0</v>
+        <v>6328000</v>
       </c>
       <c r="P50" s="3">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="Q50" s="3">
         <v>0</v>
       </c>
       <c r="R50" s="3">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="S50" s="4" t="s">
-        <v>43</v>
+        <v>125</v>
       </c>
       <c r="T50" s="4" t="s">
         <v>44</v>
@@ -6342,10 +6378,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W50" s="3">
-        <v>1960000</v>
+        <v>78400000</v>
       </c>
       <c r="X50" s="5" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="Y50" s="4" t="s">
         <v>47</v>
@@ -6357,22 +6393,22 @@
         <v>49</v>
       </c>
       <c r="AB50" s="4" t="s">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="AC50" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD50" s="4" t="s">
-        <v>217</v>
+        <v>288</v>
       </c>
       <c r="AE50" s="4" t="s">
-        <v>208</v>
+        <v>120</v>
       </c>
       <c r="AF50" s="4" t="s">
-        <v>193</v>
+        <v>121</v>
       </c>
       <c r="AG50" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:33" x14ac:dyDescent="0.3">
@@ -6383,13 +6419,13 @@
         <v>34</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>273</v>
+        <v>189</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>273</v>
+        <v>189</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>273</v>
+        <v>58</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>36</v>
@@ -6404,34 +6440,34 @@
         <v>39</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>151</v>
+        <v>55</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>152</v>
+        <v>56</v>
       </c>
       <c r="L51" s="4" t="s">
-        <v>153</v>
+        <v>57</v>
       </c>
       <c r="M51" s="3">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="N51" s="3">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="O51" s="3">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="P51" s="3">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="Q51" s="3">
         <v>0</v>
       </c>
       <c r="R51" s="3">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="S51" s="4" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T51" s="4" t="s">
         <v>44</v>
@@ -6443,10 +6479,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W51" s="3">
-        <v>9800000</v>
+        <v>19600000</v>
       </c>
       <c r="X51" s="5" t="s">
-        <v>274</v>
+        <v>126</v>
       </c>
       <c r="Y51" s="4" t="s">
         <v>47</v>
@@ -6464,35 +6500,320 @@
         <v>50</v>
       </c>
       <c r="AD51" s="4" t="s">
-        <v>276</v>
+        <v>191</v>
       </c>
       <c r="AE51" s="4" t="s">
-        <v>277</v>
+        <v>190</v>
       </c>
       <c r="AF51" s="4" t="s">
-        <v>271</v>
+        <v>171</v>
       </c>
       <c r="AG51" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="X52" s="2"/>
+      <c r="A52" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J52" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="K52" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="L52" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="M52" s="3">
+        <v>3000000</v>
+      </c>
+      <c r="N52" s="3">
+        <v>3000000</v>
+      </c>
+      <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3">
+        <v>3000000</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
+        <v>3000000</v>
+      </c>
+      <c r="S52" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="T52" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="U52" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="V52" s="3">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="W52" s="3">
+        <v>29400000</v>
+      </c>
+      <c r="X52" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="Y52" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z52" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA52" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB52" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="AC52" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD52" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="AE52" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="AF52" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="AG52" s="3">
+        <v>5</v>
+      </c>
     </row>
     <row r="53" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
-      <c r="X53" s="2"/>
+      <c r="A53" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J53" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="K53" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="L53" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="M53" s="3">
+        <v>200000</v>
+      </c>
+      <c r="N53" s="3">
+        <v>200000</v>
+      </c>
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3">
+        <v>200000</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>200000</v>
+      </c>
+      <c r="S53" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="T53" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="U53" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="V53" s="3">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="W53" s="3">
+        <v>1960000</v>
+      </c>
+      <c r="X53" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="Y53" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z53" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA53" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB53" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC53" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD53" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="AE53" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="AF53" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="54" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="X54" s="2"/>
+      <c r="A54" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I54" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J54" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="K54" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="L54" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="M54" s="3">
+        <v>1000000</v>
+      </c>
+      <c r="N54" s="3">
+        <v>0</v>
+      </c>
+      <c r="O54" s="3">
+        <v>1000000</v>
+      </c>
+      <c r="P54" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="3">
+        <v>0</v>
+      </c>
+      <c r="R54" s="3">
+        <v>0</v>
+      </c>
+      <c r="S54" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="T54" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="U54" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="V54" s="3">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="W54" s="3">
+        <v>9800000</v>
+      </c>
+      <c r="X54" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="Y54" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z54" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA54" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB54" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC54" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD54" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="AE54" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="AF54" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="AG54" s="3">
+        <v>3</v>
+      </c>
     </row>
     <row r="55" spans="1:33" x14ac:dyDescent="0.3">
       <c r="C55" s="2"/>
@@ -6575,7 +6896,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8105D0C-47A0-4625-B289-24FCAF816E36}">
-  <dimension ref="A1:AH51"/>
+  <dimension ref="A1:AH54"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:34" x14ac:dyDescent="0.3">
@@ -7543,7 +7864,7 @@
         <v>93</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>206</v>
+        <v>118</v>
       </c>
       <c r="K10" s="7" t="s">
         <v>36</v>
@@ -9695,7 +10016,7 @@
         <v>47</v>
       </c>
       <c r="AH30" s="7" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
     </row>
     <row r="31" spans="1:34" x14ac:dyDescent="0.3">
@@ -10351,7 +10672,7 @@
         <v>180</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>273</v>
+        <v>118</v>
       </c>
       <c r="K37" s="7" t="s">
         <v>36</v>
@@ -10975,7 +11296,7 @@
         <v>93</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>206</v>
+        <v>118</v>
       </c>
       <c r="K43" s="7" t="s">
         <v>36</v>
@@ -11047,7 +11368,7 @@
         <v>47</v>
       </c>
       <c r="AH43" s="7" t="s">
-        <v>207</v>
+        <v>288</v>
       </c>
     </row>
     <row r="44" spans="1:34" x14ac:dyDescent="0.3">
@@ -11599,7 +11920,7 @@
         <v>180</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>273</v>
+        <v>118</v>
       </c>
       <c r="K49" s="7" t="s">
         <v>36</v>
@@ -11671,7 +11992,7 @@
         <v>47</v>
       </c>
       <c r="AH49" s="7" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
     </row>
     <row r="50" spans="1:34" x14ac:dyDescent="0.3">
@@ -11880,6 +12201,318 @@
       </c>
       <c r="AH51" s="7" t="s">
         <v>276</v>
+      </c>
+    </row>
+    <row r="52" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A52" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D52" s="6">
+        <v>1</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="H52" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="I52" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="J52" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="K52" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L52" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="M52" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="N52" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="O52" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="P52" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q52" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="R52" s="6">
+        <v>1000000</v>
+      </c>
+      <c r="S52" s="6">
+        <v>1000000</v>
+      </c>
+      <c r="T52" s="6">
+        <v>0</v>
+      </c>
+      <c r="U52" s="6">
+        <v>0</v>
+      </c>
+      <c r="V52" s="6">
+        <v>0</v>
+      </c>
+      <c r="W52" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="X52" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y52" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z52" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA52" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB52" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC52" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="AD52" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="AE52" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF52" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG52" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH52" s="7" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="53" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A53" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D53" s="6">
+        <v>2</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="G53" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="H53" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="I53" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="J53" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="K53" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L53" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="M53" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="N53" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="O53" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="P53" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q53" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="R53" s="6">
+        <v>300000</v>
+      </c>
+      <c r="S53" s="6">
+        <v>300000</v>
+      </c>
+      <c r="T53" s="6">
+        <v>0</v>
+      </c>
+      <c r="U53" s="6">
+        <v>0</v>
+      </c>
+      <c r="V53" s="6">
+        <v>0</v>
+      </c>
+      <c r="W53" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="X53" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y53" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="Z53" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA53" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB53" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC53" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="AD53" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="AE53" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF53" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG53" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH53" s="7" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="54" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A54" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D54" s="6">
+        <v>3</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="H54" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="I54" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="J54" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="K54" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L54" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="M54" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="N54" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="O54" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="P54" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q54" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="R54" s="6">
+        <v>500000</v>
+      </c>
+      <c r="S54" s="6">
+        <v>500000</v>
+      </c>
+      <c r="T54" s="6">
+        <v>0</v>
+      </c>
+      <c r="U54" s="6">
+        <v>0</v>
+      </c>
+      <c r="V54" s="6">
+        <v>0</v>
+      </c>
+      <c r="W54" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="X54" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y54" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="Z54" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA54" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AB54" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC54" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="AD54" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="AE54" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF54" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG54" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH54" s="7" t="s">
+        <v>285</v>
       </c>
     </row>
   </sheetData>

--- a/리드지 발주현황.xlsx
+++ b/리드지 발주현황.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\유현아\Documents\GitHub\INTEROJO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CCBF8DD-29DF-4D26-8C7C-FF1B85D61547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F299585A-CD1B-4C3E-AEEA-7EB7C844698F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{500E376A-1243-49DE-9EFA-B2AD708B3011}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2823" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2823" uniqueCount="295">
   <si>
     <t>G/W</t>
   </si>
@@ -687,9 +687,6 @@
     <t>알루미늄리드지 (폴란드 FML eyeVista Metha1Day 리드지)_유광 코팅</t>
   </si>
   <si>
-    <t>2026-06-11 오전 11:23:48</t>
-  </si>
-  <si>
     <t>PO-2606100018</t>
   </si>
   <si>
@@ -882,9 +879,6 @@
     <t>2026-06-17 오후 5:59:48</t>
   </si>
   <si>
-    <t>2026-06-18 오후 5:06:56</t>
-  </si>
-  <si>
     <t>2026-06-18 오전 9:16:17</t>
   </si>
   <si>
@@ -909,9 +903,6 @@
     <t>PR-2606190005</t>
   </si>
   <si>
-    <t>2026-06-19 오후 3:14:46</t>
-  </si>
-  <si>
     <t>BS0031</t>
   </si>
   <si>
@@ -925,6 +916,18 @@
   </si>
   <si>
     <t>20260619P227-0027</t>
+  </si>
+  <si>
+    <t>2026-06-22 오후 6:05:28</t>
+  </si>
+  <si>
+    <t>2026-06-22 오후 6:06:09</t>
+  </si>
+  <si>
+    <t>2026-06-21 오전 10:47:41</t>
+  </si>
+  <si>
+    <t>2026-06-22 오후 2:14:04</t>
   </si>
 </sst>
 </file>
@@ -1470,13 +1473,13 @@
         <v>34</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>36</v>
@@ -1491,34 +1494,34 @@
         <v>39</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="M2" s="3">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="N2" s="3">
-        <v>351000</v>
+        <v>200000</v>
       </c>
       <c r="O2" s="3">
-        <v>1649000</v>
+        <v>0</v>
       </c>
       <c r="P2" s="3">
-        <v>351000</v>
+        <v>200000</v>
       </c>
       <c r="Q2" s="3">
         <v>0</v>
       </c>
       <c r="R2" s="3">
-        <v>351000</v>
+        <v>200000</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>125</v>
+        <v>43</v>
       </c>
       <c r="T2" s="4" t="s">
         <v>44</v>
@@ -1530,10 +1533,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W2" s="3">
-        <v>19600000</v>
+        <v>1960000</v>
       </c>
       <c r="X2" s="5" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="Y2" s="4" t="s">
         <v>47</v>
@@ -1545,22 +1548,22 @@
         <v>49</v>
       </c>
       <c r="AB2" s="4" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="AC2" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD2" s="4" t="s">
-        <v>279</v>
+        <v>106</v>
       </c>
       <c r="AE2" s="4" t="s">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="AF2" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="AG2" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.3">
@@ -1592,31 +1595,31 @@
         <v>39</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="M3" s="3">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="N3" s="3">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="O3" s="3">
         <v>0</v>
       </c>
       <c r="P3" s="3">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="Q3" s="3">
         <v>0</v>
       </c>
       <c r="R3" s="3">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="S3" s="4" t="s">
         <v>43</v>
@@ -1628,13 +1631,13 @@
         <v>45</v>
       </c>
       <c r="V3" s="3">
-        <v>9.8000000000000007</v>
+        <v>8.5</v>
       </c>
       <c r="W3" s="3">
-        <v>1960000</v>
+        <v>2550000</v>
       </c>
       <c r="X3" s="5" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="Y3" s="4" t="s">
         <v>47</v>
@@ -1646,22 +1649,22 @@
         <v>49</v>
       </c>
       <c r="AB3" s="4" t="s">
-        <v>122</v>
+        <v>39</v>
       </c>
       <c r="AC3" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD3" s="4" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="AE3" s="4" t="s">
         <v>52</v>
       </c>
       <c r="AF3" s="4" t="s">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c r="AG3" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.3">
@@ -1672,13 +1675,13 @@
         <v>34</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>210</v>
+        <v>35</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>126</v>
+        <v>35</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>210</v>
+        <v>35</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>36</v>
@@ -1693,31 +1696,31 @@
         <v>39</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>211</v>
+        <v>99</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>212</v>
+        <v>100</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>213</v>
+        <v>101</v>
       </c>
       <c r="M4" s="3">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="N4" s="3">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="O4" s="3">
         <v>0</v>
       </c>
       <c r="P4" s="3">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="Q4" s="3">
         <v>0</v>
       </c>
       <c r="R4" s="3">
-        <v>200000</v>
+        <v>2000000</v>
       </c>
       <c r="S4" s="4" t="s">
         <v>43</v>
@@ -1729,13 +1732,13 @@
         <v>45</v>
       </c>
       <c r="V4" s="3">
-        <v>9.8000000000000007</v>
+        <v>6.7</v>
       </c>
       <c r="W4" s="3">
-        <v>1960000</v>
+        <v>13400000</v>
       </c>
       <c r="X4" s="5" t="s">
-        <v>197</v>
+        <v>107</v>
       </c>
       <c r="Y4" s="4" t="s">
         <v>47</v>
@@ -1753,13 +1756,13 @@
         <v>50</v>
       </c>
       <c r="AD4" s="4" t="s">
-        <v>280</v>
+        <v>154</v>
       </c>
       <c r="AE4" s="4" t="s">
-        <v>215</v>
+        <v>52</v>
       </c>
       <c r="AF4" s="4" t="s">
-        <v>216</v>
+        <v>53</v>
       </c>
       <c r="AG4" s="3">
         <v>3</v>
@@ -1773,13 +1776,13 @@
         <v>34</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>36</v>
@@ -1794,13 +1797,13 @@
         <v>39</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="M5" s="3">
         <v>200000</v>
@@ -1836,7 +1839,7 @@
         <v>1960000</v>
       </c>
       <c r="X5" s="5" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="Y5" s="4" t="s">
         <v>47</v>
@@ -1848,19 +1851,19 @@
         <v>49</v>
       </c>
       <c r="AB5" s="4" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="AC5" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD5" s="4" t="s">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="AE5" s="4" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="AF5" s="4" t="s">
-        <v>60</v>
+        <v>123</v>
       </c>
       <c r="AG5" s="3">
         <v>1</v>
@@ -1874,13 +1877,13 @@
         <v>34</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>36</v>
@@ -1895,13 +1898,13 @@
         <v>39</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>131</v>
+        <v>40</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>132</v>
+        <v>41</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>133</v>
+        <v>42</v>
       </c>
       <c r="M6" s="3">
         <v>200000</v>
@@ -1931,13 +1934,13 @@
         <v>45</v>
       </c>
       <c r="V6" s="3">
-        <v>34</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="W6" s="3">
-        <v>6800000</v>
+        <v>1960000</v>
       </c>
       <c r="X6" s="5" t="s">
-        <v>134</v>
+        <v>46</v>
       </c>
       <c r="Y6" s="4" t="s">
         <v>47</v>
@@ -1955,16 +1958,16 @@
         <v>50</v>
       </c>
       <c r="AD6" s="4" t="s">
-        <v>205</v>
+        <v>51</v>
       </c>
       <c r="AE6" s="4" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="AF6" s="4" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="AG6" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.3">
@@ -1975,13 +1978,13 @@
         <v>34</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>36</v>
@@ -1996,13 +1999,13 @@
         <v>39</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>69</v>
+        <v>112</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>71</v>
+        <v>114</v>
       </c>
       <c r="M7" s="3">
         <v>200000</v>
@@ -2038,7 +2041,7 @@
         <v>1960000</v>
       </c>
       <c r="X7" s="5" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="Y7" s="4" t="s">
         <v>47</v>
@@ -2050,22 +2053,22 @@
         <v>49</v>
       </c>
       <c r="AB7" s="4" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="AC7" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD7" s="4" t="s">
-        <v>188</v>
+        <v>106</v>
       </c>
       <c r="AE7" s="4" t="s">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="AF7" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="AG7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.3">
@@ -2076,13 +2079,13 @@
         <v>34</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>206</v>
+        <v>108</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>206</v>
+        <v>108</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>206</v>
+        <v>108</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>36</v>
@@ -2097,34 +2100,34 @@
         <v>39</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>158</v>
+        <v>127</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="M8" s="3">
-        <v>1500000</v>
+        <v>2000000</v>
       </c>
       <c r="N8" s="3">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="O8" s="3">
-        <v>1500000</v>
+        <v>0</v>
       </c>
       <c r="P8" s="3">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
       </c>
       <c r="R8" s="3">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T8" s="4" t="s">
         <v>44</v>
@@ -2133,13 +2136,13 @@
         <v>45</v>
       </c>
       <c r="V8" s="3">
-        <v>7.7</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="W8" s="3">
-        <v>11550000</v>
+        <v>19600000</v>
       </c>
       <c r="X8" s="5" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="Y8" s="4" t="s">
         <v>47</v>
@@ -2157,16 +2160,16 @@
         <v>50</v>
       </c>
       <c r="AD8" s="4" t="s">
-        <v>207</v>
+        <v>291</v>
       </c>
       <c r="AE8" s="4" t="s">
-        <v>208</v>
+        <v>130</v>
       </c>
       <c r="AF8" s="4" t="s">
-        <v>193</v>
+        <v>135</v>
       </c>
       <c r="AG8" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.3">
@@ -2177,13 +2180,13 @@
         <v>34</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>206</v>
+        <v>108</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>206</v>
+        <v>108</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>206</v>
+        <v>108</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>36</v>
@@ -2198,34 +2201,34 @@
         <v>39</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>200</v>
+        <v>81</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>199</v>
+        <v>82</v>
       </c>
       <c r="M9" s="3">
         <v>200000</v>
       </c>
       <c r="N9" s="3">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="O9" s="3">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3">
         <v>200000</v>
       </c>
-      <c r="P9" s="3">
-        <v>0</v>
-      </c>
       <c r="Q9" s="3">
         <v>0</v>
       </c>
       <c r="R9" s="3">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T9" s="4" t="s">
         <v>44</v>
@@ -2240,7 +2243,7 @@
         <v>1960000</v>
       </c>
       <c r="X9" s="5" t="s">
-        <v>118</v>
+        <v>72</v>
       </c>
       <c r="Y9" s="4" t="s">
         <v>47</v>
@@ -2258,16 +2261,16 @@
         <v>50</v>
       </c>
       <c r="AD9" s="4" t="s">
-        <v>207</v>
+        <v>83</v>
       </c>
       <c r="AE9" s="4" t="s">
-        <v>208</v>
+        <v>130</v>
       </c>
       <c r="AF9" s="4" t="s">
-        <v>193</v>
+        <v>135</v>
       </c>
       <c r="AG9" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.3">
@@ -2278,13 +2281,13 @@
         <v>34</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>36</v>
@@ -2299,34 +2302,34 @@
         <v>39</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>281</v>
+        <v>99</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>282</v>
+        <v>100</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>283</v>
+        <v>101</v>
       </c>
       <c r="M10" s="3">
-        <v>300000</v>
+        <v>2000000</v>
       </c>
       <c r="N10" s="3">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="O10" s="3">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="P10" s="3">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="Q10" s="3">
         <v>0</v>
       </c>
       <c r="R10" s="3">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T10" s="4" t="s">
         <v>44</v>
@@ -2335,13 +2338,13 @@
         <v>45</v>
       </c>
       <c r="V10" s="3">
-        <v>9.8000000000000007</v>
+        <v>6.7</v>
       </c>
       <c r="W10" s="3">
-        <v>2940000</v>
+        <v>13400000</v>
       </c>
       <c r="X10" s="5" t="s">
-        <v>284</v>
+        <v>90</v>
       </c>
       <c r="Y10" s="4" t="s">
         <v>47</v>
@@ -2359,16 +2362,16 @@
         <v>50</v>
       </c>
       <c r="AD10" s="4" t="s">
-        <v>285</v>
+        <v>140</v>
       </c>
       <c r="AE10" s="4" t="s">
-        <v>286</v>
+        <v>130</v>
       </c>
       <c r="AF10" s="4" t="s">
-        <v>287</v>
+        <v>135</v>
       </c>
       <c r="AG10" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.3">
@@ -2400,31 +2403,31 @@
         <v>39</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>128</v>
+        <v>85</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>129</v>
+        <v>86</v>
       </c>
       <c r="M11" s="3">
-        <v>2000000</v>
+        <v>500000</v>
       </c>
       <c r="N11" s="3">
-        <v>2000000</v>
+        <v>500000</v>
       </c>
       <c r="O11" s="3">
         <v>0</v>
       </c>
       <c r="P11" s="3">
-        <v>2000000</v>
+        <v>500000</v>
       </c>
       <c r="Q11" s="3">
         <v>0</v>
       </c>
       <c r="R11" s="3">
-        <v>2000000</v>
+        <v>500000</v>
       </c>
       <c r="S11" s="4" t="s">
         <v>43</v>
@@ -2439,10 +2442,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W11" s="3">
-        <v>19600000</v>
+        <v>4900000</v>
       </c>
       <c r="X11" s="5" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="Y11" s="4" t="s">
         <v>47</v>
@@ -2460,7 +2463,7 @@
         <v>50</v>
       </c>
       <c r="AD11" s="4" t="s">
-        <v>279</v>
+        <v>83</v>
       </c>
       <c r="AE11" s="4" t="s">
         <v>130</v>
@@ -2469,7 +2472,7 @@
         <v>135</v>
       </c>
       <c r="AG11" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.3">
@@ -2501,13 +2504,13 @@
         <v>39</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="M12" s="3">
         <v>200000</v>
@@ -2561,7 +2564,7 @@
         <v>50</v>
       </c>
       <c r="AD12" s="4" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AE12" s="4" t="s">
         <v>130</v>
@@ -2570,7 +2573,7 @@
         <v>135</v>
       </c>
       <c r="AG12" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.3">
@@ -2581,13 +2584,13 @@
         <v>34</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>61</v>
+        <v>108</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>61</v>
+        <v>108</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>61</v>
+        <v>108</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>36</v>
@@ -2602,31 +2605,31 @@
         <v>39</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="M13" s="3">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="N13" s="3">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="O13" s="3">
         <v>0</v>
       </c>
       <c r="P13" s="3">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="Q13" s="3">
         <v>0</v>
       </c>
       <c r="R13" s="3">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="S13" s="4" t="s">
         <v>43</v>
@@ -2641,7 +2644,7 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W13" s="3">
-        <v>19600000</v>
+        <v>1960000</v>
       </c>
       <c r="X13" s="5" t="s">
         <v>72</v>
@@ -2662,16 +2665,16 @@
         <v>50</v>
       </c>
       <c r="AD13" s="4" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AE13" s="4" t="s">
-        <v>67</v>
+        <v>130</v>
       </c>
       <c r="AF13" s="4" t="s">
-        <v>68</v>
+        <v>135</v>
       </c>
       <c r="AG13" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.3">
@@ -2682,13 +2685,13 @@
         <v>34</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>91</v>
+        <v>46</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>91</v>
+        <v>46</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>36</v>
@@ -2703,31 +2706,31 @@
         <v>39</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="M14" s="3">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="N14" s="3">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
       <c r="P14" s="3">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
       <c r="R14" s="3">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="S14" s="4" t="s">
         <v>43</v>
@@ -2742,10 +2745,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W14" s="3">
-        <v>2940000</v>
+        <v>1960000</v>
       </c>
       <c r="X14" s="5" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="Y14" s="4" t="s">
         <v>47</v>
@@ -2757,22 +2760,22 @@
         <v>49</v>
       </c>
       <c r="AB14" s="4" t="s">
-        <v>139</v>
+        <v>39</v>
       </c>
       <c r="AC14" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD14" s="4" t="s">
-        <v>209</v>
+        <v>73</v>
       </c>
       <c r="AE14" s="4" t="s">
-        <v>120</v>
+        <v>59</v>
       </c>
       <c r="AF14" s="4" t="s">
-        <v>121</v>
+        <v>60</v>
       </c>
       <c r="AG14" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.3">
@@ -2783,13 +2786,13 @@
         <v>34</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>206</v>
+        <v>54</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>206</v>
+        <v>46</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>206</v>
+        <v>46</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>36</v>
@@ -2804,13 +2807,13 @@
         <v>39</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>93</v>
+        <v>145</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>94</v>
+        <v>146</v>
       </c>
       <c r="M15" s="3">
         <v>300000</v>
@@ -2822,13 +2825,13 @@
         <v>0</v>
       </c>
       <c r="P15" s="3">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
       <c r="R15" s="3">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="S15" s="4" t="s">
         <v>43</v>
@@ -2840,13 +2843,13 @@
         <v>45</v>
       </c>
       <c r="V15" s="3">
-        <v>9.8000000000000007</v>
+        <v>0</v>
       </c>
       <c r="W15" s="3">
-        <v>2940000</v>
+        <v>0</v>
       </c>
       <c r="X15" s="5" t="s">
-        <v>197</v>
+        <v>58</v>
       </c>
       <c r="Y15" s="4" t="s">
         <v>47</v>
@@ -2864,16 +2867,16 @@
         <v>50</v>
       </c>
       <c r="AD15" s="4" t="s">
-        <v>288</v>
+        <v>191</v>
       </c>
       <c r="AE15" s="4" t="s">
-        <v>208</v>
+        <v>59</v>
       </c>
       <c r="AF15" s="4" t="s">
-        <v>193</v>
+        <v>60</v>
       </c>
       <c r="AG15" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.3">
@@ -2884,13 +2887,13 @@
         <v>34</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>189</v>
+        <v>54</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>189</v>
+        <v>46</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>36</v>
@@ -2905,13 +2908,13 @@
         <v>39</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>172</v>
+        <v>147</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="M16" s="3">
         <v>200000</v>
@@ -2941,13 +2944,13 @@
         <v>45</v>
       </c>
       <c r="V16" s="3">
-        <v>9.8000000000000007</v>
+        <v>34</v>
       </c>
       <c r="W16" s="3">
-        <v>1960000</v>
+        <v>6800000</v>
       </c>
       <c r="X16" s="5" t="s">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="Y16" s="4" t="s">
         <v>47</v>
@@ -2965,16 +2968,16 @@
         <v>50</v>
       </c>
       <c r="AD16" s="4" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="AE16" s="4" t="s">
-        <v>190</v>
+        <v>59</v>
       </c>
       <c r="AF16" s="4" t="s">
-        <v>171</v>
+        <v>60</v>
       </c>
       <c r="AG16" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.3">
@@ -2985,13 +2988,13 @@
         <v>34</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>108</v>
+        <v>54</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>108</v>
+        <v>46</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>108</v>
+        <v>46</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>36</v>
@@ -3006,31 +3009,31 @@
         <v>39</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>99</v>
+        <v>155</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>100</v>
+        <v>156</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>101</v>
+        <v>157</v>
       </c>
       <c r="M17" s="3">
-        <v>2000000</v>
+        <v>300000</v>
       </c>
       <c r="N17" s="3">
-        <v>2000000</v>
+        <v>300000</v>
       </c>
       <c r="O17" s="3">
         <v>0</v>
       </c>
       <c r="P17" s="3">
-        <v>2000000</v>
+        <v>300000</v>
       </c>
       <c r="Q17" s="3">
         <v>0</v>
       </c>
       <c r="R17" s="3">
-        <v>2000000</v>
+        <v>300000</v>
       </c>
       <c r="S17" s="4" t="s">
         <v>43</v>
@@ -3042,13 +3045,13 @@
         <v>45</v>
       </c>
       <c r="V17" s="3">
-        <v>6.7</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="W17" s="3">
-        <v>13400000</v>
+        <v>2940000</v>
       </c>
       <c r="X17" s="5" t="s">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="Y17" s="4" t="s">
         <v>47</v>
@@ -3066,16 +3069,16 @@
         <v>50</v>
       </c>
       <c r="AD17" s="4" t="s">
-        <v>140</v>
+        <v>186</v>
       </c>
       <c r="AE17" s="4" t="s">
-        <v>130</v>
+        <v>59</v>
       </c>
       <c r="AF17" s="4" t="s">
-        <v>135</v>
+        <v>60</v>
       </c>
       <c r="AG17" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.3">
@@ -3086,13 +3089,13 @@
         <v>34</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>91</v>
+        <v>46</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>91</v>
+        <v>46</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>36</v>
@@ -3107,31 +3110,31 @@
         <v>39</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>141</v>
+        <v>55</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>142</v>
+        <v>56</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>143</v>
+        <v>57</v>
       </c>
       <c r="M18" s="3">
-        <v>300000</v>
+        <v>2000000</v>
       </c>
       <c r="N18" s="3">
-        <v>300000</v>
+        <v>2000000</v>
       </c>
       <c r="O18" s="3">
         <v>0</v>
       </c>
       <c r="P18" s="3">
-        <v>300000</v>
+        <v>2000000</v>
       </c>
       <c r="Q18" s="3">
         <v>0</v>
       </c>
       <c r="R18" s="3">
-        <v>300000</v>
+        <v>2000000</v>
       </c>
       <c r="S18" s="4" t="s">
         <v>43</v>
@@ -3146,10 +3149,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W18" s="3">
-        <v>2940000</v>
+        <v>19600000</v>
       </c>
       <c r="X18" s="5" t="s">
-        <v>126</v>
+        <v>58</v>
       </c>
       <c r="Y18" s="4" t="s">
         <v>47</v>
@@ -3167,16 +3170,16 @@
         <v>50</v>
       </c>
       <c r="AD18" s="4" t="s">
-        <v>191</v>
+        <v>51</v>
       </c>
       <c r="AE18" s="4" t="s">
-        <v>120</v>
+        <v>59</v>
       </c>
       <c r="AF18" s="4" t="s">
-        <v>121</v>
+        <v>60</v>
       </c>
       <c r="AG18" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.3">
@@ -3187,13 +3190,13 @@
         <v>34</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>189</v>
+        <v>61</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>189</v>
+        <v>61</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>36</v>
@@ -3208,13 +3211,13 @@
         <v>39</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>175</v>
+        <v>131</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>177</v>
+        <v>132</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>176</v>
+        <v>133</v>
       </c>
       <c r="M19" s="3">
         <v>200000</v>
@@ -3244,13 +3247,13 @@
         <v>45</v>
       </c>
       <c r="V19" s="3">
-        <v>9.8000000000000007</v>
+        <v>34</v>
       </c>
       <c r="W19" s="3">
-        <v>1960000</v>
+        <v>6800000</v>
       </c>
       <c r="X19" s="5" t="s">
-        <v>166</v>
+        <v>134</v>
       </c>
       <c r="Y19" s="4" t="s">
         <v>47</v>
@@ -3268,13 +3271,13 @@
         <v>50</v>
       </c>
       <c r="AD19" s="4" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="AE19" s="4" t="s">
-        <v>190</v>
+        <v>67</v>
       </c>
       <c r="AF19" s="4" t="s">
-        <v>171</v>
+        <v>68</v>
       </c>
       <c r="AG19" s="3">
         <v>4</v>
@@ -3288,13 +3291,13 @@
         <v>34</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>273</v>
+        <v>61</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>273</v>
+        <v>61</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>273</v>
+        <v>61</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>36</v>
@@ -3309,34 +3312,34 @@
         <v>39</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="M20" s="3">
-        <v>500000</v>
+        <v>2000000</v>
       </c>
       <c r="N20" s="3">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="O20" s="3">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="P20" s="3">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
       <c r="R20" s="3">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="S20" s="4" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T20" s="4" t="s">
         <v>44</v>
@@ -3348,10 +3351,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W20" s="3">
-        <v>4900000</v>
+        <v>19600000</v>
       </c>
       <c r="X20" s="5" t="s">
-        <v>274</v>
+        <v>72</v>
       </c>
       <c r="Y20" s="4" t="s">
         <v>47</v>
@@ -3369,16 +3372,16 @@
         <v>50</v>
       </c>
       <c r="AD20" s="4" t="s">
-        <v>276</v>
+        <v>73</v>
       </c>
       <c r="AE20" s="4" t="s">
-        <v>277</v>
+        <v>67</v>
       </c>
       <c r="AF20" s="4" t="s">
-        <v>271</v>
+        <v>68</v>
       </c>
       <c r="AG20" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.3">
@@ -3389,13 +3392,13 @@
         <v>34</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>108</v>
+        <v>61</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>108</v>
+        <v>61</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>108</v>
+        <v>61</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>36</v>
@@ -3410,31 +3413,31 @@
         <v>39</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>85</v>
+        <v>152</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>86</v>
+        <v>153</v>
       </c>
       <c r="M21" s="3">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
       <c r="N21" s="3">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
       <c r="O21" s="3">
         <v>0</v>
       </c>
       <c r="P21" s="3">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
       <c r="Q21" s="3">
         <v>0</v>
       </c>
       <c r="R21" s="3">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
       <c r="S21" s="4" t="s">
         <v>43</v>
@@ -3449,7 +3452,7 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W21" s="3">
-        <v>4900000</v>
+        <v>9800000</v>
       </c>
       <c r="X21" s="5" t="s">
         <v>72</v>
@@ -3470,16 +3473,16 @@
         <v>50</v>
       </c>
       <c r="AD21" s="4" t="s">
-        <v>83</v>
+        <v>187</v>
       </c>
       <c r="AE21" s="4" t="s">
-        <v>130</v>
+        <v>67</v>
       </c>
       <c r="AF21" s="4" t="s">
-        <v>135</v>
+        <v>68</v>
       </c>
       <c r="AG21" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.3">
@@ -3490,13 +3493,13 @@
         <v>34</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>210</v>
+        <v>61</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>126</v>
+        <v>61</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>210</v>
+        <v>61</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>36</v>
@@ -3511,34 +3514,34 @@
         <v>39</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>218</v>
+        <v>163</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>219</v>
+        <v>164</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>220</v>
+        <v>165</v>
       </c>
       <c r="M22" s="3">
-        <v>20000</v>
+        <v>500000</v>
       </c>
       <c r="N22" s="3">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="O22" s="3">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="P22" s="3">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
       <c r="R22" s="3">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="S22" s="4" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T22" s="4" t="s">
         <v>44</v>
@@ -3550,10 +3553,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W22" s="3">
-        <v>196000</v>
+        <v>4900000</v>
       </c>
       <c r="X22" s="5" t="s">
-        <v>66</v>
+        <v>166</v>
       </c>
       <c r="Y22" s="4" t="s">
         <v>47</v>
@@ -3571,16 +3574,16 @@
         <v>50</v>
       </c>
       <c r="AD22" s="4" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="AE22" s="4" t="s">
-        <v>215</v>
+        <v>67</v>
       </c>
       <c r="AF22" s="4" t="s">
-        <v>216</v>
+        <v>68</v>
       </c>
       <c r="AG22" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.3">
@@ -3591,13 +3594,13 @@
         <v>34</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>36</v>
@@ -3612,31 +3615,31 @@
         <v>39</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="M23" s="3">
-        <v>300000</v>
+        <v>500000</v>
       </c>
       <c r="N23" s="3">
-        <v>300000</v>
+        <v>500000</v>
       </c>
       <c r="O23" s="3">
         <v>0</v>
       </c>
       <c r="P23" s="3">
-        <v>300000</v>
+        <v>500000</v>
       </c>
       <c r="Q23" s="3">
         <v>0</v>
       </c>
       <c r="R23" s="3">
-        <v>300000</v>
+        <v>500000</v>
       </c>
       <c r="S23" s="4" t="s">
         <v>43</v>
@@ -3648,13 +3651,13 @@
         <v>45</v>
       </c>
       <c r="V23" s="3">
-        <v>8.5</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="W23" s="3">
-        <v>2550000</v>
+        <v>4900000</v>
       </c>
       <c r="X23" s="5" t="s">
-        <v>46</v>
+        <v>124</v>
       </c>
       <c r="Y23" s="4" t="s">
         <v>47</v>
@@ -3672,16 +3675,16 @@
         <v>50</v>
       </c>
       <c r="AD23" s="4" t="s">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="AE23" s="4" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="AF23" s="4" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="AG23" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.3">
@@ -3692,13 +3695,13 @@
         <v>34</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>36</v>
@@ -3713,31 +3716,31 @@
         <v>39</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>144</v>
+        <v>62</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>145</v>
+        <v>63</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>146</v>
+        <v>64</v>
       </c>
       <c r="M24" s="3">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="N24" s="3">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
       <c r="P24" s="3">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
       <c r="R24" s="3">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="S24" s="4" t="s">
         <v>43</v>
@@ -3749,13 +3752,13 @@
         <v>45</v>
       </c>
       <c r="V24" s="3">
-        <v>0</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="W24" s="3">
-        <v>0</v>
+        <v>1960000</v>
       </c>
       <c r="X24" s="5" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="Y24" s="4" t="s">
         <v>47</v>
@@ -3773,16 +3776,16 @@
         <v>50</v>
       </c>
       <c r="AD24" s="4" t="s">
-        <v>191</v>
+        <v>225</v>
       </c>
       <c r="AE24" s="4" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="AF24" s="4" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="AG24" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.3">
@@ -3793,13 +3796,13 @@
         <v>34</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>36</v>
@@ -3814,34 +3817,34 @@
         <v>39</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>289</v>
+        <v>127</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>290</v>
+        <v>128</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>291</v>
+        <v>129</v>
       </c>
       <c r="M25" s="3">
-        <v>500000</v>
+        <v>2000000</v>
       </c>
       <c r="N25" s="3">
-        <v>0</v>
+        <v>351000</v>
       </c>
       <c r="O25" s="3">
-        <v>500000</v>
+        <v>1649000</v>
       </c>
       <c r="P25" s="3">
-        <v>0</v>
+        <v>351000</v>
       </c>
       <c r="Q25" s="3">
         <v>0</v>
       </c>
       <c r="R25" s="3">
-        <v>0</v>
+        <v>351000</v>
       </c>
       <c r="S25" s="4" t="s">
-        <v>65</v>
+        <v>125</v>
       </c>
       <c r="T25" s="4" t="s">
         <v>44</v>
@@ -3853,10 +3856,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W25" s="3">
-        <v>4900000</v>
+        <v>19600000</v>
       </c>
       <c r="X25" s="5" t="s">
-        <v>292</v>
+        <v>118</v>
       </c>
       <c r="Y25" s="4" t="s">
         <v>47</v>
@@ -3874,16 +3877,16 @@
         <v>50</v>
       </c>
       <c r="AD25" s="4" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="AE25" s="4" t="s">
-        <v>286</v>
+        <v>120</v>
       </c>
       <c r="AF25" s="4" t="s">
-        <v>287</v>
+        <v>121</v>
       </c>
       <c r="AG25" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:33" x14ac:dyDescent="0.3">
@@ -3894,13 +3897,13 @@
         <v>34</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>206</v>
+        <v>91</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>206</v>
+        <v>91</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>206</v>
+        <v>91</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>36</v>
@@ -3915,34 +3918,34 @@
         <v>39</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="M26" s="3">
-        <v>5000000</v>
+        <v>200000</v>
       </c>
       <c r="N26" s="3">
-        <v>2478000</v>
+        <v>200000</v>
       </c>
       <c r="O26" s="3">
-        <v>2522000</v>
+        <v>0</v>
       </c>
       <c r="P26" s="3">
-        <v>2478000</v>
+        <v>200000</v>
       </c>
       <c r="Q26" s="3">
         <v>0</v>
       </c>
       <c r="R26" s="3">
-        <v>2478000</v>
+        <v>200000</v>
       </c>
       <c r="S26" s="4" t="s">
-        <v>125</v>
+        <v>43</v>
       </c>
       <c r="T26" s="4" t="s">
         <v>44</v>
@@ -3954,10 +3957,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W26" s="3">
-        <v>49000000</v>
+        <v>1960000</v>
       </c>
       <c r="X26" s="5" t="s">
-        <v>166</v>
+        <v>124</v>
       </c>
       <c r="Y26" s="4" t="s">
         <v>47</v>
@@ -3975,13 +3978,13 @@
         <v>50</v>
       </c>
       <c r="AD26" s="4" t="s">
-        <v>226</v>
+        <v>188</v>
       </c>
       <c r="AE26" s="4" t="s">
-        <v>208</v>
+        <v>120</v>
       </c>
       <c r="AF26" s="4" t="s">
-        <v>193</v>
+        <v>121</v>
       </c>
       <c r="AG26" s="3">
         <v>2</v>
@@ -3995,13 +3998,13 @@
         <v>34</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>206</v>
+        <v>91</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>206</v>
+        <v>91</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>206</v>
+        <v>91</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>36</v>
@@ -4016,34 +4019,34 @@
         <v>39</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>201</v>
+        <v>136</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>203</v>
+        <v>137</v>
       </c>
       <c r="L27" s="4" t="s">
-        <v>202</v>
+        <v>138</v>
       </c>
       <c r="M27" s="3">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="N27" s="3">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="O27" s="3">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="P27" s="3">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="Q27" s="3">
         <v>0</v>
       </c>
       <c r="R27" s="3">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="S27" s="4" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T27" s="4" t="s">
         <v>44</v>
@@ -4055,10 +4058,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W27" s="3">
-        <v>4900000</v>
+        <v>2940000</v>
       </c>
       <c r="X27" s="5" t="s">
-        <v>185</v>
+        <v>118</v>
       </c>
       <c r="Y27" s="4" t="s">
         <v>47</v>
@@ -4070,19 +4073,19 @@
         <v>49</v>
       </c>
       <c r="AB27" s="4" t="s">
-        <v>204</v>
+        <v>139</v>
       </c>
       <c r="AC27" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD27" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AE27" s="4" t="s">
-        <v>208</v>
+        <v>120</v>
       </c>
       <c r="AF27" s="4" t="s">
-        <v>193</v>
+        <v>121</v>
       </c>
       <c r="AG27" s="3">
         <v>7</v>
@@ -4096,13 +4099,13 @@
         <v>34</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>189</v>
+        <v>91</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>189</v>
+        <v>91</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>36</v>
@@ -4117,31 +4120,31 @@
         <v>39</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>88</v>
+        <v>142</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>89</v>
+        <v>143</v>
       </c>
       <c r="M28" s="3">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="N28" s="3">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="O28" s="3">
         <v>0</v>
       </c>
       <c r="P28" s="3">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="Q28" s="3">
         <v>0</v>
       </c>
       <c r="R28" s="3">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="S28" s="4" t="s">
         <v>43</v>
@@ -4156,7 +4159,7 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W28" s="3">
-        <v>1960000</v>
+        <v>2940000</v>
       </c>
       <c r="X28" s="5" t="s">
         <v>126</v>
@@ -4177,16 +4180,16 @@
         <v>50</v>
       </c>
       <c r="AD28" s="4" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="AE28" s="4" t="s">
-        <v>190</v>
+        <v>120</v>
       </c>
       <c r="AF28" s="4" t="s">
-        <v>171</v>
+        <v>121</v>
       </c>
       <c r="AG28" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.3">
@@ -4197,13 +4200,13 @@
         <v>34</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>273</v>
+        <v>91</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>273</v>
+        <v>91</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>273</v>
+        <v>91</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>36</v>
@@ -4218,34 +4221,34 @@
         <v>39</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="M29" s="3">
-        <v>2000000</v>
+        <v>300000</v>
       </c>
       <c r="N29" s="3">
-        <v>743000</v>
+        <v>300000</v>
       </c>
       <c r="O29" s="3">
-        <v>1257000</v>
+        <v>0</v>
       </c>
       <c r="P29" s="3">
-        <v>115000</v>
+        <v>300000</v>
       </c>
       <c r="Q29" s="3">
         <v>0</v>
       </c>
       <c r="R29" s="3">
-        <v>115000</v>
+        <v>300000</v>
       </c>
       <c r="S29" s="4" t="s">
-        <v>125</v>
+        <v>43</v>
       </c>
       <c r="T29" s="4" t="s">
         <v>44</v>
@@ -4257,10 +4260,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W29" s="3">
-        <v>19600000</v>
+        <v>2940000</v>
       </c>
       <c r="X29" s="5" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="Y29" s="4" t="s">
         <v>47</v>
@@ -4278,13 +4281,13 @@
         <v>50</v>
       </c>
       <c r="AD29" s="4" t="s">
-        <v>288</v>
+        <v>192</v>
       </c>
       <c r="AE29" s="4" t="s">
-        <v>277</v>
+        <v>120</v>
       </c>
       <c r="AF29" s="4" t="s">
-        <v>271</v>
+        <v>121</v>
       </c>
       <c r="AG29" s="3">
         <v>1</v>
@@ -4298,13 +4301,13 @@
         <v>34</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>36</v>
@@ -4319,34 +4322,34 @@
         <v>39</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>178</v>
+        <v>55</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>180</v>
+        <v>56</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>179</v>
+        <v>57</v>
       </c>
       <c r="M30" s="3">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="N30" s="3">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="O30" s="3">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="P30" s="3">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="Q30" s="3">
         <v>0</v>
       </c>
       <c r="R30" s="3">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="S30" s="4" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T30" s="4" t="s">
         <v>44</v>
@@ -4358,10 +4361,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W30" s="3">
-        <v>9800000</v>
+        <v>19600000</v>
       </c>
       <c r="X30" s="5" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="Y30" s="4" t="s">
         <v>47</v>
@@ -4379,16 +4382,16 @@
         <v>50</v>
       </c>
       <c r="AD30" s="4" t="s">
-        <v>285</v>
+        <v>225</v>
       </c>
       <c r="AE30" s="4" t="s">
-        <v>286</v>
+        <v>120</v>
       </c>
       <c r="AF30" s="4" t="s">
-        <v>287</v>
+        <v>121</v>
       </c>
       <c r="AG30" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.3">
@@ -4399,13 +4402,13 @@
         <v>34</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>36</v>
@@ -4420,34 +4423,34 @@
         <v>39</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="M31" s="3">
-        <v>200000</v>
+        <v>8000000</v>
       </c>
       <c r="N31" s="3">
-        <v>200000</v>
+        <v>2417000</v>
       </c>
       <c r="O31" s="3">
-        <v>0</v>
+        <v>5583000</v>
       </c>
       <c r="P31" s="3">
-        <v>200000</v>
+        <v>1672000</v>
       </c>
       <c r="Q31" s="3">
         <v>0</v>
       </c>
       <c r="R31" s="3">
-        <v>200000</v>
+        <v>1672000</v>
       </c>
       <c r="S31" s="4" t="s">
-        <v>43</v>
+        <v>125</v>
       </c>
       <c r="T31" s="4" t="s">
         <v>44</v>
@@ -4459,10 +4462,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W31" s="3">
-        <v>1960000</v>
+        <v>78400000</v>
       </c>
       <c r="X31" s="5" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="Y31" s="4" t="s">
         <v>47</v>
@@ -4474,22 +4477,22 @@
         <v>49</v>
       </c>
       <c r="AB31" s="4" t="s">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="AC31" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD31" s="4" t="s">
-        <v>95</v>
+        <v>292</v>
       </c>
       <c r="AE31" s="4" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF31" s="4" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="AG31" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.3">
@@ -4500,13 +4503,13 @@
         <v>34</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>36</v>
@@ -4521,34 +4524,34 @@
         <v>39</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="M32" s="3">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="N32" s="3">
-        <v>200000</v>
+        <v>345000</v>
       </c>
       <c r="O32" s="3">
-        <v>0</v>
+        <v>655000</v>
       </c>
       <c r="P32" s="3">
-        <v>200000</v>
+        <v>345000</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
       <c r="R32" s="3">
-        <v>200000</v>
+        <v>345000</v>
       </c>
       <c r="S32" s="4" t="s">
-        <v>43</v>
+        <v>125</v>
       </c>
       <c r="T32" s="4" t="s">
         <v>44</v>
@@ -4557,13 +4560,13 @@
         <v>45</v>
       </c>
       <c r="V32" s="3">
-        <v>34</v>
+        <v>7.7</v>
       </c>
       <c r="W32" s="3">
-        <v>6800000</v>
+        <v>7700000</v>
       </c>
       <c r="X32" s="5" t="s">
-        <v>150</v>
+        <v>72</v>
       </c>
       <c r="Y32" s="4" t="s">
         <v>47</v>
@@ -4581,16 +4584,16 @@
         <v>50</v>
       </c>
       <c r="AD32" s="4" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="AE32" s="4" t="s">
-        <v>59</v>
+        <v>161</v>
       </c>
       <c r="AF32" s="4" t="s">
-        <v>60</v>
+        <v>162</v>
       </c>
       <c r="AG32" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:33" x14ac:dyDescent="0.3">
@@ -4601,13 +4604,13 @@
         <v>34</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>126</v>
+        <v>189</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>210</v>
+        <v>58</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>36</v>
@@ -4622,31 +4625,31 @@
         <v>39</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>221</v>
+        <v>172</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>222</v>
+        <v>174</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>223</v>
+        <v>173</v>
       </c>
       <c r="M33" s="3">
-        <v>1500000</v>
+        <v>200000</v>
       </c>
       <c r="N33" s="3">
-        <v>1500000</v>
+        <v>200000</v>
       </c>
       <c r="O33" s="3">
         <v>0</v>
       </c>
       <c r="P33" s="3">
-        <v>1500000</v>
+        <v>200000</v>
       </c>
       <c r="Q33" s="3">
         <v>0</v>
       </c>
       <c r="R33" s="3">
-        <v>1500000</v>
+        <v>200000</v>
       </c>
       <c r="S33" s="4" t="s">
         <v>43</v>
@@ -4661,10 +4664,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W33" s="3">
-        <v>14700000</v>
+        <v>1960000</v>
       </c>
       <c r="X33" s="5" t="s">
-        <v>66</v>
+        <v>126</v>
       </c>
       <c r="Y33" s="4" t="s">
         <v>47</v>
@@ -4682,13 +4685,13 @@
         <v>50</v>
       </c>
       <c r="AD33" s="4" t="s">
-        <v>275</v>
+        <v>191</v>
       </c>
       <c r="AE33" s="4" t="s">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="AF33" s="4" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
       <c r="AG33" s="3">
         <v>1</v>
@@ -4702,13 +4705,13 @@
         <v>34</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>108</v>
+        <v>189</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>108</v>
+        <v>189</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>108</v>
+        <v>58</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>36</v>
@@ -4723,13 +4726,13 @@
         <v>39</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>87</v>
+        <v>175</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>88</v>
+        <v>177</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>89</v>
+        <v>176</v>
       </c>
       <c r="M34" s="3">
         <v>200000</v>
@@ -4765,7 +4768,7 @@
         <v>1960000</v>
       </c>
       <c r="X34" s="5" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
       <c r="Y34" s="4" t="s">
         <v>47</v>
@@ -4783,16 +4786,16 @@
         <v>50</v>
       </c>
       <c r="AD34" s="4" t="s">
-        <v>83</v>
+        <v>216</v>
       </c>
       <c r="AE34" s="4" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="AF34" s="4" t="s">
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="AG34" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:33" x14ac:dyDescent="0.3">
@@ -4803,13 +4806,13 @@
         <v>34</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>61</v>
+        <v>189</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>61</v>
+        <v>189</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>36</v>
@@ -4824,31 +4827,31 @@
         <v>39</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>151</v>
+        <v>87</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>152</v>
+        <v>88</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>153</v>
+        <v>89</v>
       </c>
       <c r="M35" s="3">
-        <v>1000000</v>
+        <v>200000</v>
       </c>
       <c r="N35" s="3">
-        <v>1000000</v>
+        <v>200000</v>
       </c>
       <c r="O35" s="3">
         <v>0</v>
       </c>
       <c r="P35" s="3">
-        <v>1000000</v>
+        <v>200000</v>
       </c>
       <c r="Q35" s="3">
         <v>0</v>
       </c>
       <c r="R35" s="3">
-        <v>1000000</v>
+        <v>200000</v>
       </c>
       <c r="S35" s="4" t="s">
         <v>43</v>
@@ -4863,10 +4866,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W35" s="3">
-        <v>9800000</v>
+        <v>1960000</v>
       </c>
       <c r="X35" s="5" t="s">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="Y35" s="4" t="s">
         <v>47</v>
@@ -4884,16 +4887,16 @@
         <v>50</v>
       </c>
       <c r="AD35" s="4" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="AE35" s="4" t="s">
-        <v>67</v>
+        <v>190</v>
       </c>
       <c r="AF35" s="4" t="s">
-        <v>68</v>
+        <v>171</v>
       </c>
       <c r="AG35" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:33" x14ac:dyDescent="0.3">
@@ -4904,13 +4907,13 @@
         <v>34</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>35</v>
+        <v>189</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>35</v>
+        <v>189</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>36</v>
@@ -4925,31 +4928,31 @@
         <v>39</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>99</v>
+        <v>182</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>100</v>
+        <v>184</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>101</v>
+        <v>183</v>
       </c>
       <c r="M36" s="3">
-        <v>2000000</v>
+        <v>300000</v>
       </c>
       <c r="N36" s="3">
-        <v>2000000</v>
+        <v>300000</v>
       </c>
       <c r="O36" s="3">
         <v>0</v>
       </c>
       <c r="P36" s="3">
-        <v>2000000</v>
+        <v>300000</v>
       </c>
       <c r="Q36" s="3">
         <v>0</v>
       </c>
       <c r="R36" s="3">
-        <v>2000000</v>
+        <v>300000</v>
       </c>
       <c r="S36" s="4" t="s">
         <v>43</v>
@@ -4961,13 +4964,13 @@
         <v>45</v>
       </c>
       <c r="V36" s="3">
-        <v>6.7</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="W36" s="3">
-        <v>13400000</v>
+        <v>2940000</v>
       </c>
       <c r="X36" s="5" t="s">
-        <v>107</v>
+        <v>185</v>
       </c>
       <c r="Y36" s="4" t="s">
         <v>47</v>
@@ -4985,16 +4988,16 @@
         <v>50</v>
       </c>
       <c r="AD36" s="4" t="s">
-        <v>154</v>
+        <v>291</v>
       </c>
       <c r="AE36" s="4" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="AF36" s="4" t="s">
-        <v>53</v>
+        <v>171</v>
       </c>
       <c r="AG36" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:33" x14ac:dyDescent="0.3">
@@ -5026,31 +5029,31 @@
         <v>39</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>182</v>
+        <v>55</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>184</v>
+        <v>56</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>183</v>
+        <v>57</v>
       </c>
       <c r="M37" s="3">
-        <v>300000</v>
+        <v>2000000</v>
       </c>
       <c r="N37" s="3">
-        <v>300000</v>
+        <v>2000000</v>
       </c>
       <c r="O37" s="3">
         <v>0</v>
       </c>
       <c r="P37" s="3">
-        <v>300000</v>
+        <v>2000000</v>
       </c>
       <c r="Q37" s="3">
         <v>0</v>
       </c>
       <c r="R37" s="3">
-        <v>300000</v>
+        <v>2000000</v>
       </c>
       <c r="S37" s="4" t="s">
         <v>43</v>
@@ -5065,10 +5068,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W37" s="3">
-        <v>2940000</v>
+        <v>19600000</v>
       </c>
       <c r="X37" s="5" t="s">
-        <v>185</v>
+        <v>126</v>
       </c>
       <c r="Y37" s="4" t="s">
         <v>47</v>
@@ -5086,7 +5089,7 @@
         <v>50</v>
       </c>
       <c r="AD37" s="4" t="s">
-        <v>279</v>
+        <v>191</v>
       </c>
       <c r="AE37" s="4" t="s">
         <v>190</v>
@@ -5095,7 +5098,7 @@
         <v>171</v>
       </c>
       <c r="AG37" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:33" x14ac:dyDescent="0.3">
@@ -5106,13 +5109,13 @@
         <v>34</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>35</v>
+        <v>189</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>35</v>
+        <v>189</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>36</v>
@@ -5127,31 +5130,31 @@
         <v>39</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>109</v>
+        <v>178</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>110</v>
+        <v>180</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>111</v>
+        <v>179</v>
       </c>
       <c r="M38" s="3">
-        <v>200000</v>
+        <v>3000000</v>
       </c>
       <c r="N38" s="3">
-        <v>200000</v>
+        <v>3000000</v>
       </c>
       <c r="O38" s="3">
         <v>0</v>
       </c>
       <c r="P38" s="3">
-        <v>200000</v>
+        <v>3000000</v>
       </c>
       <c r="Q38" s="3">
         <v>0</v>
       </c>
       <c r="R38" s="3">
-        <v>200000</v>
+        <v>3000000</v>
       </c>
       <c r="S38" s="4" t="s">
         <v>43</v>
@@ -5166,10 +5169,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W38" s="3">
-        <v>1960000</v>
+        <v>29400000</v>
       </c>
       <c r="X38" s="5" t="s">
-        <v>107</v>
+        <v>166</v>
       </c>
       <c r="Y38" s="4" t="s">
         <v>47</v>
@@ -5181,22 +5184,22 @@
         <v>49</v>
       </c>
       <c r="AB38" s="4" t="s">
-        <v>122</v>
+        <v>181</v>
       </c>
       <c r="AC38" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD38" s="4" t="s">
-        <v>106</v>
+        <v>277</v>
       </c>
       <c r="AE38" s="4" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="AF38" s="4" t="s">
-        <v>123</v>
+        <v>171</v>
       </c>
       <c r="AG38" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.3">
@@ -5207,13 +5210,13 @@
         <v>34</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>54</v>
+        <v>206</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>46</v>
+        <v>206</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>46</v>
+        <v>206</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>36</v>
@@ -5228,34 +5231,34 @@
         <v>39</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="L39" s="4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="M39" s="3">
-        <v>300000</v>
+        <v>1500000</v>
       </c>
       <c r="N39" s="3">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="O39" s="3">
-        <v>0</v>
+        <v>1500000</v>
       </c>
       <c r="P39" s="3">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="Q39" s="3">
         <v>0</v>
       </c>
       <c r="R39" s="3">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="S39" s="4" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="T39" s="4" t="s">
         <v>44</v>
@@ -5264,13 +5267,13 @@
         <v>45</v>
       </c>
       <c r="V39" s="3">
-        <v>9.8000000000000007</v>
+        <v>7.7</v>
       </c>
       <c r="W39" s="3">
-        <v>2940000</v>
+        <v>11550000</v>
       </c>
       <c r="X39" s="5" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="Y39" s="4" t="s">
         <v>47</v>
@@ -5288,16 +5291,16 @@
         <v>50</v>
       </c>
       <c r="AD39" s="4" t="s">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="AE39" s="4" t="s">
-        <v>59</v>
+        <v>208</v>
       </c>
       <c r="AF39" s="4" t="s">
-        <v>60</v>
+        <v>193</v>
       </c>
       <c r="AG39" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:33" x14ac:dyDescent="0.3">
@@ -5308,13 +5311,13 @@
         <v>34</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>72</v>
+        <v>206</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>72</v>
+        <v>206</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>72</v>
+        <v>206</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>36</v>
@@ -5329,34 +5332,34 @@
         <v>39</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>158</v>
+        <v>198</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>159</v>
+        <v>200</v>
       </c>
       <c r="L40" s="4" t="s">
-        <v>160</v>
+        <v>199</v>
       </c>
       <c r="M40" s="3">
-        <v>1000000</v>
+        <v>200000</v>
       </c>
       <c r="N40" s="3">
-        <v>345000</v>
+        <v>200000</v>
       </c>
       <c r="O40" s="3">
-        <v>655000</v>
+        <v>0</v>
       </c>
       <c r="P40" s="3">
-        <v>345000</v>
+        <v>0</v>
       </c>
       <c r="Q40" s="3">
         <v>0</v>
       </c>
       <c r="R40" s="3">
-        <v>345000</v>
+        <v>0</v>
       </c>
       <c r="S40" s="4" t="s">
-        <v>125</v>
+        <v>43</v>
       </c>
       <c r="T40" s="4" t="s">
         <v>44</v>
@@ -5365,13 +5368,13 @@
         <v>45</v>
       </c>
       <c r="V40" s="3">
-        <v>7.7</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="W40" s="3">
-        <v>7700000</v>
+        <v>1960000</v>
       </c>
       <c r="X40" s="5" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="Y40" s="4" t="s">
         <v>47</v>
@@ -5389,16 +5392,16 @@
         <v>50</v>
       </c>
       <c r="AD40" s="4" t="s">
-        <v>224</v>
+        <v>292</v>
       </c>
       <c r="AE40" s="4" t="s">
-        <v>161</v>
+        <v>208</v>
       </c>
       <c r="AF40" s="4" t="s">
-        <v>162</v>
+        <v>193</v>
       </c>
       <c r="AG40" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:33" x14ac:dyDescent="0.3">
@@ -5409,13 +5412,13 @@
         <v>34</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>61</v>
+        <v>206</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>61</v>
+        <v>206</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>61</v>
+        <v>206</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>36</v>
@@ -5430,31 +5433,31 @@
         <v>39</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>163</v>
+        <v>92</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>164</v>
+        <v>93</v>
       </c>
       <c r="L41" s="4" t="s">
-        <v>165</v>
+        <v>94</v>
       </c>
       <c r="M41" s="3">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="N41" s="3">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="O41" s="3">
         <v>0</v>
       </c>
       <c r="P41" s="3">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="Q41" s="3">
         <v>0</v>
       </c>
       <c r="R41" s="3">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="S41" s="4" t="s">
         <v>43</v>
@@ -5469,10 +5472,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W41" s="3">
-        <v>4900000</v>
+        <v>2940000</v>
       </c>
       <c r="X41" s="5" t="s">
-        <v>166</v>
+        <v>197</v>
       </c>
       <c r="Y41" s="4" t="s">
         <v>47</v>
@@ -5490,13 +5493,13 @@
         <v>50</v>
       </c>
       <c r="AD41" s="4" t="s">
-        <v>225</v>
+        <v>293</v>
       </c>
       <c r="AE41" s="4" t="s">
-        <v>67</v>
+        <v>208</v>
       </c>
       <c r="AF41" s="4" t="s">
-        <v>68</v>
+        <v>193</v>
       </c>
       <c r="AG41" s="3">
         <v>5</v>
@@ -5510,13 +5513,13 @@
         <v>34</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>91</v>
+        <v>206</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>91</v>
+        <v>206</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>91</v>
+        <v>206</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>36</v>
@@ -5531,34 +5534,34 @@
         <v>39</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>167</v>
+        <v>55</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>168</v>
+        <v>56</v>
       </c>
       <c r="L42" s="4" t="s">
-        <v>169</v>
+        <v>57</v>
       </c>
       <c r="M42" s="3">
-        <v>300000</v>
+        <v>5000000</v>
       </c>
       <c r="N42" s="3">
-        <v>300000</v>
+        <v>2478000</v>
       </c>
       <c r="O42" s="3">
-        <v>0</v>
+        <v>2522000</v>
       </c>
       <c r="P42" s="3">
-        <v>300000</v>
+        <v>2478000</v>
       </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
       <c r="R42" s="3">
-        <v>300000</v>
+        <v>2478000</v>
       </c>
       <c r="S42" s="4" t="s">
-        <v>43</v>
+        <v>125</v>
       </c>
       <c r="T42" s="4" t="s">
         <v>44</v>
@@ -5570,10 +5573,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W42" s="3">
-        <v>2940000</v>
+        <v>49000000</v>
       </c>
       <c r="X42" s="5" t="s">
-        <v>124</v>
+        <v>166</v>
       </c>
       <c r="Y42" s="4" t="s">
         <v>47</v>
@@ -5591,16 +5594,16 @@
         <v>50</v>
       </c>
       <c r="AD42" s="4" t="s">
-        <v>192</v>
+        <v>225</v>
       </c>
       <c r="AE42" s="4" t="s">
-        <v>120</v>
+        <v>208</v>
       </c>
       <c r="AF42" s="4" t="s">
-        <v>121</v>
+        <v>193</v>
       </c>
       <c r="AG42" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:33" x14ac:dyDescent="0.3">
@@ -5632,34 +5635,34 @@
         <v>39</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="L43" s="4" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="M43" s="3">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="N43" s="3">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="O43" s="3">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="P43" s="3">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
       </c>
       <c r="R43" s="3">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="S43" s="4" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="T43" s="4" t="s">
         <v>44</v>
@@ -5671,10 +5674,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W43" s="3">
-        <v>9800000</v>
+        <v>4900000</v>
       </c>
       <c r="X43" s="5" t="s">
-        <v>66</v>
+        <v>185</v>
       </c>
       <c r="Y43" s="4" t="s">
         <v>47</v>
@@ -5686,13 +5689,13 @@
         <v>49</v>
       </c>
       <c r="AB43" s="4" t="s">
-        <v>39</v>
+        <v>204</v>
       </c>
       <c r="AC43" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD43" s="4" t="s">
-        <v>278</v>
+        <v>207</v>
       </c>
       <c r="AE43" s="4" t="s">
         <v>208</v>
@@ -5701,7 +5704,7 @@
         <v>193</v>
       </c>
       <c r="AG43" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:33" x14ac:dyDescent="0.3">
@@ -5712,13 +5715,13 @@
         <v>34</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>35</v>
+        <v>206</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>35</v>
+        <v>206</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>35</v>
+        <v>206</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>36</v>
@@ -5733,31 +5736,31 @@
         <v>39</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>40</v>
+        <v>194</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>41</v>
+        <v>196</v>
       </c>
       <c r="L44" s="4" t="s">
-        <v>42</v>
+        <v>195</v>
       </c>
       <c r="M44" s="3">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="N44" s="3">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
       </c>
       <c r="P44" s="3">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
       </c>
       <c r="R44" s="3">
-        <v>200000</v>
+        <v>1000000</v>
       </c>
       <c r="S44" s="4" t="s">
         <v>43</v>
@@ -5772,10 +5775,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W44" s="3">
-        <v>1960000</v>
+        <v>9800000</v>
       </c>
       <c r="X44" s="5" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="Y44" s="4" t="s">
         <v>47</v>
@@ -5793,16 +5796,16 @@
         <v>50</v>
       </c>
       <c r="AD44" s="4" t="s">
-        <v>51</v>
+        <v>277</v>
       </c>
       <c r="AE44" s="4" t="s">
-        <v>52</v>
+        <v>208</v>
       </c>
       <c r="AF44" s="4" t="s">
-        <v>53</v>
+        <v>193</v>
       </c>
       <c r="AG44" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:33" x14ac:dyDescent="0.3">
@@ -5813,13 +5816,13 @@
         <v>34</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>35</v>
+        <v>206</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>35</v>
+        <v>206</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>35</v>
+        <v>206</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>36</v>
@@ -5834,13 +5837,13 @@
         <v>39</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="M45" s="3">
         <v>200000</v>
@@ -5876,7 +5879,7 @@
         <v>1960000</v>
       </c>
       <c r="X45" s="5" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="Y45" s="4" t="s">
         <v>47</v>
@@ -5888,22 +5891,22 @@
         <v>49</v>
       </c>
       <c r="AB45" s="4" t="s">
-        <v>122</v>
+        <v>39</v>
       </c>
       <c r="AC45" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD45" s="4" t="s">
-        <v>106</v>
+        <v>216</v>
       </c>
       <c r="AE45" s="4" t="s">
-        <v>52</v>
+        <v>208</v>
       </c>
       <c r="AF45" s="4" t="s">
-        <v>123</v>
+        <v>193</v>
       </c>
       <c r="AG45" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:33" x14ac:dyDescent="0.3">
@@ -5914,13 +5917,13 @@
         <v>34</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>54</v>
+        <v>210</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>46</v>
+        <v>126</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>46</v>
+        <v>210</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>36</v>
@@ -5935,31 +5938,31 @@
         <v>39</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>55</v>
+        <v>211</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>56</v>
+        <v>212</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>57</v>
+        <v>213</v>
       </c>
       <c r="M46" s="3">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="N46" s="3">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="O46" s="3">
         <v>0</v>
       </c>
       <c r="P46" s="3">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
       <c r="R46" s="3">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="S46" s="4" t="s">
         <v>43</v>
@@ -5974,10 +5977,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W46" s="3">
-        <v>19600000</v>
+        <v>1960000</v>
       </c>
       <c r="X46" s="5" t="s">
-        <v>58</v>
+        <v>197</v>
       </c>
       <c r="Y46" s="4" t="s">
         <v>47</v>
@@ -5995,13 +5998,13 @@
         <v>50</v>
       </c>
       <c r="AD46" s="4" t="s">
-        <v>51</v>
+        <v>278</v>
       </c>
       <c r="AE46" s="4" t="s">
-        <v>59</v>
+        <v>214</v>
       </c>
       <c r="AF46" s="4" t="s">
-        <v>60</v>
+        <v>215</v>
       </c>
       <c r="AG46" s="3">
         <v>3</v>
@@ -6015,13 +6018,13 @@
         <v>34</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>61</v>
+        <v>210</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>61</v>
+        <v>126</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>61</v>
+        <v>210</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>36</v>
@@ -6036,31 +6039,31 @@
         <v>39</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>74</v>
+        <v>217</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>75</v>
+        <v>218</v>
       </c>
       <c r="L47" s="4" t="s">
-        <v>76</v>
+        <v>219</v>
       </c>
       <c r="M47" s="3">
-        <v>500000</v>
+        <v>20000</v>
       </c>
       <c r="N47" s="3">
-        <v>500000</v>
+        <v>20000</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
       </c>
       <c r="P47" s="3">
-        <v>500000</v>
+        <v>20000</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
       </c>
       <c r="R47" s="3">
-        <v>500000</v>
+        <v>20000</v>
       </c>
       <c r="S47" s="4" t="s">
         <v>43</v>
@@ -6075,10 +6078,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W47" s="3">
-        <v>4900000</v>
+        <v>196000</v>
       </c>
       <c r="X47" s="5" t="s">
-        <v>124</v>
+        <v>66</v>
       </c>
       <c r="Y47" s="4" t="s">
         <v>47</v>
@@ -6096,16 +6099,16 @@
         <v>50</v>
       </c>
       <c r="AD47" s="4" t="s">
-        <v>170</v>
+        <v>294</v>
       </c>
       <c r="AE47" s="4" t="s">
-        <v>67</v>
+        <v>214</v>
       </c>
       <c r="AF47" s="4" t="s">
-        <v>68</v>
+        <v>215</v>
       </c>
       <c r="AG47" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:33" x14ac:dyDescent="0.3">
@@ -6116,13 +6119,13 @@
         <v>34</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>61</v>
+        <v>210</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>61</v>
+        <v>126</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>61</v>
+        <v>210</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>36</v>
@@ -6137,31 +6140,31 @@
         <v>39</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>62</v>
+        <v>220</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>63</v>
+        <v>221</v>
       </c>
       <c r="L48" s="4" t="s">
-        <v>64</v>
+        <v>222</v>
       </c>
       <c r="M48" s="3">
-        <v>200000</v>
+        <v>1500000</v>
       </c>
       <c r="N48" s="3">
-        <v>200000</v>
+        <v>1500000</v>
       </c>
       <c r="O48" s="3">
         <v>0</v>
       </c>
       <c r="P48" s="3">
-        <v>200000</v>
+        <v>1500000</v>
       </c>
       <c r="Q48" s="3">
         <v>0</v>
       </c>
       <c r="R48" s="3">
-        <v>200000</v>
+        <v>1500000</v>
       </c>
       <c r="S48" s="4" t="s">
         <v>43</v>
@@ -6176,7 +6179,7 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W48" s="3">
-        <v>1960000</v>
+        <v>14700000</v>
       </c>
       <c r="X48" s="5" t="s">
         <v>66</v>
@@ -6197,16 +6200,16 @@
         <v>50</v>
       </c>
       <c r="AD48" s="4" t="s">
-        <v>226</v>
+        <v>274</v>
       </c>
       <c r="AE48" s="4" t="s">
-        <v>67</v>
+        <v>214</v>
       </c>
       <c r="AF48" s="4" t="s">
-        <v>68</v>
+        <v>215</v>
       </c>
       <c r="AG48" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:33" x14ac:dyDescent="0.3">
@@ -6217,13 +6220,13 @@
         <v>34</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>91</v>
+        <v>272</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>91</v>
+        <v>272</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>91</v>
+        <v>272</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>36</v>
@@ -6238,34 +6241,34 @@
         <v>39</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="L49" s="4" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="M49" s="3">
-        <v>2000000</v>
+        <v>500000</v>
       </c>
       <c r="N49" s="3">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="O49" s="3">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="P49" s="3">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="Q49" s="3">
         <v>0</v>
       </c>
       <c r="R49" s="3">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="S49" s="4" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="T49" s="4" t="s">
         <v>44</v>
@@ -6277,10 +6280,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W49" s="3">
-        <v>19600000</v>
+        <v>4900000</v>
       </c>
       <c r="X49" s="5" t="s">
-        <v>126</v>
+        <v>273</v>
       </c>
       <c r="Y49" s="4" t="s">
         <v>47</v>
@@ -6298,16 +6301,16 @@
         <v>50</v>
       </c>
       <c r="AD49" s="4" t="s">
-        <v>226</v>
+        <v>275</v>
       </c>
       <c r="AE49" s="4" t="s">
-        <v>120</v>
+        <v>276</v>
       </c>
       <c r="AF49" s="4" t="s">
-        <v>121</v>
+        <v>270</v>
       </c>
       <c r="AG49" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:33" x14ac:dyDescent="0.3">
@@ -6318,13 +6321,13 @@
         <v>34</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>91</v>
+        <v>272</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>91</v>
+        <v>272</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>91</v>
+        <v>272</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>36</v>
@@ -6339,31 +6342,31 @@
         <v>39</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>115</v>
+        <v>178</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>116</v>
+        <v>180</v>
       </c>
       <c r="L50" s="4" t="s">
-        <v>117</v>
+        <v>179</v>
       </c>
       <c r="M50" s="3">
-        <v>8000000</v>
+        <v>2000000</v>
       </c>
       <c r="N50" s="3">
-        <v>1672000</v>
+        <v>1652000</v>
       </c>
       <c r="O50" s="3">
-        <v>6328000</v>
+        <v>348000</v>
       </c>
       <c r="P50" s="3">
-        <v>0</v>
+        <v>743000</v>
       </c>
       <c r="Q50" s="3">
         <v>0</v>
       </c>
       <c r="R50" s="3">
-        <v>0</v>
+        <v>743000</v>
       </c>
       <c r="S50" s="4" t="s">
         <v>125</v>
@@ -6378,7 +6381,7 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W50" s="3">
-        <v>78400000</v>
+        <v>19600000</v>
       </c>
       <c r="X50" s="5" t="s">
         <v>118</v>
@@ -6393,22 +6396,22 @@
         <v>49</v>
       </c>
       <c r="AB50" s="4" t="s">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="AC50" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD50" s="4" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="AE50" s="4" t="s">
-        <v>120</v>
+        <v>276</v>
       </c>
       <c r="AF50" s="4" t="s">
-        <v>121</v>
+        <v>270</v>
       </c>
       <c r="AG50" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:33" x14ac:dyDescent="0.3">
@@ -6419,13 +6422,13 @@
         <v>34</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>189</v>
+        <v>272</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>189</v>
+        <v>272</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>58</v>
+        <v>272</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>36</v>
@@ -6440,34 +6443,34 @@
         <v>39</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>55</v>
+        <v>151</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>56</v>
+        <v>152</v>
       </c>
       <c r="L51" s="4" t="s">
-        <v>57</v>
+        <v>153</v>
       </c>
       <c r="M51" s="3">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
       <c r="N51" s="3">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="O51" s="3">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="P51" s="3">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="Q51" s="3">
         <v>0</v>
       </c>
       <c r="R51" s="3">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="S51" s="4" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="T51" s="4" t="s">
         <v>44</v>
@@ -6479,10 +6482,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W51" s="3">
-        <v>19600000</v>
+        <v>9800000</v>
       </c>
       <c r="X51" s="5" t="s">
-        <v>126</v>
+        <v>273</v>
       </c>
       <c r="Y51" s="4" t="s">
         <v>47</v>
@@ -6500,16 +6503,16 @@
         <v>50</v>
       </c>
       <c r="AD51" s="4" t="s">
-        <v>191</v>
+        <v>275</v>
       </c>
       <c r="AE51" s="4" t="s">
-        <v>190</v>
+        <v>276</v>
       </c>
       <c r="AF51" s="4" t="s">
-        <v>171</v>
+        <v>270</v>
       </c>
       <c r="AG51" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:33" x14ac:dyDescent="0.3">
@@ -6520,13 +6523,13 @@
         <v>34</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>189</v>
+        <v>118</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>189</v>
+        <v>118</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>58</v>
+        <v>118</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>36</v>
@@ -6541,34 +6544,34 @@
         <v>39</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>178</v>
+        <v>279</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>180</v>
+        <v>280</v>
       </c>
       <c r="L52" s="4" t="s">
-        <v>179</v>
+        <v>281</v>
       </c>
       <c r="M52" s="3">
-        <v>3000000</v>
+        <v>300000</v>
       </c>
       <c r="N52" s="3">
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="O52" s="3">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="P52" s="3">
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="3">
         <v>0</v>
       </c>
       <c r="R52" s="3">
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="S52" s="4" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="T52" s="4" t="s">
         <v>44</v>
@@ -6580,10 +6583,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W52" s="3">
-        <v>29400000</v>
+        <v>2940000</v>
       </c>
       <c r="X52" s="5" t="s">
-        <v>166</v>
+        <v>282</v>
       </c>
       <c r="Y52" s="4" t="s">
         <v>47</v>
@@ -6595,22 +6598,22 @@
         <v>49</v>
       </c>
       <c r="AB52" s="4" t="s">
-        <v>181</v>
+        <v>39</v>
       </c>
       <c r="AC52" s="4" t="s">
         <v>50</v>
       </c>
       <c r="AD52" s="4" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="AE52" s="4" t="s">
-        <v>190</v>
+        <v>284</v>
       </c>
       <c r="AF52" s="4" t="s">
-        <v>171</v>
+        <v>285</v>
       </c>
       <c r="AG52" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:33" x14ac:dyDescent="0.3">
@@ -6621,13 +6624,13 @@
         <v>34</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>206</v>
+        <v>118</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>206</v>
+        <v>118</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>206</v>
+        <v>118</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>36</v>
@@ -6642,34 +6645,34 @@
         <v>39</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>136</v>
+        <v>286</v>
       </c>
       <c r="K53" s="4" t="s">
-        <v>137</v>
+        <v>287</v>
       </c>
       <c r="L53" s="4" t="s">
-        <v>138</v>
+        <v>288</v>
       </c>
       <c r="M53" s="3">
-        <v>200000</v>
+        <v>500000</v>
       </c>
       <c r="N53" s="3">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="O53" s="3">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="P53" s="3">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="Q53" s="3">
         <v>0</v>
       </c>
       <c r="R53" s="3">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="S53" s="4" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="T53" s="4" t="s">
         <v>44</v>
@@ -6681,10 +6684,10 @@
         <v>9.8000000000000007</v>
       </c>
       <c r="W53" s="3">
-        <v>1960000</v>
+        <v>4900000</v>
       </c>
       <c r="X53" s="5" t="s">
-        <v>126</v>
+        <v>289</v>
       </c>
       <c r="Y53" s="4" t="s">
         <v>47</v>
@@ -6702,16 +6705,16 @@
         <v>50</v>
       </c>
       <c r="AD53" s="4" t="s">
-        <v>217</v>
+        <v>283</v>
       </c>
       <c r="AE53" s="4" t="s">
-        <v>208</v>
+        <v>284</v>
       </c>
       <c r="AF53" s="4" t="s">
-        <v>193</v>
+        <v>285</v>
       </c>
       <c r="AG53" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:33" x14ac:dyDescent="0.3">
@@ -6722,13 +6725,13 @@
         <v>34</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>273</v>
+        <v>118</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>273</v>
+        <v>118</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>273</v>
+        <v>118</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>36</v>
@@ -6743,13 +6746,13 @@
         <v>39</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>152</v>
+        <v>180</v>
       </c>
       <c r="L54" s="4" t="s">
-        <v>153</v>
+        <v>179</v>
       </c>
       <c r="M54" s="3">
         <v>1000000</v>
@@ -6785,7 +6788,7 @@
         <v>9800000</v>
       </c>
       <c r="X54" s="5" t="s">
-        <v>274</v>
+        <v>118</v>
       </c>
       <c r="Y54" s="4" t="s">
         <v>47</v>
@@ -6803,16 +6806,16 @@
         <v>50</v>
       </c>
       <c r="AD54" s="4" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="AE54" s="4" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="AF54" s="4" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="AG54" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:33" x14ac:dyDescent="0.3">
@@ -6907,16 +6910,16 @@
         <v>31</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>32</v>
       </c>
       <c r="E1" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>228</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>229</v>
       </c>
       <c r="G1" s="7" t="s">
         <v>9</v>
@@ -6928,16 +6931,16 @@
         <v>10</v>
       </c>
       <c r="J1" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="K1" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="L1" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="M1" s="7" t="s">
         <v>232</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>233</v>
       </c>
       <c r="N1" s="7" t="s">
         <v>5</v>
@@ -6946,55 +6949,55 @@
         <v>24</v>
       </c>
       <c r="P1" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q1" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="R1" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="S1" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>238</v>
-      </c>
-      <c r="U1" s="6" t="s">
-        <v>239</v>
       </c>
       <c r="V1" s="6" t="s">
         <v>17</v>
       </c>
       <c r="W1" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="X1" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="X1" s="7" t="s">
+      <c r="Y1" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="Y1" s="7" t="s">
+      <c r="Z1" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="Z1" s="7" t="s">
+      <c r="AA1" s="7" t="s">
         <v>243</v>
-      </c>
-      <c r="AA1" s="7" t="s">
-        <v>244</v>
       </c>
       <c r="AB1" s="7" t="s">
         <v>27</v>
       </c>
       <c r="AC1" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="AD1" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="AD1" s="7" t="s">
+      <c r="AE1" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="AE1" s="7" t="s">
+      <c r="AF1" s="7" t="s">
         <v>247</v>
-      </c>
-      <c r="AF1" s="7" t="s">
-        <v>248</v>
       </c>
       <c r="AG1" s="7" t="s">
         <v>28</v>
@@ -7011,16 +7014,16 @@
         <v>53</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D2" s="6">
         <v>1</v>
       </c>
       <c r="E2" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="F2" s="7" t="s">
         <v>250</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>251</v>
       </c>
       <c r="G2" s="7" t="s">
         <v>96</v>
@@ -7050,7 +7053,7 @@
         <v>47</v>
       </c>
       <c r="P2" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q2" s="7" t="s">
         <v>45</v>
@@ -7083,28 +7086,28 @@
         <v>39</v>
       </c>
       <c r="AA2" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC2" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB2" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC2" s="7" t="s">
+      <c r="AD2" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AE2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG2" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH2" s="7" t="s">
         <v>254</v>
-      </c>
-      <c r="AD2" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="AE2" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF2" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG2" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH2" s="7" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.3">
@@ -7115,16 +7118,16 @@
         <v>53</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D3" s="6">
         <v>2</v>
       </c>
       <c r="E3" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>250</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>251</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>40</v>
@@ -7154,7 +7157,7 @@
         <v>47</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q3" s="7" t="s">
         <v>45</v>
@@ -7187,28 +7190,28 @@
         <v>39</v>
       </c>
       <c r="AA3" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB3" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC3" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB3" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC3" s="7" t="s">
+      <c r="AD3" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AE3" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF3" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG3" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH3" s="7" t="s">
         <v>254</v>
-      </c>
-      <c r="AD3" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="AE3" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF3" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG3" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH3" s="7" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.3">
@@ -7219,16 +7222,16 @@
         <v>53</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D4" s="6">
         <v>3</v>
       </c>
       <c r="E4" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>250</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>251</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>99</v>
@@ -7240,7 +7243,7 @@
         <v>100</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K4" s="7" t="s">
         <v>36</v>
@@ -7258,7 +7261,7 @@
         <v>47</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q4" s="7" t="s">
         <v>45</v>
@@ -7291,28 +7294,28 @@
         <v>39</v>
       </c>
       <c r="AA4" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB4" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC4" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB4" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC4" s="7" t="s">
+      <c r="AD4" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AE4" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF4" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG4" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH4" s="7" t="s">
         <v>254</v>
-      </c>
-      <c r="AD4" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="AE4" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF4" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG4" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH4" s="7" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.3">
@@ -7323,16 +7326,16 @@
         <v>123</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D5" s="6">
         <v>1</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>109</v>
@@ -7362,7 +7365,7 @@
         <v>47</v>
       </c>
       <c r="P5" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q5" s="7" t="s">
         <v>45</v>
@@ -7395,28 +7398,28 @@
         <v>39</v>
       </c>
       <c r="AA5" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AB5" s="7" t="s">
         <v>122</v>
       </c>
       <c r="AC5" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AD5" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AE5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG5" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH5" s="7" t="s">
         <v>254</v>
-      </c>
-      <c r="AD5" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="AE5" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF5" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG5" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH5" s="7" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.3">
@@ -7427,16 +7430,16 @@
         <v>123</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D6" s="6">
         <v>2</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>103</v>
@@ -7466,7 +7469,7 @@
         <v>47</v>
       </c>
       <c r="P6" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q6" s="7" t="s">
         <v>45</v>
@@ -7499,28 +7502,28 @@
         <v>39</v>
       </c>
       <c r="AA6" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AB6" s="7" t="s">
         <v>122</v>
       </c>
       <c r="AC6" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AD6" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AE6" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF6" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG6" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH6" s="7" t="s">
         <v>254</v>
-      </c>
-      <c r="AD6" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="AE6" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF6" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG6" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH6" s="7" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.3">
@@ -7531,16 +7534,16 @@
         <v>123</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D7" s="6">
         <v>3</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>112</v>
@@ -7570,7 +7573,7 @@
         <v>47</v>
       </c>
       <c r="P7" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q7" s="7" t="s">
         <v>45</v>
@@ -7603,28 +7606,28 @@
         <v>39</v>
       </c>
       <c r="AA7" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AB7" s="7" t="s">
         <v>122</v>
       </c>
       <c r="AC7" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AD7" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AE7" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF7" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG7" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH7" s="7" t="s">
         <v>254</v>
-      </c>
-      <c r="AD7" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="AE7" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF7" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG7" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH7" s="7" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="8" spans="1:34" x14ac:dyDescent="0.3">
@@ -7635,16 +7638,16 @@
         <v>135</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D8" s="6">
         <v>1</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G8" s="7" t="s">
         <v>99</v>
@@ -7656,7 +7659,7 @@
         <v>100</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K8" s="7" t="s">
         <v>36</v>
@@ -7674,7 +7677,7 @@
         <v>47</v>
       </c>
       <c r="P8" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q8" s="7" t="s">
         <v>39</v>
@@ -7707,28 +7710,28 @@
         <v>39</v>
       </c>
       <c r="AA8" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC8" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB8" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC8" s="7" t="s">
+      <c r="AD8" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AE8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG8" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH8" s="7" t="s">
         <v>254</v>
-      </c>
-      <c r="AD8" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="AE8" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF8" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG8" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH8" s="7" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.3">
@@ -7739,16 +7742,16 @@
         <v>135</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D9" s="6">
         <v>2</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>127</v>
@@ -7778,7 +7781,7 @@
         <v>47</v>
       </c>
       <c r="P9" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q9" s="7" t="s">
         <v>39</v>
@@ -7811,16 +7814,16 @@
         <v>39</v>
       </c>
       <c r="AA9" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC9" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB9" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC9" s="7" t="s">
-        <v>254</v>
-      </c>
       <c r="AD9" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE9" s="7" t="s">
         <v>39</v>
@@ -7832,7 +7835,7 @@
         <v>47</v>
       </c>
       <c r="AH9" s="7" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.3">
@@ -7843,16 +7846,16 @@
         <v>135</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D10" s="6">
         <v>3</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>92</v>
@@ -7882,7 +7885,7 @@
         <v>47</v>
       </c>
       <c r="P10" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q10" s="7" t="s">
         <v>39</v>
@@ -7915,28 +7918,28 @@
         <v>39</v>
       </c>
       <c r="AA10" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB10" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC10" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB10" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC10" s="7" t="s">
+      <c r="AD10" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AE10" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF10" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG10" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH10" s="7" t="s">
         <v>254</v>
-      </c>
-      <c r="AD10" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="AE10" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF10" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG10" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH10" s="7" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.3">
@@ -7947,16 +7950,16 @@
         <v>135</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D11" s="6">
         <v>4</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>84</v>
@@ -7968,7 +7971,7 @@
         <v>85</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="K11" s="7" t="s">
         <v>36</v>
@@ -7986,7 +7989,7 @@
         <v>47</v>
       </c>
       <c r="P11" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q11" s="7" t="s">
         <v>39</v>
@@ -8019,28 +8022,28 @@
         <v>39</v>
       </c>
       <c r="AA11" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB11" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC11" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB11" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC11" s="7" t="s">
+      <c r="AD11" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AE11" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF11" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG11" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH11" s="7" t="s">
         <v>254</v>
-      </c>
-      <c r="AD11" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="AE11" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF11" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG11" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH11" s="7" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.3">
@@ -8051,16 +8054,16 @@
         <v>135</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D12" s="6">
         <v>5</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>80</v>
@@ -8072,7 +8075,7 @@
         <v>81</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="K12" s="7" t="s">
         <v>36</v>
@@ -8090,7 +8093,7 @@
         <v>47</v>
       </c>
       <c r="P12" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q12" s="7" t="s">
         <v>39</v>
@@ -8123,28 +8126,28 @@
         <v>39</v>
       </c>
       <c r="AA12" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB12" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC12" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB12" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC12" s="7" t="s">
+      <c r="AD12" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AE12" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF12" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG12" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH12" s="7" t="s">
         <v>254</v>
-      </c>
-      <c r="AD12" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="AE12" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF12" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG12" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH12" s="7" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="13" spans="1:34" x14ac:dyDescent="0.3">
@@ -8155,16 +8158,16 @@
         <v>135</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D13" s="6">
         <v>6</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>87</v>
@@ -8194,7 +8197,7 @@
         <v>47</v>
       </c>
       <c r="P13" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q13" s="7" t="s">
         <v>39</v>
@@ -8227,28 +8230,28 @@
         <v>39</v>
       </c>
       <c r="AA13" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB13" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC13" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB13" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC13" s="7" t="s">
+      <c r="AD13" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AE13" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF13" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG13" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH13" s="7" t="s">
         <v>254</v>
-      </c>
-      <c r="AD13" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="AE13" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF13" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG13" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH13" s="7" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.3">
@@ -8259,16 +8262,16 @@
         <v>60</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D14" s="6">
         <v>1</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>77</v>
@@ -8298,7 +8301,7 @@
         <v>47</v>
       </c>
       <c r="P14" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q14" s="7" t="s">
         <v>39</v>
@@ -8331,28 +8334,28 @@
         <v>39</v>
       </c>
       <c r="AA14" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB14" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC14" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB14" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC14" s="7" t="s">
+      <c r="AD14" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AE14" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF14" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG14" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH14" s="7" t="s">
         <v>254</v>
-      </c>
-      <c r="AD14" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="AE14" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF14" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG14" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH14" s="7" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="15" spans="1:34" x14ac:dyDescent="0.3">
@@ -8363,16 +8366,16 @@
         <v>60</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D15" s="6">
         <v>2</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>155</v>
@@ -8384,7 +8387,7 @@
         <v>156</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="K15" s="7" t="s">
         <v>36</v>
@@ -8402,7 +8405,7 @@
         <v>47</v>
       </c>
       <c r="P15" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q15" s="7" t="s">
         <v>39</v>
@@ -8435,16 +8438,16 @@
         <v>39</v>
       </c>
       <c r="AA15" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB15" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC15" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB15" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC15" s="7" t="s">
-        <v>254</v>
-      </c>
       <c r="AD15" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE15" s="7" t="s">
         <v>39</v>
@@ -8467,16 +8470,16 @@
         <v>60</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D16" s="6">
         <v>3</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>55</v>
@@ -8506,7 +8509,7 @@
         <v>47</v>
       </c>
       <c r="P16" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q16" s="7" t="s">
         <v>39</v>
@@ -8539,28 +8542,28 @@
         <v>39</v>
       </c>
       <c r="AA16" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB16" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC16" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB16" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC16" s="7" t="s">
+      <c r="AD16" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AE16" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF16" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG16" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH16" s="7" t="s">
         <v>254</v>
-      </c>
-      <c r="AD16" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="AE16" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF16" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG16" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH16" s="7" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="17" spans="1:34" x14ac:dyDescent="0.3">
@@ -8571,16 +8574,16 @@
         <v>60</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D17" s="6">
         <v>4</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>144</v>
@@ -8610,7 +8613,7 @@
         <v>47</v>
       </c>
       <c r="P17" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q17" s="7" t="s">
         <v>39</v>
@@ -8643,16 +8646,16 @@
         <v>39</v>
       </c>
       <c r="AA17" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB17" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC17" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB17" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC17" s="7" t="s">
-        <v>254</v>
-      </c>
       <c r="AD17" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE17" s="7" t="s">
         <v>39</v>
@@ -8675,16 +8678,16 @@
         <v>60</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D18" s="6">
         <v>5</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>147</v>
@@ -8714,7 +8717,7 @@
         <v>47</v>
       </c>
       <c r="P18" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q18" s="7" t="s">
         <v>39</v>
@@ -8747,16 +8750,16 @@
         <v>39</v>
       </c>
       <c r="AA18" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB18" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC18" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB18" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC18" s="7" t="s">
-        <v>254</v>
-      </c>
       <c r="AD18" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE18" s="7" t="s">
         <v>39</v>
@@ -8779,7 +8782,7 @@
         <v>68</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D19" s="6">
         <v>1</v>
@@ -8788,7 +8791,7 @@
         <v>54</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>55</v>
@@ -8818,7 +8821,7 @@
         <v>47</v>
       </c>
       <c r="P19" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q19" s="7" t="s">
         <v>39</v>
@@ -8851,28 +8854,28 @@
         <v>39</v>
       </c>
       <c r="AA19" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB19" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC19" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB19" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC19" s="7" t="s">
+      <c r="AD19" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AE19" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF19" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG19" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH19" s="7" t="s">
         <v>254</v>
-      </c>
-      <c r="AD19" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="AE19" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF19" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG19" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH19" s="7" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="20" spans="1:34" x14ac:dyDescent="0.3">
@@ -8883,7 +8886,7 @@
         <v>68</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D20" s="6">
         <v>2</v>
@@ -8892,7 +8895,7 @@
         <v>54</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G20" s="7" t="s">
         <v>151</v>
@@ -8904,7 +8907,7 @@
         <v>152</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K20" s="7" t="s">
         <v>36</v>
@@ -8922,7 +8925,7 @@
         <v>47</v>
       </c>
       <c r="P20" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q20" s="7" t="s">
         <v>39</v>
@@ -8955,16 +8958,16 @@
         <v>39</v>
       </c>
       <c r="AA20" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB20" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC20" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB20" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC20" s="7" t="s">
-        <v>254</v>
-      </c>
       <c r="AD20" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE20" s="7" t="s">
         <v>39</v>
@@ -8987,7 +8990,7 @@
         <v>68</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D21" s="6">
         <v>3</v>
@@ -8996,7 +8999,7 @@
         <v>54</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G21" s="7" t="s">
         <v>74</v>
@@ -9008,7 +9011,7 @@
         <v>75</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K21" s="7" t="s">
         <v>36</v>
@@ -9026,7 +9029,7 @@
         <v>47</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q21" s="7" t="s">
         <v>39</v>
@@ -9059,28 +9062,28 @@
         <v>39</v>
       </c>
       <c r="AA21" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB21" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC21" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB21" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC21" s="7" t="s">
+      <c r="AD21" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="AE21" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF21" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG21" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH21" s="7" t="s">
         <v>254</v>
-      </c>
-      <c r="AD21" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="AE21" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AF21" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG21" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH21" s="7" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="22" spans="1:34" x14ac:dyDescent="0.3">
@@ -9091,7 +9094,7 @@
         <v>68</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D22" s="6">
         <v>4</v>
@@ -9100,7 +9103,7 @@
         <v>54</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G22" s="7" t="s">
         <v>131</v>
@@ -9130,7 +9133,7 @@
         <v>47</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q22" s="7" t="s">
         <v>39</v>
@@ -9163,16 +9166,16 @@
         <v>39</v>
       </c>
       <c r="AA22" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB22" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC22" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB22" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC22" s="7" t="s">
-        <v>254</v>
-      </c>
       <c r="AD22" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE22" s="7" t="s">
         <v>39</v>
@@ -9195,7 +9198,7 @@
         <v>68</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D23" s="6">
         <v>5</v>
@@ -9204,7 +9207,7 @@
         <v>54</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G23" s="7" t="s">
         <v>163</v>
@@ -9234,7 +9237,7 @@
         <v>47</v>
       </c>
       <c r="P23" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q23" s="7" t="s">
         <v>39</v>
@@ -9267,16 +9270,16 @@
         <v>39</v>
       </c>
       <c r="AA23" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB23" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC23" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB23" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC23" s="7" t="s">
-        <v>254</v>
-      </c>
       <c r="AD23" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE23" s="7" t="s">
         <v>39</v>
@@ -9288,7 +9291,7 @@
         <v>47</v>
       </c>
       <c r="AH23" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="24" spans="1:34" x14ac:dyDescent="0.3">
@@ -9299,7 +9302,7 @@
         <v>68</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D24" s="6">
         <v>6</v>
@@ -9308,7 +9311,7 @@
         <v>54</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G24" s="7" t="s">
         <v>62</v>
@@ -9338,7 +9341,7 @@
         <v>47</v>
       </c>
       <c r="P24" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q24" s="7" t="s">
         <v>39</v>
@@ -9371,16 +9374,16 @@
         <v>39</v>
       </c>
       <c r="AA24" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB24" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC24" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB24" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC24" s="7" t="s">
-        <v>254</v>
-      </c>
       <c r="AD24" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE24" s="7" t="s">
         <v>39</v>
@@ -9392,7 +9395,7 @@
         <v>47</v>
       </c>
       <c r="AH24" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="25" spans="1:34" x14ac:dyDescent="0.3">
@@ -9403,7 +9406,7 @@
         <v>121</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D25" s="6">
         <v>1</v>
@@ -9412,7 +9415,7 @@
         <v>91</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G25" s="7" t="s">
         <v>167</v>
@@ -9442,7 +9445,7 @@
         <v>47</v>
       </c>
       <c r="P25" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q25" s="7" t="s">
         <v>39</v>
@@ -9475,16 +9478,16 @@
         <v>39</v>
       </c>
       <c r="AA25" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB25" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC25" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB25" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC25" s="7" t="s">
-        <v>254</v>
-      </c>
       <c r="AD25" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE25" s="7" t="s">
         <v>39</v>
@@ -9507,7 +9510,7 @@
         <v>121</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D26" s="6">
         <v>2</v>
@@ -9516,7 +9519,7 @@
         <v>91</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G26" s="7" t="s">
         <v>69</v>
@@ -9546,7 +9549,7 @@
         <v>47</v>
       </c>
       <c r="P26" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q26" s="7" t="s">
         <v>39</v>
@@ -9579,16 +9582,16 @@
         <v>39</v>
       </c>
       <c r="AA26" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB26" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC26" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB26" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC26" s="7" t="s">
-        <v>254</v>
-      </c>
       <c r="AD26" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE26" s="7" t="s">
         <v>39</v>
@@ -9611,7 +9614,7 @@
         <v>121</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D27" s="6">
         <v>3</v>
@@ -9620,7 +9623,7 @@
         <v>91</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G27" s="7" t="s">
         <v>55</v>
@@ -9650,7 +9653,7 @@
         <v>47</v>
       </c>
       <c r="P27" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q27" s="7" t="s">
         <v>39</v>
@@ -9683,16 +9686,16 @@
         <v>39</v>
       </c>
       <c r="AA27" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB27" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC27" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB27" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC27" s="7" t="s">
-        <v>254</v>
-      </c>
       <c r="AD27" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE27" s="7" t="s">
         <v>39</v>
@@ -9704,7 +9707,7 @@
         <v>47</v>
       </c>
       <c r="AH27" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="28" spans="1:34" x14ac:dyDescent="0.3">
@@ -9715,7 +9718,7 @@
         <v>121</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D28" s="6">
         <v>4</v>
@@ -9724,7 +9727,7 @@
         <v>91</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G28" s="7" t="s">
         <v>141</v>
@@ -9754,7 +9757,7 @@
         <v>47</v>
       </c>
       <c r="P28" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q28" s="7" t="s">
         <v>39</v>
@@ -9787,16 +9790,16 @@
         <v>39</v>
       </c>
       <c r="AA28" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB28" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC28" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB28" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC28" s="7" t="s">
-        <v>254</v>
-      </c>
       <c r="AD28" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE28" s="7" t="s">
         <v>39</v>
@@ -9819,7 +9822,7 @@
         <v>121</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D29" s="6">
         <v>5</v>
@@ -9828,7 +9831,7 @@
         <v>91</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G29" s="7" t="s">
         <v>127</v>
@@ -9858,7 +9861,7 @@
         <v>47</v>
       </c>
       <c r="P29" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q29" s="7" t="s">
         <v>39</v>
@@ -9891,16 +9894,16 @@
         <v>39</v>
       </c>
       <c r="AA29" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB29" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC29" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB29" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC29" s="7" t="s">
-        <v>254</v>
-      </c>
       <c r="AD29" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE29" s="7" t="s">
         <v>39</v>
@@ -9912,7 +9915,7 @@
         <v>47</v>
       </c>
       <c r="AH29" s="7" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30" spans="1:34" x14ac:dyDescent="0.3">
@@ -9923,7 +9926,7 @@
         <v>121</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D30" s="6">
         <v>6</v>
@@ -9932,7 +9935,7 @@
         <v>91</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G30" s="7" t="s">
         <v>115</v>
@@ -9962,7 +9965,7 @@
         <v>47</v>
       </c>
       <c r="P30" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q30" s="7" t="s">
         <v>39</v>
@@ -9980,7 +9983,7 @@
         <v>0</v>
       </c>
       <c r="V30" s="6">
-        <v>0</v>
+        <v>1672000</v>
       </c>
       <c r="W30" s="7" t="s">
         <v>50</v>
@@ -9995,16 +9998,16 @@
         <v>39</v>
       </c>
       <c r="AA30" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AB30" s="7" t="s">
         <v>119</v>
       </c>
       <c r="AC30" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AD30" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE30" s="7" t="s">
         <v>39</v>
@@ -10016,7 +10019,7 @@
         <v>47</v>
       </c>
       <c r="AH30" s="7" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="1:34" x14ac:dyDescent="0.3">
@@ -10027,7 +10030,7 @@
         <v>121</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D31" s="6">
         <v>7</v>
@@ -10036,7 +10039,7 @@
         <v>91</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G31" s="7" t="s">
         <v>136</v>
@@ -10066,7 +10069,7 @@
         <v>47</v>
       </c>
       <c r="P31" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q31" s="7" t="s">
         <v>39</v>
@@ -10099,16 +10102,16 @@
         <v>39</v>
       </c>
       <c r="AA31" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AB31" s="7" t="s">
         <v>139</v>
       </c>
       <c r="AC31" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AD31" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE31" s="7" t="s">
         <v>39</v>
@@ -10131,7 +10134,7 @@
         <v>162</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D32" s="6">
         <v>1</v>
@@ -10140,7 +10143,7 @@
         <v>72</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G32" s="7" t="s">
         <v>158</v>
@@ -10170,7 +10173,7 @@
         <v>47</v>
       </c>
       <c r="P32" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q32" s="7" t="s">
         <v>45</v>
@@ -10197,22 +10200,22 @@
         <v>49</v>
       </c>
       <c r="Y32" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Z32" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AA32" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB32" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC32" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB32" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC32" s="7" t="s">
-        <v>254</v>
-      </c>
       <c r="AD32" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE32" s="7" t="s">
         <v>39</v>
@@ -10224,7 +10227,7 @@
         <v>47</v>
       </c>
       <c r="AH32" s="7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="33" spans="1:34" x14ac:dyDescent="0.3">
@@ -10235,7 +10238,7 @@
         <v>171</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D33" s="6">
         <v>1</v>
@@ -10244,7 +10247,7 @@
         <v>58</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G33" s="7" t="s">
         <v>172</v>
@@ -10274,7 +10277,7 @@
         <v>47</v>
       </c>
       <c r="P33" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q33" s="7" t="s">
         <v>39</v>
@@ -10307,16 +10310,16 @@
         <v>39</v>
       </c>
       <c r="AA33" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB33" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC33" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB33" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC33" s="7" t="s">
-        <v>254</v>
-      </c>
       <c r="AD33" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE33" s="7" t="s">
         <v>39</v>
@@ -10339,7 +10342,7 @@
         <v>171</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D34" s="6">
         <v>2</v>
@@ -10348,7 +10351,7 @@
         <v>58</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G34" s="7" t="s">
         <v>55</v>
@@ -10378,7 +10381,7 @@
         <v>47</v>
       </c>
       <c r="P34" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q34" s="7" t="s">
         <v>39</v>
@@ -10411,16 +10414,16 @@
         <v>39</v>
       </c>
       <c r="AA34" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB34" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC34" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB34" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC34" s="7" t="s">
-        <v>254</v>
-      </c>
       <c r="AD34" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE34" s="7" t="s">
         <v>39</v>
@@ -10443,7 +10446,7 @@
         <v>171</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D35" s="6">
         <v>3</v>
@@ -10452,7 +10455,7 @@
         <v>58</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G35" s="7" t="s">
         <v>87</v>
@@ -10482,7 +10485,7 @@
         <v>47</v>
       </c>
       <c r="P35" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q35" s="7" t="s">
         <v>39</v>
@@ -10515,16 +10518,16 @@
         <v>39</v>
       </c>
       <c r="AA35" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB35" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC35" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB35" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC35" s="7" t="s">
-        <v>254</v>
-      </c>
       <c r="AD35" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE35" s="7" t="s">
         <v>39</v>
@@ -10547,7 +10550,7 @@
         <v>171</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D36" s="6">
         <v>4</v>
@@ -10556,7 +10559,7 @@
         <v>58</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G36" s="7" t="s">
         <v>175</v>
@@ -10586,7 +10589,7 @@
         <v>47</v>
       </c>
       <c r="P36" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q36" s="7" t="s">
         <v>39</v>
@@ -10619,16 +10622,16 @@
         <v>39</v>
       </c>
       <c r="AA36" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB36" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC36" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB36" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC36" s="7" t="s">
-        <v>254</v>
-      </c>
       <c r="AD36" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE36" s="7" t="s">
         <v>39</v>
@@ -10640,7 +10643,7 @@
         <v>47</v>
       </c>
       <c r="AH36" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="37" spans="1:34" x14ac:dyDescent="0.3">
@@ -10651,7 +10654,7 @@
         <v>171</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D37" s="6">
         <v>5</v>
@@ -10660,7 +10663,7 @@
         <v>58</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G37" s="7" t="s">
         <v>178</v>
@@ -10690,7 +10693,7 @@
         <v>47</v>
       </c>
       <c r="P37" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q37" s="7" t="s">
         <v>39</v>
@@ -10723,16 +10726,16 @@
         <v>39</v>
       </c>
       <c r="AA37" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AB37" s="7" t="s">
         <v>181</v>
       </c>
       <c r="AC37" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AD37" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE37" s="7" t="s">
         <v>39</v>
@@ -10744,7 +10747,7 @@
         <v>47</v>
       </c>
       <c r="AH37" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="38" spans="1:34" x14ac:dyDescent="0.3">
@@ -10755,7 +10758,7 @@
         <v>171</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D38" s="6">
         <v>6</v>
@@ -10764,7 +10767,7 @@
         <v>58</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G38" s="7" t="s">
         <v>182</v>
@@ -10776,7 +10779,7 @@
         <v>184</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="K38" s="7" t="s">
         <v>36</v>
@@ -10794,7 +10797,7 @@
         <v>47</v>
       </c>
       <c r="P38" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q38" s="7" t="s">
         <v>39</v>
@@ -10827,16 +10830,16 @@
         <v>39</v>
       </c>
       <c r="AA38" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB38" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC38" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB38" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC38" s="7" t="s">
-        <v>254</v>
-      </c>
       <c r="AD38" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE38" s="7" t="s">
         <v>39</v>
@@ -10848,7 +10851,7 @@
         <v>47</v>
       </c>
       <c r="AH38" s="7" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
     </row>
     <row r="39" spans="1:34" x14ac:dyDescent="0.3">
@@ -10859,7 +10862,7 @@
         <v>193</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D39" s="6">
         <v>1</v>
@@ -10868,7 +10871,7 @@
         <v>134</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G39" s="7" t="s">
         <v>136</v>
@@ -10898,7 +10901,7 @@
         <v>47</v>
       </c>
       <c r="P39" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q39" s="7" t="s">
         <v>39</v>
@@ -10931,16 +10934,16 @@
         <v>39</v>
       </c>
       <c r="AA39" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB39" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC39" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB39" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC39" s="7" t="s">
-        <v>254</v>
-      </c>
       <c r="AD39" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE39" s="7" t="s">
         <v>39</v>
@@ -10952,7 +10955,7 @@
         <v>47</v>
       </c>
       <c r="AH39" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="40" spans="1:34" x14ac:dyDescent="0.3">
@@ -10963,7 +10966,7 @@
         <v>193</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D40" s="6">
         <v>2</v>
@@ -10972,7 +10975,7 @@
         <v>134</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G40" s="7" t="s">
         <v>55</v>
@@ -11002,7 +11005,7 @@
         <v>47</v>
       </c>
       <c r="P40" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q40" s="7" t="s">
         <v>39</v>
@@ -11035,16 +11038,16 @@
         <v>39</v>
       </c>
       <c r="AA40" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB40" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC40" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB40" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC40" s="7" t="s">
-        <v>254</v>
-      </c>
       <c r="AD40" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE40" s="7" t="s">
         <v>39</v>
@@ -11056,7 +11059,7 @@
         <v>47</v>
       </c>
       <c r="AH40" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="41" spans="1:34" x14ac:dyDescent="0.3">
@@ -11067,7 +11070,7 @@
         <v>193</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D41" s="6">
         <v>3</v>
@@ -11076,7 +11079,7 @@
         <v>134</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G41" s="7" t="s">
         <v>158</v>
@@ -11106,7 +11109,7 @@
         <v>47</v>
       </c>
       <c r="P41" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q41" s="7" t="s">
         <v>39</v>
@@ -11139,16 +11142,16 @@
         <v>39</v>
       </c>
       <c r="AA41" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB41" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC41" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB41" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC41" s="7" t="s">
-        <v>254</v>
-      </c>
       <c r="AD41" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE41" s="7" t="s">
         <v>39</v>
@@ -11171,7 +11174,7 @@
         <v>193</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D42" s="6">
         <v>4</v>
@@ -11180,7 +11183,7 @@
         <v>134</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G42" s="7" t="s">
         <v>194</v>
@@ -11210,7 +11213,7 @@
         <v>47</v>
       </c>
       <c r="P42" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q42" s="7" t="s">
         <v>39</v>
@@ -11243,16 +11246,16 @@
         <v>39</v>
       </c>
       <c r="AA42" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB42" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC42" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB42" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC42" s="7" t="s">
-        <v>254</v>
-      </c>
       <c r="AD42" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE42" s="7" t="s">
         <v>39</v>
@@ -11264,7 +11267,7 @@
         <v>47</v>
       </c>
       <c r="AH42" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="43" spans="1:34" x14ac:dyDescent="0.3">
@@ -11275,7 +11278,7 @@
         <v>193</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D43" s="6">
         <v>5</v>
@@ -11284,7 +11287,7 @@
         <v>134</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G43" s="7" t="s">
         <v>92</v>
@@ -11314,7 +11317,7 @@
         <v>47</v>
       </c>
       <c r="P43" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q43" s="7" t="s">
         <v>39</v>
@@ -11332,7 +11335,7 @@
         <v>0</v>
       </c>
       <c r="V43" s="6">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="W43" s="7" t="s">
         <v>50</v>
@@ -11347,16 +11350,16 @@
         <v>39</v>
       </c>
       <c r="AA43" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB43" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC43" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB43" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC43" s="7" t="s">
-        <v>254</v>
-      </c>
       <c r="AD43" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE43" s="7" t="s">
         <v>39</v>
@@ -11368,7 +11371,7 @@
         <v>47</v>
       </c>
       <c r="AH43" s="7" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
     </row>
     <row r="44" spans="1:34" x14ac:dyDescent="0.3">
@@ -11379,7 +11382,7 @@
         <v>193</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D44" s="6">
         <v>6</v>
@@ -11388,7 +11391,7 @@
         <v>134</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G44" s="7" t="s">
         <v>198</v>
@@ -11400,7 +11403,7 @@
         <v>200</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="K44" s="7" t="s">
         <v>36</v>
@@ -11418,7 +11421,7 @@
         <v>47</v>
       </c>
       <c r="P44" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q44" s="7" t="s">
         <v>39</v>
@@ -11451,16 +11454,16 @@
         <v>39</v>
       </c>
       <c r="AA44" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB44" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC44" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB44" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC44" s="7" t="s">
-        <v>254</v>
-      </c>
       <c r="AD44" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE44" s="7" t="s">
         <v>39</v>
@@ -11472,7 +11475,7 @@
         <v>47</v>
       </c>
       <c r="AH44" s="7" t="s">
-        <v>207</v>
+        <v>292</v>
       </c>
     </row>
     <row r="45" spans="1:34" x14ac:dyDescent="0.3">
@@ -11483,7 +11486,7 @@
         <v>193</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D45" s="6">
         <v>7</v>
@@ -11492,7 +11495,7 @@
         <v>134</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G45" s="7" t="s">
         <v>201</v>
@@ -11522,7 +11525,7 @@
         <v>47</v>
       </c>
       <c r="P45" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q45" s="7" t="s">
         <v>39</v>
@@ -11555,16 +11558,16 @@
         <v>39</v>
       </c>
       <c r="AA45" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AB45" s="7" t="s">
         <v>204</v>
       </c>
       <c r="AC45" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AD45" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE45" s="7" t="s">
         <v>39</v>
@@ -11584,10 +11587,10 @@
         <v>33</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D46" s="6">
         <v>1</v>
@@ -11596,16 +11599,16 @@
         <v>210</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G46" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="I46" s="7" t="s">
         <v>221</v>
-      </c>
-      <c r="H46" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="I46" s="7" t="s">
-        <v>222</v>
       </c>
       <c r="J46" s="7" t="s">
         <v>66</v>
@@ -11626,7 +11629,7 @@
         <v>47</v>
       </c>
       <c r="P46" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q46" s="7" t="s">
         <v>39</v>
@@ -11659,16 +11662,16 @@
         <v>39</v>
       </c>
       <c r="AA46" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB46" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC46" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB46" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC46" s="7" t="s">
-        <v>254</v>
-      </c>
       <c r="AD46" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE46" s="7" t="s">
         <v>39</v>
@@ -11680,7 +11683,7 @@
         <v>47</v>
       </c>
       <c r="AH46" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="47" spans="1:34" x14ac:dyDescent="0.3">
@@ -11688,10 +11691,10 @@
         <v>33</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D47" s="6">
         <v>2</v>
@@ -11700,19 +11703,19 @@
         <v>210</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G47" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="I47" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="H47" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="I47" s="7" t="s">
-        <v>219</v>
-      </c>
       <c r="J47" s="7" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="K47" s="7" t="s">
         <v>36</v>
@@ -11730,7 +11733,7 @@
         <v>47</v>
       </c>
       <c r="P47" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q47" s="7" t="s">
         <v>39</v>
@@ -11748,7 +11751,7 @@
         <v>0</v>
       </c>
       <c r="V47" s="6">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="W47" s="7" t="s">
         <v>50</v>
@@ -11763,16 +11766,16 @@
         <v>39</v>
       </c>
       <c r="AA47" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB47" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC47" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB47" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC47" s="7" t="s">
-        <v>254</v>
-      </c>
       <c r="AD47" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE47" s="7" t="s">
         <v>39</v>
@@ -11784,7 +11787,7 @@
         <v>47</v>
       </c>
       <c r="AH47" s="7" t="s">
-        <v>214</v>
+        <v>294</v>
       </c>
     </row>
     <row r="48" spans="1:34" x14ac:dyDescent="0.3">
@@ -11792,10 +11795,10 @@
         <v>33</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D48" s="6">
         <v>3</v>
@@ -11804,7 +11807,7 @@
         <v>210</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G48" s="7" t="s">
         <v>211</v>
@@ -11834,7 +11837,7 @@
         <v>47</v>
       </c>
       <c r="P48" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q48" s="7" t="s">
         <v>39</v>
@@ -11867,16 +11870,16 @@
         <v>39</v>
       </c>
       <c r="AA48" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB48" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC48" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB48" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC48" s="7" t="s">
-        <v>254</v>
-      </c>
       <c r="AD48" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE48" s="7" t="s">
         <v>39</v>
@@ -11888,7 +11891,7 @@
         <v>47</v>
       </c>
       <c r="AH48" s="7" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="49" spans="1:34" x14ac:dyDescent="0.3">
@@ -11896,19 +11899,19 @@
         <v>33</v>
       </c>
       <c r="B49" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="C49" s="7" t="s">
         <v>271</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>272</v>
       </c>
       <c r="D49" s="6">
         <v>1</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G49" s="7" t="s">
         <v>178</v>
@@ -11938,7 +11941,7 @@
         <v>47</v>
       </c>
       <c r="P49" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q49" s="7" t="s">
         <v>39</v>
@@ -11956,7 +11959,7 @@
         <v>0</v>
       </c>
       <c r="V49" s="6">
-        <v>115000</v>
+        <v>743000</v>
       </c>
       <c r="W49" s="7" t="s">
         <v>50</v>
@@ -11971,16 +11974,16 @@
         <v>39</v>
       </c>
       <c r="AA49" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB49" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC49" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB49" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC49" s="7" t="s">
-        <v>254</v>
-      </c>
       <c r="AD49" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE49" s="7" t="s">
         <v>39</v>
@@ -11992,7 +11995,7 @@
         <v>47</v>
       </c>
       <c r="AH49" s="7" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="50" spans="1:34" x14ac:dyDescent="0.3">
@@ -12000,19 +12003,19 @@
         <v>33</v>
       </c>
       <c r="B50" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="C50" s="7" t="s">
         <v>271</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>272</v>
       </c>
       <c r="D50" s="6">
         <v>2</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G50" s="7" t="s">
         <v>74</v>
@@ -12024,7 +12027,7 @@
         <v>75</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K50" s="7" t="s">
         <v>36</v>
@@ -12042,7 +12045,7 @@
         <v>47</v>
       </c>
       <c r="P50" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q50" s="7" t="s">
         <v>39</v>
@@ -12069,22 +12072,22 @@
         <v>49</v>
       </c>
       <c r="Y50" s="8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Z50" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AA50" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB50" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC50" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB50" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC50" s="7" t="s">
-        <v>254</v>
-      </c>
       <c r="AD50" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE50" s="7" t="s">
         <v>39</v>
@@ -12096,7 +12099,7 @@
         <v>47</v>
       </c>
       <c r="AH50" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="51" spans="1:34" x14ac:dyDescent="0.3">
@@ -12104,19 +12107,19 @@
         <v>33</v>
       </c>
       <c r="B51" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="C51" s="7" t="s">
         <v>271</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>272</v>
       </c>
       <c r="D51" s="6">
         <v>3</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G51" s="7" t="s">
         <v>151</v>
@@ -12128,7 +12131,7 @@
         <v>152</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K51" s="7" t="s">
         <v>36</v>
@@ -12146,7 +12149,7 @@
         <v>47</v>
       </c>
       <c r="P51" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q51" s="7" t="s">
         <v>39</v>
@@ -12173,22 +12176,22 @@
         <v>49</v>
       </c>
       <c r="Y51" s="8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Z51" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AA51" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB51" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC51" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB51" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC51" s="7" t="s">
-        <v>254</v>
-      </c>
       <c r="AD51" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE51" s="7" t="s">
         <v>39</v>
@@ -12200,7 +12203,7 @@
         <v>47</v>
       </c>
       <c r="AH51" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="52" spans="1:34" x14ac:dyDescent="0.3">
@@ -12208,10 +12211,10 @@
         <v>33</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D52" s="6">
         <v>1</v>
@@ -12220,7 +12223,7 @@
         <v>118</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>178</v>
@@ -12250,7 +12253,7 @@
         <v>47</v>
       </c>
       <c r="P52" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q52" s="7" t="s">
         <v>39</v>
@@ -12283,16 +12286,16 @@
         <v>39</v>
       </c>
       <c r="AA52" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB52" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC52" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB52" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC52" s="7" t="s">
-        <v>254</v>
-      </c>
       <c r="AD52" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE52" s="7" t="s">
         <v>39</v>
@@ -12304,7 +12307,7 @@
         <v>47</v>
       </c>
       <c r="AH52" s="7" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="53" spans="1:34" x14ac:dyDescent="0.3">
@@ -12312,10 +12315,10 @@
         <v>33</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D53" s="6">
         <v>2</v>
@@ -12324,16 +12327,16 @@
         <v>118</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G53" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="H53" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="H53" s="7" t="s">
-        <v>283</v>
-      </c>
       <c r="I53" s="7" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="J53" s="7" t="s">
         <v>118</v>
@@ -12354,7 +12357,7 @@
         <v>47</v>
       </c>
       <c r="P53" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q53" s="7" t="s">
         <v>39</v>
@@ -12381,22 +12384,22 @@
         <v>49</v>
       </c>
       <c r="Y53" s="8" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="Z53" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AA53" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB53" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC53" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB53" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC53" s="7" t="s">
-        <v>254</v>
-      </c>
       <c r="AD53" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE53" s="7" t="s">
         <v>39</v>
@@ -12408,7 +12411,7 @@
         <v>47</v>
       </c>
       <c r="AH53" s="7" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="54" spans="1:34" x14ac:dyDescent="0.3">
@@ -12416,10 +12419,10 @@
         <v>33</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D54" s="6">
         <v>3</v>
@@ -12428,16 +12431,16 @@
         <v>118</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H54" s="7" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="I54" s="7" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="J54" s="7" t="s">
         <v>118</v>
@@ -12458,7 +12461,7 @@
         <v>47</v>
       </c>
       <c r="P54" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q54" s="7" t="s">
         <v>39</v>
@@ -12485,22 +12488,22 @@
         <v>49</v>
       </c>
       <c r="Y54" s="8" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="Z54" s="7" t="s">
         <v>39</v>
       </c>
       <c r="AA54" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB54" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AC54" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="AB54" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC54" s="7" t="s">
-        <v>254</v>
-      </c>
       <c r="AD54" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE54" s="7" t="s">
         <v>39</v>
@@ -12512,7 +12515,7 @@
         <v>47</v>
       </c>
       <c r="AH54" s="7" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
   </sheetData>
